--- a/database/IRBR3.xlsx
+++ b/database/IRBR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2266"/>
+  <dimension ref="A1:F2267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>42947</v>
       </c>
       <c r="B2" t="n">
-        <v>197.0598602294922</v>
+        <v>197.0598754882812</v>
       </c>
       <c r="C2" t="n">
-        <v>199.1455052304281</v>
+        <v>199.1455206507133</v>
       </c>
       <c r="D2" t="n">
-        <v>188.8518371039546</v>
+        <v>188.851851727178</v>
       </c>
       <c r="E2" t="n">
-        <v>190.130140835655</v>
+        <v>190.1301555578603</v>
       </c>
       <c r="F2" t="n">
         <v>1448107</v>
@@ -472,16 +472,16 @@
         <v>42948</v>
       </c>
       <c r="B3" t="n">
-        <v>197.7999572753906</v>
+        <v>197.7999420166016</v>
       </c>
       <c r="C3" t="n">
-        <v>199.8183240497441</v>
+        <v>199.8183086352532</v>
       </c>
       <c r="D3" t="n">
-        <v>197.0598809785888</v>
+        <v>197.0598657768911</v>
       </c>
       <c r="E3" t="n">
-        <v>199.0109693067554</v>
+        <v>199.0109539545458</v>
       </c>
       <c r="F3" t="n">
         <v>496061</v>
@@ -492,16 +492,16 @@
         <v>42949</v>
       </c>
       <c r="B4" t="n">
-        <v>198.1363372802734</v>
+        <v>198.1363525390625</v>
       </c>
       <c r="C4" t="n">
-        <v>198.3381726063799</v>
+        <v>198.3381878807127</v>
       </c>
       <c r="D4" t="n">
-        <v>195.7142999782507</v>
+        <v>195.7143150505149</v>
       </c>
       <c r="E4" t="n">
-        <v>197.7999450700959</v>
+        <v>197.7999603029789</v>
       </c>
       <c r="F4" t="n">
         <v>146838</v>
@@ -512,16 +512,16 @@
         <v>42950</v>
       </c>
       <c r="B5" t="n">
-        <v>197.3963012695312</v>
+        <v>197.3962707519531</v>
       </c>
       <c r="C5" t="n">
-        <v>198.2036426837792</v>
+        <v>198.2036120413857</v>
       </c>
       <c r="D5" t="n">
-        <v>196.0507188570381</v>
+        <v>196.0506885474878</v>
       </c>
       <c r="E5" t="n">
-        <v>196.7907818200988</v>
+        <v>196.7907513961343</v>
       </c>
       <c r="F5" t="n">
         <v>88032</v>
@@ -552,16 +552,16 @@
         <v>42954</v>
       </c>
       <c r="B7" t="n">
-        <v>192.0812530517578</v>
+        <v>192.0812377929688</v>
       </c>
       <c r="C7" t="n">
-        <v>195.7815944440546</v>
+        <v>195.7815788913132</v>
       </c>
       <c r="D7" t="n">
-        <v>191.7448608140483</v>
+        <v>191.7448455819819</v>
       </c>
       <c r="E7" t="n">
-        <v>194.4360121044706</v>
+        <v>194.4359966586212</v>
       </c>
       <c r="F7" t="n">
         <v>212322</v>
@@ -592,16 +592,16 @@
         <v>42956</v>
       </c>
       <c r="B9" t="n">
-        <v>186.6989288330078</v>
+        <v>186.6989135742188</v>
       </c>
       <c r="C9" t="n">
-        <v>190.3992700618077</v>
+        <v>190.399254500592</v>
       </c>
       <c r="D9" t="n">
-        <v>183.738663883215</v>
+        <v>183.7386488663666</v>
       </c>
       <c r="E9" t="n">
-        <v>189.726485616115</v>
+        <v>189.7264701098856</v>
       </c>
       <c r="F9" t="n">
         <v>202188</v>
@@ -612,16 +612,16 @@
         <v>42957</v>
       </c>
       <c r="B10" t="n">
-        <v>189.9956207275391</v>
+        <v>189.9955902099609</v>
       </c>
       <c r="C10" t="n">
-        <v>191.1393544136376</v>
+        <v>191.1393237123501</v>
       </c>
       <c r="D10" t="n">
-        <v>185.5552161098984</v>
+        <v>185.5551863055493</v>
       </c>
       <c r="E10" t="n">
-        <v>186.2952790832563</v>
+        <v>186.2952491600364</v>
       </c>
       <c r="F10" t="n">
         <v>83768</v>
@@ -632,16 +632,16 @@
         <v>42958</v>
       </c>
       <c r="B11" t="n">
-        <v>191.0720520019531</v>
+        <v>191.0720367431641</v>
       </c>
       <c r="C11" t="n">
-        <v>192.1485204896907</v>
+        <v>192.1485051449361</v>
       </c>
       <c r="D11" t="n">
-        <v>188.3809008657267</v>
+        <v>188.3808858218499</v>
       </c>
       <c r="E11" t="n">
-        <v>191.1393304456402</v>
+        <v>191.1393151814783</v>
       </c>
       <c r="F11" t="n">
         <v>48476</v>
@@ -652,16 +652,16 @@
         <v>42961</v>
       </c>
       <c r="B12" t="n">
-        <v>191.0720520019531</v>
+        <v>191.0720367431641</v>
       </c>
       <c r="C12" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="D12" t="n">
-        <v>188.784571527849</v>
+        <v>188.7845564517354</v>
       </c>
       <c r="E12" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="F12" t="n">
         <v>42790</v>
@@ -672,16 +672,16 @@
         <v>42962</v>
       </c>
       <c r="B13" t="n">
-        <v>191.0720520019531</v>
+        <v>191.0720367431641</v>
       </c>
       <c r="C13" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="D13" t="n">
-        <v>190.4665460087698</v>
+        <v>190.4665307983358</v>
       </c>
       <c r="E13" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="F13" t="n">
         <v>72604</v>
@@ -712,16 +712,16 @@
         <v>42964</v>
       </c>
       <c r="B15" t="n">
-        <v>190.0628814697266</v>
+        <v>190.0628662109375</v>
       </c>
       <c r="C15" t="n">
-        <v>191.9466913423975</v>
+        <v>191.9466759323708</v>
       </c>
       <c r="D15" t="n">
-        <v>189.7264892404542</v>
+        <v>189.7264740086716</v>
       </c>
       <c r="E15" t="n">
-        <v>191.744856004834</v>
+        <v>191.7448406110113</v>
       </c>
       <c r="F15" t="n">
         <v>247261</v>
@@ -752,16 +752,16 @@
         <v>42968</v>
       </c>
       <c r="B17" t="n">
-        <v>192.5521850585938</v>
+        <v>192.5522003173828</v>
       </c>
       <c r="C17" t="n">
-        <v>193.0231341495</v>
+        <v>193.0231494456094</v>
       </c>
       <c r="D17" t="n">
-        <v>187.3044264508328</v>
+        <v>187.3044412937635</v>
       </c>
       <c r="E17" t="n">
-        <v>191.8121222014553</v>
+        <v>191.8121374015981</v>
       </c>
       <c r="F17" t="n">
         <v>257303</v>
@@ -832,16 +832,16 @@
         <v>42972</v>
       </c>
       <c r="B21" t="n">
-        <v>200.4910888671875</v>
+        <v>200.4910736083984</v>
       </c>
       <c r="C21" t="n">
-        <v>200.4910888671875</v>
+        <v>200.4910736083984</v>
       </c>
       <c r="D21" t="n">
-        <v>193.4940909830865</v>
+        <v>193.4940762568184</v>
       </c>
       <c r="E21" t="n">
-        <v>194.5705460166047</v>
+        <v>194.5705312084108</v>
       </c>
       <c r="F21" t="n">
         <v>198745</v>
@@ -892,16 +892,16 @@
         <v>42977</v>
       </c>
       <c r="B24" t="n">
-        <v>203.8550720214844</v>
+        <v>203.8550415039062</v>
       </c>
       <c r="C24" t="n">
-        <v>204.3932996290602</v>
+        <v>204.3932690309082</v>
       </c>
       <c r="D24" t="n">
-        <v>199.9528950890667</v>
+        <v>199.9528651556535</v>
       </c>
       <c r="E24" t="n">
-        <v>204.1914642762193</v>
+        <v>204.1914337082824</v>
       </c>
       <c r="F24" t="n">
         <v>64518</v>
@@ -972,16 +972,16 @@
         <v>42983</v>
       </c>
       <c r="B28" t="n">
-        <v>203.8550720214844</v>
+        <v>203.8550415039062</v>
       </c>
       <c r="C28" t="n">
-        <v>205.133362589477</v>
+        <v>205.1333318805358</v>
       </c>
       <c r="D28" t="n">
-        <v>201.2984641080063</v>
+        <v>201.2984339731583</v>
       </c>
       <c r="E28" t="n">
-        <v>201.8367051043286</v>
+        <v>201.8366748889046</v>
       </c>
       <c r="F28" t="n">
         <v>252530</v>
@@ -992,16 +992,16 @@
         <v>42984</v>
       </c>
       <c r="B29" t="n">
-        <v>207.0844421386719</v>
+        <v>207.0844268798828</v>
       </c>
       <c r="C29" t="n">
-        <v>208.5645813845174</v>
+        <v>208.5645660166659</v>
       </c>
       <c r="D29" t="n">
-        <v>205.2006322045265</v>
+        <v>205.2006170845439</v>
       </c>
       <c r="E29" t="n">
-        <v>205.2006322045265</v>
+        <v>205.2006170845439</v>
       </c>
       <c r="F29" t="n">
         <v>109786</v>
@@ -1072,16 +1072,16 @@
         <v>42991</v>
       </c>
       <c r="B33" t="n">
-        <v>209.8428649902344</v>
+        <v>209.8428955078125</v>
       </c>
       <c r="C33" t="n">
-        <v>212.803129806863</v>
+        <v>212.8031607549543</v>
       </c>
       <c r="D33" t="n">
-        <v>208.5645612121762</v>
+        <v>208.5645915438498</v>
       </c>
       <c r="E33" t="n">
-        <v>211.9957885083492</v>
+        <v>211.9958193390283</v>
       </c>
       <c r="F33" t="n">
         <v>61349</v>
@@ -1112,16 +1112,16 @@
         <v>42993</v>
       </c>
       <c r="B35" t="n">
-        <v>213.5431976318359</v>
+        <v>213.5432281494141</v>
       </c>
       <c r="C35" t="n">
-        <v>213.6777545096155</v>
+        <v>213.6777850464233</v>
       </c>
       <c r="D35" t="n">
-        <v>209.3046158155464</v>
+        <v>209.3046457273865</v>
       </c>
       <c r="E35" t="n">
-        <v>209.3046158155464</v>
+        <v>209.3046457273865</v>
       </c>
       <c r="F35" t="n">
         <v>102613</v>
@@ -1172,16 +1172,16 @@
         <v>42998</v>
       </c>
       <c r="B38" t="n">
-        <v>210.1119689941406</v>
+        <v>210.1119842529297</v>
       </c>
       <c r="C38" t="n">
-        <v>213.6104745693081</v>
+        <v>213.6104900821663</v>
       </c>
       <c r="D38" t="n">
-        <v>209.9774121173068</v>
+        <v>209.9774273663241</v>
       </c>
       <c r="E38" t="n">
-        <v>213.1395121116458</v>
+        <v>213.1395275903016</v>
       </c>
       <c r="F38" t="n">
         <v>64974</v>
@@ -1212,16 +1212,16 @@
         <v>43000</v>
       </c>
       <c r="B40" t="n">
-        <v>214.5523986816406</v>
+        <v>214.5523834228516</v>
       </c>
       <c r="C40" t="n">
-        <v>214.6196771282025</v>
+        <v>214.6196618646287</v>
       </c>
       <c r="D40" t="n">
-        <v>210.4483866638742</v>
+        <v>210.4483716969591</v>
       </c>
       <c r="E40" t="n">
-        <v>211.7266905372957</v>
+        <v>211.7266754794687</v>
       </c>
       <c r="F40" t="n">
         <v>36999</v>
@@ -1232,16 +1232,16 @@
         <v>43003</v>
       </c>
       <c r="B41" t="n">
-        <v>210.9193115234375</v>
+        <v>210.9193267822266</v>
       </c>
       <c r="C41" t="n">
-        <v>215.8979561624585</v>
+        <v>215.8979717814236</v>
       </c>
       <c r="D41" t="n">
-        <v>209.9774133799369</v>
+        <v>209.9774285705851</v>
       </c>
       <c r="E41" t="n">
-        <v>214.7542093137495</v>
+        <v>214.7542248499711</v>
       </c>
       <c r="F41" t="n">
         <v>77912</v>
@@ -1272,16 +1272,16 @@
         <v>43005</v>
       </c>
       <c r="B43" t="n">
-        <v>206.5462036132812</v>
+        <v>206.5461883544922</v>
       </c>
       <c r="C43" t="n">
-        <v>210.9866077268585</v>
+        <v>210.9865921400306</v>
       </c>
       <c r="D43" t="n">
-        <v>205.9406976129058</v>
+        <v>205.940682398849</v>
       </c>
       <c r="E43" t="n">
-        <v>209.9101526150799</v>
+        <v>209.910137107776</v>
       </c>
       <c r="F43" t="n">
         <v>41486</v>
@@ -1292,16 +1292,16 @@
         <v>43006</v>
       </c>
       <c r="B44" t="n">
-        <v>204.5278472900391</v>
+        <v>204.5278167724609</v>
       </c>
       <c r="C44" t="n">
-        <v>210.8520615595557</v>
+        <v>210.8520300983423</v>
       </c>
       <c r="D44" t="n">
-        <v>201.8366959850042</v>
+        <v>201.8366658689725</v>
       </c>
       <c r="E44" t="n">
-        <v>207.4208473275414</v>
+        <v>207.4208163782991</v>
       </c>
       <c r="F44" t="n">
         <v>111156</v>
@@ -1352,16 +1352,16 @@
         <v>43011</v>
       </c>
       <c r="B47" t="n">
-        <v>206.9498443603516</v>
+        <v>206.9498748779297</v>
       </c>
       <c r="C47" t="n">
-        <v>208.093591140004</v>
+        <v>208.0936218262432</v>
       </c>
       <c r="D47" t="n">
-        <v>203.7204661031589</v>
+        <v>203.7204961445212</v>
       </c>
       <c r="E47" t="n">
-        <v>207.0171227951109</v>
+        <v>207.0171533226102</v>
       </c>
       <c r="F47" t="n">
         <v>216534</v>
@@ -1372,16 +1372,16 @@
         <v>43012</v>
       </c>
       <c r="B48" t="n">
-        <v>206.8825988769531</v>
+        <v>206.8826141357422</v>
       </c>
       <c r="C48" t="n">
-        <v>208.564573402578</v>
+        <v>208.5645887854224</v>
       </c>
       <c r="D48" t="n">
-        <v>204.1914476692005</v>
+        <v>204.1914627295016</v>
       </c>
       <c r="E48" t="n">
-        <v>208.564573402578</v>
+        <v>208.5645887854224</v>
       </c>
       <c r="F48" t="n">
         <v>147256</v>
@@ -1412,16 +1412,16 @@
         <v>43014</v>
       </c>
       <c r="B50" t="n">
-        <v>201.5002746582031</v>
+        <v>201.5002593994141</v>
       </c>
       <c r="C50" t="n">
-        <v>205.2678805858865</v>
+        <v>205.2678650417921</v>
       </c>
       <c r="D50" t="n">
-        <v>200.491084696529</v>
+        <v>200.4910695141617</v>
       </c>
       <c r="E50" t="n">
-        <v>204.191425574761</v>
+        <v>204.1914101121821</v>
       </c>
       <c r="F50" t="n">
         <v>72512</v>
@@ -1432,16 +1432,16 @@
         <v>43017</v>
       </c>
       <c r="B51" t="n">
-        <v>207.0844421386719</v>
+        <v>207.0844268798828</v>
       </c>
       <c r="C51" t="n">
-        <v>207.0844421386719</v>
+        <v>207.0844268798828</v>
       </c>
       <c r="D51" t="n">
-        <v>202.1730886535314</v>
+        <v>202.17307375663</v>
       </c>
       <c r="E51" t="n">
-        <v>202.1730886535314</v>
+        <v>202.17307375663</v>
       </c>
       <c r="F51" t="n">
         <v>84107</v>
@@ -1452,16 +1452,16 @@
         <v>43018</v>
       </c>
       <c r="B52" t="n">
-        <v>206.8825988769531</v>
+        <v>206.8826141357422</v>
       </c>
       <c r="C52" t="n">
-        <v>208.564573402578</v>
+        <v>208.5645887854224</v>
       </c>
       <c r="D52" t="n">
-        <v>204.1914476692005</v>
+        <v>204.1914627295016</v>
       </c>
       <c r="E52" t="n">
-        <v>207.5553967204503</v>
+        <v>207.5554120288621</v>
       </c>
       <c r="F52" t="n">
         <v>108639</v>
@@ -1492,16 +1492,16 @@
         <v>43021</v>
       </c>
       <c r="B54" t="n">
-        <v>211.0538940429688</v>
+        <v>211.0539093017578</v>
       </c>
       <c r="C54" t="n">
-        <v>213.0722608415774</v>
+        <v>213.0722762462905</v>
       </c>
       <c r="D54" t="n">
-        <v>210.2465526790236</v>
+        <v>210.2465678794434</v>
       </c>
       <c r="E54" t="n">
-        <v>210.2465526790236</v>
+        <v>210.2465678794434</v>
       </c>
       <c r="F54" t="n">
         <v>88189</v>
@@ -1512,16 +1512,16 @@
         <v>43024</v>
       </c>
       <c r="B55" t="n">
-        <v>214.148681640625</v>
+        <v>214.1487274169922</v>
       </c>
       <c r="C55" t="n">
-        <v>215.2924149845671</v>
+        <v>215.2924610054184</v>
       </c>
       <c r="D55" t="n">
-        <v>211.390252540022</v>
+        <v>211.3902977267481</v>
       </c>
       <c r="E55" t="n">
-        <v>211.9284799959947</v>
+        <v>211.9285252977722</v>
       </c>
       <c r="F55" t="n">
         <v>160232</v>
@@ -1532,16 +1532,16 @@
         <v>43025</v>
       </c>
       <c r="B56" t="n">
-        <v>213.2740783691406</v>
+        <v>213.2740936279297</v>
       </c>
       <c r="C56" t="n">
-        <v>215.1578881164158</v>
+        <v>215.1579035099829</v>
       </c>
       <c r="D56" t="n">
-        <v>212.130344865747</v>
+        <v>212.1303600427072</v>
       </c>
       <c r="E56" t="n">
-        <v>214.1487114957744</v>
+        <v>214.1487268171395</v>
       </c>
       <c r="F56" t="n">
         <v>68039</v>
@@ -1552,16 +1552,16 @@
         <v>43026</v>
       </c>
       <c r="B57" t="n">
-        <v>215.6288604736328</v>
+        <v>215.6288452148438</v>
       </c>
       <c r="C57" t="n">
-        <v>215.6288604736328</v>
+        <v>215.6288452148438</v>
       </c>
       <c r="D57" t="n">
-        <v>211.9957976953891</v>
+        <v>211.9957826936906</v>
       </c>
       <c r="E57" t="n">
-        <v>214.6196704180117</v>
+        <v>214.6196552306371</v>
       </c>
       <c r="F57" t="n">
         <v>93014</v>
@@ -1592,16 +1592,16 @@
         <v>43028</v>
       </c>
       <c r="B59" t="n">
-        <v>223.50048828125</v>
+        <v>223.5004730224609</v>
       </c>
       <c r="C59" t="n">
-        <v>225.9225122411252</v>
+        <v>225.9224968169801</v>
       </c>
       <c r="D59" t="n">
-        <v>220.9438806572252</v>
+        <v>220.9438655729804</v>
       </c>
       <c r="E59" t="n">
-        <v>220.9438806572252</v>
+        <v>220.9438655729804</v>
       </c>
       <c r="F59" t="n">
         <v>90497</v>
@@ -1612,16 +1612,16 @@
         <v>43031</v>
       </c>
       <c r="B60" t="n">
-        <v>221.3475341796875</v>
+        <v>221.3475494384766</v>
       </c>
       <c r="C60" t="n">
-        <v>226.1243434525052</v>
+        <v>226.1243590405879</v>
       </c>
       <c r="D60" t="n">
-        <v>220.876585112841</v>
+        <v>220.8766003391648</v>
       </c>
       <c r="E60" t="n">
-        <v>225.5188241206729</v>
+        <v>225.5188396670136</v>
       </c>
       <c r="F60" t="n">
         <v>72604</v>
@@ -1652,16 +1652,16 @@
         <v>43033</v>
       </c>
       <c r="B62" t="n">
-        <v>218.9927978515625</v>
+        <v>218.9927825927734</v>
       </c>
       <c r="C62" t="n">
-        <v>221.1457214803405</v>
+        <v>221.1457060715419</v>
       </c>
       <c r="D62" t="n">
-        <v>217.1089880027886</v>
+        <v>217.108972875258</v>
       </c>
       <c r="E62" t="n">
-        <v>219.80015258032</v>
+        <v>219.8001372652768</v>
       </c>
       <c r="F62" t="n">
         <v>83611</v>
@@ -1672,16 +1672,16 @@
         <v>43034</v>
       </c>
       <c r="B63" t="n">
-        <v>221.8185272216797</v>
+        <v>221.8185119628906</v>
       </c>
       <c r="C63" t="n">
-        <v>223.3659315118316</v>
+        <v>223.3659161465973</v>
       </c>
       <c r="D63" t="n">
-        <v>218.320021179497</v>
+        <v>218.3200061613684</v>
       </c>
       <c r="E63" t="n">
-        <v>219.598325068803</v>
+        <v>219.5983099627405</v>
       </c>
       <c r="F63" t="n">
         <v>55545</v>
@@ -1712,16 +1712,16 @@
         <v>43038</v>
       </c>
       <c r="B65" t="n">
-        <v>222.0203399658203</v>
+        <v>222.0203552246094</v>
       </c>
       <c r="C65" t="n">
-        <v>223.7695928088662</v>
+        <v>223.7696081878762</v>
       </c>
       <c r="D65" t="n">
-        <v>220.6074793255247</v>
+        <v>220.6074944872121</v>
       </c>
       <c r="E65" t="n">
-        <v>222.8949596929711</v>
+        <v>222.8949750118701</v>
       </c>
       <c r="F65" t="n">
         <v>160324</v>
@@ -1732,16 +1732,16 @@
         <v>43039</v>
       </c>
       <c r="B66" t="n">
-        <v>220.7420501708984</v>
+        <v>220.7420806884766</v>
       </c>
       <c r="C66" t="n">
-        <v>223.0968091278583</v>
+        <v>223.0968399709818</v>
       </c>
       <c r="D66" t="n">
-        <v>219.9347088332248</v>
+        <v>219.934739239188</v>
       </c>
       <c r="E66" t="n">
-        <v>223.0968091278583</v>
+        <v>223.0968399709818</v>
       </c>
       <c r="F66" t="n">
         <v>91632</v>
@@ -1752,16 +1752,16 @@
         <v>43040</v>
       </c>
       <c r="B67" t="n">
-        <v>223.7696075439453</v>
+        <v>223.7695922851562</v>
       </c>
       <c r="C67" t="n">
-        <v>227.6044922965676</v>
+        <v>227.6044767762788</v>
       </c>
       <c r="D67" t="n">
-        <v>222.4913037005743</v>
+        <v>222.4912885289525</v>
       </c>
       <c r="E67" t="n">
-        <v>225.3842902234725</v>
+        <v>225.3842748545786</v>
       </c>
       <c r="F67" t="n">
         <v>232015</v>
@@ -1772,16 +1772,16 @@
         <v>43042</v>
       </c>
       <c r="B68" t="n">
-        <v>225.2497406005859</v>
+        <v>225.249755859375</v>
       </c>
       <c r="C68" t="n">
-        <v>227.0662720624047</v>
+        <v>227.0662874442486</v>
       </c>
       <c r="D68" t="n">
-        <v>223.5005009746637</v>
+        <v>223.5005161149564</v>
       </c>
       <c r="E68" t="n">
-        <v>226.7298932153962</v>
+        <v>226.7299085744532</v>
       </c>
       <c r="F68" t="n">
         <v>201288</v>
@@ -1812,16 +1812,16 @@
         <v>43046</v>
       </c>
       <c r="B70" t="n">
-        <v>228.8155364990234</v>
+        <v>228.8154907226562</v>
       </c>
       <c r="C70" t="n">
-        <v>229.4210291294309</v>
+        <v>229.4209832319301</v>
       </c>
       <c r="D70" t="n">
-        <v>227.2008270037908</v>
+        <v>227.2007815504591</v>
       </c>
       <c r="E70" t="n">
-        <v>229.4210291294309</v>
+        <v>229.4209832319301</v>
       </c>
       <c r="F70" t="n">
         <v>136939</v>
@@ -1832,16 +1832,16 @@
         <v>43047</v>
       </c>
       <c r="B71" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C71" t="n">
-        <v>234.0994316756239</v>
+        <v>234.0994470241699</v>
       </c>
       <c r="D71" t="n">
-        <v>230.1293234466875</v>
+        <v>230.1293385349365</v>
       </c>
       <c r="E71" t="n">
-        <v>230.8138474119391</v>
+        <v>230.8138625450684</v>
       </c>
       <c r="F71" t="n">
         <v>198823</v>
@@ -1852,16 +1852,16 @@
         <v>43048</v>
       </c>
       <c r="B72" t="n">
-        <v>231.9090423583984</v>
+        <v>231.9090118408203</v>
       </c>
       <c r="C72" t="n">
-        <v>233.4149351471667</v>
+        <v>233.4149044314238</v>
       </c>
       <c r="D72" t="n">
-        <v>228.9656928312533</v>
+        <v>228.965662700999</v>
       </c>
       <c r="E72" t="n">
-        <v>232.7304384249993</v>
+        <v>232.7304077993313</v>
       </c>
       <c r="F72" t="n">
         <v>198249</v>
@@ -1892,16 +1892,16 @@
         <v>43052</v>
       </c>
       <c r="B74" t="n">
-        <v>232.6620025634766</v>
+        <v>232.6619720458984</v>
       </c>
       <c r="C74" t="n">
-        <v>232.7304386139235</v>
+        <v>232.7304080873689</v>
       </c>
       <c r="D74" t="n">
-        <v>228.7603303784792</v>
+        <v>228.7603003726717</v>
       </c>
       <c r="E74" t="n">
-        <v>231.0191831852906</v>
+        <v>231.0191528831962</v>
       </c>
       <c r="F74" t="n">
         <v>214187</v>
@@ -1912,16 +1912,16 @@
         <v>43053</v>
       </c>
       <c r="B75" t="n">
-        <v>230.5400390625</v>
+        <v>230.5400543212891</v>
       </c>
       <c r="C75" t="n">
-        <v>232.4566298026679</v>
+        <v>232.4566451883106</v>
       </c>
       <c r="D75" t="n">
-        <v>228.9656830469659</v>
+        <v>228.9656982015528</v>
       </c>
       <c r="E75" t="n">
-        <v>232.4566298026679</v>
+        <v>232.4566451883106</v>
       </c>
       <c r="F75" t="n">
         <v>164145</v>
@@ -1932,16 +1932,16 @@
         <v>43055</v>
       </c>
       <c r="B76" t="n">
-        <v>229.9924163818359</v>
+        <v>229.9924011230469</v>
       </c>
       <c r="C76" t="n">
-        <v>232.7988937116663</v>
+        <v>232.7988782666822</v>
       </c>
       <c r="D76" t="n">
-        <v>229.1710203434879</v>
+        <v>229.1710051391942</v>
       </c>
       <c r="E76" t="n">
-        <v>230.4715776926971</v>
+        <v>230.4715624021183</v>
       </c>
       <c r="F76" t="n">
         <v>84511</v>
@@ -1952,16 +1952,16 @@
         <v>43056</v>
       </c>
       <c r="B77" t="n">
-        <v>230.6084747314453</v>
+        <v>230.6084899902344</v>
       </c>
       <c r="C77" t="n">
-        <v>232.3197300827539</v>
+        <v>232.3197454547725</v>
       </c>
       <c r="D77" t="n">
-        <v>226.2961183294964</v>
+        <v>226.2961333029476</v>
       </c>
       <c r="E77" t="n">
-        <v>229.9924140870064</v>
+        <v>229.9924293050323</v>
       </c>
       <c r="F77" t="n">
         <v>104830</v>
@@ -1972,16 +1972,16 @@
         <v>43060</v>
       </c>
       <c r="B78" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C78" t="n">
-        <v>235.3999890684911</v>
+        <v>235.4000045023071</v>
       </c>
       <c r="D78" t="n">
-        <v>228.9656926417911</v>
+        <v>228.9657076537476</v>
       </c>
       <c r="E78" t="n">
-        <v>231.0191828065941</v>
+        <v>231.019197953186</v>
       </c>
       <c r="F78" t="n">
         <v>104948</v>
@@ -2032,16 +2032,16 @@
         <v>43063</v>
       </c>
       <c r="B81" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C81" t="n">
-        <v>234.4416936582497</v>
+        <v>234.4417090292359</v>
       </c>
       <c r="D81" t="n">
-        <v>230.6769480676189</v>
+        <v>230.6769631917725</v>
       </c>
       <c r="E81" t="n">
-        <v>232.0459415108209</v>
+        <v>232.0459567247315</v>
       </c>
       <c r="F81" t="n">
         <v>49924</v>
@@ -2052,16 +2052,16 @@
         <v>43066</v>
       </c>
       <c r="B82" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C82" t="n">
-        <v>233.4833982480083</v>
+        <v>233.4834135561646</v>
       </c>
       <c r="D82" t="n">
-        <v>231.5667801838749</v>
+        <v>231.5667953663696</v>
       </c>
       <c r="E82" t="n">
-        <v>233.4833982480083</v>
+        <v>233.4834135561646</v>
       </c>
       <c r="F82" t="n">
         <v>74064</v>
@@ -2072,16 +2072,16 @@
         <v>43067</v>
       </c>
       <c r="B83" t="n">
-        <v>231.7721405029297</v>
+        <v>231.7721252441406</v>
       </c>
       <c r="C83" t="n">
-        <v>233.0726978827827</v>
+        <v>233.0726825383711</v>
       </c>
       <c r="D83" t="n">
-        <v>231.7721405029297</v>
+        <v>231.7721252441406</v>
       </c>
       <c r="E83" t="n">
-        <v>232.7304359035818</v>
+        <v>232.7304205817031</v>
       </c>
       <c r="F83" t="n">
         <v>48463</v>
@@ -2092,16 +2092,16 @@
         <v>43068</v>
       </c>
       <c r="B84" t="n">
-        <v>232.5251007080078</v>
+        <v>232.5250854492188</v>
       </c>
       <c r="C84" t="n">
-        <v>232.7304361007821</v>
+        <v>232.7304208285185</v>
       </c>
       <c r="D84" t="n">
-        <v>229.3763885738325</v>
+        <v>229.3763735216686</v>
       </c>
       <c r="E84" t="n">
-        <v>231.772140699318</v>
+        <v>231.7721254899398</v>
       </c>
       <c r="F84" t="n">
         <v>67439</v>
@@ -2112,16 +2112,16 @@
         <v>43069</v>
       </c>
       <c r="B85" t="n">
-        <v>235.1262054443359</v>
+        <v>235.1261901855469</v>
       </c>
       <c r="C85" t="n">
-        <v>235.1262054443359</v>
+        <v>235.1261901855469</v>
       </c>
       <c r="D85" t="n">
-        <v>230.0609021363051</v>
+        <v>230.0608872062348</v>
       </c>
       <c r="E85" t="n">
-        <v>232.4566544372292</v>
+        <v>232.4566393516838</v>
       </c>
       <c r="F85" t="n">
         <v>138609</v>
@@ -2132,16 +2132,16 @@
         <v>43070</v>
       </c>
       <c r="B86" t="n">
-        <v>234.7154693603516</v>
+        <v>234.7154846191406</v>
       </c>
       <c r="C86" t="n">
-        <v>237.8641812150019</v>
+        <v>237.8641966784879</v>
       </c>
       <c r="D86" t="n">
-        <v>233.6887107566789</v>
+        <v>233.6887259487187</v>
       </c>
       <c r="E86" t="n">
-        <v>234.7154693603516</v>
+        <v>234.7154846191406</v>
       </c>
       <c r="F86" t="n">
         <v>135061</v>
@@ -2152,16 +2152,16 @@
         <v>43073</v>
       </c>
       <c r="B87" t="n">
-        <v>232.6620025634766</v>
+        <v>232.6619720458984</v>
       </c>
       <c r="C87" t="n">
-        <v>237.5219429166355</v>
+        <v>237.5219117615936</v>
       </c>
       <c r="D87" t="n">
-        <v>232.6620025634766</v>
+        <v>232.6619720458984</v>
       </c>
       <c r="E87" t="n">
-        <v>235.4684527484664</v>
+        <v>235.4684218627746</v>
       </c>
       <c r="F87" t="n">
         <v>80546</v>
@@ -2172,16 +2172,16 @@
         <v>43074</v>
       </c>
       <c r="B88" t="n">
-        <v>230.1293182373047</v>
+        <v>230.1292877197266</v>
       </c>
       <c r="C88" t="n">
-        <v>234.2363257175919</v>
+        <v>234.2362946553812</v>
       </c>
       <c r="D88" t="n">
-        <v>230.1293182373047</v>
+        <v>230.1292877197266</v>
       </c>
       <c r="E88" t="n">
-        <v>232.7304329641582</v>
+        <v>232.7304021016448</v>
       </c>
       <c r="F88" t="n">
         <v>50811</v>
@@ -2192,16 +2192,16 @@
         <v>43075</v>
       </c>
       <c r="B89" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C89" t="n">
-        <v>235.3999890684911</v>
+        <v>235.4000045023071</v>
       </c>
       <c r="D89" t="n">
-        <v>229.5132900190719</v>
+        <v>229.5133050669312</v>
       </c>
       <c r="E89" t="n">
-        <v>229.9239880520325</v>
+        <v>229.9240031268189</v>
       </c>
       <c r="F89" t="n">
         <v>49754</v>
@@ -2252,16 +2252,16 @@
         <v>43080</v>
       </c>
       <c r="B92" t="n">
-        <v>231.8405456542969</v>
+        <v>231.840576171875</v>
       </c>
       <c r="C92" t="n">
-        <v>232.730404886704</v>
+        <v>232.7304355214159</v>
       </c>
       <c r="D92" t="n">
-        <v>227.2543910330259</v>
+        <v>227.2544209469205</v>
       </c>
       <c r="E92" t="n">
-        <v>229.6501564590137</v>
+        <v>229.650186688267</v>
       </c>
       <c r="F92" t="n">
         <v>117298</v>
@@ -2272,16 +2272,16 @@
         <v>43081</v>
       </c>
       <c r="B93" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C93" t="n">
-        <v>232.9358008707275</v>
+        <v>232.935816142981</v>
       </c>
       <c r="D93" t="n">
-        <v>230.8822834622739</v>
+        <v>230.8822985998901</v>
       </c>
       <c r="E93" t="n">
-        <v>231.5667801838749</v>
+        <v>231.5667953663696</v>
       </c>
       <c r="F93" t="n">
         <v>108939</v>
@@ -2292,16 +2292,16 @@
         <v>43082</v>
       </c>
       <c r="B94" t="n">
-        <v>228.1442718505859</v>
+        <v>228.144287109375</v>
       </c>
       <c r="C94" t="n">
-        <v>235.2630782742499</v>
+        <v>235.2630940091604</v>
       </c>
       <c r="D94" t="n">
-        <v>226.0907681638988</v>
+        <v>226.090783285345</v>
       </c>
       <c r="E94" t="n">
-        <v>233.3464875470449</v>
+        <v>233.3465031537696</v>
       </c>
       <c r="F94" t="n">
         <v>51971</v>
@@ -2352,16 +2352,16 @@
         <v>43087</v>
       </c>
       <c r="B97" t="n">
-        <v>225.8854064941406</v>
+        <v>225.8854217529297</v>
       </c>
       <c r="C97" t="n">
-        <v>229.9924000154498</v>
+        <v>229.9924155516704</v>
       </c>
       <c r="D97" t="n">
-        <v>219.5879964494582</v>
+        <v>219.5880112828508</v>
       </c>
       <c r="E97" t="n">
-        <v>227.3913127457758</v>
+        <v>227.3913281062903</v>
       </c>
       <c r="F97" t="n">
         <v>41081</v>
@@ -2372,16 +2372,16 @@
         <v>43088</v>
       </c>
       <c r="B98" t="n">
-        <v>224.5163879394531</v>
+        <v>224.5164184570312</v>
       </c>
       <c r="C98" t="n">
-        <v>226.4329920817304</v>
+        <v>226.4330228598245</v>
       </c>
       <c r="D98" t="n">
-        <v>223.1473810887342</v>
+        <v>223.1474114202289</v>
       </c>
       <c r="E98" t="n">
-        <v>225.9538444516168</v>
+        <v>225.9538751645824</v>
       </c>
       <c r="F98" t="n">
         <v>28066</v>
@@ -2392,16 +2392,16 @@
         <v>43089</v>
       </c>
       <c r="B99" t="n">
-        <v>224.7217712402344</v>
+        <v>224.7217559814453</v>
       </c>
       <c r="C99" t="n">
-        <v>226.6383756751893</v>
+        <v>226.6383602862613</v>
       </c>
       <c r="D99" t="n">
-        <v>220.683213354632</v>
+        <v>220.6831983700643</v>
       </c>
       <c r="E99" t="n">
-        <v>223.6265764898746</v>
+        <v>223.6265613054501</v>
       </c>
       <c r="F99" t="n">
         <v>282957</v>
@@ -2432,16 +2432,16 @@
         <v>43091</v>
       </c>
       <c r="B101" t="n">
-        <v>230.5400390625</v>
+        <v>230.5400543212891</v>
       </c>
       <c r="C101" t="n">
-        <v>230.5400390625</v>
+        <v>230.5400543212891</v>
       </c>
       <c r="D101" t="n">
-        <v>225.2009103704476</v>
+        <v>225.200925275855</v>
       </c>
       <c r="E101" t="n">
-        <v>226.9806153938569</v>
+        <v>226.9806304170578</v>
       </c>
       <c r="F101" t="n">
         <v>94553</v>
@@ -2452,16 +2452,16 @@
         <v>43095</v>
       </c>
       <c r="B102" t="n">
-        <v>232.7989196777344</v>
+        <v>232.7988739013672</v>
       </c>
       <c r="C102" t="n">
-        <v>233.6887518633706</v>
+        <v>233.6887059120314</v>
       </c>
       <c r="D102" t="n">
-        <v>226.5699445381911</v>
+        <v>226.5698999866571</v>
       </c>
       <c r="E102" t="n">
-        <v>230.6085027541738</v>
+        <v>230.6084574085188</v>
       </c>
       <c r="F102" t="n">
         <v>75564</v>
@@ -2472,16 +2472,16 @@
         <v>43096</v>
       </c>
       <c r="B103" t="n">
-        <v>230.6769256591797</v>
+        <v>230.6769561767578</v>
       </c>
       <c r="C103" t="n">
-        <v>232.7304156245024</v>
+        <v>232.7304464137485</v>
       </c>
       <c r="D103" t="n">
-        <v>230.6769256591797</v>
+        <v>230.6769561767578</v>
       </c>
       <c r="E103" t="n">
-        <v>232.6619795808156</v>
+        <v>232.6620103610079</v>
       </c>
       <c r="F103" t="n">
         <v>56145</v>
@@ -2492,16 +2492,16 @@
         <v>43097</v>
       </c>
       <c r="B104" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C104" t="n">
-        <v>233.0727002150477</v>
+        <v>233.0727154962769</v>
       </c>
       <c r="D104" t="n">
-        <v>228.1442829540446</v>
+        <v>228.144297912146</v>
       </c>
       <c r="E104" t="n">
-        <v>230.7453841179537</v>
+        <v>230.7453992465942</v>
       </c>
       <c r="F104" t="n">
         <v>86715</v>
@@ -2552,16 +2552,16 @@
         <v>43104</v>
       </c>
       <c r="B107" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C107" t="n">
-        <v>234.0994316756239</v>
+        <v>234.0994470241699</v>
       </c>
       <c r="D107" t="n">
-        <v>228.9656926417911</v>
+        <v>228.9657076537476</v>
       </c>
       <c r="E107" t="n">
-        <v>230.8138474119391</v>
+        <v>230.8138625450684</v>
       </c>
       <c r="F107" t="n">
         <v>136353</v>
@@ -2572,16 +2572,16 @@
         <v>43105</v>
       </c>
       <c r="B108" t="n">
-        <v>235.7422637939453</v>
+        <v>235.7422332763672</v>
       </c>
       <c r="C108" t="n">
-        <v>236.7690225536726</v>
+        <v>236.7689919031773</v>
       </c>
       <c r="D108" t="n">
-        <v>230.8138598883673</v>
+        <v>230.8138300087865</v>
       </c>
       <c r="E108" t="n">
-        <v>231.3614572952479</v>
+        <v>231.361427344779</v>
       </c>
       <c r="F108" t="n">
         <v>47198</v>
@@ -2592,16 +2592,16 @@
         <v>43108</v>
       </c>
       <c r="B109" t="n">
-        <v>239.5754547119141</v>
+        <v>239.5754699707031</v>
       </c>
       <c r="C109" t="n">
-        <v>240.8075487839307</v>
+        <v>240.807564121193</v>
       </c>
       <c r="D109" t="n">
-        <v>233.6202924983588</v>
+        <v>233.6203073778579</v>
       </c>
       <c r="E109" t="n">
-        <v>235.8791452522142</v>
+        <v>235.8791602755818</v>
       </c>
       <c r="F109" t="n">
         <v>106434</v>
@@ -2652,16 +2652,16 @@
         <v>43111</v>
       </c>
       <c r="B112" t="n">
-        <v>246.4204406738281</v>
+        <v>246.4204559326172</v>
       </c>
       <c r="C112" t="n">
-        <v>246.4204406738281</v>
+        <v>246.4204559326172</v>
       </c>
       <c r="D112" t="n">
-        <v>238.3433253213977</v>
+        <v>238.3433400800375</v>
       </c>
       <c r="E112" t="n">
-        <v>239.5754465953212</v>
+        <v>239.5754614302561</v>
       </c>
       <c r="F112" t="n">
         <v>230476</v>
@@ -2672,16 +2672,16 @@
         <v>43112</v>
       </c>
       <c r="B113" t="n">
-        <v>253.1969757080078</v>
+        <v>253.1970367431641</v>
       </c>
       <c r="C113" t="n">
-        <v>255.2504653509947</v>
+        <v>255.250526881161</v>
       </c>
       <c r="D113" t="n">
-        <v>244.2984388574671</v>
+        <v>244.2984977475599</v>
       </c>
       <c r="E113" t="n">
-        <v>244.4353381669996</v>
+        <v>244.435397090093</v>
       </c>
       <c r="F113" t="n">
         <v>209648</v>
@@ -2692,16 +2692,16 @@
         <v>43115</v>
       </c>
       <c r="B114" t="n">
-        <v>256.6879272460938</v>
+        <v>256.6880493164062</v>
       </c>
       <c r="C114" t="n">
-        <v>260.7949338640821</v>
+        <v>260.7950578875195</v>
       </c>
       <c r="D114" t="n">
-        <v>256.0034306837031</v>
+        <v>256.0035524284969</v>
       </c>
       <c r="E114" t="n">
-        <v>256.0034306837031</v>
+        <v>256.0035524284969</v>
       </c>
       <c r="F114" t="n">
         <v>103578</v>
@@ -2712,16 +2712,16 @@
         <v>43116</v>
       </c>
       <c r="B115" t="n">
-        <v>258.4676513671875</v>
+        <v>258.4676818847656</v>
       </c>
       <c r="C115" t="n">
-        <v>260.1104705706915</v>
+        <v>260.1105012822392</v>
       </c>
       <c r="D115" t="n">
-        <v>257.5093560572714</v>
+        <v>257.5093864617024</v>
       </c>
       <c r="E115" t="n">
-        <v>257.5093560572714</v>
+        <v>257.5093864617024</v>
       </c>
       <c r="F115" t="n">
         <v>112382</v>
@@ -2732,16 +2732,16 @@
         <v>43117</v>
       </c>
       <c r="B116" t="n">
-        <v>256.6879272460938</v>
+        <v>256.6880493164062</v>
       </c>
       <c r="C116" t="n">
-        <v>259.2890414268226</v>
+        <v>259.289164734119</v>
       </c>
       <c r="D116" t="n">
-        <v>256.0034306837031</v>
+        <v>256.0035524284969</v>
       </c>
       <c r="E116" t="n">
-        <v>258.5360815863707</v>
+        <v>258.5362045355901</v>
       </c>
       <c r="F116" t="n">
         <v>84224</v>
@@ -2752,16 +2752,16 @@
         <v>43118</v>
       </c>
       <c r="B117" t="n">
-        <v>256.6879272460938</v>
+        <v>256.6880493164062</v>
       </c>
       <c r="C117" t="n">
-        <v>260.1104373016914</v>
+        <v>260.1105609996102</v>
       </c>
       <c r="D117" t="n">
-        <v>255.7296320587468</v>
+        <v>255.7297536733332</v>
       </c>
       <c r="E117" t="n">
-        <v>257.3039877740675</v>
+        <v>257.3041101373533</v>
       </c>
       <c r="F117" t="n">
         <v>137800</v>
@@ -2772,16 +2772,16 @@
         <v>43119</v>
       </c>
       <c r="B118" t="n">
-        <v>256.6879272460938</v>
+        <v>256.6880493164062</v>
       </c>
       <c r="C118" t="n">
-        <v>259.9050747111521</v>
+        <v>259.9051983114088</v>
       </c>
       <c r="D118" t="n">
-        <v>256.6879272460938</v>
+        <v>256.6880493164062</v>
       </c>
       <c r="E118" t="n">
-        <v>256.6879272460938</v>
+        <v>256.6880493164062</v>
       </c>
       <c r="F118" t="n">
         <v>172753</v>
@@ -2792,16 +2792,16 @@
         <v>43122</v>
       </c>
       <c r="B119" t="n">
-        <v>261.1372680664062</v>
+        <v>261.1372375488281</v>
       </c>
       <c r="C119" t="n">
-        <v>265.3127118748384</v>
+        <v>265.3126808693007</v>
       </c>
       <c r="D119" t="n">
-        <v>256.0035015616586</v>
+        <v>256.0034716440336</v>
       </c>
       <c r="E119" t="n">
-        <v>256.6879983135613</v>
+        <v>256.6879683159431</v>
       </c>
       <c r="F119" t="n">
         <v>99157</v>
@@ -2812,16 +2812,16 @@
         <v>43123</v>
       </c>
       <c r="B120" t="n">
-        <v>261.4794921875</v>
+        <v>261.4794616699219</v>
       </c>
       <c r="C120" t="n">
-        <v>268.1876145706647</v>
+        <v>268.1875832701738</v>
       </c>
       <c r="D120" t="n">
-        <v>258.7414780475785</v>
+        <v>258.7414478495573</v>
       </c>
       <c r="E120" t="n">
-        <v>258.7414780475785</v>
+        <v>258.7414478495573</v>
       </c>
       <c r="F120" t="n">
         <v>126649</v>
@@ -2832,16 +2832,16 @@
         <v>43124</v>
       </c>
       <c r="B121" t="n">
-        <v>261.4794921875</v>
+        <v>261.4794616699219</v>
       </c>
       <c r="C121" t="n">
-        <v>265.5864997755568</v>
+        <v>265.586468778645</v>
       </c>
       <c r="D121" t="n">
-        <v>260.5211967738052</v>
+        <v>260.5211663680709</v>
       </c>
       <c r="E121" t="n">
-        <v>261.8901902219406</v>
+        <v>261.8901596564294</v>
       </c>
       <c r="F121" t="n">
         <v>135740</v>
@@ -2852,16 +2852,16 @@
         <v>43126</v>
       </c>
       <c r="B122" t="n">
-        <v>260.7949829101562</v>
+        <v>260.7950134277344</v>
       </c>
       <c r="C122" t="n">
-        <v>268.2560377088348</v>
+        <v>268.2560690994869</v>
       </c>
       <c r="D122" t="n">
-        <v>256.0719148759564</v>
+        <v>256.0719448408529</v>
       </c>
       <c r="E122" t="n">
-        <v>262.5062382597801</v>
+        <v>262.5062689776051</v>
       </c>
       <c r="F122" t="n">
         <v>251382</v>
@@ -2872,16 +2872,16 @@
         <v>43129</v>
       </c>
       <c r="B123" t="n">
-        <v>254.9766998291016</v>
+        <v>254.9767608642578</v>
       </c>
       <c r="C123" t="n">
-        <v>264.2174725311472</v>
+        <v>264.2175357783174</v>
       </c>
       <c r="D123" t="n">
-        <v>250.6643301535979</v>
+        <v>250.6643901564788</v>
       </c>
       <c r="E123" t="n">
-        <v>260.1104654684211</v>
+        <v>260.1105277324746</v>
       </c>
       <c r="F123" t="n">
         <v>143447</v>
@@ -2892,16 +2892,16 @@
         <v>43130</v>
       </c>
       <c r="B124" t="n">
-        <v>254.9766998291016</v>
+        <v>254.9767608642578</v>
       </c>
       <c r="C124" t="n">
-        <v>256.6194917567331</v>
+        <v>256.6195531851334</v>
       </c>
       <c r="D124" t="n">
-        <v>249.911397475257</v>
+        <v>249.9114572979043</v>
       </c>
       <c r="E124" t="n">
-        <v>256.4825924294305</v>
+        <v>256.4826538250604</v>
       </c>
       <c r="F124" t="n">
         <v>107087</v>
@@ -2932,16 +2932,16 @@
         <v>43132</v>
       </c>
       <c r="B126" t="n">
-        <v>259.0836791992188</v>
+        <v>259.083740234375</v>
       </c>
       <c r="C126" t="n">
-        <v>261.0002968202418</v>
+        <v>261.0003583069165</v>
       </c>
       <c r="D126" t="n">
-        <v>256.6879276056732</v>
+        <v>256.6879880764362</v>
       </c>
       <c r="E126" t="n">
-        <v>260.1104376660653</v>
+        <v>260.1104989431061</v>
       </c>
       <c r="F126" t="n">
         <v>203518</v>
@@ -2952,16 +2952,16 @@
         <v>43133</v>
       </c>
       <c r="B127" t="n">
-        <v>260.0420227050781</v>
+        <v>260.0420532226562</v>
       </c>
       <c r="C127" t="n">
-        <v>262.3008754056605</v>
+        <v>262.3009061883292</v>
       </c>
       <c r="D127" t="n">
-        <v>257.1671366048411</v>
+        <v>257.1671667850331</v>
       </c>
       <c r="E127" t="n">
-        <v>257.6462706663893</v>
+        <v>257.6463009028107</v>
       </c>
       <c r="F127" t="n">
         <v>110412</v>
@@ -2972,16 +2972,16 @@
         <v>43136</v>
       </c>
       <c r="B128" t="n">
-        <v>266.2709655761719</v>
+        <v>266.27099609375</v>
       </c>
       <c r="C128" t="n">
-        <v>266.9554622207453</v>
+        <v>266.9554928167743</v>
       </c>
       <c r="D128" t="n">
-        <v>257.5093540383363</v>
+        <v>257.5093835517375</v>
       </c>
       <c r="E128" t="n">
-        <v>260.042005245082</v>
+        <v>260.0420350487528</v>
       </c>
       <c r="F128" t="n">
         <v>164614</v>
@@ -2992,16 +2992,16 @@
         <v>43137</v>
       </c>
       <c r="B129" t="n">
-        <v>265.0389404296875</v>
+        <v>265.0388793945312</v>
       </c>
       <c r="C129" t="n">
-        <v>266.8870954717079</v>
+        <v>266.8870340109447</v>
       </c>
       <c r="D129" t="n">
-        <v>260.7950328878117</v>
+        <v>260.7949728299743</v>
       </c>
       <c r="E129" t="n">
-        <v>264.8335777611721</v>
+        <v>264.8335167733082</v>
       </c>
       <c r="F129" t="n">
         <v>121863</v>
@@ -3012,16 +3012,16 @@
         <v>43138</v>
       </c>
       <c r="B130" t="n">
-        <v>264.2174682617188</v>
+        <v>264.2174987792969</v>
       </c>
       <c r="C130" t="n">
-        <v>266.4763207475355</v>
+        <v>266.476351526015</v>
       </c>
       <c r="D130" t="n">
-        <v>261.2056558660808</v>
+        <v>261.2056860357894</v>
       </c>
       <c r="E130" t="n">
-        <v>265.5864615126238</v>
+        <v>265.5864921883231</v>
       </c>
       <c r="F130" t="n">
         <v>107778</v>
@@ -3052,16 +3052,16 @@
         <v>43140</v>
       </c>
       <c r="B132" t="n">
-        <v>258.0570068359375</v>
+        <v>258.0569763183594</v>
       </c>
       <c r="C132" t="n">
-        <v>270.24113145986</v>
+        <v>270.2410995013987</v>
       </c>
       <c r="D132" t="n">
-        <v>256.5511138941107</v>
+        <v>256.5510835546181</v>
       </c>
       <c r="E132" t="n">
-        <v>266.2025867667705</v>
+        <v>266.2025552859037</v>
       </c>
       <c r="F132" t="n">
         <v>222103</v>
@@ -3092,16 +3092,16 @@
         <v>43146</v>
       </c>
       <c r="B134" t="n">
-        <v>262.2324523925781</v>
+        <v>262.232421875</v>
       </c>
       <c r="C134" t="n">
-        <v>267.6400173820405</v>
+        <v>267.6399862351513</v>
       </c>
       <c r="D134" t="n">
-        <v>262.2324523925781</v>
+        <v>262.232421875</v>
       </c>
       <c r="E134" t="n">
-        <v>267.5715540877596</v>
+        <v>267.5715229488379</v>
       </c>
       <c r="F134" t="n">
         <v>86167</v>
@@ -3112,16 +3112,16 @@
         <v>43147</v>
       </c>
       <c r="B135" t="n">
-        <v>264.9019775390625</v>
+        <v>264.9020080566406</v>
       </c>
       <c r="C135" t="n">
-        <v>265.7233735288359</v>
+        <v>265.7234041410416</v>
       </c>
       <c r="D135" t="n">
-        <v>261.1372322974435</v>
+        <v>261.1372623813106</v>
       </c>
       <c r="E135" t="n">
-        <v>264.9019775390625</v>
+        <v>264.9020080566406</v>
       </c>
       <c r="F135" t="n">
         <v>112655</v>
@@ -3132,16 +3132,16 @@
         <v>43150</v>
       </c>
       <c r="B136" t="n">
-        <v>262.7799987792969</v>
+        <v>262.7800598144531</v>
       </c>
       <c r="C136" t="n">
-        <v>267.434602846689</v>
+        <v>267.4346649629567</v>
       </c>
       <c r="D136" t="n">
-        <v>261.479441633192</v>
+        <v>261.4795023662716</v>
       </c>
       <c r="E136" t="n">
-        <v>266.2025089815795</v>
+        <v>266.2025708116724</v>
       </c>
       <c r="F136" t="n">
         <v>88593</v>
@@ -3152,16 +3152,16 @@
         <v>43151</v>
       </c>
       <c r="B137" t="n">
-        <v>264.6966552734375</v>
+        <v>264.6966247558594</v>
       </c>
       <c r="C137" t="n">
-        <v>266.9555082115061</v>
+        <v>266.9554774334989</v>
       </c>
       <c r="D137" t="n">
-        <v>262.1640036303698</v>
+        <v>262.1639734047878</v>
       </c>
       <c r="E137" t="n">
-        <v>264.3544205140147</v>
+        <v>264.3543900358938</v>
       </c>
       <c r="F137" t="n">
         <v>192250</v>
@@ -3172,16 +3172,16 @@
         <v>43152</v>
       </c>
       <c r="B138" t="n">
-        <v>266.2709655761719</v>
+        <v>266.27099609375</v>
       </c>
       <c r="C138" t="n">
-        <v>268.735180740284</v>
+        <v>268.7352115402882</v>
       </c>
       <c r="D138" t="n">
-        <v>265.312670273769</v>
+        <v>265.3127006815159</v>
       </c>
       <c r="E138" t="n">
-        <v>266.1340662472572</v>
+        <v>266.1340967491452</v>
       </c>
       <c r="F138" t="n">
         <v>151246</v>
@@ -3192,16 +3192,16 @@
         <v>43153</v>
       </c>
       <c r="B139" t="n">
-        <v>266.9555053710938</v>
+        <v>266.9554748535156</v>
       </c>
       <c r="C139" t="n">
-        <v>269.6250835819088</v>
+        <v>269.6250527591523</v>
       </c>
       <c r="D139" t="n">
-        <v>263.2592228929346</v>
+        <v>263.2591927979047</v>
       </c>
       <c r="E139" t="n">
-        <v>267.3662306678745</v>
+        <v>267.3662001033434</v>
       </c>
       <c r="F139" t="n">
         <v>196828</v>
@@ -3212,16 +3212,16 @@
         <v>43154</v>
       </c>
       <c r="B140" t="n">
-        <v>266.476318359375</v>
+        <v>266.4763793945312</v>
       </c>
       <c r="C140" t="n">
-        <v>270.3095266712028</v>
+        <v>270.3095885843375</v>
       </c>
       <c r="D140" t="n">
-        <v>266.3394190355114</v>
+        <v>266.3394800393115</v>
       </c>
       <c r="E140" t="n">
-        <v>267.0239156548295</v>
+        <v>267.0239768154103</v>
       </c>
       <c r="F140" t="n">
         <v>164562</v>
@@ -3232,16 +3232,16 @@
         <v>43157</v>
       </c>
       <c r="B141" t="n">
-        <v>266.3395080566406</v>
+        <v>266.3394470214844</v>
       </c>
       <c r="C141" t="n">
-        <v>269.6935562341772</v>
+        <v>269.6934944303972</v>
       </c>
       <c r="D141" t="n">
-        <v>265.9972460107609</v>
+        <v>265.9971850540384</v>
       </c>
       <c r="E141" t="n">
-        <v>268.9405960794351</v>
+        <v>268.9405344482058</v>
       </c>
       <c r="F141" t="n">
         <v>58114</v>
@@ -3272,16 +3272,16 @@
         <v>43159</v>
       </c>
       <c r="B143" t="n">
-        <v>264.9019775390625</v>
+        <v>264.9020080566406</v>
       </c>
       <c r="C143" t="n">
-        <v>268.73518606832</v>
+        <v>268.7352170274963</v>
       </c>
       <c r="D143" t="n">
-        <v>261.7532656679495</v>
+        <v>261.7532958227857</v>
       </c>
       <c r="E143" t="n">
-        <v>266.9554675134961</v>
+        <v>266.955498267643</v>
       </c>
       <c r="F143" t="n">
         <v>75330</v>
@@ -3292,16 +3292,16 @@
         <v>43160</v>
       </c>
       <c r="B144" t="n">
-        <v>263.5329895019531</v>
+        <v>263.5330200195312</v>
       </c>
       <c r="C144" t="n">
-        <v>267.4346341533601</v>
+        <v>267.4346651227554</v>
       </c>
       <c r="D144" t="n">
-        <v>262.5062308723439</v>
+        <v>262.5062612710216</v>
       </c>
       <c r="E144" t="n">
-        <v>264.9019828456663</v>
+        <v>264.9020135217763</v>
       </c>
       <c r="F144" t="n">
         <v>57645</v>
@@ -3312,16 +3312,16 @@
         <v>43161</v>
       </c>
       <c r="B145" t="n">
-        <v>266.2709655761719</v>
+        <v>266.27099609375</v>
       </c>
       <c r="C145" t="n">
-        <v>266.9554622207453</v>
+        <v>266.9554928167743</v>
       </c>
       <c r="D145" t="n">
-        <v>262.4377571229129</v>
+        <v>262.4377872011632</v>
       </c>
       <c r="E145" t="n">
-        <v>264.9019722870249</v>
+        <v>264.9020026477014</v>
       </c>
       <c r="F145" t="n">
         <v>44407</v>
@@ -3332,16 +3332,16 @@
         <v>43164</v>
       </c>
       <c r="B146" t="n">
-        <v>263.5329895019531</v>
+        <v>263.5330200195312</v>
       </c>
       <c r="C146" t="n">
-        <v>267.2977348189888</v>
+        <v>267.2977657725309</v>
       </c>
       <c r="D146" t="n">
-        <v>262.9169288754579</v>
+        <v>262.9169593216951</v>
       </c>
       <c r="E146" t="n">
-        <v>266.6816741924935</v>
+        <v>266.6817050746948</v>
       </c>
       <c r="F146" t="n">
         <v>71404</v>
@@ -3352,16 +3352,16 @@
         <v>43165</v>
       </c>
       <c r="B147" t="n">
-        <v>267.9137573242188</v>
+        <v>267.9138488769531</v>
       </c>
       <c r="C147" t="n">
-        <v>268.8720525284629</v>
+        <v>268.8721444086703</v>
       </c>
       <c r="D147" t="n">
-        <v>263.9436499487057</v>
+        <v>263.9437401447565</v>
       </c>
       <c r="E147" t="n">
-        <v>264.2174485784897</v>
+        <v>264.2175388681043</v>
       </c>
       <c r="F147" t="n">
         <v>60553</v>
@@ -3372,16 +3372,16 @@
         <v>43166</v>
       </c>
       <c r="B148" t="n">
-        <v>272.6368713378906</v>
+        <v>272.6368103027344</v>
       </c>
       <c r="C148" t="n">
-        <v>273.1160326919399</v>
+        <v>273.1159715495139</v>
       </c>
       <c r="D148" t="n">
-        <v>266.6132726034321</v>
+        <v>266.6132129167775</v>
       </c>
       <c r="E148" t="n">
-        <v>266.6132726034321</v>
+        <v>266.6132129167775</v>
       </c>
       <c r="F148" t="n">
         <v>73125</v>
@@ -3392,16 +3392,16 @@
         <v>43167</v>
       </c>
       <c r="B149" t="n">
-        <v>277.2229919433594</v>
+        <v>277.2230224609375</v>
       </c>
       <c r="C149" t="n">
-        <v>279.2765091083056</v>
+        <v>279.2765398519413</v>
       </c>
       <c r="D149" t="n">
-        <v>273.1159848571144</v>
+        <v>273.1160149225803</v>
       </c>
       <c r="E149" t="n">
-        <v>273.8004814975473</v>
+        <v>273.8005116383648</v>
       </c>
       <c r="F149" t="n">
         <v>360517</v>
@@ -3412,16 +3412,16 @@
         <v>43168</v>
       </c>
       <c r="B150" t="n">
-        <v>289.2017822265625</v>
+        <v>289.2017517089844</v>
       </c>
       <c r="C150" t="n">
-        <v>291.5975615900788</v>
+        <v>291.5975308196897</v>
       </c>
       <c r="D150" t="n">
-        <v>277.9759816341563</v>
+        <v>277.9759523011636</v>
       </c>
       <c r="E150" t="n">
-        <v>278.0444176837037</v>
+        <v>278.0443883434895</v>
       </c>
       <c r="F150" t="n">
         <v>178074</v>
@@ -3432,16 +3432,16 @@
         <v>43171</v>
       </c>
       <c r="B151" t="n">
-        <v>295.4992370605469</v>
+        <v>295.4992065429688</v>
       </c>
       <c r="C151" t="n">
-        <v>296.5259958592174</v>
+        <v>296.5259652356011</v>
       </c>
       <c r="D151" t="n">
-        <v>286.8745230877512</v>
+        <v>286.8744934608874</v>
       </c>
       <c r="E151" t="n">
-        <v>287.4905838156842</v>
+        <v>287.4905541251969</v>
       </c>
       <c r="F151" t="n">
         <v>187725</v>
@@ -3452,16 +3452,16 @@
         <v>43172</v>
       </c>
       <c r="B152" t="n">
-        <v>298.4425659179688</v>
+        <v>298.4425354003906</v>
       </c>
       <c r="C152" t="n">
-        <v>298.4425659179688</v>
+        <v>298.4425354003906</v>
       </c>
       <c r="D152" t="n">
-        <v>293.2403634766137</v>
+        <v>293.2403334909926</v>
       </c>
       <c r="E152" t="n">
-        <v>296.5259750556568</v>
+        <v>296.5259447340618</v>
       </c>
       <c r="F152" t="n">
         <v>244066</v>
@@ -3512,16 +3512,16 @@
         <v>43175</v>
       </c>
       <c r="B155" t="n">
-        <v>277.5653076171875</v>
+        <v>277.5652465820312</v>
       </c>
       <c r="C155" t="n">
-        <v>288.1750757068819</v>
+        <v>288.1750123386933</v>
       </c>
       <c r="D155" t="n">
-        <v>275.1695280464202</v>
+        <v>275.1694675380833</v>
       </c>
       <c r="E155" t="n">
-        <v>287.2167529811139</v>
+        <v>287.2166898236554</v>
       </c>
       <c r="F155" t="n">
         <v>330507</v>
@@ -3532,16 +3532,16 @@
         <v>43178</v>
       </c>
       <c r="B156" t="n">
-        <v>286.8059997558594</v>
+        <v>286.8060607910156</v>
       </c>
       <c r="C156" t="n">
-        <v>289.2017516221983</v>
+        <v>289.2018131671943</v>
       </c>
       <c r="D156" t="n">
-        <v>278.2497508742624</v>
+        <v>278.2498100885641</v>
       </c>
       <c r="E156" t="n">
-        <v>278.9342475155524</v>
+        <v>278.9343068755218</v>
       </c>
       <c r="F156" t="n">
         <v>266146</v>
@@ -3552,16 +3552,16 @@
         <v>43179</v>
       </c>
       <c r="B157" t="n">
-        <v>290.9130249023438</v>
+        <v>290.9130554199219</v>
       </c>
       <c r="C157" t="n">
-        <v>291.5975488297652</v>
+        <v>291.5975794191518</v>
       </c>
       <c r="D157" t="n">
-        <v>287.4905414834819</v>
+        <v>287.4905716420321</v>
       </c>
       <c r="E157" t="n">
-        <v>287.4905414834819</v>
+        <v>287.4905716420321</v>
       </c>
       <c r="F157" t="n">
         <v>107700</v>
@@ -3572,16 +3572,16 @@
         <v>43180</v>
       </c>
       <c r="B158" t="n">
-        <v>292.6927490234375</v>
+        <v>292.6927795410156</v>
       </c>
       <c r="C158" t="n">
-        <v>293.651044398725</v>
+        <v>293.6510750162197</v>
       </c>
       <c r="D158" t="n">
-        <v>291.8713529874768</v>
+        <v>291.8713834194122</v>
       </c>
       <c r="E158" t="n">
-        <v>293.1718830892564</v>
+        <v>293.1719136567914</v>
       </c>
       <c r="F158" t="n">
         <v>118055</v>
@@ -3592,16 +3592,16 @@
         <v>43181</v>
       </c>
       <c r="B159" t="n">
-        <v>301.467041015625</v>
+        <v>301.4669799804688</v>
       </c>
       <c r="C159" t="n">
-        <v>302.3924212294524</v>
+        <v>302.3923600069432</v>
       </c>
       <c r="D159" t="n">
-        <v>293.4943558484136</v>
+        <v>293.4942964274109</v>
       </c>
       <c r="E159" t="n">
-        <v>294.6333027774401</v>
+        <v>294.6332431258456</v>
       </c>
       <c r="F159" t="n">
         <v>263759</v>
@@ -3612,16 +3612,16 @@
         <v>43182</v>
       </c>
       <c r="B160" t="n">
-        <v>299.3314514160156</v>
+        <v>299.3314208984375</v>
       </c>
       <c r="C160" t="n">
-        <v>305.5245171004302</v>
+        <v>305.5244859514538</v>
       </c>
       <c r="D160" t="n">
-        <v>298.1213062825533</v>
+        <v>298.1212758883524</v>
       </c>
       <c r="E160" t="n">
-        <v>301.467004984715</v>
+        <v>301.4669742494119</v>
       </c>
       <c r="F160" t="n">
         <v>128358</v>
@@ -3632,16 +3632,16 @@
         <v>43185</v>
       </c>
       <c r="B161" t="n">
-        <v>301.8229064941406</v>
+        <v>301.8228759765625</v>
       </c>
       <c r="C161" t="n">
-        <v>303.9584600260661</v>
+        <v>303.9584292925603</v>
       </c>
       <c r="D161" t="n">
-        <v>300.8974980748389</v>
+        <v>300.8974676508297</v>
       </c>
       <c r="E161" t="n">
-        <v>301.6805381474795</v>
+        <v>301.6805076442964</v>
       </c>
       <c r="F161" t="n">
         <v>81498</v>
@@ -3692,16 +3692,16 @@
         <v>43188</v>
       </c>
       <c r="B164" t="n">
-        <v>297.9789733886719</v>
+        <v>297.9789123535156</v>
       </c>
       <c r="C164" t="n">
-        <v>301.1111057738386</v>
+        <v>301.1110440971264</v>
       </c>
       <c r="D164" t="n">
-        <v>297.0535931753376</v>
+        <v>297.0535323297274</v>
       </c>
       <c r="E164" t="n">
-        <v>298.9043819340193</v>
+        <v>298.9043207093112</v>
       </c>
       <c r="F164" t="n">
         <v>133366</v>
@@ -3712,16 +3712,16 @@
         <v>43192</v>
       </c>
       <c r="B165" t="n">
-        <v>296.1282043457031</v>
+        <v>296.1281433105469</v>
       </c>
       <c r="C165" t="n">
-        <v>299.7586120877532</v>
+        <v>299.7585503043315</v>
       </c>
       <c r="D165" t="n">
-        <v>291.9282947695136</v>
+        <v>291.9282346000032</v>
       </c>
       <c r="E165" t="n">
-        <v>299.7586120877532</v>
+        <v>299.7585503043315</v>
       </c>
       <c r="F165" t="n">
         <v>76921</v>
@@ -3812,16 +3812,16 @@
         <v>43199</v>
       </c>
       <c r="B170" t="n">
-        <v>305.0262451171875</v>
+        <v>305.0262145996094</v>
       </c>
       <c r="C170" t="n">
-        <v>306.3787587390135</v>
+        <v>306.3787280861177</v>
       </c>
       <c r="D170" t="n">
-        <v>301.3246676591547</v>
+        <v>301.3246375119157</v>
       </c>
       <c r="E170" t="n">
-        <v>303.6025614794826</v>
+        <v>303.6025311043426</v>
       </c>
       <c r="F170" t="n">
         <v>72199</v>
@@ -3872,16 +3872,16 @@
         <v>43202</v>
       </c>
       <c r="B173" t="n">
-        <v>301.8229064941406</v>
+        <v>301.8228759765625</v>
       </c>
       <c r="C173" t="n">
-        <v>308.8701821518778</v>
+        <v>308.8701509217435</v>
       </c>
       <c r="D173" t="n">
-        <v>300.4703930348558</v>
+        <v>300.4703626540315</v>
       </c>
       <c r="E173" t="n">
-        <v>308.5142754512298</v>
+        <v>308.5142442570815</v>
       </c>
       <c r="F173" t="n">
         <v>107060</v>
@@ -3892,16 +3892,16 @@
         <v>43203</v>
       </c>
       <c r="B174" t="n">
-        <v>301.8229064941406</v>
+        <v>301.8228759765625</v>
       </c>
       <c r="C174" t="n">
-        <v>305.3821434926768</v>
+        <v>305.3821126152211</v>
       </c>
       <c r="D174" t="n">
-        <v>298.9755395609191</v>
+        <v>298.9755093312407</v>
       </c>
       <c r="E174" t="n">
-        <v>301.8941048334758</v>
+        <v>301.8940743086987</v>
       </c>
       <c r="F174" t="n">
         <v>180213</v>
@@ -3912,16 +3912,16 @@
         <v>43206</v>
       </c>
       <c r="B175" t="n">
-        <v>303.24658203125</v>
+        <v>303.2466430664062</v>
       </c>
       <c r="C175" t="n">
-        <v>308.2295019005512</v>
+        <v>308.2295639386315</v>
       </c>
       <c r="D175" t="n">
-        <v>300.8974620942305</v>
+        <v>300.8975226565739</v>
       </c>
       <c r="E175" t="n">
-        <v>304.7414353264356</v>
+        <v>304.7414966624646</v>
       </c>
       <c r="F175" t="n">
         <v>159737</v>
@@ -3932,16 +3932,16 @@
         <v>43207</v>
       </c>
       <c r="B176" t="n">
-        <v>314.2802429199219</v>
+        <v>314.2802734375</v>
       </c>
       <c r="C176" t="n">
-        <v>315.7039264179295</v>
+        <v>315.7039570737517</v>
       </c>
       <c r="D176" t="n">
-        <v>305.0974135277479</v>
+        <v>305.097443153645</v>
       </c>
       <c r="E176" t="n">
-        <v>306.0939919763533</v>
+        <v>306.0940216990212</v>
       </c>
       <c r="F176" t="n">
         <v>399969</v>
@@ -3972,16 +3972,16 @@
         <v>43209</v>
       </c>
       <c r="B178" t="n">
-        <v>335.9915466308594</v>
+        <v>335.9915771484375</v>
       </c>
       <c r="C178" t="n">
-        <v>338.8389419832259</v>
+        <v>338.8389727594285</v>
       </c>
       <c r="D178" t="n">
-        <v>324.9579285969529</v>
+        <v>324.957958112365</v>
       </c>
       <c r="E178" t="n">
-        <v>324.9579285969529</v>
+        <v>324.957958112365</v>
       </c>
       <c r="F178" t="n">
         <v>241809</v>
@@ -3992,16 +3992,16 @@
         <v>43210</v>
       </c>
       <c r="B179" t="n">
-        <v>336.3475036621094</v>
+        <v>336.3474731445312</v>
       </c>
       <c r="C179" t="n">
-        <v>340.2626477370452</v>
+        <v>340.2626168642371</v>
       </c>
       <c r="D179" t="n">
-        <v>331.934056160031</v>
+        <v>331.934026042895</v>
       </c>
       <c r="E179" t="n">
-        <v>335.9203985811352</v>
+        <v>335.9203681023093</v>
       </c>
       <c r="F179" t="n">
         <v>100696</v>
@@ -4012,16 +4012,16 @@
         <v>43213</v>
       </c>
       <c r="B180" t="n">
-        <v>328.5883483886719</v>
+        <v>328.58837890625</v>
       </c>
       <c r="C180" t="n">
-        <v>337.842347427897</v>
+        <v>337.8423788049385</v>
       </c>
       <c r="D180" t="n">
-        <v>328.1612150239612</v>
+        <v>328.1612455018694</v>
       </c>
       <c r="E180" t="n">
-        <v>334.7102155227411</v>
+        <v>334.7102466088864</v>
       </c>
       <c r="F180" t="n">
         <v>112942</v>
@@ -4092,16 +4092,16 @@
         <v>43217</v>
       </c>
       <c r="B184" t="n">
-        <v>340.4761962890625</v>
+        <v>340.4762268066406</v>
       </c>
       <c r="C184" t="n">
-        <v>347.3811038946541</v>
+        <v>347.3811350311332</v>
       </c>
       <c r="D184" t="n">
-        <v>336.7745907859804</v>
+        <v>336.7746209717761</v>
       </c>
       <c r="E184" t="n">
-        <v>347.309905552282</v>
+        <v>347.3099366823795</v>
       </c>
       <c r="F184" t="n">
         <v>216052</v>
@@ -4112,16 +4112,16 @@
         <v>43220</v>
       </c>
       <c r="B185" t="n">
-        <v>336.703369140625</v>
+        <v>336.7034301757812</v>
       </c>
       <c r="C185" t="n">
-        <v>341.1880144393678</v>
+        <v>341.1880762874682</v>
       </c>
       <c r="D185" t="n">
-        <v>334.8525806831809</v>
+        <v>334.8526413828396</v>
       </c>
       <c r="E185" t="n">
-        <v>340.4761727249662</v>
+        <v>340.476234444029</v>
       </c>
       <c r="F185" t="n">
         <v>66083</v>
@@ -4152,16 +4152,16 @@
         <v>43223</v>
       </c>
       <c r="B187" t="n">
-        <v>343.0389099121094</v>
+        <v>343.038818359375</v>
       </c>
       <c r="C187" t="n">
-        <v>343.6795818209407</v>
+        <v>343.6794900972192</v>
       </c>
       <c r="D187" t="n">
-        <v>335.4221586938584</v>
+        <v>335.4220691739383</v>
       </c>
       <c r="E187" t="n">
-        <v>341.6864243988257</v>
+        <v>341.6863332070527</v>
       </c>
       <c r="F187" t="n">
         <v>146682</v>
@@ -4172,16 +4172,16 @@
         <v>43224</v>
       </c>
       <c r="B188" t="n">
-        <v>358.0588073730469</v>
+        <v>358.0587463378906</v>
       </c>
       <c r="C188" t="n">
-        <v>358.0588073730469</v>
+        <v>358.0587463378906</v>
       </c>
       <c r="D188" t="n">
-        <v>328.5171883430254</v>
+        <v>328.5171323435708</v>
       </c>
       <c r="E188" t="n">
-        <v>345.245569902433</v>
+        <v>345.2455110514373</v>
       </c>
       <c r="F188" t="n">
         <v>336833</v>
@@ -4252,16 +4252,16 @@
         <v>43230</v>
       </c>
       <c r="B192" t="n">
-        <v>337.6287841796875</v>
+        <v>337.6288146972656</v>
       </c>
       <c r="C192" t="n">
-        <v>340.2626127408098</v>
+        <v>340.2626434964544</v>
       </c>
       <c r="D192" t="n">
-        <v>329.1578251135923</v>
+        <v>329.1578548654977</v>
       </c>
       <c r="E192" t="n">
-        <v>340.2626127408098</v>
+        <v>340.2626434964544</v>
       </c>
       <c r="F192" t="n">
         <v>218204</v>
@@ -4272,16 +4272,16 @@
         <v>43231</v>
       </c>
       <c r="B193" t="n">
-        <v>343.1100463867188</v>
+        <v>343.1100158691406</v>
       </c>
       <c r="C193" t="n">
-        <v>349.5878493382494</v>
+        <v>349.5878182445096</v>
       </c>
       <c r="D193" t="n">
-        <v>338.1271253981586</v>
+        <v>338.1270953237814</v>
       </c>
       <c r="E193" t="n">
-        <v>338.1271253981586</v>
+        <v>338.1270953237814</v>
       </c>
       <c r="F193" t="n">
         <v>94240</v>
@@ -4292,16 +4292,16 @@
         <v>43234</v>
       </c>
       <c r="B194" t="n">
-        <v>341.6863403320312</v>
+        <v>341.6863708496094</v>
       </c>
       <c r="C194" t="n">
-        <v>350.7267731989587</v>
+        <v>350.7268045239795</v>
       </c>
       <c r="D194" t="n">
-        <v>341.6863403320312</v>
+        <v>341.6863708496094</v>
       </c>
       <c r="E194" t="n">
-        <v>343.2523922069608</v>
+        <v>343.2524228644103</v>
       </c>
       <c r="F194" t="n">
         <v>112773</v>
@@ -4332,16 +4332,16 @@
         <v>43236</v>
       </c>
       <c r="B196" t="n">
-        <v>363.9671020507812</v>
+        <v>363.9671325683594</v>
       </c>
       <c r="C196" t="n">
-        <v>370.1601676527981</v>
+        <v>370.1601986896467</v>
       </c>
       <c r="D196" t="n">
-        <v>360.9061684195798</v>
+        <v>360.9061986805075</v>
       </c>
       <c r="E196" t="n">
-        <v>360.9061684195798</v>
+        <v>360.9061986805075</v>
       </c>
       <c r="F196" t="n">
         <v>163245</v>
@@ -4352,16 +4352,16 @@
         <v>43237</v>
       </c>
       <c r="B197" t="n">
-        <v>359.1265258789062</v>
+        <v>359.1265563964844</v>
       </c>
       <c r="C197" t="n">
-        <v>368.0957878174224</v>
+        <v>368.0958190971836</v>
       </c>
       <c r="D197" t="n">
-        <v>357.8452108396918</v>
+        <v>357.8452412483873</v>
       </c>
       <c r="E197" t="n">
-        <v>365.7466960795255</v>
+        <v>365.7467271596673</v>
       </c>
       <c r="F197" t="n">
         <v>115420</v>
@@ -4372,16 +4372,16 @@
         <v>43238</v>
       </c>
       <c r="B198" t="n">
-        <v>347.0964050292969</v>
+        <v>347.0963745117188</v>
       </c>
       <c r="C198" t="n">
-        <v>358.7706962221969</v>
+        <v>358.7706646781861</v>
       </c>
       <c r="D198" t="n">
-        <v>339.9067599344302</v>
+        <v>339.9067300489835</v>
       </c>
       <c r="E198" t="n">
-        <v>358.7706962221969</v>
+        <v>358.7706646781861</v>
       </c>
       <c r="F198" t="n">
         <v>310384</v>
@@ -4392,16 +4392,16 @@
         <v>43241</v>
       </c>
       <c r="B199" t="n">
-        <v>343.1100463867188</v>
+        <v>343.1100158691406</v>
       </c>
       <c r="C199" t="n">
-        <v>355.8520855813504</v>
+        <v>355.8520539304444</v>
       </c>
       <c r="D199" t="n">
-        <v>339.9779140991621</v>
+        <v>339.9778838601683</v>
       </c>
       <c r="E199" t="n">
-        <v>348.8048091833572</v>
+        <v>348.8047781592641</v>
       </c>
       <c r="F199" t="n">
         <v>199215</v>
@@ -4432,16 +4432,16 @@
         <v>43243</v>
       </c>
       <c r="B201" t="n">
-        <v>343.3947448730469</v>
+        <v>343.394775390625</v>
       </c>
       <c r="C201" t="n">
-        <v>349.3030737202242</v>
+        <v>349.303104762877</v>
       </c>
       <c r="D201" t="n">
-        <v>333.500074012497</v>
+        <v>333.5001036507331</v>
       </c>
       <c r="E201" t="n">
-        <v>349.3030737202242</v>
+        <v>349.303104762877</v>
       </c>
       <c r="F201" t="n">
         <v>194780</v>
@@ -4452,16 +4452,16 @@
         <v>43244</v>
       </c>
       <c r="B202" t="n">
-        <v>345.1744079589844</v>
+        <v>345.1743469238281</v>
       </c>
       <c r="C202" t="n">
-        <v>346.9540266769599</v>
+        <v>346.9539653271242</v>
       </c>
       <c r="D202" t="n">
-        <v>336.8457878257366</v>
+        <v>336.8457282632812</v>
       </c>
       <c r="E202" t="n">
-        <v>336.8457878257366</v>
+        <v>336.8457282632812</v>
       </c>
       <c r="F202" t="n">
         <v>202723</v>
@@ -4552,16 +4552,16 @@
         <v>43252</v>
       </c>
       <c r="B207" t="n">
-        <v>348.8047790527344</v>
+        <v>348.8047485351562</v>
       </c>
       <c r="C207" t="n">
-        <v>351.296239331796</v>
+        <v>351.2962085962353</v>
       </c>
       <c r="D207" t="n">
-        <v>339.1948446437771</v>
+        <v>339.19481496699</v>
       </c>
       <c r="E207" t="n">
-        <v>348.0929373061468</v>
+        <v>348.092906850849</v>
       </c>
       <c r="F207" t="n">
         <v>197871</v>
@@ -4592,16 +4592,16 @@
         <v>43256</v>
       </c>
       <c r="B209" t="n">
-        <v>356.9910278320312</v>
+        <v>356.9910888671875</v>
       </c>
       <c r="C209" t="n">
-        <v>362.045118368561</v>
+        <v>362.0451802678207</v>
       </c>
       <c r="D209" t="n">
-        <v>351.7945406150264</v>
+        <v>351.7946007617334</v>
       </c>
       <c r="E209" t="n">
-        <v>361.6180133231645</v>
+        <v>361.6180751494016</v>
       </c>
       <c r="F209" t="n">
         <v>177500</v>
@@ -4612,16 +4612,16 @@
         <v>43257</v>
       </c>
       <c r="B210" t="n">
-        <v>364.038330078125</v>
+        <v>364.0382995605469</v>
       </c>
       <c r="C210" t="n">
-        <v>364.2518684503623</v>
+        <v>364.2518379148831</v>
       </c>
       <c r="D210" t="n">
-        <v>352.5776063623812</v>
+        <v>352.5775768055633</v>
       </c>
       <c r="E210" t="n">
-        <v>352.71997472121</v>
+        <v>352.7199451524572</v>
       </c>
       <c r="F210" t="n">
         <v>162971</v>
@@ -4672,16 +4672,16 @@
         <v>43262</v>
       </c>
       <c r="B213" t="n">
-        <v>357.7028503417969</v>
+        <v>357.7029113769531</v>
       </c>
       <c r="C213" t="n">
-        <v>374.4312295490931</v>
+        <v>374.4312934386277</v>
       </c>
       <c r="D213" t="n">
-        <v>352.3639950633801</v>
+        <v>352.3640551875627</v>
       </c>
       <c r="E213" t="n">
-        <v>368.7364675846534</v>
+        <v>368.7365305024857</v>
       </c>
       <c r="F213" t="n">
         <v>371642</v>
@@ -4692,16 +4692,16 @@
         <v>43263</v>
       </c>
       <c r="B214" t="n">
-        <v>348.6623840332031</v>
+        <v>348.6624145507812</v>
       </c>
       <c r="C214" t="n">
-        <v>358.129949368641</v>
+        <v>358.1299807148922</v>
       </c>
       <c r="D214" t="n">
-        <v>341.8286754566828</v>
+        <v>341.8287053761229</v>
       </c>
       <c r="E214" t="n">
-        <v>355.9232259570132</v>
+        <v>355.9232571101153</v>
       </c>
       <c r="F214" t="n">
         <v>229511</v>
@@ -4752,16 +4752,16 @@
         <v>43266</v>
       </c>
       <c r="B217" t="n">
-        <v>357.4181823730469</v>
+        <v>357.4181518554688</v>
       </c>
       <c r="C217" t="n">
-        <v>357.4181823730469</v>
+        <v>357.4181518554688</v>
       </c>
       <c r="D217" t="n">
-        <v>346.7404697634461</v>
+        <v>346.7404401575673</v>
       </c>
       <c r="E217" t="n">
-        <v>354.4996166593337</v>
+        <v>354.4995863909526</v>
       </c>
       <c r="F217" t="n">
         <v>246296</v>
@@ -4772,16 +4772,16 @@
         <v>43269</v>
       </c>
       <c r="B218" t="n">
-        <v>353.9300842285156</v>
+        <v>353.9300537109375</v>
       </c>
       <c r="C218" t="n">
-        <v>358.5570982920298</v>
+        <v>358.557067375488</v>
       </c>
       <c r="D218" t="n">
-        <v>348.1641516501209</v>
+        <v>348.1641216297096</v>
       </c>
       <c r="E218" t="n">
-        <v>357.4181514451381</v>
+        <v>357.4181206268018</v>
       </c>
       <c r="F218" t="n">
         <v>104843</v>
@@ -4792,16 +4792,16 @@
         <v>43270</v>
       </c>
       <c r="B219" t="n">
-        <v>347.9506225585938</v>
+        <v>347.9505920410156</v>
       </c>
       <c r="C219" t="n">
-        <v>353.289478978466</v>
+        <v>353.2894479926347</v>
       </c>
       <c r="D219" t="n">
-        <v>344.8896884107255</v>
+        <v>344.8896581616116</v>
       </c>
       <c r="E219" t="n">
-        <v>348.7336627664723</v>
+        <v>348.7336321802163</v>
       </c>
       <c r="F219" t="n">
         <v>184986</v>
@@ -4812,16 +4812,16 @@
         <v>43271</v>
       </c>
       <c r="B220" t="n">
-        <v>343.8218688964844</v>
+        <v>343.8218383789062</v>
       </c>
       <c r="C220" t="n">
-        <v>351.7945533634882</v>
+        <v>351.7945221382558</v>
       </c>
       <c r="D220" t="n">
-        <v>343.465962178428</v>
+        <v>343.4659316924401</v>
       </c>
       <c r="E220" t="n">
-        <v>351.4386183134212</v>
+        <v>351.4385871197815</v>
       </c>
       <c r="F220" t="n">
         <v>79346</v>
@@ -4832,16 +4832,16 @@
         <v>43272</v>
       </c>
       <c r="B221" t="n">
-        <v>337.5576477050781</v>
+        <v>337.5576782226562</v>
       </c>
       <c r="C221" t="n">
-        <v>347.3811211969993</v>
+        <v>347.3811526026883</v>
       </c>
       <c r="D221" t="n">
-        <v>334.5678838167496</v>
+        <v>334.5679140640321</v>
       </c>
       <c r="E221" t="n">
-        <v>341.7575284859097</v>
+        <v>341.7575593831866</v>
       </c>
       <c r="F221" t="n">
         <v>160480</v>
@@ -4872,16 +4872,16 @@
         <v>43276</v>
       </c>
       <c r="B223" t="n">
-        <v>337.2729187011719</v>
+        <v>337.2728881835938</v>
       </c>
       <c r="C223" t="n">
-        <v>340.3338526734312</v>
+        <v>340.3338218788896</v>
       </c>
       <c r="D223" t="n">
-        <v>333.1442078397947</v>
+        <v>333.144177695796</v>
       </c>
       <c r="E223" t="n">
-        <v>334.56789147061</v>
+        <v>334.5678611977918</v>
       </c>
       <c r="F223" t="n">
         <v>136953</v>
@@ -4912,16 +4912,16 @@
         <v>43278</v>
       </c>
       <c r="B225" t="n">
-        <v>339.1948852539062</v>
+        <v>339.1948547363281</v>
       </c>
       <c r="C225" t="n">
-        <v>343.6795312923475</v>
+        <v>343.6795003712829</v>
       </c>
       <c r="D225" t="n">
-        <v>334.6390691982904</v>
+        <v>334.6390390906019</v>
       </c>
       <c r="E225" t="n">
-        <v>342.2558476287216</v>
+        <v>342.2558168357468</v>
       </c>
       <c r="F225" t="n">
         <v>83103</v>
@@ -4932,16 +4932,16 @@
         <v>43279</v>
       </c>
       <c r="B226" t="n">
-        <v>335.8492126464844</v>
+        <v>335.8491821289062</v>
       </c>
       <c r="C226" t="n">
-        <v>341.4728055851523</v>
+        <v>341.4727745565757</v>
       </c>
       <c r="D226" t="n">
-        <v>335.8492126464844</v>
+        <v>335.8491821289062</v>
       </c>
       <c r="E226" t="n">
-        <v>340.9745021395947</v>
+        <v>340.9744711562973</v>
       </c>
       <c r="F226" t="n">
         <v>117507</v>
@@ -4972,16 +4972,16 @@
         <v>43283</v>
       </c>
       <c r="B228" t="n">
-        <v>343.5370788574219</v>
+        <v>343.5371398925781</v>
       </c>
       <c r="C228" t="n">
-        <v>346.8827488142147</v>
+        <v>346.8828104437856</v>
       </c>
       <c r="D228" t="n">
-        <v>340.9744205580022</v>
+        <v>340.974481137859</v>
       </c>
       <c r="E228" t="n">
-        <v>341.6862905476233</v>
+        <v>341.6863512539558</v>
       </c>
       <c r="F228" t="n">
         <v>58036</v>
@@ -5072,16 +5072,16 @@
         <v>43291</v>
       </c>
       <c r="B233" t="n">
-        <v>351.5809631347656</v>
+        <v>351.5809936523438</v>
       </c>
       <c r="C233" t="n">
-        <v>352.2216348492001</v>
+        <v>352.2216654223892</v>
       </c>
       <c r="D233" t="n">
-        <v>341.7574907281528</v>
+        <v>341.7575203930438</v>
       </c>
       <c r="E233" t="n">
-        <v>341.7574907281528</v>
+        <v>341.7575203930438</v>
       </c>
       <c r="F233" t="n">
         <v>97553</v>
@@ -5112,16 +5112,16 @@
         <v>43293</v>
       </c>
       <c r="B235" t="n">
-        <v>366.6009826660156</v>
+        <v>366.6009216308594</v>
       </c>
       <c r="C235" t="n">
-        <v>369.7331150813234</v>
+        <v>369.7330535247005</v>
       </c>
       <c r="D235" t="n">
-        <v>353.2894694819811</v>
+        <v>353.2894106630499</v>
       </c>
       <c r="E235" t="n">
-        <v>353.2894694819811</v>
+        <v>353.2894106630499</v>
       </c>
       <c r="F235" t="n">
         <v>158172</v>
@@ -5132,16 +5132,16 @@
         <v>43294</v>
       </c>
       <c r="B236" t="n">
-        <v>373.7194213867188</v>
+        <v>373.7193908691406</v>
       </c>
       <c r="C236" t="n">
-        <v>378.9870788015035</v>
+        <v>378.9870478537733</v>
       </c>
       <c r="D236" t="n">
-        <v>362.8993698499723</v>
+        <v>362.8993402159495</v>
       </c>
       <c r="E236" t="n">
-        <v>363.3264749107378</v>
+        <v>363.326445241838</v>
       </c>
       <c r="F236" t="n">
         <v>107608</v>
@@ -5172,16 +5172,16 @@
         <v>43298</v>
       </c>
       <c r="B238" t="n">
-        <v>373.7906494140625</v>
+        <v>373.7906799316406</v>
       </c>
       <c r="C238" t="n">
-        <v>374.9295963332197</v>
+        <v>374.9296269437855</v>
       </c>
       <c r="D238" t="n">
-        <v>365.5332275861466</v>
+        <v>365.5332574295599</v>
       </c>
       <c r="E238" t="n">
-        <v>370.1602136112294</v>
+        <v>370.160243832406</v>
       </c>
       <c r="F238" t="n">
         <v>126219</v>
@@ -5212,16 +5212,16 @@
         <v>43300</v>
       </c>
       <c r="B240" t="n">
-        <v>382.0480651855469</v>
+        <v>382.048095703125</v>
       </c>
       <c r="C240" t="n">
-        <v>382.1192352008595</v>
+        <v>382.1192657241226</v>
       </c>
       <c r="D240" t="n">
-        <v>367.597577215771</v>
+        <v>367.5976065790601</v>
       </c>
       <c r="E240" t="n">
-        <v>374.858392042309</v>
+        <v>374.858421985584</v>
       </c>
       <c r="F240" t="n">
         <v>96340</v>
@@ -5232,16 +5232,16 @@
         <v>43301</v>
       </c>
       <c r="B241" t="n">
-        <v>385.6072692871094</v>
+        <v>385.6072387695312</v>
       </c>
       <c r="C241" t="n">
-        <v>392.8681123521824</v>
+        <v>392.8680812599695</v>
       </c>
       <c r="D241" t="n">
-        <v>382.1904286277923</v>
+        <v>382.1903983806284</v>
       </c>
       <c r="E241" t="n">
-        <v>382.9022704318167</v>
+        <v>382.9022401283165</v>
       </c>
       <c r="F241" t="n">
         <v>143200</v>
@@ -5252,16 +5252,16 @@
         <v>43304</v>
       </c>
       <c r="B242" t="n">
-        <v>387.031005859375</v>
+        <v>387.0309448242188</v>
       </c>
       <c r="C242" t="n">
-        <v>388.0987827993753</v>
+        <v>388.0987215958296</v>
       </c>
       <c r="D242" t="n">
-        <v>379.9837290529984</v>
+        <v>379.9836691292044</v>
       </c>
       <c r="E242" t="n">
-        <v>384.1836101300456</v>
+        <v>384.1835495439264</v>
       </c>
       <c r="F242" t="n">
         <v>54684</v>
@@ -5292,16 +5292,16 @@
         <v>43306</v>
       </c>
       <c r="B244" t="n">
-        <v>392.5833129882812</v>
+        <v>392.5833435058594</v>
       </c>
       <c r="C244" t="n">
-        <v>392.5833129882812</v>
+        <v>392.5833435058594</v>
       </c>
       <c r="D244" t="n">
-        <v>382.4039059849724</v>
+        <v>382.4039357112513</v>
       </c>
       <c r="E244" t="n">
-        <v>386.4614461184909</v>
+        <v>386.4614761601839</v>
       </c>
       <c r="F244" t="n">
         <v>87563</v>
@@ -5312,16 +5312,16 @@
         <v>43307</v>
       </c>
       <c r="B245" t="n">
-        <v>380.8379516601562</v>
+        <v>380.837890625</v>
       </c>
       <c r="C245" t="n">
-        <v>395.5019792293666</v>
+        <v>395.5019158440737</v>
       </c>
       <c r="D245" t="n">
-        <v>379.5566362896855</v>
+        <v>379.5565754598798</v>
       </c>
       <c r="E245" t="n">
-        <v>393.0105185096659</v>
+        <v>393.0104555236681</v>
       </c>
       <c r="F245" t="n">
         <v>118211</v>
@@ -5332,16 +5332,16 @@
         <v>43308</v>
       </c>
       <c r="B246" t="n">
-        <v>370.2314147949219</v>
+        <v>370.2313537597656</v>
       </c>
       <c r="C246" t="n">
-        <v>384.3971663724669</v>
+        <v>384.3971030019906</v>
       </c>
       <c r="D246" t="n">
-        <v>369.875479713953</v>
+        <v>369.8754187374751</v>
       </c>
       <c r="E246" t="n">
-        <v>383.6141261935433</v>
+        <v>383.6140629521565</v>
       </c>
       <c r="F246" t="n">
         <v>107087</v>
@@ -5412,16 +5412,16 @@
         <v>43314</v>
       </c>
       <c r="B250" t="n">
-        <v>390.6613464355469</v>
+        <v>390.6614074707031</v>
       </c>
       <c r="C250" t="n">
-        <v>390.8749131197132</v>
+        <v>390.8749741882362</v>
       </c>
       <c r="D250" t="n">
-        <v>377.1362686226036</v>
+        <v>377.1363275446631</v>
       </c>
       <c r="E250" t="n">
-        <v>379.7700971792707</v>
+        <v>379.7701565128276</v>
       </c>
       <c r="F250" t="n">
         <v>67674</v>
@@ -5432,16 +5432,16 @@
         <v>43315</v>
       </c>
       <c r="B251" t="n">
-        <v>394.861328125</v>
+        <v>394.8612976074219</v>
       </c>
       <c r="C251" t="n">
-        <v>396.8544853296668</v>
+        <v>396.8544546580439</v>
       </c>
       <c r="D251" t="n">
-        <v>384.5395503422257</v>
+        <v>384.5395206223849</v>
       </c>
       <c r="E251" t="n">
-        <v>392.2274990813975</v>
+        <v>392.2274687673797</v>
       </c>
       <c r="F251" t="n">
         <v>193633</v>
@@ -5452,16 +5452,16 @@
         <v>43318</v>
       </c>
       <c r="B252" t="n">
-        <v>399.4171142578125</v>
+        <v>399.4170532226562</v>
       </c>
       <c r="C252" t="n">
-        <v>403.0475216302017</v>
+        <v>403.0474600402808</v>
       </c>
       <c r="D252" t="n">
-        <v>395.0748367482379</v>
+        <v>395.0747763766276</v>
       </c>
       <c r="E252" t="n">
-        <v>395.0748367482379</v>
+        <v>395.0747763766276</v>
       </c>
       <c r="F252" t="n">
         <v>103174</v>
@@ -5472,16 +5472,16 @@
         <v>43319</v>
       </c>
       <c r="B253" t="n">
-        <v>405.325439453125</v>
+        <v>405.3253784179688</v>
       </c>
       <c r="C253" t="n">
-        <v>410.8778338067805</v>
+        <v>410.8777719355276</v>
       </c>
       <c r="D253" t="n">
-        <v>402.0509388519387</v>
+        <v>402.0508783098668</v>
       </c>
       <c r="E253" t="n">
-        <v>402.9763473548852</v>
+        <v>402.9762866734625</v>
       </c>
       <c r="F253" t="n">
         <v>123311</v>
@@ -5512,16 +5512,16 @@
         <v>43321</v>
       </c>
       <c r="B255" t="n">
-        <v>413.5827941894531</v>
+        <v>413.5828552246094</v>
       </c>
       <c r="C255" t="n">
-        <v>422.2673193824925</v>
+        <v>422.2673816992818</v>
       </c>
       <c r="D255" t="n">
-        <v>412.0167141554905</v>
+        <v>412.01677495953</v>
       </c>
       <c r="E255" t="n">
-        <v>413.938700864803</v>
+        <v>413.9387619524828</v>
       </c>
       <c r="F255" t="n">
         <v>86363</v>
@@ -5552,16 +5552,16 @@
         <v>43325</v>
       </c>
       <c r="B257" t="n">
-        <v>409.6676635742188</v>
+        <v>409.6676940917969</v>
       </c>
       <c r="C257" t="n">
-        <v>413.7963740805197</v>
+        <v>413.79640490566</v>
       </c>
       <c r="D257" t="n">
-        <v>405.7525197601792</v>
+        <v>405.7525499861046</v>
       </c>
       <c r="E257" t="n">
-        <v>411.8743871782069</v>
+        <v>411.8744178601715</v>
       </c>
       <c r="F257" t="n">
         <v>49754</v>
@@ -5572,16 +5572,16 @@
         <v>43326</v>
       </c>
       <c r="B258" t="n">
-        <v>420.2741394042969</v>
+        <v>420.274169921875</v>
       </c>
       <c r="C258" t="n">
-        <v>421.4842844454877</v>
+        <v>421.4843150509387</v>
       </c>
       <c r="D258" t="n">
-        <v>410.094732388881</v>
+        <v>410.0947621672968</v>
       </c>
       <c r="E258" t="n">
-        <v>414.0099041889681</v>
+        <v>414.0099342516782</v>
       </c>
       <c r="F258" t="n">
         <v>82646</v>
@@ -5592,16 +5592,16 @@
         <v>43327</v>
       </c>
       <c r="B259" t="n">
-        <v>422.4809265136719</v>
+        <v>422.4808959960938</v>
       </c>
       <c r="C259" t="n">
-        <v>426.7520056373787</v>
+        <v>426.7519748112825</v>
       </c>
       <c r="D259" t="n">
-        <v>418.2810457358325</v>
+        <v>418.2810155216295</v>
       </c>
       <c r="E259" t="n">
-        <v>420.2742027719569</v>
+        <v>420.2741724137797</v>
       </c>
       <c r="F259" t="n">
         <v>76308</v>
@@ -5612,16 +5612,16 @@
         <v>43328</v>
       </c>
       <c r="B260" t="n">
-        <v>423.5487060546875</v>
+        <v>423.5486755371094</v>
       </c>
       <c r="C260" t="n">
-        <v>426.2537332385369</v>
+        <v>426.2537025260559</v>
       </c>
       <c r="D260" t="n">
-        <v>417.7115749371317</v>
+        <v>417.7115448401312</v>
       </c>
       <c r="E260" t="n">
-        <v>426.2537332385369</v>
+        <v>426.2537025260559</v>
       </c>
       <c r="F260" t="n">
         <v>68717</v>
@@ -5632,16 +5632,16 @@
         <v>43329</v>
       </c>
       <c r="B261" t="n">
-        <v>420.3453369140625</v>
+        <v>420.3453979492188</v>
       </c>
       <c r="C261" t="n">
-        <v>425.684163754232</v>
+        <v>425.6842255645988</v>
       </c>
       <c r="D261" t="n">
-        <v>414.2234417170041</v>
+        <v>414.2235018632464</v>
       </c>
       <c r="E261" t="n">
-        <v>423.6198086875508</v>
+        <v>423.6198701981683</v>
       </c>
       <c r="F261" t="n">
         <v>64270</v>
@@ -5692,16 +5692,16 @@
         <v>43334</v>
       </c>
       <c r="B264" t="n">
-        <v>419.9894714355469</v>
+        <v>419.9894409179688</v>
       </c>
       <c r="C264" t="n">
-        <v>426.2537360076794</v>
+        <v>426.2537050349228</v>
       </c>
       <c r="D264" t="n">
-        <v>419.2064312810272</v>
+        <v>419.206400820347</v>
       </c>
       <c r="E264" t="n">
-        <v>421.3419850362582</v>
+        <v>421.3419544204027</v>
       </c>
       <c r="F264" t="n">
         <v>60566</v>
@@ -5712,16 +5712,16 @@
         <v>43335</v>
       </c>
       <c r="B265" t="n">
-        <v>406.1796264648438</v>
+        <v>406.1795959472656</v>
       </c>
       <c r="C265" t="n">
-        <v>423.1927436211759</v>
+        <v>423.1927118253477</v>
       </c>
       <c r="D265" t="n">
-        <v>400.2000990413216</v>
+        <v>400.2000689730046</v>
       </c>
       <c r="E265" t="n">
-        <v>420.5589149539617</v>
+        <v>420.5588833560216</v>
       </c>
       <c r="F265" t="n">
         <v>95258</v>
@@ -5732,16 +5732,16 @@
         <v>43336</v>
       </c>
       <c r="B266" t="n">
-        <v>405.7525634765625</v>
+        <v>405.7525329589844</v>
       </c>
       <c r="C266" t="n">
-        <v>415.2201023253259</v>
+        <v>415.2200710956725</v>
       </c>
       <c r="D266" t="n">
-        <v>402.9051678210174</v>
+        <v>402.9051375175985</v>
       </c>
       <c r="E266" t="n">
-        <v>408.3863924168361</v>
+        <v>408.3863617011617</v>
       </c>
       <c r="F266" t="n">
         <v>110243</v>
@@ -5752,16 +5752,16 @@
         <v>43339</v>
       </c>
       <c r="B267" t="n">
-        <v>411.1625366210938</v>
+        <v>411.1625671386719</v>
       </c>
       <c r="C267" t="n">
-        <v>413.2268918300467</v>
+        <v>413.2269225008468</v>
       </c>
       <c r="D267" t="n">
-        <v>405.8948794208715</v>
+        <v>405.8949095474701</v>
       </c>
       <c r="E267" t="n">
-        <v>405.8948794208715</v>
+        <v>405.8949095474701</v>
       </c>
       <c r="F267" t="n">
         <v>61388</v>
@@ -5772,16 +5772,16 @@
         <v>43340</v>
       </c>
       <c r="B268" t="n">
-        <v>414.3658752441406</v>
+        <v>414.3658447265625</v>
       </c>
       <c r="C268" t="n">
-        <v>419.7047312562409</v>
+        <v>419.7047003454621</v>
       </c>
       <c r="D268" t="n">
-        <v>413.5828634280812</v>
+        <v>413.5828329681711</v>
       </c>
       <c r="E268" t="n">
-        <v>413.5828634280812</v>
+        <v>413.5828329681711</v>
       </c>
       <c r="F268" t="n">
         <v>46390</v>
@@ -5852,16 +5852,16 @@
         <v>43346</v>
       </c>
       <c r="B272" t="n">
-        <v>423.5487060546875</v>
+        <v>423.5486755371094</v>
       </c>
       <c r="C272" t="n">
-        <v>430.2400473359814</v>
+        <v>430.2400163362781</v>
       </c>
       <c r="D272" t="n">
-        <v>420.3454037746636</v>
+        <v>420.3453734878901</v>
       </c>
       <c r="E272" t="n">
-        <v>422.8368642515724</v>
+        <v>422.836833785284</v>
       </c>
       <c r="F272" t="n">
         <v>33765</v>
@@ -5872,16 +5872,16 @@
         <v>43347</v>
       </c>
       <c r="B273" t="n">
-        <v>425.613037109375</v>
+        <v>425.6130065917969</v>
       </c>
       <c r="C273" t="n">
-        <v>427.107918976432</v>
+        <v>427.1078883516669</v>
       </c>
       <c r="D273" t="n">
-        <v>417.9962877536191</v>
+        <v>417.996257782182</v>
       </c>
       <c r="E273" t="n">
-        <v>420.4165497457982</v>
+        <v>420.416519600822</v>
       </c>
       <c r="F273" t="n">
         <v>35382</v>
@@ -5892,16 +5892,16 @@
         <v>43348</v>
       </c>
       <c r="B274" t="n">
-        <v>446.3989868164062</v>
+        <v>446.3989562988281</v>
       </c>
       <c r="C274" t="n">
-        <v>446.8972619159915</v>
+        <v>446.8972313643494</v>
       </c>
       <c r="D274" t="n">
-        <v>425.3283276399078</v>
+        <v>425.3282985628022</v>
       </c>
       <c r="E274" t="n">
-        <v>426.9655779642857</v>
+        <v>426.9655487752514</v>
       </c>
       <c r="F274" t="n">
         <v>107452</v>
@@ -5912,16 +5912,16 @@
         <v>43349</v>
       </c>
       <c r="B275" t="n">
-        <v>466.6866149902344</v>
+        <v>466.6865844726562</v>
       </c>
       <c r="C275" t="n">
-        <v>469.4628122618363</v>
+        <v>469.462781562717</v>
       </c>
       <c r="D275" t="n">
-        <v>448.5345210365138</v>
+        <v>448.5344917059376</v>
       </c>
       <c r="E275" t="n">
-        <v>448.5345210365138</v>
+        <v>448.5344917059376</v>
       </c>
       <c r="F275" t="n">
         <v>140070</v>
@@ -5972,16 +5972,16 @@
         <v>43355</v>
       </c>
       <c r="B278" t="n">
-        <v>449.5310668945312</v>
+        <v>449.5311279296875</v>
       </c>
       <c r="C278" t="n">
-        <v>459.1409726842791</v>
+        <v>459.1410350242219</v>
       </c>
       <c r="D278" t="n">
-        <v>448.3920918020204</v>
+        <v>448.3921526825321</v>
       </c>
       <c r="E278" t="n">
-        <v>459.0698026777523</v>
+        <v>459.0698650080319</v>
       </c>
       <c r="F278" t="n">
         <v>50876</v>
@@ -5992,16 +5992,16 @@
         <v>43356</v>
       </c>
       <c r="B279" t="n">
-        <v>446.3989868164062</v>
+        <v>446.3989562988281</v>
       </c>
       <c r="C279" t="n">
-        <v>452.7344214055155</v>
+        <v>452.7343904548224</v>
       </c>
       <c r="D279" t="n">
-        <v>443.4804212376504</v>
+        <v>443.4803909195968</v>
       </c>
       <c r="E279" t="n">
-        <v>448.2497755171743</v>
+        <v>448.2497448730691</v>
       </c>
       <c r="F279" t="n">
         <v>76764</v>
@@ -6052,16 +6052,16 @@
         <v>43361</v>
       </c>
       <c r="B282" t="n">
-        <v>439.0669860839844</v>
+        <v>439.0669555664062</v>
       </c>
       <c r="C282" t="n">
-        <v>450.5988803627721</v>
+        <v>450.5988490436637</v>
       </c>
       <c r="D282" t="n">
-        <v>437.0738006333705</v>
+        <v>437.0737702543298</v>
       </c>
       <c r="E282" t="n">
-        <v>450.4565119971577</v>
+        <v>450.4564806879447</v>
       </c>
       <c r="F282" t="n">
         <v>72004</v>
@@ -6072,16 +6072,16 @@
         <v>43362</v>
       </c>
       <c r="B283" t="n">
-        <v>443.6227416992188</v>
+        <v>443.6227722167969</v>
       </c>
       <c r="C283" t="n">
-        <v>446.1853719312754</v>
+        <v>446.1854026251413</v>
       </c>
       <c r="D283" t="n">
-        <v>434.5110825447675</v>
+        <v>434.5111124355388</v>
       </c>
       <c r="E283" t="n">
-        <v>434.5110825447675</v>
+        <v>434.5111124355388</v>
       </c>
       <c r="F283" t="n">
         <v>53158</v>
@@ -6092,16 +6092,16 @@
         <v>43363</v>
       </c>
       <c r="B284" t="n">
-        <v>447.9649658203125</v>
+        <v>447.9650573730469</v>
       </c>
       <c r="C284" t="n">
-        <v>451.6665709508681</v>
+        <v>451.6666632601172</v>
       </c>
       <c r="D284" t="n">
-        <v>442.7684789704933</v>
+        <v>442.7685694611969</v>
       </c>
       <c r="E284" t="n">
-        <v>445.9718090826328</v>
+        <v>445.9719002280163</v>
       </c>
       <c r="F284" t="n">
         <v>54997</v>
@@ -6112,16 +6112,16 @@
         <v>43364</v>
       </c>
       <c r="B285" t="n">
-        <v>450.5988464355469</v>
+        <v>450.598876953125</v>
       </c>
       <c r="C285" t="n">
-        <v>453.6598085638038</v>
+        <v>453.6598392886909</v>
       </c>
       <c r="D285" t="n">
-        <v>445.6159256822141</v>
+        <v>445.6159558623154</v>
       </c>
       <c r="E285" t="n">
-        <v>448.4633211121233</v>
+        <v>448.4633514850693</v>
       </c>
       <c r="F285" t="n">
         <v>102809</v>
@@ -6132,16 +6132,16 @@
         <v>43367</v>
       </c>
       <c r="B286" t="n">
-        <v>455.5817565917969</v>
+        <v>455.5817260742188</v>
       </c>
       <c r="C286" t="n">
-        <v>472.5949021000526</v>
+        <v>472.5948704428327</v>
       </c>
       <c r="D286" t="n">
-        <v>452.0937178119998</v>
+        <v>452.0936875280713</v>
       </c>
       <c r="E286" t="n">
-        <v>465.6187962084482</v>
+        <v>465.6187650185294</v>
       </c>
       <c r="F286" t="n">
         <v>114729</v>
@@ -6152,16 +6152,16 @@
         <v>43368</v>
       </c>
       <c r="B287" t="n">
-        <v>461.7036437988281</v>
+        <v>461.7037048339844</v>
       </c>
       <c r="C287" t="n">
-        <v>461.9883804967065</v>
+        <v>461.9884415695037</v>
       </c>
       <c r="D287" t="n">
-        <v>455.0834730751416</v>
+        <v>455.0835332351409</v>
       </c>
       <c r="E287" t="n">
-        <v>457.0766299602901</v>
+        <v>457.0766903837758</v>
       </c>
       <c r="F287" t="n">
         <v>76842</v>
@@ -6172,16 +6172,16 @@
         <v>43369</v>
       </c>
       <c r="B288" t="n">
-        <v>466.2594909667969</v>
+        <v>466.2594604492188</v>
       </c>
       <c r="C288" t="n">
-        <v>469.6763599054322</v>
+        <v>469.6763291642134</v>
       </c>
       <c r="D288" t="n">
-        <v>462.4155169523336</v>
+        <v>462.415486686351</v>
       </c>
       <c r="E288" t="n">
-        <v>466.1171226081876</v>
+        <v>466.1170920999277</v>
       </c>
       <c r="F288" t="n">
         <v>57175</v>
@@ -6192,16 +6192,16 @@
         <v>43370</v>
       </c>
       <c r="B289" t="n">
-        <v>464.8358154296875</v>
+        <v>464.8357849121094</v>
       </c>
       <c r="C289" t="n">
-        <v>470.4593798581377</v>
+        <v>470.4593489713591</v>
       </c>
       <c r="D289" t="n">
-        <v>462.7002616815574</v>
+        <v>462.7002313041834</v>
       </c>
       <c r="E289" t="n">
-        <v>466.9001708312743</v>
+        <v>466.9001401781663</v>
       </c>
       <c r="F289" t="n">
         <v>111443</v>
@@ -6232,16 +6232,16 @@
         <v>43374</v>
       </c>
       <c r="B291" t="n">
-        <v>469.8186950683594</v>
+        <v>469.8187255859375</v>
       </c>
       <c r="C291" t="n">
-        <v>479.7845644628944</v>
+        <v>479.7845956278163</v>
       </c>
       <c r="D291" t="n">
-        <v>464.8357745370967</v>
+        <v>464.8358047310038</v>
       </c>
       <c r="E291" t="n">
-        <v>476.9371408278733</v>
+        <v>476.9371718078378</v>
       </c>
       <c r="F291" t="n">
         <v>76882</v>
@@ -6252,16 +6252,16 @@
         <v>43375</v>
       </c>
       <c r="B292" t="n">
-        <v>478.7168273925781</v>
+        <v>478.716796875</v>
       </c>
       <c r="C292" t="n">
-        <v>484.0556550720698</v>
+        <v>484.0556242141483</v>
       </c>
       <c r="D292" t="n">
-        <v>474.3033515574059</v>
+        <v>474.3033213211812</v>
       </c>
       <c r="E292" t="n">
-        <v>476.2253669202788</v>
+        <v>476.2253365615281</v>
       </c>
       <c r="F292" t="n">
         <v>103031</v>
@@ -6292,16 +6292,16 @@
         <v>43377</v>
       </c>
       <c r="B294" t="n">
-        <v>455.5817565917969</v>
+        <v>455.5817260742188</v>
       </c>
       <c r="C294" t="n">
-        <v>472.8084687934327</v>
+        <v>472.8084371219069</v>
       </c>
       <c r="D294" t="n">
-        <v>446.4701254264423</v>
+        <v>446.4700955192155</v>
       </c>
       <c r="E294" t="n">
-        <v>463.4120725929013</v>
+        <v>463.412041550802</v>
       </c>
       <c r="F294" t="n">
         <v>143591</v>
@@ -6312,16 +6312,16 @@
         <v>43378</v>
       </c>
       <c r="B295" t="n">
-        <v>455.1546630859375</v>
+        <v>455.1547241210938</v>
       </c>
       <c r="C295" t="n">
-        <v>463.6256510501111</v>
+        <v>463.6257132212068</v>
       </c>
       <c r="D295" t="n">
-        <v>441.4160459795217</v>
+        <v>441.4161051723621</v>
       </c>
       <c r="E295" t="n">
-        <v>456.3648082711067</v>
+        <v>456.3648694685406</v>
       </c>
       <c r="F295" t="n">
         <v>188272</v>
@@ -6332,16 +6332,16 @@
         <v>43381</v>
       </c>
       <c r="B296" t="n">
-        <v>438.1415100097656</v>
+        <v>438.1415405273438</v>
       </c>
       <c r="C296" t="n">
-        <v>467.8966921610223</v>
+        <v>467.8967247511182</v>
       </c>
       <c r="D296" t="n">
-        <v>435.0093781169995</v>
+        <v>435.0094084164173</v>
       </c>
       <c r="E296" t="n">
-        <v>462.7002051190253</v>
+        <v>462.7002373471738</v>
       </c>
       <c r="F296" t="n">
         <v>227176</v>
@@ -6372,16 +6372,16 @@
         <v>43383</v>
       </c>
       <c r="B298" t="n">
-        <v>438.7110290527344</v>
+        <v>438.7109680175781</v>
       </c>
       <c r="C298" t="n">
-        <v>442.7685414357292</v>
+        <v>442.7684798360763</v>
       </c>
       <c r="D298" t="n">
-        <v>431.0230810302057</v>
+        <v>431.0230210646261</v>
       </c>
       <c r="E298" t="n">
-        <v>433.3010030980707</v>
+        <v>433.300942815578</v>
       </c>
       <c r="F298" t="n">
         <v>196176</v>
@@ -6392,16 +6392,16 @@
         <v>43384</v>
       </c>
       <c r="B299" t="n">
-        <v>450.0293884277344</v>
+        <v>450.0293579101562</v>
       </c>
       <c r="C299" t="n">
-        <v>450.527691852937</v>
+        <v>450.5276613015677</v>
       </c>
       <c r="D299" t="n">
-        <v>437.7856244914378</v>
+        <v>437.7855948041388</v>
       </c>
       <c r="E299" t="n">
-        <v>438.782231341843</v>
+        <v>438.7822015869618</v>
       </c>
       <c r="F299" t="n">
         <v>120559</v>
@@ -6412,16 +6412,16 @@
         <v>43388</v>
       </c>
       <c r="B300" t="n">
-        <v>450.5988464355469</v>
+        <v>450.598876953125</v>
       </c>
       <c r="C300" t="n">
-        <v>465.690005382451</v>
+        <v>465.6900369221037</v>
       </c>
       <c r="D300" t="n">
-        <v>446.1142290903517</v>
+        <v>446.1142593042015</v>
       </c>
       <c r="E300" t="n">
-        <v>450.2429397143151</v>
+        <v>450.2429702077888</v>
       </c>
       <c r="F300" t="n">
         <v>243088</v>
@@ -6452,16 +6452,16 @@
         <v>43390</v>
       </c>
       <c r="B302" t="n">
-        <v>491.31640625</v>
+        <v>491.3164367675781</v>
       </c>
       <c r="C302" t="n">
-        <v>494.3773964319433</v>
+        <v>494.3774271396515</v>
       </c>
       <c r="D302" t="n">
-        <v>464.9069229922511</v>
+        <v>464.9069518694333</v>
       </c>
       <c r="E302" t="n">
-        <v>469.1068315777851</v>
+        <v>469.10686071584</v>
       </c>
       <c r="F302" t="n">
         <v>187503</v>
@@ -6472,16 +6472,16 @@
         <v>43391</v>
       </c>
       <c r="B303" t="n">
-        <v>493.879150390625</v>
+        <v>493.8790893554688</v>
       </c>
       <c r="C303" t="n">
-        <v>498.2214278220903</v>
+        <v>498.2213662503016</v>
       </c>
       <c r="D303" t="n">
-        <v>489.4657029459287</v>
+        <v>489.4656424562003</v>
       </c>
       <c r="E303" t="n">
-        <v>492.3130701154026</v>
+        <v>492.3130092737876</v>
       </c>
       <c r="F303" t="n">
         <v>132636</v>
@@ -6512,16 +6512,16 @@
         <v>43395</v>
       </c>
       <c r="B305" t="n">
-        <v>489.1097412109375</v>
+        <v>489.1096801757812</v>
       </c>
       <c r="C305" t="n">
-        <v>497.1536526540297</v>
+        <v>497.1535906150876</v>
       </c>
       <c r="D305" t="n">
-        <v>487.1877541990168</v>
+        <v>487.1876934037019</v>
       </c>
       <c r="E305" t="n">
-        <v>496.726519245148</v>
+        <v>496.7264572595072</v>
       </c>
       <c r="F305" t="n">
         <v>60501</v>
@@ -6532,16 +6532,16 @@
         <v>43396</v>
       </c>
       <c r="B306" t="n">
-        <v>511.4617614746094</v>
+        <v>511.4617919921875</v>
       </c>
       <c r="C306" t="n">
-        <v>517.441232429009</v>
+        <v>517.4412633033664</v>
       </c>
       <c r="D306" t="n">
-        <v>487.2589709528297</v>
+        <v>487.2590000262909</v>
       </c>
       <c r="E306" t="n">
-        <v>494.7333521438459</v>
+        <v>494.7333816632839</v>
       </c>
       <c r="F306" t="n">
         <v>160702</v>
@@ -6612,16 +6612,16 @@
         <v>43402</v>
       </c>
       <c r="B310" t="n">
-        <v>484.2692260742188</v>
+        <v>484.2691955566406</v>
       </c>
       <c r="C310" t="n">
-        <v>487.9708034764029</v>
+        <v>487.9707727255595</v>
       </c>
       <c r="D310" t="n">
-        <v>477.4354880523159</v>
+        <v>477.4354579653848</v>
       </c>
       <c r="E310" t="n">
-        <v>479.4998717938601</v>
+        <v>479.4998415768361</v>
       </c>
       <c r="F310" t="n">
         <v>124850</v>
@@ -6632,16 +6632,16 @@
         <v>43403</v>
       </c>
       <c r="B311" t="n">
-        <v>507.68896484375</v>
+        <v>507.6889038085938</v>
       </c>
       <c r="C311" t="n">
-        <v>511.4617688315493</v>
+        <v>511.4617073428208</v>
       </c>
       <c r="D311" t="n">
-        <v>479.7845966631043</v>
+        <v>479.7845389826546</v>
       </c>
       <c r="E311" t="n">
-        <v>491.5300287047826</v>
+        <v>491.5299696122788</v>
       </c>
       <c r="F311" t="n">
         <v>130875</v>
@@ -6672,16 +6672,16 @@
         <v>43405</v>
       </c>
       <c r="B313" t="n">
-        <v>494.0215454101562</v>
+        <v>494.021484375</v>
       </c>
       <c r="C313" t="n">
-        <v>500.1434138380059</v>
+        <v>500.1433520465077</v>
       </c>
       <c r="D313" t="n">
-        <v>485.9065197418022</v>
+        <v>485.9064597092376</v>
       </c>
       <c r="E313" t="n">
-        <v>491.1741779237214</v>
+        <v>491.1741172403505</v>
       </c>
       <c r="F313" t="n">
         <v>268389</v>
@@ -6692,16 +6692,16 @@
         <v>43409</v>
       </c>
       <c r="B314" t="n">
-        <v>487.6148376464844</v>
+        <v>487.6148681640625</v>
       </c>
       <c r="C314" t="n">
-        <v>501.8517854114677</v>
+        <v>501.8518168200711</v>
       </c>
       <c r="D314" t="n">
-        <v>480.4963637639927</v>
+        <v>480.4963938360582</v>
       </c>
       <c r="E314" t="n">
-        <v>498.2925484702219</v>
+        <v>498.292579656069</v>
       </c>
       <c r="F314" t="n">
         <v>153555</v>
@@ -6712,16 +6712,16 @@
         <v>43410</v>
       </c>
       <c r="B315" t="n">
-        <v>485.4792785644531</v>
+        <v>485.4793090820312</v>
       </c>
       <c r="C315" t="n">
-        <v>488.3267020831064</v>
+        <v>488.3267327796756</v>
       </c>
       <c r="D315" t="n">
-        <v>480.5675282421928</v>
+        <v>480.5675584510147</v>
       </c>
       <c r="E315" t="n">
-        <v>487.6148320374388</v>
+        <v>487.6148626892594</v>
       </c>
       <c r="F315" t="n">
         <v>70726</v>
@@ -6732,16 +6732,16 @@
         <v>43411</v>
       </c>
       <c r="B316" t="n">
-        <v>466.1882629394531</v>
+        <v>466.1883239746094</v>
       </c>
       <c r="C316" t="n">
-        <v>486.9029852922626</v>
+        <v>486.9030490394698</v>
       </c>
       <c r="D316" t="n">
-        <v>458.429145391248</v>
+        <v>458.4292054105508</v>
       </c>
       <c r="E316" t="n">
-        <v>486.9029852922626</v>
+        <v>486.9030490394698</v>
       </c>
       <c r="F316" t="n">
         <v>167692</v>
@@ -6772,16 +6772,16 @@
         <v>43413</v>
       </c>
       <c r="B318" t="n">
-        <v>486.4524230957031</v>
+        <v>486.4523620605469</v>
       </c>
       <c r="C318" t="n">
-        <v>496.8666868693256</v>
+        <v>496.8666245274923</v>
       </c>
       <c r="D318" t="n">
-        <v>481.2093874459508</v>
+        <v>481.2093270686379</v>
       </c>
       <c r="E318" t="n">
-        <v>482.6458238215822</v>
+        <v>482.6457632640397</v>
       </c>
       <c r="F318" t="n">
         <v>220056</v>
@@ -6792,16 +6792,16 @@
         <v>43416</v>
       </c>
       <c r="B319" t="n">
-        <v>497.0103149414062</v>
+        <v>497.01025390625</v>
       </c>
       <c r="C319" t="n">
-        <v>497.0103149414062</v>
+        <v>497.01025390625</v>
       </c>
       <c r="D319" t="n">
-        <v>482.4304138822976</v>
+        <v>482.4303546376204</v>
       </c>
       <c r="E319" t="n">
-        <v>486.9552028769729</v>
+        <v>486.9551430766307</v>
       </c>
       <c r="F319" t="n">
         <v>67570</v>
@@ -6812,16 +6812,16 @@
         <v>43417</v>
       </c>
       <c r="B320" t="n">
-        <v>509.9383239746094</v>
+        <v>509.9383544921875</v>
       </c>
       <c r="C320" t="n">
-        <v>514.8940149864776</v>
+        <v>514.8940458006322</v>
       </c>
       <c r="D320" t="n">
-        <v>495.1428869473325</v>
+        <v>495.1429165794685</v>
       </c>
       <c r="E320" t="n">
-        <v>497.225762490351</v>
+        <v>497.2257922471379</v>
       </c>
       <c r="F320" t="n">
         <v>127693</v>
@@ -6852,16 +6852,16 @@
         <v>43420</v>
       </c>
       <c r="B322" t="n">
-        <v>522.1481323242188</v>
+        <v>522.1480712890625</v>
       </c>
       <c r="C322" t="n">
-        <v>522.1481323242188</v>
+        <v>522.1480712890625</v>
       </c>
       <c r="D322" t="n">
-        <v>509.2200907556082</v>
+        <v>509.220031231642</v>
       </c>
       <c r="E322" t="n">
-        <v>512.0929634723677</v>
+        <v>512.0929036125845</v>
       </c>
       <c r="F322" t="n">
         <v>83637</v>
@@ -6912,16 +6912,16 @@
         <v>43426</v>
       </c>
       <c r="B325" t="n">
-        <v>530.6948852539062</v>
+        <v>530.6949462890625</v>
       </c>
       <c r="C325" t="n">
-        <v>535.3633457897967</v>
+        <v>535.363407361872</v>
       </c>
       <c r="D325" t="n">
-        <v>524.0154140349154</v>
+        <v>524.0154743018664</v>
       </c>
       <c r="E325" t="n">
-        <v>528.6120670535926</v>
+        <v>528.6121278492041</v>
       </c>
       <c r="F325" t="n">
         <v>55036</v>
@@ -6932,16 +6932,16 @@
         <v>43427</v>
       </c>
       <c r="B326" t="n">
-        <v>531.700439453125</v>
+        <v>531.7005004882812</v>
       </c>
       <c r="C326" t="n">
-        <v>540.8218811494445</v>
+        <v>540.8219432316728</v>
       </c>
       <c r="D326" t="n">
-        <v>528.6120872077179</v>
+        <v>528.6121478883548</v>
       </c>
       <c r="E326" t="n">
-        <v>531.5567672416307</v>
+        <v>531.5568282602945</v>
       </c>
       <c r="F326" t="n">
         <v>87641</v>
@@ -6992,16 +6992,16 @@
         <v>43432</v>
       </c>
       <c r="B329" t="n">
-        <v>545.8494262695312</v>
+        <v>545.8495483398438</v>
       </c>
       <c r="C329" t="n">
-        <v>551.8825156058812</v>
+        <v>551.8826390253956</v>
       </c>
       <c r="D329" t="n">
-        <v>542.3301146280619</v>
+        <v>542.3302359113378</v>
       </c>
       <c r="E329" t="n">
-        <v>548.7222987289401</v>
+        <v>548.7224214417237</v>
       </c>
       <c r="F329" t="n">
         <v>68365</v>
@@ -7012,16 +7012,16 @@
         <v>43433</v>
       </c>
       <c r="B330" t="n">
-        <v>542.9765625</v>
+        <v>542.9765014648438</v>
       </c>
       <c r="C330" t="n">
-        <v>548.2914629519753</v>
+        <v>548.2914013193791</v>
       </c>
       <c r="D330" t="n">
-        <v>529.4021956040685</v>
+        <v>529.4021360947859</v>
       </c>
       <c r="E330" t="n">
-        <v>545.993107534073</v>
+        <v>545.9930461598316</v>
       </c>
       <c r="F330" t="n">
         <v>103670</v>
@@ -7132,16 +7132,16 @@
         <v>43441</v>
       </c>
       <c r="B336" t="n">
-        <v>545.1312255859375</v>
+        <v>545.1311645507812</v>
       </c>
       <c r="C336" t="n">
-        <v>548.3632502542961</v>
+        <v>548.3631888572691</v>
       </c>
       <c r="D336" t="n">
-        <v>538.4517536752732</v>
+        <v>538.4516933879784</v>
       </c>
       <c r="E336" t="n">
-        <v>538.9545206910084</v>
+        <v>538.9544603474218</v>
       </c>
       <c r="F336" t="n">
         <v>82581</v>
@@ -7172,16 +7172,16 @@
         <v>43445</v>
       </c>
       <c r="B338" t="n">
-        <v>541.5400390625</v>
+        <v>541.5401000976562</v>
       </c>
       <c r="C338" t="n">
-        <v>544.9156783621429</v>
+        <v>544.9157397777561</v>
       </c>
       <c r="D338" t="n">
-        <v>530.5512594597212</v>
+        <v>530.5513192563691</v>
       </c>
       <c r="E338" t="n">
-        <v>544.9156783621429</v>
+        <v>544.9157397777561</v>
       </c>
       <c r="F338" t="n">
         <v>121498</v>
@@ -7212,16 +7212,16 @@
         <v>43447</v>
       </c>
       <c r="B340" t="n">
-        <v>545.8494262695312</v>
+        <v>545.8495483398438</v>
       </c>
       <c r="C340" t="n">
-        <v>547.2140549806483</v>
+        <v>547.2141773561377</v>
       </c>
       <c r="D340" t="n">
-        <v>535.2915485167144</v>
+        <v>535.2916682259299</v>
       </c>
       <c r="E340" t="n">
-        <v>544.4129900398268</v>
+        <v>544.4131117889037</v>
       </c>
       <c r="F340" t="n">
         <v>85033</v>
@@ -7232,16 +7232,16 @@
         <v>43448</v>
       </c>
       <c r="B341" t="n">
-        <v>551.5233764648438</v>
+        <v>551.5234375</v>
       </c>
       <c r="C341" t="n">
-        <v>553.6062519249303</v>
+        <v>553.6063131905911</v>
       </c>
       <c r="D341" t="n">
-        <v>540.8936909468359</v>
+        <v>540.8937508056421</v>
       </c>
       <c r="E341" t="n">
-        <v>542.5456069422175</v>
+        <v>542.5456669838354</v>
       </c>
       <c r="F341" t="n">
         <v>76086</v>
@@ -7292,16 +7292,16 @@
         <v>43453</v>
       </c>
       <c r="B344" t="n">
-        <v>573.9319458007812</v>
+        <v>573.9320678710938</v>
       </c>
       <c r="C344" t="n">
-        <v>579.3904035253281</v>
+        <v>579.3905267566068</v>
       </c>
       <c r="D344" t="n">
-        <v>563.3022604287561</v>
+        <v>563.3023802382274</v>
       </c>
       <c r="E344" t="n">
-        <v>569.4789648607498</v>
+        <v>569.4790859839521</v>
       </c>
       <c r="F344" t="n">
         <v>143734</v>
@@ -7332,16 +7332,16 @@
         <v>43455</v>
       </c>
       <c r="B346" t="n">
-        <v>580.3241577148438</v>
+        <v>580.3240966796875</v>
       </c>
       <c r="C346" t="n">
-        <v>582.9815505991379</v>
+        <v>582.9814892844923</v>
       </c>
       <c r="D346" t="n">
-        <v>570.2690463592767</v>
+        <v>570.2689863816593</v>
       </c>
       <c r="E346" t="n">
-        <v>577.7385723532508</v>
+        <v>577.7385115900315</v>
       </c>
       <c r="F346" t="n">
         <v>378071</v>
@@ -7352,16 +7352,16 @@
         <v>43460</v>
       </c>
       <c r="B347" t="n">
-        <v>579.60595703125</v>
+        <v>579.6058349609375</v>
       </c>
       <c r="C347" t="n">
-        <v>586.5727165767382</v>
+        <v>586.5725930391625</v>
       </c>
       <c r="D347" t="n">
-        <v>573.501059341447</v>
+        <v>573.5009385568818</v>
       </c>
       <c r="E347" t="n">
-        <v>576.6612766505585</v>
+        <v>576.6611552004226</v>
       </c>
       <c r="F347" t="n">
         <v>118120</v>
@@ -7452,16 +7452,16 @@
         <v>43469</v>
       </c>
       <c r="B352" t="n">
-        <v>584.6334228515625</v>
+        <v>584.6334838867188</v>
       </c>
       <c r="C352" t="n">
-        <v>597.9205577923778</v>
+        <v>597.9206202146979</v>
       </c>
       <c r="D352" t="n">
-        <v>576.6611876243454</v>
+        <v>576.6612478272082</v>
       </c>
       <c r="E352" t="n">
-        <v>597.9205577923778</v>
+        <v>597.9206202146979</v>
       </c>
       <c r="F352" t="n">
         <v>186720</v>
@@ -7472,16 +7472,16 @@
         <v>43472</v>
       </c>
       <c r="B353" t="n">
-        <v>590.5228881835938</v>
+        <v>590.52294921875</v>
       </c>
       <c r="C353" t="n">
-        <v>591.4565574095307</v>
+        <v>591.4566185411891</v>
       </c>
       <c r="D353" t="n">
-        <v>575.2965503025016</v>
+        <v>575.2966097638969</v>
       </c>
       <c r="E353" t="n">
-        <v>587.1471916894753</v>
+        <v>587.1472523757269</v>
       </c>
       <c r="F353" t="n">
         <v>82163</v>
@@ -7492,16 +7492,16 @@
         <v>43473</v>
       </c>
       <c r="B354" t="n">
-        <v>596.125</v>
+        <v>596.1250610351562</v>
       </c>
       <c r="C354" t="n">
-        <v>600.8652678469101</v>
+        <v>600.8653293674058</v>
       </c>
       <c r="D354" t="n">
-        <v>589.94823884177</v>
+        <v>589.9482992445093</v>
       </c>
       <c r="E354" t="n">
-        <v>591.0974449251435</v>
+        <v>591.0975054455459</v>
       </c>
       <c r="F354" t="n">
         <v>213026</v>
@@ -7512,16 +7512,16 @@
         <v>43474</v>
       </c>
       <c r="B355" t="n">
-        <v>594.544921875</v>
+        <v>594.5449829101562</v>
       </c>
       <c r="C355" t="n">
-        <v>600.5780111400617</v>
+        <v>600.5780727945665</v>
       </c>
       <c r="D355" t="n">
-        <v>591.8156644850154</v>
+        <v>591.8157252399899</v>
       </c>
       <c r="E355" t="n">
-        <v>600.5061464507322</v>
+        <v>600.5062080978595</v>
       </c>
       <c r="F355" t="n">
         <v>147321</v>
@@ -7532,16 +7532,16 @@
         <v>43475</v>
       </c>
       <c r="B356" t="n">
-        <v>582.335205078125</v>
+        <v>582.3351440429688</v>
       </c>
       <c r="C356" t="n">
-        <v>596.9869707226937</v>
+        <v>596.9869081518708</v>
       </c>
       <c r="D356" t="n">
-        <v>582.335205078125</v>
+        <v>582.3351440429688</v>
       </c>
       <c r="E356" t="n">
-        <v>595.6941493750089</v>
+        <v>595.6940869396878</v>
       </c>
       <c r="F356" t="n">
         <v>131058</v>
@@ -7552,16 +7552,16 @@
         <v>43476</v>
       </c>
       <c r="B357" t="n">
-        <v>570.6281127929688</v>
+        <v>570.628173828125</v>
       </c>
       <c r="C357" t="n">
-        <v>587.1472153175711</v>
+        <v>587.1472781196329</v>
       </c>
       <c r="D357" t="n">
-        <v>569.6944435294589</v>
+        <v>569.6945044647485</v>
       </c>
       <c r="E357" t="n">
-        <v>583.9152480690574</v>
+        <v>583.9153105254236</v>
       </c>
       <c r="F357" t="n">
         <v>387970</v>
@@ -7572,16 +7572,16 @@
         <v>43479</v>
       </c>
       <c r="B358" t="n">
-        <v>568.1143798828125</v>
+        <v>568.1143188476562</v>
       </c>
       <c r="C358" t="n">
-        <v>581.5451312563724</v>
+        <v>581.5450687782884</v>
       </c>
       <c r="D358" t="n">
-        <v>562.3685772955737</v>
+        <v>562.3685168777156</v>
       </c>
       <c r="E358" t="n">
-        <v>571.4182120826051</v>
+        <v>571.4181506925029</v>
       </c>
       <c r="F358" t="n">
         <v>172283</v>
@@ -7612,16 +7612,16 @@
         <v>43481</v>
       </c>
       <c r="B360" t="n">
-        <v>596.125</v>
+        <v>596.1250610351562</v>
       </c>
       <c r="C360" t="n">
-        <v>599.5724467353573</v>
+        <v>599.5725081234856</v>
       </c>
       <c r="D360" t="n">
-        <v>578.1694053243783</v>
+        <v>578.1694645211239</v>
       </c>
       <c r="E360" t="n">
-        <v>578.1694053243783</v>
+        <v>578.1694645211239</v>
       </c>
       <c r="F360" t="n">
         <v>342845</v>
@@ -7632,16 +7632,16 @@
         <v>43482</v>
       </c>
       <c r="B361" t="n">
-        <v>600.4344482421875</v>
+        <v>600.4343872070312</v>
       </c>
       <c r="C361" t="n">
-        <v>604.7438148364927</v>
+        <v>604.7437533632822</v>
       </c>
       <c r="D361" t="n">
-        <v>587.7218853949083</v>
+        <v>587.7218256520052</v>
       </c>
       <c r="E361" t="n">
-        <v>598.9262042371413</v>
+        <v>598.9261433553005</v>
       </c>
       <c r="F361" t="n">
         <v>221295</v>
@@ -7652,16 +7652,16 @@
         <v>43483</v>
       </c>
       <c r="B362" t="n">
-        <v>619.1800537109375</v>
+        <v>619.1799926757812</v>
       </c>
       <c r="C362" t="n">
-        <v>619.8982433068784</v>
+        <v>619.8981822009272</v>
       </c>
       <c r="D362" t="n">
-        <v>597.4178569965536</v>
+        <v>597.4177981065877</v>
       </c>
       <c r="E362" t="n">
-        <v>603.2354671473379</v>
+        <v>603.2354076839059</v>
       </c>
       <c r="F362" t="n">
         <v>144739</v>
@@ -7692,16 +7692,16 @@
         <v>43487</v>
       </c>
       <c r="B364" t="n">
-        <v>621.9093017578125</v>
+        <v>621.9092407226562</v>
       </c>
       <c r="C364" t="n">
-        <v>624.4949445813302</v>
+        <v>624.4948832924149</v>
       </c>
       <c r="D364" t="n">
-        <v>614.2243523328264</v>
+        <v>614.224292051883</v>
       </c>
       <c r="E364" t="n">
-        <v>618.3182391603953</v>
+        <v>618.3181784776715</v>
       </c>
       <c r="F364" t="n">
         <v>56158</v>
@@ -7752,16 +7752,16 @@
         <v>43493</v>
       </c>
       <c r="B367" t="n">
-        <v>633.3290405273438</v>
+        <v>633.3289794921875</v>
       </c>
       <c r="C367" t="n">
-        <v>651.5000602481508</v>
+        <v>651.4999974618179</v>
       </c>
       <c r="D367" t="n">
-        <v>610.4895026590767</v>
+        <v>610.4894438250113</v>
       </c>
       <c r="E367" t="n">
-        <v>611.2795569376502</v>
+        <v>611.2794980274457</v>
       </c>
       <c r="F367" t="n">
         <v>160193</v>
@@ -7772,16 +7772,16 @@
         <v>43494</v>
       </c>
       <c r="B368" t="n">
-        <v>620.6163940429688</v>
+        <v>620.616455078125</v>
       </c>
       <c r="C368" t="n">
-        <v>643.5276791313473</v>
+        <v>643.5277424197374</v>
       </c>
       <c r="D368" t="n">
-        <v>618.3180962170321</v>
+        <v>618.3181570261598</v>
       </c>
       <c r="E368" t="n">
-        <v>639.2183707077161</v>
+        <v>639.2184335723028</v>
       </c>
       <c r="F368" t="n">
         <v>112016</v>
@@ -7792,16 +7792,16 @@
         <v>43495</v>
       </c>
       <c r="B369" t="n">
-        <v>616.2353515625</v>
+        <v>616.2352905273438</v>
       </c>
       <c r="C369" t="n">
-        <v>636.9201507238472</v>
+        <v>636.9200876399608</v>
       </c>
       <c r="D369" t="n">
-        <v>612.3569445732975</v>
+        <v>612.3568839222787</v>
       </c>
       <c r="E369" t="n">
-        <v>624.5667401191871</v>
+        <v>624.5666782588467</v>
       </c>
       <c r="F369" t="n">
         <v>160897</v>
@@ -7852,16 +7852,16 @@
         <v>43500</v>
       </c>
       <c r="B372" t="n">
-        <v>628.445068359375</v>
+        <v>628.4451293945312</v>
       </c>
       <c r="C372" t="n">
-        <v>634.549965367329</v>
+        <v>634.5500269953985</v>
       </c>
       <c r="D372" t="n">
-        <v>617.7435181295621</v>
+        <v>617.743578125374</v>
       </c>
       <c r="E372" t="n">
-        <v>628.3013961470078</v>
+        <v>628.3014571682105</v>
       </c>
       <c r="F372" t="n">
         <v>140148</v>
@@ -7912,16 +7912,16 @@
         <v>43503</v>
       </c>
       <c r="B375" t="n">
-        <v>616.2353515625</v>
+        <v>616.2352905273438</v>
       </c>
       <c r="C375" t="n">
-        <v>622.5557290952005</v>
+        <v>622.5556674340411</v>
       </c>
       <c r="D375" t="n">
-        <v>603.3791739089432</v>
+        <v>603.3791141471297</v>
       </c>
       <c r="E375" t="n">
-        <v>621.1192926494958</v>
+        <v>621.1192311306086</v>
       </c>
       <c r="F375" t="n">
         <v>104504</v>
@@ -7932,16 +7932,16 @@
         <v>43504</v>
       </c>
       <c r="B376" t="n">
-        <v>640.7266845703125</v>
+        <v>640.7266235351562</v>
       </c>
       <c r="C376" t="n">
-        <v>640.7266845703125</v>
+        <v>640.7266235351562</v>
       </c>
       <c r="D376" t="n">
-        <v>609.8431040496826</v>
+        <v>609.8430459564737</v>
       </c>
       <c r="E376" t="n">
-        <v>625.5722101555159</v>
+        <v>625.5721505639639</v>
       </c>
       <c r="F376" t="n">
         <v>269863</v>
@@ -7972,16 +7972,16 @@
         <v>43508</v>
       </c>
       <c r="B378" t="n">
-        <v>667.229248046875</v>
+        <v>667.2291259765625</v>
       </c>
       <c r="C378" t="n">
-        <v>669.3838742298877</v>
+        <v>669.3837517653841</v>
       </c>
       <c r="D378" t="n">
-        <v>643.5278454893119</v>
+        <v>643.5277277551967</v>
       </c>
       <c r="E378" t="n">
-        <v>645.6107213112007</v>
+        <v>645.610603196021</v>
       </c>
       <c r="F378" t="n">
         <v>195928</v>
@@ -8052,16 +8052,16 @@
         <v>43514</v>
       </c>
       <c r="B382" t="n">
-        <v>658.6104736328125</v>
+        <v>658.6104125976562</v>
       </c>
       <c r="C382" t="n">
-        <v>664.7153713098178</v>
+        <v>664.7153097089048</v>
       </c>
       <c r="D382" t="n">
-        <v>650.7818522480502</v>
+        <v>650.7817919383928</v>
       </c>
       <c r="E382" t="n">
-        <v>660.7651568533082</v>
+        <v>660.7650956184718</v>
       </c>
       <c r="F382" t="n">
         <v>91084</v>
@@ -8072,16 +8072,16 @@
         <v>43515</v>
       </c>
       <c r="B383" t="n">
-        <v>661.4833984375</v>
+        <v>661.4832763671875</v>
       </c>
       <c r="C383" t="n">
-        <v>662.8480273216194</v>
+        <v>662.8479049994779</v>
       </c>
       <c r="D383" t="n">
-        <v>651.0691344015784</v>
+        <v>651.0690142531167</v>
       </c>
       <c r="E383" t="n">
-        <v>660.0469620256898</v>
+        <v>660.0468402204576</v>
       </c>
       <c r="F383" t="n">
         <v>188559</v>
@@ -8092,16 +8092,16 @@
         <v>43516</v>
       </c>
       <c r="B384" t="n">
-        <v>666.1519165039062</v>
+        <v>666.1517944335938</v>
       </c>
       <c r="C384" t="n">
-        <v>666.5110113446043</v>
+        <v>666.5108892084887</v>
       </c>
       <c r="D384" t="n">
-        <v>648.6272764410736</v>
+        <v>648.6271575820981</v>
       </c>
       <c r="E384" t="n">
-        <v>662.8480838889948</v>
+        <v>662.8479624240995</v>
       </c>
       <c r="F384" t="n">
         <v>179613</v>
@@ -8112,16 +8112,16 @@
         <v>43517</v>
       </c>
       <c r="B385" t="n">
-        <v>681.3062133789062</v>
+        <v>681.3063354492188</v>
       </c>
       <c r="C385" t="n">
-        <v>681.3062133789062</v>
+        <v>681.3063354492188</v>
       </c>
       <c r="D385" t="n">
-        <v>663.637962917069</v>
+        <v>663.6380818217434</v>
       </c>
       <c r="E385" t="n">
-        <v>663.637962917069</v>
+        <v>663.6380818217434</v>
       </c>
       <c r="F385" t="n">
         <v>232784</v>
@@ -8132,16 +8132,16 @@
         <v>43518</v>
       </c>
       <c r="B386" t="n">
-        <v>670.8201904296875</v>
+        <v>670.8201293945312</v>
       </c>
       <c r="C386" t="n">
-        <v>685.6874343041444</v>
+        <v>685.6873719162792</v>
       </c>
       <c r="D386" t="n">
-        <v>670.5329031787044</v>
+        <v>670.5328421696872</v>
       </c>
       <c r="E386" t="n">
-        <v>678.2897161268398</v>
+        <v>678.2896544120623</v>
       </c>
       <c r="F386" t="n">
         <v>142026</v>
@@ -8172,16 +8172,16 @@
         <v>43522</v>
       </c>
       <c r="B388" t="n">
-        <v>673.3339233398438</v>
+        <v>673.333984375</v>
       </c>
       <c r="C388" t="n">
-        <v>679.5824920972024</v>
+        <v>679.5825536987676</v>
       </c>
       <c r="D388" t="n">
-        <v>659.1849842922329</v>
+        <v>659.1850440448417</v>
       </c>
       <c r="E388" t="n">
-        <v>673.1185007946428</v>
+        <v>673.1185618102719</v>
       </c>
       <c r="F388" t="n">
         <v>234558</v>
@@ -8212,16 +8212,16 @@
         <v>43524</v>
       </c>
       <c r="B390" t="n">
-        <v>639.2184448242188</v>
+        <v>639.218505859375</v>
       </c>
       <c r="C390" t="n">
-        <v>654.0856320740612</v>
+        <v>654.0856945287965</v>
       </c>
       <c r="D390" t="n">
-        <v>634.2626966837398</v>
+        <v>634.2627572457012</v>
       </c>
       <c r="E390" t="n">
-        <v>652.649195766298</v>
+        <v>652.6492580838765</v>
       </c>
       <c r="F390" t="n">
         <v>276723</v>
@@ -8232,16 +8232,16 @@
         <v>43525</v>
       </c>
       <c r="B391" t="n">
-        <v>646.9034423828125</v>
+        <v>646.9033203125</v>
       </c>
       <c r="C391" t="n">
-        <v>651.715575842952</v>
+        <v>651.7154528645927</v>
       </c>
       <c r="D391" t="n">
-        <v>639.8648753556274</v>
+        <v>639.8647546134886</v>
       </c>
       <c r="E391" t="n">
-        <v>639.8648753556274</v>
+        <v>639.8647546134886</v>
       </c>
       <c r="F391" t="n">
         <v>193907</v>
@@ -8272,16 +8272,16 @@
         <v>43531</v>
       </c>
       <c r="B393" t="n">
-        <v>621.2628173828125</v>
+        <v>621.2628784179688</v>
       </c>
       <c r="C393" t="n">
-        <v>625.5721832649873</v>
+        <v>625.5722447235116</v>
       </c>
       <c r="D393" t="n">
-        <v>601.9426499467455</v>
+        <v>601.942709083817</v>
       </c>
       <c r="E393" t="n">
-        <v>624.853936560761</v>
+        <v>624.8539979487221</v>
       </c>
       <c r="F393" t="n">
         <v>310579</v>
@@ -8292,16 +8292,16 @@
         <v>43532</v>
       </c>
       <c r="B394" t="n">
-        <v>654.301025390625</v>
+        <v>654.3010864257812</v>
       </c>
       <c r="C394" t="n">
-        <v>654.301025390625</v>
+        <v>654.3010864257812</v>
       </c>
       <c r="D394" t="n">
-        <v>611.4949432152944</v>
+        <v>611.4950002573712</v>
       </c>
       <c r="E394" t="n">
-        <v>621.1909584765036</v>
+        <v>621.1910164230537</v>
       </c>
       <c r="F394" t="n">
         <v>586768</v>
@@ -8332,16 +8332,16 @@
         <v>43536</v>
       </c>
       <c r="B396" t="n">
-        <v>647.4779663085938</v>
+        <v>647.47802734375</v>
       </c>
       <c r="C396" t="n">
-        <v>659.3286658690457</v>
+        <v>659.32872802132</v>
       </c>
       <c r="D396" t="n">
-        <v>639.5775380493552</v>
+        <v>639.5775983397697</v>
       </c>
       <c r="E396" t="n">
-        <v>655.1629720008887</v>
+        <v>655.1630337604796</v>
       </c>
       <c r="F396" t="n">
         <v>122580</v>
@@ -8352,16 +8352,16 @@
         <v>43537</v>
       </c>
       <c r="B397" t="n">
-        <v>640.870361328125</v>
+        <v>640.8703002929688</v>
       </c>
       <c r="C397" t="n">
-        <v>653.0801557102122</v>
+        <v>653.0800935122207</v>
       </c>
       <c r="D397" t="n">
-        <v>630.5997702557997</v>
+        <v>630.5997101987931</v>
       </c>
       <c r="E397" t="n">
-        <v>647.334353303467</v>
+        <v>647.3342916526937</v>
       </c>
       <c r="F397" t="n">
         <v>145482</v>
@@ -8372,16 +8372,16 @@
         <v>43538</v>
       </c>
       <c r="B398" t="n">
-        <v>639.2184448242188</v>
+        <v>639.218505859375</v>
       </c>
       <c r="C398" t="n">
-        <v>651.2127594585347</v>
+        <v>651.2128216389566</v>
       </c>
       <c r="D398" t="n">
-        <v>629.8815230663662</v>
+        <v>629.8815832099955</v>
       </c>
       <c r="E398" t="n">
-        <v>642.809564179424</v>
+        <v>642.8096255574749</v>
       </c>
       <c r="F398" t="n">
         <v>180995</v>
@@ -8392,16 +8392,16 @@
         <v>43539</v>
       </c>
       <c r="B399" t="n">
-        <v>632.6826171875</v>
+        <v>632.6825561523438</v>
       </c>
       <c r="C399" t="n">
-        <v>648.4835316410457</v>
+        <v>648.4834690815687</v>
       </c>
       <c r="D399" t="n">
-        <v>628.5169231180633</v>
+        <v>628.5168624847732</v>
       </c>
       <c r="E399" t="n">
-        <v>642.1631544253081</v>
+        <v>642.1630924755605</v>
       </c>
       <c r="F399" t="n">
         <v>241457</v>
@@ -8492,16 +8492,16 @@
         <v>43546</v>
       </c>
       <c r="B404" t="n">
-        <v>657.0747680664062</v>
+        <v>657.0748291015625</v>
       </c>
       <c r="C404" t="n">
-        <v>663.2680393651752</v>
+        <v>663.2681009756196</v>
       </c>
       <c r="D404" t="n">
-        <v>635.5458053085566</v>
+        <v>635.5458643439046</v>
       </c>
       <c r="E404" t="n">
-        <v>647.7848611182527</v>
+        <v>647.7849212904769</v>
       </c>
       <c r="F404" t="n">
         <v>199032</v>
@@ -8532,16 +8532,16 @@
         <v>43550</v>
       </c>
       <c r="B406" t="n">
-        <v>667.3968505859375</v>
+        <v>667.3969116210938</v>
       </c>
       <c r="C406" t="n">
-        <v>670.3459994599175</v>
+        <v>670.346060764781</v>
       </c>
       <c r="D406" t="n">
-        <v>658.4756312250007</v>
+        <v>658.4756914442885</v>
       </c>
       <c r="E406" t="n">
-        <v>667.2493637974736</v>
+        <v>667.2494248191418</v>
       </c>
       <c r="F406" t="n">
         <v>144960</v>
@@ -8632,16 +8632,16 @@
         <v>43557</v>
       </c>
       <c r="B411" t="n">
-        <v>679.7833251953125</v>
+        <v>679.7833862304688</v>
       </c>
       <c r="C411" t="n">
-        <v>685.3130526198722</v>
+        <v>685.3131141515216</v>
       </c>
       <c r="D411" t="n">
-        <v>671.3045076268693</v>
+        <v>671.3045679007448</v>
       </c>
       <c r="E411" t="n">
-        <v>680.0045260302006</v>
+        <v>680.0045870852177</v>
       </c>
       <c r="F411" t="n">
         <v>117077</v>
@@ -8652,16 +8652,16 @@
         <v>43558</v>
       </c>
       <c r="B412" t="n">
-        <v>689.3681640625</v>
+        <v>689.3682250976562</v>
       </c>
       <c r="C412" t="n">
-        <v>696.7410950187081</v>
+        <v>696.7411567066476</v>
       </c>
       <c r="D412" t="n">
-        <v>677.4240229561865</v>
+        <v>677.4240829338345</v>
       </c>
       <c r="E412" t="n">
-        <v>679.7833420815233</v>
+        <v>679.7834022680604</v>
       </c>
       <c r="F412" t="n">
         <v>159059</v>
@@ -8672,16 +8672,16 @@
         <v>43559</v>
       </c>
       <c r="B413" t="n">
-        <v>678.5299682617188</v>
+        <v>678.5299072265625</v>
       </c>
       <c r="C413" t="n">
-        <v>694.3080029418946</v>
+        <v>694.3079404874719</v>
       </c>
       <c r="D413" t="n">
-        <v>677.2028219093562</v>
+        <v>677.2027609935794</v>
       </c>
       <c r="E413" t="n">
-        <v>689.5156506423978</v>
+        <v>689.515588619057</v>
       </c>
       <c r="F413" t="n">
         <v>158706</v>
@@ -8692,16 +8692,16 @@
         <v>43560</v>
       </c>
       <c r="B414" t="n">
-        <v>701.017333984375</v>
+        <v>701.0174560546875</v>
       </c>
       <c r="C414" t="n">
-        <v>702.2707074966779</v>
+        <v>702.2708297852442</v>
       </c>
       <c r="D414" t="n">
-        <v>682.4375799852958</v>
+        <v>682.4376988202584</v>
       </c>
       <c r="E414" t="n">
-        <v>689.8105103494357</v>
+        <v>689.8106304682694</v>
       </c>
       <c r="F414" t="n">
         <v>143643</v>
@@ -8712,16 +8712,16 @@
         <v>43563</v>
       </c>
       <c r="B415" t="n">
-        <v>712.0029907226562</v>
+        <v>712.0030517578125</v>
       </c>
       <c r="C415" t="n">
-        <v>712.0029907226562</v>
+        <v>712.0030517578125</v>
       </c>
       <c r="D415" t="n">
-        <v>694.6766680998304</v>
+        <v>694.6767276497193</v>
       </c>
       <c r="E415" t="n">
-        <v>701.8283979821206</v>
+        <v>701.8284581450785</v>
       </c>
       <c r="F415" t="n">
         <v>133157</v>
@@ -8732,16 +8732,16 @@
         <v>43564</v>
       </c>
       <c r="B416" t="n">
-        <v>701.9021606445312</v>
+        <v>701.9022216796875</v>
       </c>
       <c r="C416" t="n">
-        <v>710.8970944839187</v>
+        <v>710.8971563012457</v>
       </c>
       <c r="D416" t="n">
-        <v>698.5106099329405</v>
+        <v>698.5106706731784</v>
       </c>
       <c r="E416" t="n">
-        <v>707.8005173633237</v>
+        <v>707.8005789113821</v>
       </c>
       <c r="F416" t="n">
         <v>71169</v>
@@ -8752,16 +8752,16 @@
         <v>43565</v>
       </c>
       <c r="B417" t="n">
-        <v>688.7783813476562</v>
+        <v>688.7783203125</v>
       </c>
       <c r="C417" t="n">
-        <v>705.588648643443</v>
+        <v>705.5885861186679</v>
       </c>
       <c r="D417" t="n">
-        <v>679.0461306010747</v>
+        <v>679.0460704283284</v>
       </c>
       <c r="E417" t="n">
-        <v>702.1970978242502</v>
+        <v>702.1970356000127</v>
       </c>
       <c r="F417" t="n">
         <v>228911</v>
@@ -8852,16 +8852,16 @@
         <v>43572</v>
       </c>
       <c r="B422" t="n">
-        <v>700.427490234375</v>
+        <v>700.4275512695312</v>
       </c>
       <c r="C422" t="n">
-        <v>705.441042872788</v>
+        <v>705.4411043448246</v>
       </c>
       <c r="D422" t="n">
-        <v>693.7918765152425</v>
+        <v>693.7919369721723</v>
       </c>
       <c r="E422" t="n">
-        <v>700.8698331812374</v>
+        <v>700.8698942549393</v>
       </c>
       <c r="F422" t="n">
         <v>106252</v>
@@ -8872,16 +8872,16 @@
         <v>43573</v>
       </c>
       <c r="B423" t="n">
-        <v>684.7969360351562</v>
+        <v>684.7969970703125</v>
       </c>
       <c r="C423" t="n">
-        <v>704.556350573076</v>
+        <v>704.5564133693659</v>
       </c>
       <c r="D423" t="n">
-        <v>684.7969360351562</v>
+        <v>684.7969970703125</v>
       </c>
       <c r="E423" t="n">
-        <v>700.5012562598826</v>
+        <v>700.5013186947467</v>
       </c>
       <c r="F423" t="n">
         <v>125776</v>
@@ -8892,16 +8892,16 @@
         <v>43577</v>
       </c>
       <c r="B424" t="n">
-        <v>697.9207763671875</v>
+        <v>697.9207153320312</v>
       </c>
       <c r="C424" t="n">
-        <v>703.3767313596035</v>
+        <v>703.3766698473084</v>
       </c>
       <c r="D424" t="n">
-        <v>686.2715497879069</v>
+        <v>686.2714897715088</v>
       </c>
       <c r="E424" t="n">
-        <v>686.3452638404921</v>
+        <v>686.3452038176474</v>
       </c>
       <c r="F424" t="n">
         <v>77260</v>
@@ -8912,16 +8912,16 @@
         <v>43578</v>
       </c>
       <c r="B425" t="n">
-        <v>721.36669921875</v>
+        <v>721.3666381835938</v>
       </c>
       <c r="C425" t="n">
-        <v>722.9150465494968</v>
+        <v>722.9149853833342</v>
       </c>
       <c r="D425" t="n">
-        <v>697.9208166033296</v>
+        <v>697.9207575519399</v>
       </c>
       <c r="E425" t="n">
-        <v>697.9208166033296</v>
+        <v>697.9207575519399</v>
       </c>
       <c r="F425" t="n">
         <v>178282</v>
@@ -8952,16 +8952,16 @@
         <v>43580</v>
       </c>
       <c r="B427" t="n">
-        <v>722.5462646484375</v>
+        <v>722.5463256835938</v>
       </c>
       <c r="C427" t="n">
-        <v>724.7581555812845</v>
+        <v>724.7582168032844</v>
       </c>
       <c r="D427" t="n">
-        <v>711.5606414104789</v>
+        <v>711.5607015176541</v>
       </c>
       <c r="E427" t="n">
-        <v>717.3115108842588</v>
+        <v>717.3115714772234</v>
       </c>
       <c r="F427" t="n">
         <v>179547</v>
@@ -8972,16 +8972,16 @@
         <v>43581</v>
       </c>
       <c r="B428" t="n">
-        <v>697.9207763671875</v>
+        <v>697.9207153320312</v>
       </c>
       <c r="C428" t="n">
-        <v>723.7259768299026</v>
+        <v>723.7259135380083</v>
       </c>
       <c r="D428" t="n">
-        <v>697.9207763671875</v>
+        <v>697.9207153320312</v>
       </c>
       <c r="E428" t="n">
-        <v>722.5463172304108</v>
+        <v>722.546254041681</v>
       </c>
       <c r="F428" t="n">
         <v>338189</v>
@@ -8992,16 +8992,16 @@
         <v>43584</v>
       </c>
       <c r="B429" t="n">
-        <v>699.6902465820312</v>
+        <v>699.6903076171875</v>
       </c>
       <c r="C429" t="n">
-        <v>708.7589528663908</v>
+        <v>708.7590146926256</v>
       </c>
       <c r="D429" t="n">
-        <v>673.5163591949721</v>
+        <v>673.5164179469361</v>
       </c>
       <c r="E429" t="n">
-        <v>697.9207572313101</v>
+        <v>697.9208181121107</v>
       </c>
       <c r="F429" t="n">
         <v>175687</v>
@@ -9052,16 +9052,16 @@
         <v>43588</v>
       </c>
       <c r="B432" t="n">
-        <v>738.0294799804688</v>
+        <v>738.029541015625</v>
       </c>
       <c r="C432" t="n">
-        <v>738.1031940314342</v>
+        <v>738.1032550726866</v>
       </c>
       <c r="D432" t="n">
-        <v>705.6623210001189</v>
+        <v>705.662379358506</v>
       </c>
       <c r="E432" t="n">
-        <v>714.7310273338567</v>
+        <v>714.731086442227</v>
       </c>
       <c r="F432" t="n">
         <v>687008</v>
@@ -9072,16 +9072,16 @@
         <v>43591</v>
       </c>
       <c r="B433" t="n">
-        <v>726.2327880859375</v>
+        <v>726.2327270507812</v>
       </c>
       <c r="C433" t="n">
-        <v>744.2227144876096</v>
+        <v>744.2226519405167</v>
       </c>
       <c r="D433" t="n">
-        <v>719.3022585439375</v>
+        <v>719.3021980912473</v>
       </c>
       <c r="E433" t="n">
-        <v>729.9192537058282</v>
+        <v>729.9191923608485</v>
       </c>
       <c r="F433" t="n">
         <v>141178</v>
@@ -9152,16 +9152,16 @@
         <v>43595</v>
       </c>
       <c r="B437" t="n">
-        <v>745.2548217773438</v>
+        <v>745.2550048828125</v>
       </c>
       <c r="C437" t="n">
-        <v>746.0658522950794</v>
+        <v>746.0660355998143</v>
       </c>
       <c r="D437" t="n">
-        <v>727.6335272677526</v>
+        <v>727.6337060437554</v>
       </c>
       <c r="E437" t="n">
-        <v>735.0064572786833</v>
+        <v>735.0066378661789</v>
       </c>
       <c r="F437" t="n">
         <v>130275</v>
@@ -9172,16 +9172,16 @@
         <v>43598</v>
       </c>
       <c r="B438" t="n">
-        <v>721.4403686523438</v>
+        <v>721.4404296875</v>
       </c>
       <c r="C438" t="n">
-        <v>742.2320157298615</v>
+        <v>742.2320785240286</v>
       </c>
       <c r="D438" t="n">
-        <v>721.3666546000683</v>
+        <v>721.3667156289882</v>
       </c>
       <c r="E438" t="n">
-        <v>733.458282823121</v>
+        <v>733.4583448750144</v>
       </c>
       <c r="F438" t="n">
         <v>104165</v>
@@ -9232,16 +9232,16 @@
         <v>43601</v>
       </c>
       <c r="B441" t="n">
-        <v>713.4776000976562</v>
+        <v>713.4776611328125</v>
       </c>
       <c r="C441" t="n">
-        <v>725.9377974243679</v>
+        <v>725.9378595254442</v>
       </c>
       <c r="D441" t="n">
-        <v>704.1876936195474</v>
+        <v>704.1877538599894</v>
       </c>
       <c r="E441" t="n">
-        <v>715.1733165900973</v>
+        <v>715.1733777703154</v>
       </c>
       <c r="F441" t="n">
         <v>192694</v>
@@ -9292,16 +9292,16 @@
         <v>43606</v>
       </c>
       <c r="B444" t="n">
-        <v>766.0465698242188</v>
+        <v>766.046630859375</v>
       </c>
       <c r="C444" t="n">
-        <v>770.2490923766624</v>
+        <v>770.2491537466567</v>
       </c>
       <c r="D444" t="n">
-        <v>750.2684763264823</v>
+        <v>750.2685361045108</v>
       </c>
       <c r="E444" t="n">
-        <v>755.7244898807286</v>
+        <v>755.7245500934678</v>
       </c>
       <c r="F444" t="n">
         <v>224959</v>
@@ -9312,16 +9312,16 @@
         <v>43607</v>
       </c>
       <c r="B445" t="n">
-        <v>761.032958984375</v>
+        <v>761.0330200195312</v>
       </c>
       <c r="C445" t="n">
-        <v>769.7330363730712</v>
+        <v>769.7330981059772</v>
       </c>
       <c r="D445" t="n">
-        <v>746.9506994640686</v>
+        <v>746.9507593698219</v>
       </c>
       <c r="E445" t="n">
-        <v>766.0465708611872</v>
+        <v>766.0466322984372</v>
       </c>
       <c r="F445" t="n">
         <v>111769</v>
@@ -9332,16 +9332,16 @@
         <v>43608</v>
       </c>
       <c r="B446" t="n">
-        <v>757.936279296875</v>
+        <v>757.9363403320312</v>
       </c>
       <c r="C446" t="n">
-        <v>764.6456660937819</v>
+        <v>764.6457276692322</v>
       </c>
       <c r="D446" t="n">
-        <v>749.9735189482298</v>
+        <v>749.9735793421601</v>
       </c>
       <c r="E446" t="n">
-        <v>757.1252487147682</v>
+        <v>757.1253096846136</v>
       </c>
       <c r="F446" t="n">
         <v>76516</v>
@@ -9352,16 +9352,16 @@
         <v>43609</v>
       </c>
       <c r="B447" t="n">
-        <v>736.5548095703125</v>
+        <v>736.5548706054688</v>
       </c>
       <c r="C447" t="n">
-        <v>761.0329205524349</v>
+        <v>761.0329836159879</v>
       </c>
       <c r="D447" t="n">
-        <v>726.2327301341116</v>
+        <v>726.2327903139212</v>
       </c>
       <c r="E447" t="n">
-        <v>759.4108593760509</v>
+        <v>759.4109223051905</v>
       </c>
       <c r="F447" t="n">
         <v>221503</v>
@@ -9372,16 +9372,16 @@
         <v>43612</v>
       </c>
       <c r="B448" t="n">
-        <v>731.836181640625</v>
+        <v>731.8361206054688</v>
       </c>
       <c r="C448" t="n">
-        <v>746.5820431475281</v>
+        <v>746.5819808825665</v>
       </c>
       <c r="D448" t="n">
-        <v>731.836181640625</v>
+        <v>731.8361206054688</v>
       </c>
       <c r="E448" t="n">
-        <v>742.6743769365024</v>
+        <v>742.6743149974403</v>
       </c>
       <c r="F448" t="n">
         <v>96223</v>
@@ -9392,16 +9392,16 @@
         <v>43613</v>
       </c>
       <c r="B449" t="n">
-        <v>752.7015991210938</v>
+        <v>752.7015380859375</v>
       </c>
       <c r="C449" t="n">
-        <v>754.9872043078567</v>
+        <v>754.9871430873651</v>
       </c>
       <c r="D449" t="n">
-        <v>734.711672532071</v>
+        <v>734.7116129556841</v>
       </c>
       <c r="E449" t="n">
-        <v>736.5548760164455</v>
+        <v>736.5548162905967</v>
       </c>
       <c r="F449" t="n">
         <v>327508</v>
@@ -9412,16 +9412,16 @@
         <v>43614</v>
       </c>
       <c r="B450" t="n">
-        <v>758.7474365234375</v>
+        <v>758.7473754882812</v>
       </c>
       <c r="C450" t="n">
-        <v>759.263552315427</v>
+        <v>759.2634912387533</v>
       </c>
       <c r="D450" t="n">
-        <v>744.6651754694344</v>
+        <v>744.6651155670833</v>
       </c>
       <c r="E450" t="n">
-        <v>748.3516413828108</v>
+        <v>748.3515811839129</v>
       </c>
       <c r="F450" t="n">
         <v>128084</v>
@@ -9452,16 +9452,16 @@
         <v>43616</v>
       </c>
       <c r="B452" t="n">
-        <v>751.1532592773438</v>
+        <v>751.1533203125</v>
       </c>
       <c r="C452" t="n">
-        <v>780.6449238413311</v>
+        <v>780.6449872728404</v>
       </c>
       <c r="D452" t="n">
-        <v>749.5311980653321</v>
+        <v>749.5312589686873</v>
       </c>
       <c r="E452" t="n">
-        <v>768.6270689175442</v>
+        <v>768.6271313725395</v>
       </c>
       <c r="F452" t="n">
         <v>226903</v>
@@ -9472,16 +9472,16 @@
         <v>43619</v>
       </c>
       <c r="B453" t="n">
-        <v>736.5548095703125</v>
+        <v>736.5548706054688</v>
       </c>
       <c r="C453" t="n">
-        <v>752.4066163398552</v>
+        <v>752.406678688583</v>
       </c>
       <c r="D453" t="n">
-        <v>733.6056607855488</v>
+        <v>733.6057215763217</v>
       </c>
       <c r="E453" t="n">
-        <v>752.0379874141418</v>
+        <v>752.0380497323229</v>
       </c>
       <c r="F453" t="n">
         <v>267306</v>
@@ -9532,16 +9532,16 @@
         <v>43622</v>
       </c>
       <c r="B456" t="n">
-        <v>699.3215942382812</v>
+        <v>699.3216552734375</v>
       </c>
       <c r="C456" t="n">
-        <v>733.4582412508018</v>
+        <v>733.458305265325</v>
       </c>
       <c r="D456" t="n">
-        <v>699.3215942382812</v>
+        <v>699.3216552734375</v>
       </c>
       <c r="E456" t="n">
-        <v>725.6429088456783</v>
+        <v>725.6429721780975</v>
       </c>
       <c r="F456" t="n">
         <v>226537</v>
@@ -9572,16 +9572,16 @@
         <v>43626</v>
       </c>
       <c r="B458" t="n">
-        <v>726.7489013671875</v>
+        <v>726.7488403320312</v>
       </c>
       <c r="C458" t="n">
-        <v>732.6472580768752</v>
+        <v>732.6471965463523</v>
       </c>
       <c r="D458" t="n">
-        <v>720.776830604631</v>
+        <v>720.776770071032</v>
       </c>
       <c r="E458" t="n">
-        <v>729.919251225404</v>
+        <v>729.9191899239896</v>
       </c>
       <c r="F458" t="n">
         <v>82229</v>
@@ -9632,16 +9632,16 @@
         <v>43629</v>
       </c>
       <c r="B461" t="n">
-        <v>707.8004150390625</v>
+        <v>707.8004760742188</v>
       </c>
       <c r="C461" t="n">
-        <v>728.886974169087</v>
+        <v>728.8870370225827</v>
       </c>
       <c r="D461" t="n">
-        <v>702.2706880741292</v>
+        <v>702.2707486324451</v>
       </c>
       <c r="E461" t="n">
-        <v>717.3114632534141</v>
+        <v>717.3115251087285</v>
       </c>
       <c r="F461" t="n">
         <v>234349</v>
@@ -9652,16 +9652,16 @@
         <v>43630</v>
       </c>
       <c r="B462" t="n">
-        <v>690.1054077148438</v>
+        <v>690.1055297851562</v>
       </c>
       <c r="C462" t="n">
-        <v>718.7860391979269</v>
+        <v>718.7861663414552</v>
       </c>
       <c r="D462" t="n">
-        <v>690.1054077148438</v>
+        <v>690.1055297851562</v>
       </c>
       <c r="E462" t="n">
-        <v>707.7266439321913</v>
+        <v>707.7267691194622</v>
       </c>
       <c r="F462" t="n">
         <v>150777</v>
@@ -9692,16 +9692,16 @@
         <v>43634</v>
       </c>
       <c r="B464" t="n">
-        <v>724.2421264648438</v>
+        <v>724.2420654296875</v>
       </c>
       <c r="C464" t="n">
-        <v>726.3803036061188</v>
+        <v>726.3802423907686</v>
       </c>
       <c r="D464" t="n">
-        <v>710.8971239144889</v>
+        <v>710.8970640039762</v>
       </c>
       <c r="E464" t="n">
-        <v>712.2242703707815</v>
+        <v>712.2242103484242</v>
       </c>
       <c r="F464" t="n">
         <v>134318</v>
@@ -9732,16 +9732,16 @@
         <v>43637</v>
       </c>
       <c r="B466" t="n">
-        <v>733.4581909179688</v>
+        <v>733.458251953125</v>
       </c>
       <c r="C466" t="n">
-        <v>733.4581909179688</v>
+        <v>733.458251953125</v>
       </c>
       <c r="D466" t="n">
-        <v>723.3572541987642</v>
+        <v>723.3573143933651</v>
       </c>
       <c r="E466" t="n">
-        <v>728.4445795798858</v>
+        <v>728.4446401978315</v>
       </c>
       <c r="F466" t="n">
         <v>181934</v>
@@ -9752,16 +9752,16 @@
         <v>43640</v>
       </c>
       <c r="B467" t="n">
-        <v>745.03369140625</v>
+        <v>745.0337524414062</v>
       </c>
       <c r="C467" t="n">
-        <v>752.037993185729</v>
+        <v>752.0380547946963</v>
       </c>
       <c r="D467" t="n">
-        <v>733.8268672486123</v>
+        <v>733.8269273656755</v>
       </c>
       <c r="E467" t="n">
-        <v>734.0480680815492</v>
+        <v>734.0481282167337</v>
       </c>
       <c r="F467" t="n">
         <v>155459</v>
@@ -9792,16 +9792,16 @@
         <v>43642</v>
       </c>
       <c r="B469" t="n">
-        <v>737.2921752929688</v>
+        <v>737.2921142578125</v>
       </c>
       <c r="C469" t="n">
-        <v>751.0058060911912</v>
+        <v>751.0057439207814</v>
       </c>
       <c r="D469" t="n">
-        <v>732.6472509747404</v>
+        <v>732.6471903241043</v>
       </c>
       <c r="E469" t="n">
-        <v>733.6057097213413</v>
+        <v>733.6056489913612</v>
       </c>
       <c r="F469" t="n">
         <v>130066</v>
@@ -9812,16 +9812,16 @@
         <v>43643</v>
       </c>
       <c r="B470" t="n">
-        <v>732.8683471679688</v>
+        <v>732.868408203125</v>
       </c>
       <c r="C470" t="n">
-        <v>740.7573935605906</v>
+        <v>740.7574552527669</v>
       </c>
       <c r="D470" t="n">
-        <v>731.4675455067643</v>
+        <v>731.4676064252583</v>
       </c>
       <c r="E470" t="n">
-        <v>737.6607579794724</v>
+        <v>737.660819413753</v>
       </c>
       <c r="F470" t="n">
         <v>127497</v>
@@ -9832,16 +9832,16 @@
         <v>43644</v>
       </c>
       <c r="B471" t="n">
-        <v>726.2327880859375</v>
+        <v>726.2327270507812</v>
       </c>
       <c r="C471" t="n">
-        <v>740.2413339657089</v>
+        <v>740.2412717532253</v>
       </c>
       <c r="D471" t="n">
-        <v>724.6844995227684</v>
+        <v>724.6844386177359</v>
       </c>
       <c r="E471" t="n">
-        <v>737.2921849456095</v>
+        <v>737.2921229809828</v>
       </c>
       <c r="F471" t="n">
         <v>201679</v>
@@ -9952,16 +9952,16 @@
         <v>43654</v>
       </c>
       <c r="B477" t="n">
-        <v>700.427490234375</v>
+        <v>700.4275512695312</v>
       </c>
       <c r="C477" t="n">
-        <v>718.4174141394944</v>
+        <v>718.4174767422902</v>
       </c>
       <c r="D477" t="n">
-        <v>689.3680949094711</v>
+        <v>689.3681549809131</v>
       </c>
       <c r="E477" t="n">
-        <v>715.5419795715528</v>
+        <v>715.5420419237837</v>
       </c>
       <c r="F477" t="n">
         <v>449084</v>
@@ -10012,16 +10012,16 @@
         <v>43658</v>
       </c>
       <c r="B480" t="n">
-        <v>693.2758178710938</v>
+        <v>693.27587890625</v>
       </c>
       <c r="C480" t="n">
-        <v>719.6708468333378</v>
+        <v>719.6709101922801</v>
       </c>
       <c r="D480" t="n">
-        <v>693.2758178710938</v>
+        <v>693.27587890625</v>
       </c>
       <c r="E480" t="n">
-        <v>713.3301474536453</v>
+        <v>713.3302102543602</v>
       </c>
       <c r="F480" t="n">
         <v>217604</v>
@@ -10052,16 +10052,16 @@
         <v>43662</v>
       </c>
       <c r="B482" t="n">
-        <v>683.6910400390625</v>
+        <v>683.6909790039062</v>
       </c>
       <c r="C482" t="n">
-        <v>700.132678006064</v>
+        <v>700.1326155031132</v>
       </c>
       <c r="D482" t="n">
-        <v>678.308799018167</v>
+        <v>678.3087384634996</v>
       </c>
       <c r="E482" t="n">
-        <v>683.9122408896819</v>
+        <v>683.9121798347784</v>
       </c>
       <c r="F482" t="n">
         <v>150151</v>
@@ -10072,16 +10072,16 @@
         <v>43663</v>
       </c>
       <c r="B483" t="n">
-        <v>673.8849487304688</v>
+        <v>673.8850708007812</v>
       </c>
       <c r="C483" t="n">
-        <v>692.0960726987868</v>
+        <v>692.0961980679377</v>
       </c>
       <c r="D483" t="n">
-        <v>668.0603071036488</v>
+        <v>668.0604281188615</v>
       </c>
       <c r="E483" t="n">
-        <v>689.0731514808654</v>
+        <v>689.0732763024319</v>
       </c>
       <c r="F483" t="n">
         <v>281209</v>
@@ -10092,16 +10092,16 @@
         <v>43664</v>
       </c>
       <c r="B484" t="n">
-        <v>663.56298828125</v>
+        <v>663.5629272460938</v>
       </c>
       <c r="C484" t="n">
-        <v>680.0045673894458</v>
+        <v>680.0045048419775</v>
       </c>
       <c r="D484" t="n">
-        <v>655.3053123559175</v>
+        <v>655.3052520803102</v>
       </c>
       <c r="E484" t="n">
-        <v>677.2028464825331</v>
+        <v>677.2027841927697</v>
       </c>
       <c r="F484" t="n">
         <v>395208</v>
@@ -10112,16 +10112,16 @@
         <v>43665</v>
       </c>
       <c r="B485" t="n">
-        <v>653.2408447265625</v>
+        <v>653.2407836914062</v>
       </c>
       <c r="C485" t="n">
-        <v>670.0511113593367</v>
+        <v>670.0510487535236</v>
       </c>
       <c r="D485" t="n">
-        <v>647.2687740008586</v>
+        <v>647.268713523699</v>
       </c>
       <c r="E485" t="n">
-        <v>652.134957871757</v>
+        <v>652.1348969399286</v>
       </c>
       <c r="F485" t="n">
         <v>752622</v>
@@ -10132,16 +10132,16 @@
         <v>43668</v>
       </c>
       <c r="B486" t="n">
-        <v>680.1519775390625</v>
+        <v>680.152099609375</v>
       </c>
       <c r="C486" t="n">
-        <v>686.0502748999594</v>
+        <v>686.050398028869</v>
       </c>
       <c r="D486" t="n">
-        <v>658.9179309712559</v>
+        <v>658.9180492305868</v>
       </c>
       <c r="E486" t="n">
-        <v>659.8764483095462</v>
+        <v>659.8765667409069</v>
       </c>
       <c r="F486" t="n">
         <v>819918</v>
@@ -10232,16 +10232,16 @@
         <v>43675</v>
       </c>
       <c r="B491" t="n">
-        <v>698.3632202148438</v>
+        <v>698.3631591796875</v>
       </c>
       <c r="C491" t="n">
-        <v>703.0081448405929</v>
+        <v>703.0080833994821</v>
       </c>
       <c r="D491" t="n">
-        <v>697.1097877975775</v>
+        <v>697.109726871968</v>
       </c>
       <c r="E491" t="n">
-        <v>700.4276246385616</v>
+        <v>700.4275634229816</v>
       </c>
       <c r="F491" t="n">
         <v>471177</v>
@@ -10252,16 +10252,16 @@
         <v>43676</v>
       </c>
       <c r="B492" t="n">
-        <v>690.62158203125</v>
+        <v>690.6215209960938</v>
       </c>
       <c r="C492" t="n">
-        <v>701.1648634116639</v>
+        <v>701.1648014447226</v>
       </c>
       <c r="D492" t="n">
-        <v>686.2715724421442</v>
+        <v>686.2715117914294</v>
       </c>
       <c r="E492" t="n">
-        <v>700.4276054824103</v>
+        <v>700.4275435806258</v>
       </c>
       <c r="F492" t="n">
         <v>254421</v>
@@ -10272,16 +10272,16 @@
         <v>43677</v>
       </c>
       <c r="B493" t="n">
-        <v>700.427490234375</v>
+        <v>700.4275512695312</v>
       </c>
       <c r="C493" t="n">
-        <v>700.427490234375</v>
+        <v>700.4275512695312</v>
       </c>
       <c r="D493" t="n">
-        <v>675.3595509737361</v>
+        <v>675.3596098244755</v>
       </c>
       <c r="E493" t="n">
-        <v>692.5384443384958</v>
+        <v>692.5385046862017</v>
       </c>
       <c r="F493" t="n">
         <v>490519</v>
@@ -10312,16 +10312,16 @@
         <v>43679</v>
       </c>
       <c r="B495" t="n">
-        <v>674.6222534179688</v>
+        <v>674.6223754882812</v>
       </c>
       <c r="C495" t="n">
-        <v>684.1333606616155</v>
+        <v>684.1334844529263</v>
       </c>
       <c r="D495" t="n">
-        <v>657.3696455259094</v>
+        <v>657.3697644744285</v>
       </c>
       <c r="E495" t="n">
-        <v>679.7095789316354</v>
+        <v>679.7097019224799</v>
       </c>
       <c r="F495" t="n">
         <v>683082</v>
@@ -10332,16 +10332,16 @@
         <v>43682</v>
       </c>
       <c r="B496" t="n">
-        <v>675.580810546875</v>
+        <v>675.5808715820312</v>
       </c>
       <c r="C496" t="n">
-        <v>678.3825313155912</v>
+        <v>678.3825926038681</v>
       </c>
       <c r="D496" t="n">
-        <v>662.0883224274567</v>
+        <v>662.0883822436379</v>
       </c>
       <c r="E496" t="n">
-        <v>667.9129648023204</v>
+        <v>667.9130251447273</v>
       </c>
       <c r="F496" t="n">
         <v>339376</v>
@@ -10372,16 +10372,16 @@
         <v>43684</v>
       </c>
       <c r="B498" t="n">
-        <v>729.7717895507812</v>
+        <v>729.7718505859375</v>
       </c>
       <c r="C498" t="n">
-        <v>736.5548319619454</v>
+        <v>736.554893564408</v>
       </c>
       <c r="D498" t="n">
-        <v>706.6207654732358</v>
+        <v>706.6208245721342</v>
       </c>
       <c r="E498" t="n">
-        <v>710.0123160235828</v>
+        <v>710.0123754061368</v>
       </c>
       <c r="F498" t="n">
         <v>500391</v>
@@ -10392,16 +10392,16 @@
         <v>43685</v>
       </c>
       <c r="B499" t="n">
-        <v>714.0674438476562</v>
+        <v>714.0675048828125</v>
       </c>
       <c r="C499" t="n">
-        <v>736.9234935403364</v>
+        <v>736.9235565291212</v>
       </c>
       <c r="D499" t="n">
-        <v>705.0724520643291</v>
+        <v>705.0725123306354</v>
       </c>
       <c r="E499" t="n">
-        <v>731.3937662343475</v>
+        <v>731.393828750477</v>
       </c>
       <c r="F499" t="n">
         <v>426052</v>
@@ -10412,16 +10412,16 @@
         <v>43686</v>
       </c>
       <c r="B500" t="n">
-        <v>735.080322265625</v>
+        <v>735.0802612304688</v>
       </c>
       <c r="C500" t="n">
-        <v>741.6422231062829</v>
+        <v>741.6421615262792</v>
       </c>
       <c r="D500" t="n">
-        <v>708.980205704469</v>
+        <v>708.9801468364564</v>
       </c>
       <c r="E500" t="n">
-        <v>712.5928987214315</v>
+        <v>712.5928395534499</v>
       </c>
       <c r="F500" t="n">
         <v>340941</v>
@@ -10432,16 +10432,16 @@
         <v>43689</v>
       </c>
       <c r="B501" t="n">
-        <v>724.2421264648438</v>
+        <v>724.2420654296875</v>
       </c>
       <c r="C501" t="n">
-        <v>733.2371193661494</v>
+        <v>733.2370575729444</v>
       </c>
       <c r="D501" t="n">
-        <v>713.330215969436</v>
+        <v>713.3301558538758</v>
       </c>
       <c r="E501" t="n">
-        <v>733.2371193661494</v>
+        <v>733.2370575729444</v>
       </c>
       <c r="F501" t="n">
         <v>223681</v>
@@ -10452,16 +10452,16 @@
         <v>43690</v>
       </c>
       <c r="B502" t="n">
-        <v>741.4947509765625</v>
+        <v>741.4946899414062</v>
       </c>
       <c r="C502" t="n">
-        <v>741.4947509765625</v>
+        <v>741.4946899414062</v>
       </c>
       <c r="D502" t="n">
-        <v>720.7768181427558</v>
+        <v>720.7767588129688</v>
       </c>
       <c r="E502" t="n">
-        <v>724.2420828420674</v>
+        <v>724.2420232270416</v>
       </c>
       <c r="F502" t="n">
         <v>313736</v>
@@ -10492,16 +10492,16 @@
         <v>43692</v>
       </c>
       <c r="B504" t="n">
-        <v>734.1954956054688</v>
+        <v>734.195556640625</v>
       </c>
       <c r="C504" t="n">
-        <v>755.2083422380151</v>
+        <v>755.2084050200119</v>
       </c>
       <c r="D504" t="n">
-        <v>722.9886714565573</v>
+        <v>722.9887315600677</v>
       </c>
       <c r="E504" t="n">
-        <v>739.5040221441786</v>
+        <v>739.5040836206434</v>
       </c>
       <c r="F504" t="n">
         <v>297485</v>
@@ -10512,16 +10512,16 @@
         <v>43693</v>
       </c>
       <c r="B505" t="n">
-        <v>751.1532592773438</v>
+        <v>751.1533203125</v>
       </c>
       <c r="C505" t="n">
-        <v>754.249836224596</v>
+        <v>754.2498975113654</v>
       </c>
       <c r="D505" t="n">
-        <v>732.794646292752</v>
+        <v>732.7947058361743</v>
       </c>
       <c r="E505" t="n">
-        <v>737.2921423054473</v>
+        <v>737.2922022143149</v>
       </c>
       <c r="F505" t="n">
         <v>284065</v>
@@ -10572,16 +10572,16 @@
         <v>43698</v>
       </c>
       <c r="B508" t="n">
-        <v>752.9227905273438</v>
+        <v>752.9226684570312</v>
       </c>
       <c r="C508" t="n">
-        <v>754.5447931401769</v>
+        <v>754.5446708068914</v>
       </c>
       <c r="D508" t="n">
-        <v>739.6515025861009</v>
+        <v>739.6513826674437</v>
       </c>
       <c r="E508" t="n">
-        <v>749.8998687710316</v>
+        <v>749.8997471908211</v>
       </c>
       <c r="F508" t="n">
         <v>157546</v>
@@ -10592,16 +10592,16 @@
         <v>43699</v>
       </c>
       <c r="B509" t="n">
-        <v>743.1904907226562</v>
+        <v>743.1905517578125</v>
       </c>
       <c r="C509" t="n">
-        <v>754.5447430163649</v>
+        <v>754.5448049839988</v>
       </c>
       <c r="D509" t="n">
-        <v>735.9649880844896</v>
+        <v>735.9650485262451</v>
       </c>
       <c r="E509" t="n">
-        <v>750.710849553085</v>
+        <v>750.7109112058572</v>
       </c>
       <c r="F509" t="n">
         <v>188833</v>
@@ -10612,16 +10612,16 @@
         <v>43700</v>
       </c>
       <c r="B510" t="n">
-        <v>740.9785766601562</v>
+        <v>740.9786376953125</v>
       </c>
       <c r="C510" t="n">
-        <v>751.9641996814681</v>
+        <v>751.9642616215212</v>
       </c>
       <c r="D510" t="n">
-        <v>729.6979800767225</v>
+        <v>729.6980401826845</v>
       </c>
       <c r="E510" t="n">
-        <v>741.2734915327513</v>
+        <v>741.2735525922</v>
       </c>
       <c r="F510" t="n">
         <v>182025</v>
@@ -10632,16 +10632,16 @@
         <v>43703</v>
       </c>
       <c r="B511" t="n">
-        <v>726.2327880859375</v>
+        <v>726.2327270507812</v>
       </c>
       <c r="C511" t="n">
-        <v>745.9922038996692</v>
+        <v>745.9921412038623</v>
       </c>
       <c r="D511" t="n">
-        <v>723.7259820740866</v>
+        <v>723.7259212496111</v>
       </c>
       <c r="E511" t="n">
-        <v>742.3057969693112</v>
+        <v>742.3057345833229</v>
       </c>
       <c r="F511" t="n">
         <v>116946</v>
@@ -10652,16 +10652,16 @@
         <v>43704</v>
       </c>
       <c r="B512" t="n">
-        <v>738.7667846679688</v>
+        <v>738.7666625976562</v>
       </c>
       <c r="C512" t="n">
-        <v>738.7667846679688</v>
+        <v>738.7666625976562</v>
       </c>
       <c r="D512" t="n">
-        <v>710.3810629845611</v>
+        <v>710.3809456045705</v>
       </c>
       <c r="E512" t="n">
-        <v>722.6938339255971</v>
+        <v>722.6937145111026</v>
       </c>
       <c r="F512" t="n">
         <v>286491</v>
@@ -10712,16 +10712,16 @@
         <v>43707</v>
       </c>
       <c r="B515" t="n">
-        <v>799.9619750976562</v>
+        <v>799.9620361328125</v>
       </c>
       <c r="C515" t="n">
-        <v>799.9619750976562</v>
+        <v>799.9620361328125</v>
       </c>
       <c r="D515" t="n">
-        <v>762.3600641235378</v>
+        <v>762.3601222897596</v>
       </c>
       <c r="E515" t="n">
-        <v>766.0465294360706</v>
+        <v>766.0465878835608</v>
       </c>
       <c r="F515" t="n">
         <v>691612</v>
@@ -10772,16 +10772,16 @@
         <v>43712</v>
       </c>
       <c r="B518" t="n">
-        <v>763.0973510742188</v>
+        <v>763.0972900390625</v>
       </c>
       <c r="C518" t="n">
-        <v>776.9584682207006</v>
+        <v>776.9584060768844</v>
       </c>
       <c r="D518" t="n">
-        <v>760.0744881377487</v>
+        <v>760.0744273443714</v>
       </c>
       <c r="E518" t="n">
-        <v>770.4702819804626</v>
+        <v>770.4702203555938</v>
       </c>
       <c r="F518" t="n">
         <v>189694</v>
@@ -10792,16 +10792,16 @@
         <v>43713</v>
       </c>
       <c r="B519" t="n">
-        <v>754.5447387695312</v>
+        <v>754.5448608398438</v>
       </c>
       <c r="C519" t="n">
-        <v>772.0186068134889</v>
+        <v>772.0187317107252</v>
       </c>
       <c r="D519" t="n">
-        <v>753.1439371060559</v>
+        <v>753.1440589497465</v>
       </c>
       <c r="E519" t="n">
-        <v>769.1431720598307</v>
+        <v>769.143296491879</v>
       </c>
       <c r="F519" t="n">
         <v>227216</v>
@@ -10852,16 +10852,16 @@
         <v>43718</v>
       </c>
       <c r="B522" t="n">
-        <v>765.3092041015625</v>
+        <v>765.3092651367188</v>
       </c>
       <c r="C522" t="n">
-        <v>771.6499032380112</v>
+        <v>771.6499647788528</v>
       </c>
       <c r="D522" t="n">
-        <v>755.0608388670462</v>
+        <v>755.0608990848718</v>
       </c>
       <c r="E522" t="n">
-        <v>761.6227388314006</v>
+        <v>761.6227995725528</v>
       </c>
       <c r="F522" t="n">
         <v>185012</v>
@@ -10872,16 +10872,16 @@
         <v>43719</v>
       </c>
       <c r="B523" t="n">
-        <v>778.94921875</v>
+        <v>778.9491577148438</v>
       </c>
       <c r="C523" t="n">
-        <v>782.0458546657337</v>
+        <v>782.0457933879381</v>
       </c>
       <c r="D523" t="n">
-        <v>767.5211925666582</v>
+        <v>767.5211324269536</v>
       </c>
       <c r="E523" t="n">
-        <v>767.5211925666582</v>
+        <v>767.5211324269536</v>
       </c>
       <c r="F523" t="n">
         <v>193476</v>
@@ -10932,16 +10932,16 @@
         <v>43724</v>
       </c>
       <c r="B526" t="n">
-        <v>788.9027099609375</v>
+        <v>788.9026489257812</v>
       </c>
       <c r="C526" t="n">
-        <v>788.9027099609375</v>
+        <v>788.9026489257812</v>
       </c>
       <c r="D526" t="n">
-        <v>750.6372488405499</v>
+        <v>750.6371907658834</v>
       </c>
       <c r="E526" t="n">
-        <v>760.1482992314815</v>
+        <v>760.1482404209721</v>
       </c>
       <c r="F526" t="n">
         <v>255829</v>
@@ -10952,16 +10952,16 @@
         <v>43725</v>
       </c>
       <c r="B527" t="n">
-        <v>831.1494750976562</v>
+        <v>831.1493530273438</v>
       </c>
       <c r="C527" t="n">
-        <v>832.8452504396112</v>
+        <v>832.8451281202413</v>
       </c>
       <c r="D527" t="n">
-        <v>775.4839210912661</v>
+        <v>775.4838071965127</v>
       </c>
       <c r="E527" t="n">
-        <v>781.5297058666796</v>
+        <v>781.5295910839861</v>
       </c>
       <c r="F527" t="n">
         <v>516981</v>
@@ -10972,16 +10972,16 @@
         <v>43726</v>
       </c>
       <c r="B528" t="n">
-        <v>822.0806884765625</v>
+        <v>822.0807495117188</v>
       </c>
       <c r="C528" t="n">
-        <v>831.0756800554901</v>
+        <v>831.075741758477</v>
       </c>
       <c r="D528" t="n">
-        <v>813.3068977227535</v>
+        <v>813.3069581065021</v>
       </c>
       <c r="E528" t="n">
-        <v>822.0806884765625</v>
+        <v>822.0807495117188</v>
       </c>
       <c r="F528" t="n">
         <v>309810</v>
@@ -10992,16 +10992,16 @@
         <v>43727</v>
       </c>
       <c r="B529" t="n">
-        <v>826.7993774414062</v>
+        <v>826.7994384765625</v>
       </c>
       <c r="C529" t="n">
-        <v>831.9604169689483</v>
+        <v>831.9604783850976</v>
       </c>
       <c r="D529" t="n">
-        <v>819.1315321946086</v>
+        <v>819.1315926637169</v>
       </c>
       <c r="E529" t="n">
-        <v>822.1543949149977</v>
+        <v>822.1544556072568</v>
       </c>
       <c r="F529" t="n">
         <v>114064</v>
@@ -11012,16 +11012,16 @@
         <v>43728</v>
       </c>
       <c r="B530" t="n">
-        <v>819.9425659179688</v>
+        <v>819.942626953125</v>
       </c>
       <c r="C530" t="n">
-        <v>843.3147306606849</v>
+        <v>843.3147934356261</v>
       </c>
       <c r="D530" t="n">
-        <v>818.7628477535394</v>
+        <v>818.7629087008795</v>
       </c>
       <c r="E530" t="n">
-        <v>833.1400796553557</v>
+        <v>833.1401416729129</v>
       </c>
       <c r="F530" t="n">
         <v>328551</v>
@@ -11032,16 +11032,16 @@
         <v>43731</v>
       </c>
       <c r="B531" t="n">
-        <v>824.8823852539062</v>
+        <v>824.8824462890625</v>
       </c>
       <c r="C531" t="n">
-        <v>828.8637652328913</v>
+        <v>828.86382656264</v>
       </c>
       <c r="D531" t="n">
-        <v>816.3297955723476</v>
+        <v>816.3298559746759</v>
       </c>
       <c r="E531" t="n">
-        <v>824.2925555303177</v>
+        <v>824.292616521831</v>
       </c>
       <c r="F531" t="n">
         <v>128162</v>
@@ -11052,16 +11052,16 @@
         <v>43732</v>
       </c>
       <c r="B532" t="n">
-        <v>813.9705200195312</v>
+        <v>813.970458984375</v>
       </c>
       <c r="C532" t="n">
-        <v>830.5595845854463</v>
+        <v>830.5595223063677</v>
       </c>
       <c r="D532" t="n">
-        <v>808.8831943655513</v>
+        <v>808.8831337118655</v>
       </c>
       <c r="E532" t="n">
-        <v>828.7900953204605</v>
+        <v>828.7900331740661</v>
       </c>
       <c r="F532" t="n">
         <v>236567</v>
@@ -11072,16 +11072,16 @@
         <v>43733</v>
       </c>
       <c r="B533" t="n">
-        <v>813.0120849609375</v>
+        <v>813.0120239257812</v>
       </c>
       <c r="C533" t="n">
-        <v>814.7078603506134</v>
+        <v>814.7077991881504</v>
       </c>
       <c r="D533" t="n">
-        <v>802.3213755521612</v>
+        <v>802.3213153195873</v>
       </c>
       <c r="E533" t="n">
-        <v>814.7078603506134</v>
+        <v>814.7077991881504</v>
       </c>
       <c r="F533" t="n">
         <v>211226</v>
@@ -11152,16 +11152,16 @@
         <v>43739</v>
       </c>
       <c r="B537" t="n">
-        <v>823.924072265625</v>
+        <v>823.9240112304688</v>
       </c>
       <c r="C537" t="n">
-        <v>840.513138880572</v>
+        <v>840.5130766165206</v>
       </c>
       <c r="D537" t="n">
-        <v>818.8367459832738</v>
+        <v>818.8366853249796</v>
       </c>
       <c r="E537" t="n">
-        <v>840.513138880572</v>
+        <v>840.5130766165206</v>
       </c>
       <c r="F537" t="n">
         <v>140869</v>
@@ -11172,16 +11172,16 @@
         <v>43740</v>
       </c>
       <c r="B538" t="n">
-        <v>810.4314575195312</v>
+        <v>810.4315795898438</v>
       </c>
       <c r="C538" t="n">
-        <v>827.2417223915742</v>
+        <v>827.2418469939136</v>
       </c>
       <c r="D538" t="n">
-        <v>805.3441320242448</v>
+        <v>805.3442533282847</v>
       </c>
       <c r="E538" t="n">
-        <v>820.6061085101043</v>
+        <v>820.6062321129618</v>
       </c>
       <c r="F538" t="n">
         <v>168666</v>
@@ -11192,16 +11192,16 @@
         <v>43741</v>
       </c>
       <c r="B539" t="n">
-        <v>787.4280395507812</v>
+        <v>787.4281005859375</v>
       </c>
       <c r="C539" t="n">
-        <v>812.201007727376</v>
+        <v>812.2010706827356</v>
       </c>
       <c r="D539" t="n">
-        <v>782.7830566643306</v>
+        <v>782.7831173394447</v>
       </c>
       <c r="E539" t="n">
-        <v>812.201007727376</v>
+        <v>812.2010706827356</v>
       </c>
       <c r="F539" t="n">
         <v>247000</v>
@@ -11252,16 +11252,16 @@
         <v>43746</v>
       </c>
       <c r="B542" t="n">
-        <v>784.773681640625</v>
+        <v>784.7737426757812</v>
       </c>
       <c r="C542" t="n">
-        <v>793.4000441761112</v>
+        <v>793.4001058821761</v>
       </c>
       <c r="D542" t="n">
-        <v>770.8389102077002</v>
+        <v>770.8389701590906</v>
       </c>
       <c r="E542" t="n">
-        <v>782.5618494908194</v>
+        <v>782.5619103539522</v>
       </c>
       <c r="F542" t="n">
         <v>161376</v>
@@ -11272,16 +11272,16 @@
         <v>43747</v>
       </c>
       <c r="B543" t="n">
-        <v>795.1696166992188</v>
+        <v>795.169677734375</v>
       </c>
       <c r="C543" t="n">
-        <v>795.1696166992188</v>
+        <v>795.169677734375</v>
       </c>
       <c r="D543" t="n">
-        <v>777.4746055093244</v>
+        <v>777.4746651862575</v>
       </c>
       <c r="E543" t="n">
-        <v>789.6398890214194</v>
+        <v>789.6399496321282</v>
       </c>
       <c r="F543" t="n">
         <v>80085</v>
@@ -11292,16 +11292,16 @@
         <v>43748</v>
       </c>
       <c r="B544" t="n">
-        <v>792.5152587890625</v>
+        <v>792.5153198242188</v>
       </c>
       <c r="C544" t="n">
-        <v>808.8831809423796</v>
+        <v>808.8832432381029</v>
       </c>
       <c r="D544" t="n">
-        <v>783.8889547482621</v>
+        <v>783.8890151190678</v>
       </c>
       <c r="E544" t="n">
-        <v>798.9297306300995</v>
+        <v>798.9297921592629</v>
       </c>
       <c r="F544" t="n">
         <v>229776</v>
@@ -11332,16 +11332,16 @@
         <v>43752</v>
       </c>
       <c r="B546" t="n">
-        <v>815.2976684570312</v>
+        <v>815.297607421875</v>
       </c>
       <c r="C546" t="n">
-        <v>815.2976684570312</v>
+        <v>815.297607421875</v>
       </c>
       <c r="D546" t="n">
-        <v>796.0543685577967</v>
+        <v>796.0543089632404</v>
       </c>
       <c r="E546" t="n">
-        <v>804.2383303809128</v>
+        <v>804.2382701736852</v>
       </c>
       <c r="F546" t="n">
         <v>85333</v>
@@ -11372,16 +11372,16 @@
         <v>43754</v>
       </c>
       <c r="B548" t="n">
-        <v>813.9705200195312</v>
+        <v>813.970458984375</v>
       </c>
       <c r="C548" t="n">
-        <v>817.951900210513</v>
+        <v>817.9518388768151</v>
       </c>
       <c r="D548" t="n">
-        <v>806.4501026090501</v>
+        <v>806.4500421378084</v>
       </c>
       <c r="E548" t="n">
-        <v>816.1823522559995</v>
+        <v>816.1822910549902</v>
       </c>
       <c r="F548" t="n">
         <v>165832</v>
@@ -11392,16 +11392,16 @@
         <v>43755</v>
       </c>
       <c r="B549" t="n">
-        <v>828.7901611328125</v>
+        <v>828.7901000976562</v>
       </c>
       <c r="C549" t="n">
-        <v>829.2325041394204</v>
+        <v>829.2324430716884</v>
       </c>
       <c r="D549" t="n">
-        <v>810.4315471545677</v>
+        <v>810.4314874714074</v>
       </c>
       <c r="E549" t="n">
-        <v>815.7400740605909</v>
+        <v>815.7400139864911</v>
       </c>
       <c r="F549" t="n">
         <v>123950</v>
@@ -11412,16 +11412,16 @@
         <v>43756</v>
       </c>
       <c r="B550" t="n">
-        <v>824.1452026367188</v>
+        <v>824.1450805664062</v>
       </c>
       <c r="C550" t="n">
-        <v>832.1079638882363</v>
+        <v>832.1078406384996</v>
       </c>
       <c r="D550" t="n">
-        <v>821.7121693040519</v>
+        <v>821.7120475941142</v>
       </c>
       <c r="E550" t="n">
-        <v>823.7028596169313</v>
+        <v>823.7027376121375</v>
       </c>
       <c r="F550" t="n">
         <v>77690</v>
@@ -11432,16 +11432,16 @@
         <v>43759</v>
       </c>
       <c r="B551" t="n">
-        <v>854.8902587890625</v>
+        <v>854.8901977539062</v>
       </c>
       <c r="C551" t="n">
-        <v>854.8902587890625</v>
+        <v>854.8901977539062</v>
       </c>
       <c r="D551" t="n">
-        <v>812.8646221805811</v>
+        <v>812.8645641458583</v>
       </c>
       <c r="E551" t="n">
-        <v>824.1451609229144</v>
+        <v>824.145102082814</v>
       </c>
       <c r="F551" t="n">
         <v>154924</v>
@@ -11452,16 +11452,16 @@
         <v>43760</v>
       </c>
       <c r="B552" t="n">
-        <v>867.0556030273438</v>
+        <v>867.0555419921875</v>
       </c>
       <c r="C552" t="n">
-        <v>867.0556030273438</v>
+        <v>867.0555419921875</v>
       </c>
       <c r="D552" t="n">
-        <v>846.0427553269092</v>
+        <v>846.0426957709227</v>
       </c>
       <c r="E552" t="n">
-        <v>854.0055161948831</v>
+        <v>854.0054560783693</v>
       </c>
       <c r="F552" t="n">
         <v>268545</v>
@@ -11492,16 +11492,16 @@
         <v>43762</v>
       </c>
       <c r="B554" t="n">
-        <v>860.4199829101562</v>
+        <v>860.4198608398438</v>
       </c>
       <c r="C554" t="n">
-        <v>875.2395600295914</v>
+        <v>875.2394358567818</v>
       </c>
       <c r="D554" t="n">
-        <v>855.7750583472094</v>
+        <v>855.774936935886</v>
       </c>
       <c r="E554" t="n">
-        <v>863.7378197062811</v>
+        <v>863.7376971652574</v>
       </c>
       <c r="F554" t="n">
         <v>162584</v>
@@ -11532,16 +11532,16 @@
         <v>43766</v>
       </c>
       <c r="B556" t="n">
-        <v>854.6690673828125</v>
+        <v>854.6689453125</v>
       </c>
       <c r="C556" t="n">
-        <v>862.1894853169393</v>
+        <v>862.1893621725038</v>
       </c>
       <c r="D556" t="n">
-        <v>834.9833658876955</v>
+        <v>834.9832466290442</v>
       </c>
       <c r="E556" t="n">
-        <v>860.1987950828369</v>
+        <v>860.1986722227269</v>
       </c>
       <c r="F556" t="n">
         <v>116033</v>
@@ -11592,16 +11592,16 @@
         <v>43769</v>
       </c>
       <c r="B559" t="n">
-        <v>835.8681030273438</v>
+        <v>835.8680419921875</v>
       </c>
       <c r="C559" t="n">
-        <v>840.2918851473819</v>
+        <v>840.2918237892007</v>
       </c>
       <c r="D559" t="n">
-        <v>820.3849829862731</v>
+        <v>820.3849230816957</v>
       </c>
       <c r="E559" t="n">
-        <v>827.6842000085235</v>
+        <v>827.6841395709565</v>
       </c>
       <c r="F559" t="n">
         <v>215786</v>
@@ -11612,16 +11612,16 @@
         <v>43770</v>
       </c>
       <c r="B560" t="n">
-        <v>848.2545776367188</v>
+        <v>848.2546997070312</v>
       </c>
       <c r="C560" t="n">
-        <v>858.8715717036641</v>
+        <v>858.8716953018431</v>
       </c>
       <c r="D560" t="n">
-        <v>836.3104373028327</v>
+        <v>836.3105576542922</v>
       </c>
       <c r="E560" t="n">
-        <v>840.513018240206</v>
+        <v>840.5131391964489</v>
       </c>
       <c r="F560" t="n">
         <v>349209</v>
@@ -11632,16 +11632,16 @@
         <v>43773</v>
       </c>
       <c r="B561" t="n">
-        <v>854.6690673828125</v>
+        <v>854.6689453125</v>
       </c>
       <c r="C561" t="n">
-        <v>861.7470836251247</v>
+        <v>861.7469605438763</v>
       </c>
       <c r="D561" t="n">
-        <v>842.9461268241052</v>
+        <v>842.946006428152</v>
       </c>
       <c r="E561" t="n">
-        <v>855.9962137687247</v>
+        <v>855.9960915088592</v>
       </c>
       <c r="F561" t="n">
         <v>124324</v>
@@ -11712,16 +11712,16 @@
         <v>43777</v>
       </c>
       <c r="B565" t="n">
-        <v>776.3685913085938</v>
+        <v>776.36865234375</v>
       </c>
       <c r="C565" t="n">
-        <v>807.7772304582729</v>
+        <v>807.7772939626574</v>
       </c>
       <c r="D565" t="n">
-        <v>771.9448095576114</v>
+        <v>771.9448702449868</v>
       </c>
       <c r="E565" t="n">
-        <v>807.1136866714362</v>
+        <v>807.1137501236553</v>
       </c>
       <c r="F565" t="n">
         <v>568905</v>
@@ -11732,16 +11732,16 @@
         <v>43780</v>
       </c>
       <c r="B566" t="n">
-        <v>806.2290649414062</v>
+        <v>806.22900390625</v>
       </c>
       <c r="C566" t="n">
-        <v>809.5468430707991</v>
+        <v>809.5467817844722</v>
       </c>
       <c r="D566" t="n">
-        <v>765.309312266098</v>
+        <v>765.3092543287505</v>
       </c>
       <c r="E566" t="n">
-        <v>774.1568184270383</v>
+        <v>774.1567598198949</v>
       </c>
       <c r="F566" t="n">
         <v>251817</v>
@@ -11752,16 +11752,16 @@
         <v>43781</v>
       </c>
       <c r="B567" t="n">
-        <v>808.88330078125</v>
+        <v>808.8831787109375</v>
       </c>
       <c r="C567" t="n">
-        <v>813.5282253853001</v>
+        <v>813.5281026140121</v>
       </c>
       <c r="D567" t="n">
-        <v>792.515376202968</v>
+        <v>792.5152566027742</v>
       </c>
       <c r="E567" t="n">
-        <v>808.4408990620377</v>
+        <v>808.4407770584892</v>
       </c>
       <c r="F567" t="n">
         <v>229237</v>
@@ -11792,16 +11792,16 @@
         <v>43783</v>
       </c>
       <c r="B569" t="n">
-        <v>828.3477172851562</v>
+        <v>828.34765625</v>
       </c>
       <c r="C569" t="n">
-        <v>828.3477172851562</v>
+        <v>828.34765625</v>
       </c>
       <c r="D569" t="n">
-        <v>803.13234781611</v>
+        <v>803.1322886388982</v>
       </c>
       <c r="E569" t="n">
-        <v>808.2196736151881</v>
+        <v>808.2196140631266</v>
       </c>
       <c r="F569" t="n">
         <v>179860</v>
@@ -11812,16 +11812,16 @@
         <v>43787</v>
       </c>
       <c r="B570" t="n">
-        <v>805.78662109375</v>
+        <v>805.7865600585938</v>
       </c>
       <c r="C570" t="n">
-        <v>832.7715398840436</v>
+        <v>832.7714768048862</v>
       </c>
       <c r="D570" t="n">
-        <v>805.5654202461462</v>
+        <v>805.565359227745</v>
       </c>
       <c r="E570" t="n">
-        <v>829.6749040861871</v>
+        <v>829.6748412415876</v>
       </c>
       <c r="F570" t="n">
         <v>210918</v>
@@ -11852,16 +11852,16 @@
         <v>43790</v>
       </c>
       <c r="B572" t="n">
-        <v>835.0010986328125</v>
+        <v>835.0011596679688</v>
       </c>
       <c r="C572" t="n">
-        <v>841.8982549719789</v>
+        <v>841.898316511289</v>
       </c>
       <c r="D572" t="n">
-        <v>804.9651256898997</v>
+        <v>804.9651845295494</v>
       </c>
       <c r="E572" t="n">
-        <v>814.5321318599239</v>
+        <v>814.5321913988827</v>
       </c>
       <c r="F572" t="n">
         <v>256564</v>
@@ -11912,16 +11912,16 @@
         <v>43795</v>
       </c>
       <c r="B575" t="n">
-        <v>821.4293212890625</v>
+        <v>821.4292602539062</v>
       </c>
       <c r="C575" t="n">
-        <v>829.8838756114353</v>
+        <v>829.8838139480753</v>
       </c>
       <c r="D575" t="n">
-        <v>807.8575103086214</v>
+        <v>807.8574502818997</v>
       </c>
       <c r="E575" t="n">
-        <v>823.6542257551486</v>
+        <v>823.654164554674</v>
       </c>
       <c r="F575" t="n">
         <v>294042</v>
@@ -11932,16 +11932,16 @@
         <v>43796</v>
       </c>
       <c r="B576" t="n">
-        <v>823.6541748046875</v>
+        <v>823.6542358398438</v>
       </c>
       <c r="C576" t="n">
-        <v>825.211572413714</v>
+        <v>825.2116335642778</v>
       </c>
       <c r="D576" t="n">
-        <v>800.9603041449742</v>
+        <v>800.9603634984489</v>
       </c>
       <c r="E576" t="n">
-        <v>817.6469685387498</v>
+        <v>817.6470291287546</v>
       </c>
       <c r="F576" t="n">
         <v>228902</v>
@@ -11992,16 +11992,16 @@
         <v>43801</v>
       </c>
       <c r="B579" t="n">
-        <v>827.6589965820312</v>
+        <v>827.6590576171875</v>
       </c>
       <c r="C579" t="n">
-        <v>838.3384549369663</v>
+        <v>838.3385167596721</v>
       </c>
       <c r="D579" t="n">
-        <v>823.6541923195779</v>
+        <v>823.6542530594025</v>
       </c>
       <c r="E579" t="n">
-        <v>828.3264442808328</v>
+        <v>828.3265053652095</v>
       </c>
       <c r="F579" t="n">
         <v>162406</v>
@@ -12012,16 +12012,16 @@
         <v>43802</v>
       </c>
       <c r="B580" t="n">
-        <v>828.1039428710938</v>
+        <v>828.1038818359375</v>
       </c>
       <c r="C580" t="n">
-        <v>835.4461037046005</v>
+        <v>835.4460421282926</v>
       </c>
       <c r="D580" t="n">
-        <v>820.9842842823524</v>
+        <v>820.9842237719485</v>
       </c>
       <c r="E580" t="n">
-        <v>828.9938928153337</v>
+        <v>828.9938317145838</v>
       </c>
       <c r="F580" t="n">
         <v>140261</v>
@@ -12052,16 +12052,16 @@
         <v>43804</v>
       </c>
       <c r="B582" t="n">
-        <v>827.6589965820312</v>
+        <v>827.6590576171875</v>
       </c>
       <c r="C582" t="n">
-        <v>827.8814397917504</v>
+        <v>827.8815008433105</v>
       </c>
       <c r="D582" t="n">
-        <v>808.9699297021895</v>
+        <v>808.969989359133</v>
       </c>
       <c r="E582" t="n">
-        <v>818.7594381137817</v>
+        <v>818.759498492646</v>
       </c>
       <c r="F582" t="n">
         <v>164740</v>
@@ -12072,16 +12072,16 @@
         <v>43805</v>
       </c>
       <c r="B583" t="n">
-        <v>824.7666015625</v>
+        <v>824.7666625976562</v>
       </c>
       <c r="C583" t="n">
-        <v>833.221155101445</v>
+        <v>833.2212167622632</v>
       </c>
       <c r="D583" t="n">
-        <v>820.9842407067104</v>
+        <v>820.9843014619607</v>
       </c>
       <c r="E583" t="n">
-        <v>823.2091449666292</v>
+        <v>823.209205886529</v>
       </c>
       <c r="F583" t="n">
         <v>143460</v>
@@ -12092,16 +12092,16 @@
         <v>43808</v>
       </c>
       <c r="B584" t="n">
-        <v>819.2044067382812</v>
+        <v>819.204345703125</v>
       </c>
       <c r="C584" t="n">
-        <v>826.546567772051</v>
+        <v>826.546506189864</v>
       </c>
       <c r="D584" t="n">
-        <v>815.6446068642255</v>
+        <v>815.6445460942936</v>
       </c>
       <c r="E584" t="n">
-        <v>825.2116133018682</v>
+        <v>825.2115518191425</v>
       </c>
       <c r="F584" t="n">
         <v>119759</v>
@@ -12112,16 +12112,16 @@
         <v>43809</v>
       </c>
       <c r="B585" t="n">
-        <v>819.8718872070312</v>
+        <v>819.8719482421875</v>
       </c>
       <c r="C585" t="n">
-        <v>825.6565913343355</v>
+        <v>825.6566528001326</v>
       </c>
       <c r="D585" t="n">
-        <v>812.3072241649378</v>
+        <v>812.3072846369446</v>
       </c>
       <c r="E585" t="n">
-        <v>816.5345306559764</v>
+        <v>816.5345914426839</v>
       </c>
       <c r="F585" t="n">
         <v>105717</v>
@@ -12132,16 +12132,16 @@
         <v>43810</v>
       </c>
       <c r="B586" t="n">
-        <v>817.4244995117188</v>
+        <v>817.4244384765625</v>
       </c>
       <c r="C586" t="n">
-        <v>824.0991537334627</v>
+        <v>824.0990921999258</v>
       </c>
       <c r="D586" t="n">
-        <v>812.5297452111301</v>
+        <v>812.5296845414535</v>
       </c>
       <c r="E586" t="n">
-        <v>821.6518061005801</v>
+        <v>821.6517447497808</v>
       </c>
       <c r="F586" t="n">
         <v>143517</v>
@@ -12152,16 +12152,16 @@
         <v>43811</v>
       </c>
       <c r="B587" t="n">
-        <v>835.2235717773438</v>
+        <v>835.2236328125</v>
       </c>
       <c r="C587" t="n">
-        <v>836.5585261636726</v>
+        <v>836.5585872963826</v>
       </c>
       <c r="D587" t="n">
-        <v>819.4268575175364</v>
+        <v>819.4269173983253</v>
       </c>
       <c r="E587" t="n">
-        <v>820.7618119038652</v>
+        <v>820.7618718822077</v>
       </c>
       <c r="F587" t="n">
         <v>149190</v>
@@ -12192,16 +12192,16 @@
         <v>43815</v>
       </c>
       <c r="B589" t="n">
-        <v>817.4244995117188</v>
+        <v>817.4244384765625</v>
       </c>
       <c r="C589" t="n">
-        <v>822.5417560611577</v>
+        <v>822.5416946439079</v>
       </c>
       <c r="D589" t="n">
-        <v>815.6445995905635</v>
+        <v>815.6445386883082</v>
       </c>
       <c r="E589" t="n">
-        <v>817.2019972628685</v>
+        <v>817.201936244326</v>
       </c>
       <c r="F589" t="n">
         <v>114381</v>
@@ -12212,16 +12212,16 @@
         <v>43816</v>
       </c>
       <c r="B590" t="n">
-        <v>828.1039428710938</v>
+        <v>828.1038818359375</v>
       </c>
       <c r="C590" t="n">
-        <v>829.8838427595736</v>
+        <v>829.8837815932303</v>
       </c>
       <c r="D590" t="n">
-        <v>819.2043843938726</v>
+        <v>819.2043240146558</v>
       </c>
       <c r="E590" t="n">
-        <v>819.6493888834036</v>
+        <v>819.6493284713878</v>
       </c>
       <c r="F590" t="n">
         <v>131975</v>
@@ -12432,16 +12432,16 @@
         <v>43837</v>
       </c>
       <c r="B601" t="n">
-        <v>878.1639404296875</v>
+        <v>878.1640014648438</v>
       </c>
       <c r="C601" t="n">
-        <v>879.7213379744908</v>
+        <v>879.7213991178911</v>
       </c>
       <c r="D601" t="n">
-        <v>864.592071813634</v>
+        <v>864.5921319055027</v>
       </c>
       <c r="E601" t="n">
-        <v>872.8241820685562</v>
+        <v>872.8242427325824</v>
       </c>
       <c r="F601" t="n">
         <v>133796</v>
@@ -12472,16 +12472,16 @@
         <v>43839</v>
       </c>
       <c r="B603" t="n">
-        <v>915.5420532226562</v>
+        <v>915.5421142578125</v>
       </c>
       <c r="C603" t="n">
-        <v>921.1042546664174</v>
+        <v>921.1043160723813</v>
       </c>
       <c r="D603" t="n">
-        <v>877.9414203336983</v>
+        <v>877.9414788621859</v>
       </c>
       <c r="E603" t="n">
-        <v>880.1663245251297</v>
+        <v>880.1663832019419</v>
       </c>
       <c r="F603" t="n">
         <v>555906</v>
@@ -12512,16 +12512,16 @@
         <v>43843</v>
       </c>
       <c r="B605" t="n">
-        <v>923.7742919921875</v>
+        <v>923.7743530273438</v>
       </c>
       <c r="C605" t="n">
-        <v>944.2432599141667</v>
+        <v>944.2433223017385</v>
       </c>
       <c r="D605" t="n">
-        <v>914.2072262502634</v>
+        <v>914.2072866533092</v>
       </c>
       <c r="E605" t="n">
-        <v>921.1043829766236</v>
+        <v>921.1044438353749</v>
       </c>
       <c r="F605" t="n">
         <v>375341</v>
@@ -12532,16 +12532,16 @@
         <v>43844</v>
       </c>
       <c r="B606" t="n">
-        <v>917.5445556640625</v>
+        <v>917.5444946289062</v>
       </c>
       <c r="C606" t="n">
-        <v>929.5589687716543</v>
+        <v>929.5589069372982</v>
       </c>
       <c r="D606" t="n">
-        <v>911.0923446093229</v>
+        <v>911.0922840033685</v>
       </c>
       <c r="E606" t="n">
-        <v>919.991903314781</v>
+        <v>919.991842116827</v>
       </c>
       <c r="F606" t="n">
         <v>179395</v>
@@ -12552,16 +12552,16 @@
         <v>43845</v>
       </c>
       <c r="B607" t="n">
-        <v>939.1259155273438</v>
+        <v>939.1260375976562</v>
       </c>
       <c r="C607" t="n">
-        <v>945.3556239358136</v>
+        <v>945.3557468158817</v>
       </c>
       <c r="D607" t="n">
-        <v>909.3123869030065</v>
+        <v>909.31250509807</v>
       </c>
       <c r="E607" t="n">
-        <v>912.2047388709061</v>
+        <v>912.2048574419259</v>
       </c>
       <c r="F607" t="n">
         <v>262820</v>
@@ -12592,16 +12592,16 @@
         <v>43847</v>
       </c>
       <c r="B609" t="n">
-        <v>961.3748168945312</v>
+        <v>961.3748779296875</v>
       </c>
       <c r="C609" t="n">
-        <v>961.3748168945312</v>
+        <v>961.3748779296875</v>
       </c>
       <c r="D609" t="n">
-        <v>927.7789872130055</v>
+        <v>927.779046115251</v>
       </c>
       <c r="E609" t="n">
-        <v>927.7789872130055</v>
+        <v>927.779046115251</v>
       </c>
       <c r="F609" t="n">
         <v>135692</v>
@@ -12612,16 +12612,16 @@
         <v>43850</v>
       </c>
       <c r="B610" t="n">
-        <v>975.6140747070312</v>
+        <v>975.6141357421875</v>
       </c>
       <c r="C610" t="n">
-        <v>983.178737318101</v>
+        <v>983.1787988265082</v>
       </c>
       <c r="D610" t="n">
-        <v>952.6977027124357</v>
+        <v>952.6977623139263</v>
       </c>
       <c r="E610" t="n">
-        <v>957.3700134246553</v>
+        <v>957.3700733184493</v>
       </c>
       <c r="F610" t="n">
         <v>110330</v>
@@ -12652,16 +12652,16 @@
         <v>43852</v>
       </c>
       <c r="B612" t="n">
-        <v>998.975341796875</v>
+        <v>998.9754638671875</v>
       </c>
       <c r="C612" t="n">
-        <v>998.975341796875</v>
+        <v>998.9754638671875</v>
       </c>
       <c r="D612" t="n">
-        <v>960.4847601270244</v>
+        <v>960.4848774939602</v>
       </c>
       <c r="E612" t="n">
-        <v>961.1522667864635</v>
+        <v>961.1523842349657</v>
       </c>
       <c r="F612" t="n">
         <v>125437</v>
@@ -12672,16 +12672,16 @@
         <v>43853</v>
       </c>
       <c r="B613" t="n">
-        <v>976.2816162109375</v>
+        <v>976.2815551757812</v>
       </c>
       <c r="C613" t="n">
-        <v>996.3056370206705</v>
+        <v>996.3055747336529</v>
       </c>
       <c r="D613" t="n">
-        <v>974.7241595730579</v>
+        <v>974.7240986352707</v>
       </c>
       <c r="E613" t="n">
-        <v>984.9586722168816</v>
+        <v>984.9586106392533</v>
       </c>
       <c r="F613" t="n">
         <v>197093</v>
@@ -12692,16 +12692,16 @@
         <v>43854</v>
       </c>
       <c r="B614" t="n">
-        <v>952.69775390625</v>
+        <v>952.6976928710938</v>
       </c>
       <c r="C614" t="n">
-        <v>982.7337856638734</v>
+        <v>982.7337227044407</v>
       </c>
       <c r="D614" t="n">
-        <v>952.69775390625</v>
+        <v>952.6976928710938</v>
       </c>
       <c r="E614" t="n">
-        <v>975.8366293752512</v>
+        <v>975.8365668576889</v>
       </c>
       <c r="F614" t="n">
         <v>152264</v>
@@ -12792,16 +12792,16 @@
         <v>43861</v>
       </c>
       <c r="B619" t="n">
-        <v>997.4180297851562</v>
+        <v>997.4181518554688</v>
       </c>
       <c r="C619" t="n">
-        <v>1003.202733444644</v>
+        <v>1003.202856222925</v>
       </c>
       <c r="D619" t="n">
-        <v>964.9345939460327</v>
+        <v>964.9347120408174</v>
       </c>
       <c r="E619" t="n">
-        <v>982.7337093759116</v>
+        <v>982.7338296490643</v>
       </c>
       <c r="F619" t="n">
         <v>333146</v>
@@ -12832,16 +12832,16 @@
         <v>43865</v>
       </c>
       <c r="B621" t="n">
-        <v>918.6569213867188</v>
+        <v>918.656982421875</v>
       </c>
       <c r="C621" t="n">
-        <v>943.3531929932507</v>
+        <v>943.3532556692162</v>
       </c>
       <c r="D621" t="n">
-        <v>892.180750013644</v>
+        <v>892.1808092897353</v>
       </c>
       <c r="E621" t="n">
-        <v>930.003826674543</v>
+        <v>930.0038884635826</v>
       </c>
       <c r="F621" t="n">
         <v>576304</v>
@@ -12852,16 +12852,16 @@
         <v>43866</v>
       </c>
       <c r="B622" t="n">
-        <v>945.5781860351562</v>
+        <v>945.578125</v>
       </c>
       <c r="C622" t="n">
-        <v>950.0279358694697</v>
+        <v>950.0278745470912</v>
       </c>
       <c r="D622" t="n">
-        <v>909.9799512213539</v>
+        <v>909.9798924839915</v>
       </c>
       <c r="E622" t="n">
-        <v>924.6642142268238</v>
+        <v>924.6641545416221</v>
       </c>
       <c r="F622" t="n">
         <v>652008</v>
@@ -12912,16 +12912,16 @@
         <v>43871</v>
       </c>
       <c r="B625" t="n">
-        <v>734.4360961914062</v>
+        <v>734.43603515625</v>
       </c>
       <c r="C625" t="n">
-        <v>848.7954004135134</v>
+        <v>848.7953298745514</v>
       </c>
       <c r="D625" t="n">
-        <v>727.9838853894781</v>
+        <v>727.9838248905314</v>
       </c>
       <c r="E625" t="n">
-        <v>844.3456507525469</v>
+        <v>844.3455805833804</v>
       </c>
       <c r="F625" t="n">
         <v>1847485</v>
@@ -12932,16 +12932,16 @@
         <v>43872</v>
       </c>
       <c r="B626" t="n">
-        <v>770.92431640625</v>
+        <v>770.9242553710938</v>
       </c>
       <c r="C626" t="n">
-        <v>778.4889207089454</v>
+        <v>778.4888590748888</v>
       </c>
       <c r="D626" t="n">
-        <v>716.4145114858223</v>
+        <v>716.4144547662835</v>
       </c>
       <c r="E626" t="n">
-        <v>758.6874009426435</v>
+        <v>758.6873408763009</v>
       </c>
       <c r="F626" t="n">
         <v>856496</v>
@@ -12952,16 +12952,16 @@
         <v>43873</v>
       </c>
       <c r="B627" t="n">
-        <v>749.7877807617188</v>
+        <v>749.787841796875</v>
       </c>
       <c r="C627" t="n">
-        <v>783.1611677382641</v>
+        <v>783.1612314901223</v>
       </c>
       <c r="D627" t="n">
-        <v>747.7853787238224</v>
+        <v>747.7854395959766</v>
       </c>
       <c r="E627" t="n">
-        <v>781.1587657003678</v>
+        <v>781.1588292892239</v>
       </c>
       <c r="F627" t="n">
         <v>527262</v>
@@ -12972,16 +12972,16 @@
         <v>43874</v>
       </c>
       <c r="B628" t="n">
-        <v>729.7638549804688</v>
+        <v>729.763916015625</v>
       </c>
       <c r="C628" t="n">
-        <v>743.3356654387843</v>
+        <v>743.3357276090441</v>
       </c>
       <c r="D628" t="n">
-        <v>720.8642964933267</v>
+        <v>720.8643567841518</v>
       </c>
       <c r="E628" t="n">
-        <v>736.2160068421061</v>
+        <v>736.2160684169002</v>
       </c>
       <c r="F628" t="n">
         <v>387492</v>
@@ -12992,16 +12992,16 @@
         <v>43875</v>
       </c>
       <c r="B629" t="n">
-        <v>770.92431640625</v>
+        <v>770.9242553710938</v>
       </c>
       <c r="C629" t="n">
-        <v>776.2640752895095</v>
+        <v>776.264013831597</v>
       </c>
       <c r="D629" t="n">
-        <v>731.3212768736464</v>
+        <v>731.3212189739181</v>
       </c>
       <c r="E629" t="n">
-        <v>734.2136290502549</v>
+        <v>734.2135709215351</v>
       </c>
       <c r="F629" t="n">
         <v>682665</v>
@@ -13012,16 +13012,16 @@
         <v>43878</v>
       </c>
       <c r="B630" t="n">
-        <v>814.3095703125</v>
+        <v>814.3096923828125</v>
       </c>
       <c r="C630" t="n">
-        <v>823.2091281353971</v>
+        <v>823.2092515398114</v>
       </c>
       <c r="D630" t="n">
-        <v>756.4624739810773</v>
+        <v>756.462587379733</v>
       </c>
       <c r="E630" t="n">
-        <v>776.708937034889</v>
+        <v>776.7090534686215</v>
       </c>
       <c r="F630" t="n">
         <v>649560</v>
@@ -13092,16 +13092,16 @@
         <v>43882</v>
       </c>
       <c r="B634" t="n">
-        <v>723.5341186523438</v>
+        <v>723.5340576171875</v>
       </c>
       <c r="C634" t="n">
-        <v>766.0295073270397</v>
+        <v>766.0294427071007</v>
       </c>
       <c r="D634" t="n">
-        <v>718.8618668598937</v>
+        <v>718.8618062188744</v>
       </c>
       <c r="E634" t="n">
-        <v>766.0295073270397</v>
+        <v>766.0294427071007</v>
       </c>
       <c r="F634" t="n">
         <v>880384</v>
@@ -13112,16 +13112,16 @@
         <v>43887</v>
       </c>
       <c r="B635" t="n">
-        <v>711.9647216796875</v>
+        <v>711.9647827148438</v>
       </c>
       <c r="C635" t="n">
-        <v>716.4144713038074</v>
+        <v>716.4145327204309</v>
       </c>
       <c r="D635" t="n">
-        <v>661.2372217557945</v>
+        <v>661.2372784421947</v>
       </c>
       <c r="E635" t="n">
-        <v>670.5817254838569</v>
+        <v>670.5817829713407</v>
       </c>
       <c r="F635" t="n">
         <v>736458</v>
@@ -13132,16 +13132,16 @@
         <v>43888</v>
       </c>
       <c r="B636" t="n">
-        <v>759.3549194335938</v>
+        <v>759.3548583984375</v>
       </c>
       <c r="C636" t="n">
-        <v>784.0511939599875</v>
+        <v>784.051130939803</v>
       </c>
       <c r="D636" t="n">
-        <v>713.0771658231122</v>
+        <v>713.0771085076525</v>
       </c>
       <c r="E636" t="n">
-        <v>713.0771658231122</v>
+        <v>713.0771085076525</v>
       </c>
       <c r="F636" t="n">
         <v>1264812</v>
@@ -13152,16 +13152,16 @@
         <v>43889</v>
       </c>
       <c r="B637" t="n">
-        <v>739.77587890625</v>
+        <v>739.7758178710938</v>
       </c>
       <c r="C637" t="n">
-        <v>754.4601418177864</v>
+        <v>754.4600795711062</v>
       </c>
       <c r="D637" t="n">
-        <v>707.7374441648444</v>
+        <v>707.737385773017</v>
       </c>
       <c r="E637" t="n">
-        <v>734.6586223534063</v>
+        <v>734.6585617404489</v>
       </c>
       <c r="F637" t="n">
         <v>1007326</v>
@@ -13172,16 +13172,16 @@
         <v>43892</v>
       </c>
       <c r="B638" t="n">
-        <v>675.2540283203125</v>
+        <v>675.2540893554688</v>
       </c>
       <c r="C638" t="n">
-        <v>743.7805849573131</v>
+        <v>743.7806521864777</v>
       </c>
       <c r="D638" t="n">
-        <v>675.2540283203125</v>
+        <v>675.2540893554688</v>
       </c>
       <c r="E638" t="n">
-        <v>729.7638295325767</v>
+        <v>729.7638954947887</v>
       </c>
       <c r="F638" t="n">
         <v>787365</v>
@@ -13192,16 +13192,16 @@
         <v>43893</v>
       </c>
       <c r="B639" t="n">
-        <v>622.96923828125</v>
+        <v>622.9691162109375</v>
       </c>
       <c r="C639" t="n">
-        <v>705.0676780220954</v>
+        <v>705.0675398646607</v>
       </c>
       <c r="D639" t="n">
-        <v>622.96923828125</v>
+        <v>622.9691162109375</v>
       </c>
       <c r="E639" t="n">
-        <v>686.3785495133554</v>
+        <v>686.3784150180403</v>
       </c>
       <c r="F639" t="n">
         <v>1233255</v>
@@ -13252,16 +13252,16 @@
         <v>43896</v>
       </c>
       <c r="B642" t="n">
-        <v>364.2144165039062</v>
+        <v>364.2144470214844</v>
       </c>
       <c r="C642" t="n">
-        <v>395.3628683209269</v>
+        <v>395.3629014484382</v>
       </c>
       <c r="D642" t="n">
-        <v>341.7430201245077</v>
+        <v>341.7430487592042</v>
       </c>
       <c r="E642" t="n">
-        <v>344.8578741614322</v>
+        <v>344.8579030571229</v>
       </c>
       <c r="F642" t="n">
         <v>1945908</v>
@@ -13292,16 +13292,16 @@
         <v>43900</v>
       </c>
       <c r="B644" t="n">
-        <v>304.8098754882812</v>
+        <v>304.8098449707031</v>
       </c>
       <c r="C644" t="n">
-        <v>342.1880071868422</v>
+        <v>342.1879729269639</v>
       </c>
       <c r="D644" t="n">
-        <v>289.9031114483475</v>
+        <v>289.9030824232352</v>
       </c>
       <c r="E644" t="n">
-        <v>337.0707805360925</v>
+        <v>337.0707467885511</v>
       </c>
       <c r="F644" t="n">
         <v>1215566</v>
@@ -13332,16 +13332,16 @@
         <v>43902</v>
       </c>
       <c r="B646" t="n">
-        <v>203.577392578125</v>
+        <v>203.5774230957031</v>
       </c>
       <c r="C646" t="n">
-        <v>260.0895788500403</v>
+        <v>260.0896178391635</v>
       </c>
       <c r="D646" t="n">
-        <v>196.2352618018462</v>
+        <v>196.235291218791</v>
       </c>
       <c r="E646" t="n">
-        <v>244.7378548883766</v>
+        <v>244.7378915761763</v>
       </c>
       <c r="F646" t="n">
         <v>1306837</v>
@@ -13352,16 +13352,16 @@
         <v>43903</v>
       </c>
       <c r="B647" t="n">
-        <v>222.4889678955078</v>
+        <v>222.4889831542969</v>
       </c>
       <c r="C647" t="n">
-        <v>244.7378632091881</v>
+        <v>244.737879993856</v>
       </c>
       <c r="D647" t="n">
-        <v>200.4625600590938</v>
+        <v>200.4625738072628</v>
       </c>
       <c r="E647" t="n">
-        <v>244.7378632091881</v>
+        <v>244.737879993856</v>
       </c>
       <c r="F647" t="n">
         <v>1357909</v>
@@ -13372,16 +13372,16 @@
         <v>43906</v>
       </c>
       <c r="B648" t="n">
-        <v>194.6778411865234</v>
+        <v>194.6778564453125</v>
       </c>
       <c r="C648" t="n">
-        <v>208.2496658389243</v>
+        <v>208.2496821614688</v>
       </c>
       <c r="D648" t="n">
-        <v>191.5630017490907</v>
+        <v>191.5630167637396</v>
       </c>
       <c r="E648" t="n">
-        <v>196.9027307157482</v>
+        <v>196.9027461489235</v>
       </c>
       <c r="F648" t="n">
         <v>1146722</v>
@@ -13472,16 +13472,16 @@
         <v>43913</v>
       </c>
       <c r="B653" t="n">
-        <v>155.7422943115234</v>
+        <v>155.7422637939453</v>
       </c>
       <c r="C653" t="n">
-        <v>165.9767938411923</v>
+        <v>165.9767613181722</v>
       </c>
       <c r="D653" t="n">
-        <v>145.9527845725679</v>
+        <v>145.9527559732363</v>
       </c>
       <c r="E653" t="n">
-        <v>165.7543063251894</v>
+        <v>165.7542738457655</v>
       </c>
       <c r="F653" t="n">
         <v>1319492</v>
@@ -13532,16 +13532,16 @@
         <v>43916</v>
       </c>
       <c r="B656" t="n">
-        <v>220.9315338134766</v>
+        <v>220.9315490722656</v>
       </c>
       <c r="C656" t="n">
-        <v>242.7354534835191</v>
+        <v>242.735470248211</v>
       </c>
       <c r="D656" t="n">
-        <v>190.6730312396985</v>
+        <v>190.6730444086632</v>
       </c>
       <c r="E656" t="n">
-        <v>190.6730312396985</v>
+        <v>190.6730444086632</v>
       </c>
       <c r="F656" t="n">
         <v>1984360</v>
@@ -13592,16 +13592,16 @@
         <v>43921</v>
       </c>
       <c r="B659" t="n">
-        <v>215.3692932128906</v>
+        <v>215.3693084716797</v>
       </c>
       <c r="C659" t="n">
-        <v>244.5153571405698</v>
+        <v>244.5153744643405</v>
       </c>
       <c r="D659" t="n">
-        <v>208.4721376659349</v>
+        <v>208.4721524360645</v>
       </c>
       <c r="E659" t="n">
-        <v>244.5153571405698</v>
+        <v>244.5153744643405</v>
       </c>
       <c r="F659" t="n">
         <v>1005243</v>
@@ -13612,16 +13612,16 @@
         <v>43922</v>
       </c>
       <c r="B660" t="n">
-        <v>207.1372528076172</v>
+        <v>207.1372222900391</v>
       </c>
       <c r="C660" t="n">
-        <v>208.0272028204601</v>
+        <v>208.0271721717654</v>
       </c>
       <c r="D660" t="n">
-        <v>195.3453265852085</v>
+        <v>195.3452978049374</v>
       </c>
       <c r="E660" t="n">
-        <v>201.3525334480182</v>
+        <v>201.352503782704</v>
       </c>
       <c r="F660" t="n">
         <v>767742</v>
@@ -13692,16 +13692,16 @@
         <v>43928</v>
       </c>
       <c r="B664" t="n">
-        <v>226.9387664794922</v>
+        <v>226.9387359619141</v>
       </c>
       <c r="C664" t="n">
-        <v>254.97238288966</v>
+        <v>254.9723486022629</v>
       </c>
       <c r="D664" t="n">
-        <v>226.4937914866829</v>
+        <v>226.4937610289427</v>
       </c>
       <c r="E664" t="n">
-        <v>251.412553429773</v>
+        <v>251.4125196210838</v>
       </c>
       <c r="F664" t="n">
         <v>1047412</v>
@@ -13712,16 +13712,16 @@
         <v>43929</v>
       </c>
       <c r="B665" t="n">
-        <v>225.6038055419922</v>
+        <v>225.6038208007812</v>
       </c>
       <c r="C665" t="n">
-        <v>226.9387451536799</v>
+        <v>226.938760502758</v>
       </c>
       <c r="D665" t="n">
-        <v>214.7018454491082</v>
+        <v>214.7018599705395</v>
       </c>
       <c r="E665" t="n">
-        <v>216.9267349627844</v>
+        <v>216.9267496346969</v>
       </c>
       <c r="F665" t="n">
         <v>1185635</v>
@@ -13732,16 +13732,16 @@
         <v>43930</v>
       </c>
       <c r="B666" t="n">
-        <v>224.7138824462891</v>
+        <v>224.7138671875</v>
       </c>
       <c r="C666" t="n">
-        <v>238.0632211207989</v>
+        <v>238.0632049555472</v>
       </c>
       <c r="D666" t="n">
-        <v>219.3741381212612</v>
+        <v>219.3741232250578</v>
       </c>
       <c r="E666" t="n">
-        <v>228.7186870003833</v>
+        <v>228.7186714696553</v>
       </c>
       <c r="F666" t="n">
         <v>844989</v>
@@ -13812,16 +13812,16 @@
         <v>43937</v>
       </c>
       <c r="B670" t="n">
-        <v>262.7594909667969</v>
+        <v>262.7594299316406</v>
       </c>
       <c r="C670" t="n">
-        <v>275.6638543805785</v>
+        <v>275.663790347929</v>
       </c>
       <c r="D670" t="n">
-        <v>259.4221637438982</v>
+        <v>259.4221034839539</v>
       </c>
       <c r="E670" t="n">
-        <v>273.8839543996759</v>
+        <v>273.8838907804709</v>
       </c>
       <c r="F670" t="n">
         <v>858661</v>
@@ -13852,16 +13852,16 @@
         <v>43941</v>
       </c>
       <c r="B672" t="n">
-        <v>265.4293823242188</v>
+        <v>265.4293518066406</v>
       </c>
       <c r="C672" t="n">
-        <v>270.9915847719591</v>
+        <v>270.9915536148703</v>
       </c>
       <c r="D672" t="n">
-        <v>252.9699933485421</v>
+        <v>252.9699642634744</v>
       </c>
       <c r="E672" t="n">
-        <v>258.0872207811598</v>
+        <v>258.0871911077421</v>
       </c>
       <c r="F672" t="n">
         <v>627032</v>
@@ -13872,16 +13872,16 @@
         <v>43943</v>
       </c>
       <c r="B673" t="n">
-        <v>246.0727996826172</v>
+        <v>246.0728149414062</v>
       </c>
       <c r="C673" t="n">
-        <v>270.1016107068236</v>
+        <v>270.1016274556211</v>
       </c>
       <c r="D673" t="n">
-        <v>245.1828497315637</v>
+        <v>245.1828649351676</v>
       </c>
       <c r="E673" t="n">
-        <v>266.9867563607251</v>
+        <v>266.9867729163728</v>
       </c>
       <c r="F673" t="n">
         <v>1710454</v>
@@ -13892,16 +13892,16 @@
         <v>43944</v>
       </c>
       <c r="B674" t="n">
-        <v>225.1588287353516</v>
+        <v>225.1588439941406</v>
       </c>
       <c r="C674" t="n">
-        <v>243.6254071190605</v>
+        <v>243.6254236293111</v>
       </c>
       <c r="D674" t="n">
-        <v>216.0367832803288</v>
+        <v>216.036797920926</v>
       </c>
       <c r="E674" t="n">
-        <v>237.8407032863998</v>
+        <v>237.8407194046269</v>
       </c>
       <c r="F674" t="n">
         <v>2199225</v>
@@ -13912,16 +13912,16 @@
         <v>43945</v>
       </c>
       <c r="B675" t="n">
-        <v>201.7974700927734</v>
+        <v>201.7975006103516</v>
       </c>
       <c r="C675" t="n">
-        <v>219.5965850356764</v>
+        <v>219.5966182449923</v>
       </c>
       <c r="D675" t="n">
-        <v>183.7758676889546</v>
+        <v>183.7758954811484</v>
       </c>
       <c r="E675" t="n">
-        <v>218.261660270181</v>
+        <v>218.261693277618</v>
       </c>
       <c r="F675" t="n">
         <v>2006627</v>
@@ -13992,16 +13992,16 @@
         <v>43951</v>
       </c>
       <c r="B679" t="n">
-        <v>227.3837280273438</v>
+        <v>227.3837127685547</v>
       </c>
       <c r="C679" t="n">
-        <v>236.9507488418812</v>
+        <v>236.9507329410886</v>
       </c>
       <c r="D679" t="n">
-        <v>219.1516321123016</v>
+        <v>219.1516174059347</v>
       </c>
       <c r="E679" t="n">
-        <v>222.4889738784504</v>
+        <v>222.4889589481282</v>
       </c>
       <c r="F679" t="n">
         <v>1396400</v>
@@ -14032,16 +14032,16 @@
         <v>43956</v>
       </c>
       <c r="B681" t="n">
-        <v>200.4625549316406</v>
+        <v>200.4625396728516</v>
       </c>
       <c r="C681" t="n">
-        <v>219.5965955567701</v>
+        <v>219.596578841538</v>
       </c>
       <c r="D681" t="n">
-        <v>199.7950777582095</v>
+        <v>199.7950625502274</v>
       </c>
       <c r="E681" t="n">
-        <v>216.0367812528576</v>
+        <v>216.0367648085911</v>
       </c>
       <c r="F681" t="n">
         <v>1156334</v>
@@ -14052,16 +14052,16 @@
         <v>43957</v>
       </c>
       <c r="B682" t="n">
-        <v>203.3549194335938</v>
+        <v>203.3549041748047</v>
       </c>
       <c r="C682" t="n">
-        <v>206.9147487170036</v>
+        <v>206.9147331911019</v>
       </c>
       <c r="D682" t="n">
-        <v>198.4601652379342</v>
+        <v>198.4601503464243</v>
       </c>
       <c r="E682" t="n">
-        <v>200.6850548503891</v>
+        <v>200.685039791934</v>
       </c>
       <c r="F682" t="n">
         <v>780923</v>
@@ -14092,16 +14092,16 @@
         <v>43959</v>
       </c>
       <c r="B684" t="n">
-        <v>201.1300201416016</v>
+        <v>201.1300506591797</v>
       </c>
       <c r="C684" t="n">
-        <v>204.4673617790244</v>
+        <v>204.4673928029794</v>
       </c>
       <c r="D684" t="n">
-        <v>190.8955225133703</v>
+        <v>190.895551478062</v>
       </c>
       <c r="E684" t="n">
-        <v>194.6778391001282</v>
+        <v>194.6778686387131</v>
       </c>
       <c r="F684" t="n">
         <v>1020628</v>
@@ -14112,16 +14112,16 @@
         <v>43962</v>
       </c>
       <c r="B685" t="n">
-        <v>171.3165130615234</v>
+        <v>171.3165283203125</v>
       </c>
       <c r="C685" t="n">
-        <v>177.7686795848986</v>
+        <v>177.7686954183682</v>
       </c>
       <c r="D685" t="n">
-        <v>169.5365984391037</v>
+        <v>169.5366135393597</v>
       </c>
       <c r="E685" t="n">
-        <v>175.76629223822</v>
+        <v>175.7663078933412</v>
       </c>
       <c r="F685" t="n">
         <v>2483473</v>
@@ -14172,16 +14172,16 @@
         <v>43965</v>
       </c>
       <c r="B688" t="n">
-        <v>156.6322174072266</v>
+        <v>156.6322326660156</v>
       </c>
       <c r="C688" t="n">
-        <v>171.3164928624584</v>
+        <v>171.3165095517595</v>
       </c>
       <c r="D688" t="n">
-        <v>155.9647550370308</v>
+        <v>155.9647702307971</v>
       </c>
       <c r="E688" t="n">
-        <v>161.9719458861998</v>
+        <v>161.9719616651743</v>
       </c>
       <c r="F688" t="n">
         <v>2135798</v>
@@ -14192,16 +14192,16 @@
         <v>43966</v>
       </c>
       <c r="B689" t="n">
-        <v>149.0676116943359</v>
+        <v>149.0675964355469</v>
       </c>
       <c r="C689" t="n">
-        <v>162.861939807344</v>
+        <v>162.8619231365464</v>
       </c>
       <c r="D689" t="n">
-        <v>149.0676116943359</v>
+        <v>149.0675964355469</v>
       </c>
       <c r="E689" t="n">
-        <v>156.4097581238081</v>
+        <v>156.4097421134657</v>
       </c>
       <c r="F689" t="n">
         <v>3004141</v>
@@ -14232,16 +14232,16 @@
         <v>43970</v>
       </c>
       <c r="B691" t="n">
-        <v>156.8547210693359</v>
+        <v>156.854736328125</v>
       </c>
       <c r="C691" t="n">
-        <v>170.871520843808</v>
+        <v>170.8715374661479</v>
       </c>
       <c r="D691" t="n">
-        <v>156.8547210693359</v>
+        <v>156.854736328125</v>
       </c>
       <c r="E691" t="n">
-        <v>160.8595252216723</v>
+        <v>160.8595408700477</v>
       </c>
       <c r="F691" t="n">
         <v>1437035</v>
@@ -14272,16 +14272,16 @@
         <v>43972</v>
       </c>
       <c r="B693" t="n">
-        <v>156.8547210693359</v>
+        <v>156.854736328125</v>
       </c>
       <c r="C693" t="n">
-        <v>170.4265458843718</v>
+        <v>170.4265624634247</v>
       </c>
       <c r="D693" t="n">
-        <v>155.0748064728859</v>
+        <v>155.0748215585253</v>
       </c>
       <c r="E693" t="n">
-        <v>169.9815709249356</v>
+        <v>169.9815874607014</v>
       </c>
       <c r="F693" t="n">
         <v>2204133</v>
@@ -14292,16 +14292,16 @@
         <v>43973</v>
       </c>
       <c r="B694" t="n">
-        <v>159.5245971679688</v>
+        <v>159.5245819091797</v>
       </c>
       <c r="C694" t="n">
-        <v>163.9743766028462</v>
+        <v>163.9743609184285</v>
       </c>
       <c r="D694" t="n">
-        <v>156.6322449629103</v>
+        <v>156.6322299807794</v>
       </c>
       <c r="E694" t="n">
-        <v>158.857134680349</v>
+        <v>158.8571194854038</v>
       </c>
       <c r="F694" t="n">
         <v>1395700</v>
@@ -14312,16 +14312,16 @@
         <v>43976</v>
       </c>
       <c r="B695" t="n">
-        <v>173.5413970947266</v>
+        <v>173.5414123535156</v>
       </c>
       <c r="C695" t="n">
-        <v>176.6562365152245</v>
+        <v>176.6562520478887</v>
       </c>
       <c r="D695" t="n">
-        <v>154.8523162956244</v>
+        <v>154.8523299111586</v>
       </c>
       <c r="E695" t="n">
-        <v>155.7422661989938</v>
+        <v>155.7422798927777</v>
       </c>
       <c r="F695" t="n">
         <v>2267000</v>
@@ -14352,16 +14352,16 @@
         <v>43978</v>
       </c>
       <c r="B697" t="n">
-        <v>171.3165130615234</v>
+        <v>171.3165283203125</v>
       </c>
       <c r="C697" t="n">
-        <v>171.9839755104163</v>
+        <v>171.9839908286548</v>
       </c>
       <c r="D697" t="n">
-        <v>160.8595275686749</v>
+        <v>160.859541896083</v>
       </c>
       <c r="E697" t="n">
-        <v>165.7542817113001</v>
+        <v>165.7542964746733</v>
       </c>
       <c r="F697" t="n">
         <v>1675267</v>
@@ -14372,16 +14372,16 @@
         <v>43979</v>
       </c>
       <c r="B698" t="n">
-        <v>180.8835296630859</v>
+        <v>180.8835144042969</v>
       </c>
       <c r="C698" t="n">
-        <v>188.2256607065147</v>
+        <v>188.2256448283656</v>
       </c>
       <c r="D698" t="n">
-        <v>167.7566799208101</v>
+        <v>167.7566657693625</v>
       </c>
       <c r="E698" t="n">
-        <v>171.3165090829783</v>
+        <v>171.3164946312342</v>
       </c>
       <c r="F698" t="n">
         <v>2426350</v>
@@ -14392,16 +14392,16 @@
         <v>43980</v>
       </c>
       <c r="B699" t="n">
-        <v>184.6658477783203</v>
+        <v>184.6658325195312</v>
       </c>
       <c r="C699" t="n">
-        <v>184.6658477783203</v>
+        <v>184.6658325195312</v>
       </c>
       <c r="D699" t="n">
-        <v>174.4313499243536</v>
+        <v>174.4313355112328</v>
       </c>
       <c r="E699" t="n">
-        <v>178.88112903326</v>
+        <v>178.8811142524575</v>
       </c>
       <c r="F699" t="n">
         <v>1755787</v>
@@ -14592,16 +14592,16 @@
         <v>43997</v>
       </c>
       <c r="B709" t="n">
-        <v>230.2760772705078</v>
+        <v>230.2760620117188</v>
       </c>
       <c r="C709" t="n">
-        <v>248.742656225472</v>
+        <v>248.7426397430316</v>
       </c>
       <c r="D709" t="n">
-        <v>220.4865690916606</v>
+        <v>220.4865544815539</v>
       </c>
       <c r="E709" t="n">
-        <v>238.9531480466248</v>
+        <v>238.9531322128668</v>
       </c>
       <c r="F709" t="n">
         <v>3471845</v>
@@ -14612,16 +14612,16 @@
         <v>43998</v>
       </c>
       <c r="B710" t="n">
-        <v>227.1612548828125</v>
+        <v>227.1612396240234</v>
       </c>
       <c r="C710" t="n">
-        <v>246.2953124783596</v>
+        <v>246.295295934305</v>
       </c>
       <c r="D710" t="n">
-        <v>220.4865856879062</v>
+        <v>220.4865708774655</v>
       </c>
       <c r="E710" t="n">
-        <v>224.7138776538842</v>
+        <v>224.7138625594894</v>
       </c>
       <c r="F710" t="n">
         <v>2759414</v>
@@ -14652,16 +14652,16 @@
         <v>44000</v>
       </c>
       <c r="B712" t="n">
-        <v>225.8263092041016</v>
+        <v>225.8262939453125</v>
       </c>
       <c r="C712" t="n">
-        <v>235.6158326211861</v>
+        <v>235.6158167009318</v>
       </c>
       <c r="D712" t="n">
-        <v>222.7114695651736</v>
+        <v>222.7114545168502</v>
       </c>
       <c r="E712" t="n">
-        <v>223.6014195309513</v>
+        <v>223.6014044224952</v>
       </c>
       <c r="F712" t="n">
         <v>1478112</v>
@@ -14712,16 +14712,16 @@
         <v>44005</v>
       </c>
       <c r="B715" t="n">
-        <v>255.8623199462891</v>
+        <v>255.8623046875</v>
       </c>
       <c r="C715" t="n">
-        <v>291.2380514676505</v>
+        <v>291.2380340991689</v>
       </c>
       <c r="D715" t="n">
-        <v>252.0800179398273</v>
+        <v>252.0800029066023</v>
       </c>
       <c r="E715" t="n">
-        <v>281.4485430856947</v>
+        <v>281.4485263010272</v>
       </c>
       <c r="F715" t="n">
         <v>4336471</v>
@@ -14732,16 +14732,16 @@
         <v>44006</v>
       </c>
       <c r="B716" t="n">
-        <v>246.0727996826172</v>
+        <v>246.0728149414062</v>
       </c>
       <c r="C716" t="n">
-        <v>270.3241129532926</v>
+        <v>270.3241297158874</v>
       </c>
       <c r="D716" t="n">
-        <v>244.7378747560369</v>
+        <v>244.7378899320483</v>
       </c>
       <c r="E716" t="n">
-        <v>261.6470271369928</v>
+        <v>261.647043361528</v>
       </c>
       <c r="F716" t="n">
         <v>2500506</v>
@@ -14752,16 +14752,16 @@
         <v>44007</v>
       </c>
       <c r="B717" t="n">
-        <v>250.3000793457031</v>
+        <v>250.3000946044922</v>
       </c>
       <c r="C717" t="n">
-        <v>255.4173355925531</v>
+        <v>255.4173511633002</v>
       </c>
       <c r="D717" t="n">
-        <v>237.3957318868463</v>
+        <v>237.3957463589608</v>
       </c>
       <c r="E717" t="n">
-        <v>248.2976772941018</v>
+        <v>248.2976924308205</v>
       </c>
       <c r="F717" t="n">
         <v>2280068</v>
@@ -14772,16 +14772,16 @@
         <v>44008</v>
       </c>
       <c r="B718" t="n">
-        <v>263.8719482421875</v>
+        <v>263.8719177246094</v>
       </c>
       <c r="C718" t="n">
-        <v>270.7691050757434</v>
+        <v>270.7690737604885</v>
       </c>
       <c r="D718" t="n">
-        <v>256.3073141443666</v>
+        <v>256.307284501661</v>
       </c>
       <c r="E718" t="n">
-        <v>266.9867732681264</v>
+        <v>266.9867423903095</v>
       </c>
       <c r="F718" t="n">
         <v>3269179</v>
@@ -14832,16 +14832,16 @@
         <v>44013</v>
       </c>
       <c r="B721" t="n">
-        <v>227.1612548828125</v>
+        <v>227.1612396240234</v>
       </c>
       <c r="C721" t="n">
-        <v>238.7306785355754</v>
+        <v>238.7306624996495</v>
       </c>
       <c r="D721" t="n">
-        <v>222.9339629168346</v>
+        <v>222.9339479419995</v>
       </c>
       <c r="E721" t="n">
-        <v>231.3885468487904</v>
+        <v>231.3885313060473</v>
       </c>
       <c r="F721" t="n">
         <v>3984853</v>
@@ -14872,16 +14872,16 @@
         <v>44015</v>
       </c>
       <c r="B723" t="n">
-        <v>215.3692932128906</v>
+        <v>215.3693084716797</v>
       </c>
       <c r="C723" t="n">
-        <v>215.3692932128906</v>
+        <v>215.3693084716797</v>
       </c>
       <c r="D723" t="n">
-        <v>185.1108067421663</v>
+        <v>185.1108198571592</v>
       </c>
       <c r="E723" t="n">
-        <v>192.4529372098216</v>
+        <v>192.4529508450001</v>
       </c>
       <c r="F723" t="n">
         <v>5547968</v>
@@ -14932,16 +14932,16 @@
         <v>44020</v>
       </c>
       <c r="B726" t="n">
-        <v>207.3597106933594</v>
+        <v>207.3597259521484</v>
       </c>
       <c r="C726" t="n">
-        <v>214.4793540553144</v>
+        <v>214.4793698380102</v>
       </c>
       <c r="D726" t="n">
-        <v>206.4697460489246</v>
+        <v>206.4697612422247</v>
       </c>
       <c r="E726" t="n">
-        <v>211.8094896394194</v>
+        <v>211.8095052256502</v>
       </c>
       <c r="F726" t="n">
         <v>1622377</v>
@@ -14952,16 +14952,16 @@
         <v>44021</v>
       </c>
       <c r="B727" t="n">
-        <v>206.9147491455078</v>
+        <v>206.9147644042969</v>
       </c>
       <c r="C727" t="n">
-        <v>210.2520761917486</v>
+        <v>210.2520916966466</v>
       </c>
       <c r="D727" t="n">
-        <v>184.8883404607196</v>
+        <v>184.888354095186</v>
       </c>
       <c r="E727" t="n">
-        <v>186.8907425919463</v>
+        <v>186.8907563740785</v>
       </c>
       <c r="F727" t="n">
         <v>3744947</v>
@@ -15012,16 +15012,16 @@
         <v>44026</v>
       </c>
       <c r="B730" t="n">
-        <v>223.9059448242188</v>
+        <v>223.9059753417969</v>
       </c>
       <c r="C730" t="n">
-        <v>225.8320148017794</v>
+        <v>225.8320455818739</v>
       </c>
       <c r="D730" t="n">
-        <v>211.145716464175</v>
+        <v>211.1457452425797</v>
       </c>
       <c r="E730" t="n">
-        <v>219.3315286275123</v>
+        <v>219.3315585216138</v>
       </c>
       <c r="F730" t="n">
         <v>2477565</v>
@@ -15032,16 +15032,16 @@
         <v>44027</v>
       </c>
       <c r="B731" t="n">
-        <v>220.0538330078125</v>
+        <v>220.0538177490234</v>
       </c>
       <c r="C731" t="n">
-        <v>230.6472339976995</v>
+        <v>230.6472180043517</v>
       </c>
       <c r="D731" t="n">
-        <v>217.8870040059801</v>
+        <v>217.8869888974415</v>
       </c>
       <c r="E731" t="n">
-        <v>229.9249576637553</v>
+        <v>229.924941720491</v>
       </c>
       <c r="F731" t="n">
         <v>1488094</v>
@@ -15052,16 +15052,16 @@
         <v>44028</v>
       </c>
       <c r="B732" t="n">
-        <v>215.4793853759766</v>
+        <v>215.4794006347656</v>
       </c>
       <c r="C732" t="n">
-        <v>221.0168516147299</v>
+        <v>221.0168672656448</v>
       </c>
       <c r="D732" t="n">
-        <v>214.2755915759661</v>
+        <v>214.2756067495107</v>
       </c>
       <c r="E732" t="n">
-        <v>218.368505254707</v>
+        <v>218.3685207180839</v>
       </c>
       <c r="F732" t="n">
         <v>1169687</v>
@@ -15072,16 +15072,16 @@
         <v>44029</v>
       </c>
       <c r="B733" t="n">
-        <v>216.6831665039062</v>
+        <v>216.6831970214844</v>
       </c>
       <c r="C733" t="n">
-        <v>220.053803705519</v>
+        <v>220.0538346978164</v>
       </c>
       <c r="D733" t="n">
-        <v>215.7201315202182</v>
+        <v>215.7201619021628</v>
       </c>
       <c r="E733" t="n">
-        <v>217.6462162462988</v>
+        <v>217.6462468995125</v>
       </c>
       <c r="F733" t="n">
         <v>1022336</v>
@@ -15152,16 +15152,16 @@
         <v>44035</v>
       </c>
       <c r="B737" t="n">
-        <v>188.9958953857422</v>
+        <v>188.9958801269531</v>
       </c>
       <c r="C737" t="n">
-        <v>198.1447431759173</v>
+        <v>198.1447271784861</v>
       </c>
       <c r="D737" t="n">
-        <v>188.5143778577701</v>
+        <v>188.5143626378569</v>
       </c>
       <c r="E737" t="n">
-        <v>196.7001905920011</v>
+        <v>196.7001747111973</v>
       </c>
       <c r="F737" t="n">
         <v>1310991</v>
@@ -15232,16 +15232,16 @@
         <v>44041</v>
       </c>
       <c r="B741" t="n">
-        <v>196.9409484863281</v>
+        <v>196.9409332275391</v>
       </c>
       <c r="C741" t="n">
-        <v>200.3115711672486</v>
+        <v>200.311555647307</v>
       </c>
       <c r="D741" t="n">
-        <v>193.8110698096251</v>
+        <v>193.8110547933359</v>
       </c>
       <c r="E741" t="n">
-        <v>193.8110698096251</v>
+        <v>193.8110547933359</v>
       </c>
       <c r="F741" t="n">
         <v>806469</v>
@@ -15272,16 +15272,16 @@
         <v>44043</v>
       </c>
       <c r="B743" t="n">
-        <v>191.885009765625</v>
+        <v>191.8849792480469</v>
       </c>
       <c r="C743" t="n">
-        <v>199.1077877906642</v>
+        <v>199.1077561243685</v>
       </c>
       <c r="D743" t="n">
-        <v>191.885009765625</v>
+        <v>191.8849792480469</v>
       </c>
       <c r="E743" t="n">
-        <v>195.4963913987915</v>
+        <v>195.4963603068557</v>
       </c>
       <c r="F743" t="n">
         <v>1201151</v>
@@ -15312,16 +15312,16 @@
         <v>44047</v>
       </c>
       <c r="B745" t="n">
-        <v>182.9768981933594</v>
+        <v>182.9769134521484</v>
       </c>
       <c r="C745" t="n">
-        <v>193.0887803025982</v>
+        <v>193.0887964046362</v>
       </c>
       <c r="D745" t="n">
-        <v>179.36551699674</v>
+        <v>179.3655319543691</v>
       </c>
       <c r="E745" t="n">
-        <v>183.4584156862419</v>
+        <v>183.4584309851857</v>
       </c>
       <c r="F745" t="n">
         <v>1479244</v>
@@ -15332,16 +15332,16 @@
         <v>44048</v>
       </c>
       <c r="B746" t="n">
-        <v>181.2916107177734</v>
+        <v>181.2915954589844</v>
       </c>
       <c r="C746" t="n">
-        <v>186.588318592064</v>
+        <v>186.5883028874663</v>
       </c>
       <c r="D746" t="n">
-        <v>180.5693343838302</v>
+        <v>180.569319185833</v>
       </c>
       <c r="E746" t="n">
-        <v>185.3845247021585</v>
+        <v>185.3845090988807</v>
       </c>
       <c r="F746" t="n">
         <v>872716</v>
@@ -15372,16 +15372,16 @@
         <v>44050</v>
       </c>
       <c r="B748" t="n">
-        <v>187.06982421875</v>
+        <v>187.0698394775391</v>
       </c>
       <c r="C748" t="n">
-        <v>198.8670183462335</v>
+        <v>198.8670345672884</v>
       </c>
       <c r="D748" t="n">
-        <v>185.143754117725</v>
+        <v>185.1437692194096</v>
       </c>
       <c r="E748" t="n">
-        <v>187.7921005066344</v>
+        <v>187.7921158243376</v>
       </c>
       <c r="F748" t="n">
         <v>1923701</v>
@@ -15392,16 +15392,16 @@
         <v>44053</v>
       </c>
       <c r="B749" t="n">
-        <v>184.1806945800781</v>
+        <v>184.1807250976562</v>
       </c>
       <c r="C749" t="n">
-        <v>188.5143668371852</v>
+        <v>188.5143980728254</v>
       </c>
       <c r="D749" t="n">
-        <v>182.4953833306994</v>
+        <v>182.4954135690321</v>
       </c>
       <c r="E749" t="n">
-        <v>188.5143668371852</v>
+        <v>188.5143980728254</v>
       </c>
       <c r="F749" t="n">
         <v>940546</v>
@@ -15432,16 +15432,16 @@
         <v>44055</v>
       </c>
       <c r="B751" t="n">
-        <v>188.5143737792969</v>
+        <v>188.5143585205078</v>
       </c>
       <c r="C751" t="n">
-        <v>199.5892914417565</v>
+        <v>199.5892752865381</v>
       </c>
       <c r="D751" t="n">
-        <v>186.5883037090787</v>
+        <v>186.5882886061902</v>
       </c>
       <c r="E751" t="n">
-        <v>197.4224626127611</v>
+        <v>197.4224466329308</v>
       </c>
       <c r="F751" t="n">
         <v>1657962</v>
@@ -15452,16 +15452,16 @@
         <v>44056</v>
       </c>
       <c r="B752" t="n">
-        <v>184.9029998779297</v>
+        <v>184.9029846191406</v>
       </c>
       <c r="C752" t="n">
-        <v>195.7371444612045</v>
+        <v>195.7371283083471</v>
       </c>
       <c r="D752" t="n">
-        <v>183.9399500451549</v>
+        <v>183.9399348658399</v>
       </c>
       <c r="E752" t="n">
-        <v>189.7181752482741</v>
+        <v>189.7181595921213</v>
       </c>
       <c r="F752" t="n">
         <v>1407609</v>
@@ -15472,16 +15472,16 @@
         <v>44057</v>
       </c>
       <c r="B753" t="n">
-        <v>187.06982421875</v>
+        <v>187.0698394775391</v>
       </c>
       <c r="C753" t="n">
-        <v>189.7181706076593</v>
+        <v>189.718186082467</v>
       </c>
       <c r="D753" t="n">
-        <v>182.4953929701102</v>
+        <v>182.495407855775</v>
       </c>
       <c r="E753" t="n">
-        <v>186.5883066934938</v>
+        <v>186.5883219130067</v>
       </c>
       <c r="F753" t="n">
         <v>961878</v>
@@ -45732,19 +45732,39 @@
         <v>46281</v>
       </c>
       <c r="B2266" t="n">
-        <v>60.78</v>
+        <v>60.77999877929688</v>
       </c>
       <c r="C2266" t="n">
-        <v>61.48</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="D2266" t="n">
-        <v>60.07</v>
+        <v>60.06999969482422</v>
       </c>
       <c r="E2266" t="n">
-        <v>61.13</v>
+        <v>61.13000106811523</v>
       </c>
       <c r="F2266" t="n">
         <v>457100</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2267" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="C2267" t="n">
+        <v>61.31</v>
+      </c>
+      <c r="D2267" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>430900</v>
       </c>
     </row>
   </sheetData>

--- a/database/IRBR3.xlsx
+++ b/database/IRBR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2276"/>
+  <dimension ref="A1:F2277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>42947</v>
       </c>
       <c r="B2" t="n">
-        <v>197.0598449707031</v>
+        <v>197.0598754882812</v>
       </c>
       <c r="C2" t="n">
-        <v>199.1454898101428</v>
+        <v>199.1455206507133</v>
       </c>
       <c r="D2" t="n">
-        <v>188.8518224807313</v>
+        <v>188.851851727178</v>
       </c>
       <c r="E2" t="n">
-        <v>190.1301261134497</v>
+        <v>190.1301555578603</v>
       </c>
       <c r="F2" t="n">
         <v>1448107</v>
@@ -472,16 +472,16 @@
         <v>42948</v>
       </c>
       <c r="B3" t="n">
-        <v>197.7999420166016</v>
+        <v>197.7999572753906</v>
       </c>
       <c r="C3" t="n">
-        <v>199.8183086352532</v>
+        <v>199.8183240497441</v>
       </c>
       <c r="D3" t="n">
-        <v>197.0598657768911</v>
+        <v>197.0598809785888</v>
       </c>
       <c r="E3" t="n">
-        <v>199.0109539545458</v>
+        <v>199.0109693067554</v>
       </c>
       <c r="F3" t="n">
         <v>496061</v>
@@ -492,16 +492,16 @@
         <v>42949</v>
       </c>
       <c r="B4" t="n">
-        <v>198.1363372802734</v>
+        <v>198.1363220214844</v>
       </c>
       <c r="C4" t="n">
-        <v>198.3381726063799</v>
+        <v>198.3381573320472</v>
       </c>
       <c r="D4" t="n">
-        <v>195.7142999782507</v>
+        <v>195.7142849059865</v>
       </c>
       <c r="E4" t="n">
-        <v>197.7999450700959</v>
+        <v>197.799929837213</v>
       </c>
       <c r="F4" t="n">
         <v>146838</v>
@@ -532,16 +532,16 @@
         <v>42951</v>
       </c>
       <c r="B6" t="n">
-        <v>191.7448272705078</v>
+        <v>191.7448425292969</v>
       </c>
       <c r="C6" t="n">
-        <v>201.567545836985</v>
+        <v>201.5675618774525</v>
       </c>
       <c r="D6" t="n">
-        <v>191.2065863955858</v>
+        <v>191.2066016115423</v>
       </c>
       <c r="E6" t="n">
-        <v>199.1454953716943</v>
+        <v>199.1455112194184</v>
       </c>
       <c r="F6" t="n">
         <v>302702</v>
@@ -572,16 +572,16 @@
         <v>42955</v>
       </c>
       <c r="B8" t="n">
-        <v>189.3900604248047</v>
+        <v>189.3900909423828</v>
       </c>
       <c r="C8" t="n">
-        <v>193.6286284723212</v>
+        <v>193.6286596728857</v>
       </c>
       <c r="D8" t="n">
-        <v>188.448148976055</v>
+        <v>188.4481793418572</v>
       </c>
       <c r="E8" t="n">
-        <v>193.6286284723212</v>
+        <v>193.6286596728857</v>
       </c>
       <c r="F8" t="n">
         <v>262129</v>
@@ -592,16 +592,16 @@
         <v>42956</v>
       </c>
       <c r="B9" t="n">
-        <v>186.6989135742188</v>
+        <v>186.6989288330078</v>
       </c>
       <c r="C9" t="n">
-        <v>190.399254500592</v>
+        <v>190.3992700618077</v>
       </c>
       <c r="D9" t="n">
-        <v>183.7386488663666</v>
+        <v>183.738663883215</v>
       </c>
       <c r="E9" t="n">
-        <v>189.7264701098856</v>
+        <v>189.726485616115</v>
       </c>
       <c r="F9" t="n">
         <v>202188</v>
@@ -632,16 +632,16 @@
         <v>42958</v>
       </c>
       <c r="B11" t="n">
-        <v>191.0720672607422</v>
+        <v>191.0720367431641</v>
       </c>
       <c r="C11" t="n">
-        <v>192.1485358344453</v>
+        <v>192.1485051449361</v>
       </c>
       <c r="D11" t="n">
-        <v>188.3809159096037</v>
+        <v>188.3808858218499</v>
       </c>
       <c r="E11" t="n">
-        <v>191.139345709802</v>
+        <v>191.1393151814783</v>
       </c>
       <c r="F11" t="n">
         <v>48476</v>
@@ -652,16 +652,16 @@
         <v>42961</v>
       </c>
       <c r="B12" t="n">
-        <v>191.0720672607422</v>
+        <v>191.0720367431641</v>
       </c>
       <c r="C12" t="n">
-        <v>192.0812573853854</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="D12" t="n">
-        <v>188.7845866039625</v>
+        <v>188.7845564517354</v>
       </c>
       <c r="E12" t="n">
-        <v>192.0812573853854</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="F12" t="n">
         <v>42790</v>
@@ -672,16 +672,16 @@
         <v>42962</v>
       </c>
       <c r="B13" t="n">
-        <v>191.0720672607422</v>
+        <v>191.0720367431641</v>
       </c>
       <c r="C13" t="n">
-        <v>192.0812573853854</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="D13" t="n">
-        <v>190.4665612192039</v>
+        <v>190.4665307983358</v>
       </c>
       <c r="E13" t="n">
-        <v>192.0812573853854</v>
+        <v>192.0812267066219</v>
       </c>
       <c r="F13" t="n">
         <v>72604</v>
@@ -692,16 +692,16 @@
         <v>42963</v>
       </c>
       <c r="B14" t="n">
-        <v>191.7448272705078</v>
+        <v>191.7448425292969</v>
       </c>
       <c r="C14" t="n">
-        <v>192.3503331924588</v>
+        <v>192.3503484994332</v>
       </c>
       <c r="D14" t="n">
-        <v>187.7753727824535</v>
+        <v>187.7753877253589</v>
       </c>
       <c r="E14" t="n">
-        <v>191.0720295240411</v>
+        <v>191.0720447292898</v>
       </c>
       <c r="F14" t="n">
         <v>141908</v>
@@ -732,16 +732,16 @@
         <v>42965</v>
       </c>
       <c r="B16" t="n">
-        <v>191.7448272705078</v>
+        <v>191.7448425292969</v>
       </c>
       <c r="C16" t="n">
-        <v>192.0812194493695</v>
+        <v>192.0812347349282</v>
       </c>
       <c r="D16" t="n">
-        <v>188.4481571401768</v>
+        <v>188.4481721366214</v>
       </c>
       <c r="E16" t="n">
-        <v>190.3992451663178</v>
+        <v>190.3992603180273</v>
       </c>
       <c r="F16" t="n">
         <v>326986</v>
@@ -772,16 +772,16 @@
         <v>42969</v>
       </c>
       <c r="B18" t="n">
-        <v>191.7448272705078</v>
+        <v>191.7448425292969</v>
       </c>
       <c r="C18" t="n">
-        <v>193.0903959859544</v>
+        <v>193.090411351822</v>
       </c>
       <c r="D18" t="n">
-        <v>190.6683589094071</v>
+        <v>190.6683740825323</v>
       </c>
       <c r="E18" t="n">
-        <v>192.5521684997758</v>
+        <v>192.5521838228119</v>
       </c>
       <c r="F18" t="n">
         <v>46233</v>
@@ -792,16 +792,16 @@
         <v>42970</v>
       </c>
       <c r="B19" t="n">
-        <v>188.8518371582031</v>
+        <v>188.8518676757812</v>
       </c>
       <c r="C19" t="n">
-        <v>191.8121152570719</v>
+        <v>191.8121462530172</v>
       </c>
       <c r="D19" t="n">
-        <v>188.111774327858</v>
+        <v>188.1118047258454</v>
       </c>
       <c r="E19" t="n">
-        <v>191.7448368179496</v>
+        <v>191.744867803023</v>
       </c>
       <c r="F19" t="n">
         <v>69265</v>
@@ -852,16 +852,16 @@
         <v>42975</v>
       </c>
       <c r="B22" t="n">
-        <v>203.5186614990234</v>
+        <v>203.5186462402344</v>
       </c>
       <c r="C22" t="n">
-        <v>204.0568890582882</v>
+        <v>204.0568737591456</v>
       </c>
       <c r="D22" t="n">
-        <v>198.4727379646801</v>
+        <v>198.4727230842086</v>
       </c>
       <c r="E22" t="n">
-        <v>200.894775370117</v>
+        <v>200.8947603080535</v>
       </c>
       <c r="F22" t="n">
         <v>228259</v>
@@ -872,16 +872,16 @@
         <v>42976</v>
       </c>
       <c r="B23" t="n">
-        <v>202.9803924560547</v>
+        <v>202.9804382324219</v>
       </c>
       <c r="C23" t="n">
-        <v>207.0171253692983</v>
+        <v>207.017172056034</v>
       </c>
       <c r="D23" t="n">
-        <v>199.1454948495989</v>
+        <v>199.1455397611157</v>
       </c>
       <c r="E23" t="n">
-        <v>202.9803924560547</v>
+        <v>202.9804382324219</v>
       </c>
       <c r="F23" t="n">
         <v>110895</v>
@@ -892,16 +892,16 @@
         <v>42977</v>
       </c>
       <c r="B24" t="n">
-        <v>203.8550262451172</v>
+        <v>203.8550415039062</v>
       </c>
       <c r="C24" t="n">
-        <v>204.3932537318321</v>
+        <v>204.3932690309082</v>
       </c>
       <c r="D24" t="n">
-        <v>199.9528501889469</v>
+        <v>199.9528651556535</v>
       </c>
       <c r="E24" t="n">
-        <v>204.191418424314</v>
+        <v>204.1914337082824</v>
       </c>
       <c r="F24" t="n">
         <v>64518</v>
@@ -912,16 +912,16 @@
         <v>42978</v>
       </c>
       <c r="B25" t="n">
-        <v>201.8367004394531</v>
+        <v>201.8367156982422</v>
       </c>
       <c r="C25" t="n">
-        <v>204.0569026581363</v>
+        <v>204.0569180847719</v>
       </c>
       <c r="D25" t="n">
-        <v>201.0293456580026</v>
+        <v>201.0293608557559</v>
       </c>
       <c r="E25" t="n">
-        <v>202.3749280345894</v>
+        <v>202.3749433340683</v>
       </c>
       <c r="F25" t="n">
         <v>24192</v>
@@ -952,16 +952,16 @@
         <v>42982</v>
       </c>
       <c r="B27" t="n">
-        <v>201.8367004394531</v>
+        <v>201.8367156982422</v>
       </c>
       <c r="C27" t="n">
-        <v>202.8458771803336</v>
+        <v>202.8458925154161</v>
       </c>
       <c r="D27" t="n">
-        <v>199.818333568946</v>
+        <v>199.8183486751472</v>
       </c>
       <c r="E27" t="n">
-        <v>200.4911180628663</v>
+        <v>200.4911332199298</v>
       </c>
       <c r="F27" t="n">
         <v>26931</v>
@@ -972,16 +972,16 @@
         <v>42983</v>
       </c>
       <c r="B28" t="n">
-        <v>203.8550262451172</v>
+        <v>203.8550415039062</v>
       </c>
       <c r="C28" t="n">
-        <v>205.1333165260652</v>
+        <v>205.1333318805358</v>
       </c>
       <c r="D28" t="n">
-        <v>201.2984189057343</v>
+        <v>201.2984339731583</v>
       </c>
       <c r="E28" t="n">
-        <v>201.8366597811927</v>
+        <v>201.8366748889046</v>
       </c>
       <c r="F28" t="n">
         <v>252530</v>
@@ -992,16 +992,16 @@
         <v>42984</v>
       </c>
       <c r="B29" t="n">
-        <v>207.0844268798828</v>
+        <v>207.0844573974609</v>
       </c>
       <c r="C29" t="n">
-        <v>208.5645660166659</v>
+        <v>208.5645967523689</v>
       </c>
       <c r="D29" t="n">
-        <v>205.2006170845439</v>
+        <v>205.2006473245091</v>
       </c>
       <c r="E29" t="n">
-        <v>205.2006170845439</v>
+        <v>205.2006473245091</v>
       </c>
       <c r="F29" t="n">
         <v>109786</v>
@@ -1032,16 +1032,16 @@
         <v>42989</v>
       </c>
       <c r="B31" t="n">
-        <v>212.4667205810547</v>
+        <v>212.4667510986328</v>
       </c>
       <c r="C31" t="n">
-        <v>213.9468595651856</v>
+        <v>213.9468902953629</v>
       </c>
       <c r="D31" t="n">
-        <v>210.6501894161539</v>
+        <v>210.6502196728153</v>
       </c>
       <c r="E31" t="n">
-        <v>211.9284930918229</v>
+        <v>211.9285235320929</v>
       </c>
       <c r="F31" t="n">
         <v>119189</v>
@@ -1072,16 +1072,16 @@
         <v>42991</v>
       </c>
       <c r="B33" t="n">
-        <v>209.8428955078125</v>
+        <v>209.8428649902344</v>
       </c>
       <c r="C33" t="n">
-        <v>212.8031607549543</v>
+        <v>212.803129806863</v>
       </c>
       <c r="D33" t="n">
-        <v>208.5645915438498</v>
+        <v>208.5645612121762</v>
       </c>
       <c r="E33" t="n">
-        <v>211.9958193390283</v>
+        <v>211.9957885083492</v>
       </c>
       <c r="F33" t="n">
         <v>61349</v>
@@ -1092,16 +1092,16 @@
         <v>42992</v>
       </c>
       <c r="B34" t="n">
-        <v>209.5737457275391</v>
+        <v>209.5737609863281</v>
       </c>
       <c r="C34" t="n">
-        <v>212.6012889063066</v>
+        <v>212.6013043855272</v>
       </c>
       <c r="D34" t="n">
-        <v>208.9009479410119</v>
+        <v>208.9009631508154</v>
       </c>
       <c r="E34" t="n">
-        <v>208.9009479410119</v>
+        <v>208.9009631508154</v>
       </c>
       <c r="F34" t="n">
         <v>51645</v>
@@ -1112,16 +1112,16 @@
         <v>42993</v>
       </c>
       <c r="B35" t="n">
-        <v>213.5432281494141</v>
+        <v>213.543212890625</v>
       </c>
       <c r="C35" t="n">
-        <v>213.6777850464233</v>
+        <v>213.6777697780194</v>
       </c>
       <c r="D35" t="n">
-        <v>209.3046457273865</v>
+        <v>209.3046307714664</v>
       </c>
       <c r="E35" t="n">
-        <v>209.3046457273865</v>
+        <v>209.3046307714664</v>
       </c>
       <c r="F35" t="n">
         <v>102613</v>
@@ -1212,16 +1212,16 @@
         <v>43000</v>
       </c>
       <c r="B40" t="n">
-        <v>214.5523986816406</v>
+        <v>214.5524139404297</v>
       </c>
       <c r="C40" t="n">
-        <v>214.6196771282025</v>
+        <v>214.6196923917764</v>
       </c>
       <c r="D40" t="n">
-        <v>210.4483866638742</v>
+        <v>210.4484016307894</v>
       </c>
       <c r="E40" t="n">
-        <v>211.7266905372957</v>
+        <v>211.7267055951228</v>
       </c>
       <c r="F40" t="n">
         <v>36999</v>
@@ -1232,16 +1232,16 @@
         <v>43003</v>
       </c>
       <c r="B41" t="n">
-        <v>210.9193267822266</v>
+        <v>210.9193420410156</v>
       </c>
       <c r="C41" t="n">
-        <v>215.8979717814236</v>
+        <v>215.8979874003888</v>
       </c>
       <c r="D41" t="n">
-        <v>209.9774285705851</v>
+        <v>209.9774437612333</v>
       </c>
       <c r="E41" t="n">
-        <v>214.7542248499711</v>
+        <v>214.7542403861928</v>
       </c>
       <c r="F41" t="n">
         <v>77912</v>
@@ -1252,16 +1252,16 @@
         <v>43004</v>
       </c>
       <c r="B42" t="n">
-        <v>209.3046417236328</v>
+        <v>209.3046264648438</v>
       </c>
       <c r="C42" t="n">
-        <v>212.4667555203533</v>
+        <v>212.4667400310389</v>
       </c>
       <c r="D42" t="n">
-        <v>207.95907277928</v>
+        <v>207.959057618586</v>
       </c>
       <c r="E42" t="n">
-        <v>211.4575788120887</v>
+        <v>211.4575633963456</v>
       </c>
       <c r="F42" t="n">
         <v>43625</v>
@@ -1272,16 +1272,16 @@
         <v>43005</v>
       </c>
       <c r="B43" t="n">
-        <v>206.5461883544922</v>
+        <v>206.5462341308594</v>
       </c>
       <c r="C43" t="n">
-        <v>210.9865921400306</v>
+        <v>210.9866389005145</v>
       </c>
       <c r="D43" t="n">
-        <v>205.940682398849</v>
+        <v>205.9407280410193</v>
       </c>
       <c r="E43" t="n">
-        <v>209.910137107776</v>
+        <v>209.9101836296876</v>
       </c>
       <c r="F43" t="n">
         <v>41486</v>
@@ -1312,16 +1312,16 @@
         <v>43007</v>
       </c>
       <c r="B45" t="n">
-        <v>203.5186614990234</v>
+        <v>203.5186462402344</v>
       </c>
       <c r="C45" t="n">
-        <v>206.7480402433576</v>
+        <v>206.7480247424462</v>
       </c>
       <c r="D45" t="n">
-        <v>199.6837633617711</v>
+        <v>199.6837483905032</v>
       </c>
       <c r="E45" t="n">
-        <v>206.7480402433576</v>
+        <v>206.7480247424462</v>
       </c>
       <c r="F45" t="n">
         <v>174513</v>
@@ -1332,16 +1332,16 @@
         <v>43010</v>
       </c>
       <c r="B46" t="n">
-        <v>207.3535614013672</v>
+        <v>207.3535308837891</v>
       </c>
       <c r="C46" t="n">
-        <v>209.1700929353872</v>
+        <v>209.1700621504582</v>
       </c>
       <c r="D46" t="n">
-        <v>203.5186763725986</v>
+        <v>203.5186464194256</v>
       </c>
       <c r="E46" t="n">
-        <v>204.2587393206731</v>
+        <v>204.2587092585802</v>
       </c>
       <c r="F46" t="n">
         <v>97827</v>
@@ -1352,16 +1352,16 @@
         <v>43011</v>
       </c>
       <c r="B47" t="n">
-        <v>206.9498596191406</v>
+        <v>206.9498748779297</v>
       </c>
       <c r="C47" t="n">
-        <v>208.0936064831236</v>
+        <v>208.0936218262432</v>
       </c>
       <c r="D47" t="n">
-        <v>203.7204811238401</v>
+        <v>203.7204961445212</v>
       </c>
       <c r="E47" t="n">
-        <v>207.0171380588606</v>
+        <v>207.0171533226102</v>
       </c>
       <c r="F47" t="n">
         <v>216534</v>
@@ -1392,16 +1392,16 @@
         <v>43013</v>
       </c>
       <c r="B49" t="n">
-        <v>204.1241607666016</v>
+        <v>204.1241760253906</v>
       </c>
       <c r="C49" t="n">
-        <v>207.8917803346051</v>
+        <v>207.8917958750332</v>
       </c>
       <c r="D49" t="n">
-        <v>202.980413852165</v>
+        <v>202.9804290254561</v>
       </c>
       <c r="E49" t="n">
-        <v>207.3535394043583</v>
+        <v>207.3535549045515</v>
       </c>
       <c r="F49" t="n">
         <v>185260</v>
@@ -1412,16 +1412,16 @@
         <v>43014</v>
       </c>
       <c r="B50" t="n">
-        <v>201.5002746582031</v>
+        <v>201.5002899169922</v>
       </c>
       <c r="C50" t="n">
-        <v>205.2678805858865</v>
+        <v>205.267896129981</v>
       </c>
       <c r="D50" t="n">
-        <v>200.491084696529</v>
+        <v>200.4910998788963</v>
       </c>
       <c r="E50" t="n">
-        <v>204.191425574761</v>
+        <v>204.1914410373398</v>
       </c>
       <c r="F50" t="n">
         <v>72512</v>
@@ -1432,16 +1432,16 @@
         <v>43017</v>
       </c>
       <c r="B51" t="n">
-        <v>207.0844268798828</v>
+        <v>207.0844573974609</v>
       </c>
       <c r="C51" t="n">
-        <v>207.0844268798828</v>
+        <v>207.0844573974609</v>
       </c>
       <c r="D51" t="n">
-        <v>202.17307375663</v>
+        <v>202.1731035504328</v>
       </c>
       <c r="E51" t="n">
-        <v>202.17307375663</v>
+        <v>202.1731035504328</v>
       </c>
       <c r="F51" t="n">
         <v>84107</v>
@@ -1492,16 +1492,16 @@
         <v>43021</v>
       </c>
       <c r="B54" t="n">
-        <v>211.0538787841797</v>
+        <v>211.0538940429688</v>
       </c>
       <c r="C54" t="n">
-        <v>213.0722454368643</v>
+        <v>213.0722608415774</v>
       </c>
       <c r="D54" t="n">
-        <v>210.2465374786037</v>
+        <v>210.2465526790236</v>
       </c>
       <c r="E54" t="n">
-        <v>210.2465374786037</v>
+        <v>210.2465526790236</v>
       </c>
       <c r="F54" t="n">
         <v>88189</v>
@@ -1532,16 +1532,16 @@
         <v>43025</v>
       </c>
       <c r="B56" t="n">
-        <v>213.2740783691406</v>
+        <v>213.2740631103516</v>
       </c>
       <c r="C56" t="n">
-        <v>215.1578881164158</v>
+        <v>215.1578727228487</v>
       </c>
       <c r="D56" t="n">
-        <v>212.130344865747</v>
+        <v>212.1303296887869</v>
       </c>
       <c r="E56" t="n">
-        <v>214.1487114957744</v>
+        <v>214.1486961744093</v>
       </c>
       <c r="F56" t="n">
         <v>68039</v>
@@ -1552,16 +1552,16 @@
         <v>43026</v>
       </c>
       <c r="B57" t="n">
-        <v>215.6288452148438</v>
+        <v>215.6288757324219</v>
       </c>
       <c r="C57" t="n">
-        <v>215.6288452148438</v>
+        <v>215.6288757324219</v>
       </c>
       <c r="D57" t="n">
-        <v>211.9957826936906</v>
+        <v>211.9958126970877</v>
       </c>
       <c r="E57" t="n">
-        <v>214.6196552306371</v>
+        <v>214.6196856053863</v>
       </c>
       <c r="F57" t="n">
         <v>93014</v>
@@ -1572,16 +1572,16 @@
         <v>43027</v>
       </c>
       <c r="B58" t="n">
-        <v>219.5983123779297</v>
+        <v>219.5982971191406</v>
       </c>
       <c r="C58" t="n">
-        <v>220.8766028046159</v>
+        <v>220.8765874570048</v>
       </c>
       <c r="D58" t="n">
-        <v>212.6013006979307</v>
+        <v>212.6012859253291</v>
       </c>
       <c r="E58" t="n">
-        <v>213.0722498024993</v>
+        <v>213.0722349971738</v>
       </c>
       <c r="F58" t="n">
         <v>143656</v>
@@ -1592,16 +1592,16 @@
         <v>43028</v>
       </c>
       <c r="B59" t="n">
-        <v>223.50048828125</v>
+        <v>223.5005035400391</v>
       </c>
       <c r="C59" t="n">
-        <v>225.9225122411252</v>
+        <v>225.9225276652703</v>
       </c>
       <c r="D59" t="n">
-        <v>220.9438806572252</v>
+        <v>220.94389574147</v>
       </c>
       <c r="E59" t="n">
-        <v>220.9438806572252</v>
+        <v>220.94389574147</v>
       </c>
       <c r="F59" t="n">
         <v>90497</v>
@@ -1612,16 +1612,16 @@
         <v>43031</v>
       </c>
       <c r="B60" t="n">
-        <v>221.3475494384766</v>
+        <v>221.3475646972656</v>
       </c>
       <c r="C60" t="n">
-        <v>226.1243590405879</v>
+        <v>226.1243746286705</v>
       </c>
       <c r="D60" t="n">
-        <v>220.8766003391648</v>
+        <v>220.8766155654885</v>
       </c>
       <c r="E60" t="n">
-        <v>225.5188396670136</v>
+        <v>225.5188552133542</v>
       </c>
       <c r="F60" t="n">
         <v>72604</v>
@@ -1632,16 +1632,16 @@
         <v>43032</v>
       </c>
       <c r="B61" t="n">
-        <v>219.5983123779297</v>
+        <v>219.5982971191406</v>
       </c>
       <c r="C61" t="n">
-        <v>223.8368810965369</v>
+        <v>223.8368655432309</v>
       </c>
       <c r="D61" t="n">
-        <v>218.7236792235573</v>
+        <v>218.7236640255422</v>
       </c>
       <c r="E61" t="n">
-        <v>221.4148437414392</v>
+        <v>221.4148283564285</v>
       </c>
       <c r="F61" t="n">
         <v>87785</v>
@@ -1652,16 +1652,16 @@
         <v>43033</v>
       </c>
       <c r="B62" t="n">
-        <v>218.9927825927734</v>
+        <v>218.9928131103516</v>
       </c>
       <c r="C62" t="n">
-        <v>221.1457060715419</v>
+        <v>221.1457368891391</v>
       </c>
       <c r="D62" t="n">
-        <v>217.108972875258</v>
+        <v>217.1090031303192</v>
       </c>
       <c r="E62" t="n">
-        <v>219.8001372652768</v>
+        <v>219.8001678953632</v>
       </c>
       <c r="F62" t="n">
         <v>83611</v>
@@ -1672,16 +1672,16 @@
         <v>43034</v>
       </c>
       <c r="B63" t="n">
-        <v>221.8185119628906</v>
+        <v>221.8185272216797</v>
       </c>
       <c r="C63" t="n">
-        <v>223.3659161465973</v>
+        <v>223.3659315118316</v>
       </c>
       <c r="D63" t="n">
-        <v>218.3200061613684</v>
+        <v>218.320021179497</v>
       </c>
       <c r="E63" t="n">
-        <v>219.5983099627405</v>
+        <v>219.598325068803</v>
       </c>
       <c r="F63" t="n">
         <v>55545</v>
@@ -1692,16 +1692,16 @@
         <v>43035</v>
       </c>
       <c r="B64" t="n">
-        <v>223.029541015625</v>
+        <v>223.0295257568359</v>
       </c>
       <c r="C64" t="n">
-        <v>225.3843000816768</v>
+        <v>225.3842846617846</v>
       </c>
       <c r="D64" t="n">
-        <v>219.6656052307278</v>
+        <v>219.6655902020858</v>
       </c>
       <c r="E64" t="n">
-        <v>222.0203642967796</v>
+        <v>222.0203491070344</v>
       </c>
       <c r="F64" t="n">
         <v>55858</v>
@@ -1752,16 +1752,16 @@
         <v>43040</v>
       </c>
       <c r="B67" t="n">
-        <v>223.7696228027344</v>
+        <v>223.7695922851562</v>
       </c>
       <c r="C67" t="n">
-        <v>227.6045078168565</v>
+        <v>227.6044767762788</v>
       </c>
       <c r="D67" t="n">
-        <v>222.4913188721962</v>
+        <v>222.4912885289525</v>
       </c>
       <c r="E67" t="n">
-        <v>225.3843055923663</v>
+        <v>225.3842748545786</v>
       </c>
       <c r="F67" t="n">
         <v>232015</v>
@@ -1772,16 +1772,16 @@
         <v>43042</v>
       </c>
       <c r="B68" t="n">
-        <v>225.2497406005859</v>
+        <v>225.2497100830078</v>
       </c>
       <c r="C68" t="n">
-        <v>227.0662720624047</v>
+        <v>227.066241298717</v>
       </c>
       <c r="D68" t="n">
-        <v>223.5005009746637</v>
+        <v>223.5004706940783</v>
       </c>
       <c r="E68" t="n">
-        <v>226.7298932153962</v>
+        <v>226.7298624972821</v>
       </c>
       <c r="F68" t="n">
         <v>201288</v>
@@ -1832,16 +1832,16 @@
         <v>43047</v>
       </c>
       <c r="B71" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C71" t="n">
-        <v>234.0994316756239</v>
+        <v>234.0994470241699</v>
       </c>
       <c r="D71" t="n">
-        <v>230.1293234466875</v>
+        <v>230.1293385349365</v>
       </c>
       <c r="E71" t="n">
-        <v>230.8138474119391</v>
+        <v>230.8138625450684</v>
       </c>
       <c r="F71" t="n">
         <v>198823</v>
@@ -1892,16 +1892,16 @@
         <v>43052</v>
       </c>
       <c r="B74" t="n">
-        <v>232.6620178222656</v>
+        <v>232.6619873046875</v>
       </c>
       <c r="C74" t="n">
-        <v>232.7304538772009</v>
+        <v>232.7304233506462</v>
       </c>
       <c r="D74" t="n">
-        <v>228.7603453813829</v>
+        <v>228.7603153755755</v>
       </c>
       <c r="E74" t="n">
-        <v>231.0191983363378</v>
+        <v>231.0191680342434</v>
       </c>
       <c r="F74" t="n">
         <v>214187</v>
@@ -1912,16 +1912,16 @@
         <v>43053</v>
       </c>
       <c r="B75" t="n">
-        <v>230.5400390625</v>
+        <v>230.5400238037109</v>
       </c>
       <c r="C75" t="n">
-        <v>232.4566298026679</v>
+        <v>232.4566144170252</v>
       </c>
       <c r="D75" t="n">
-        <v>228.9656830469659</v>
+        <v>228.965667892379</v>
       </c>
       <c r="E75" t="n">
-        <v>232.4566298026679</v>
+        <v>232.4566144170252</v>
       </c>
       <c r="F75" t="n">
         <v>164145</v>
@@ -1932,16 +1932,16 @@
         <v>43055</v>
       </c>
       <c r="B76" t="n">
-        <v>229.992431640625</v>
+        <v>229.9924163818359</v>
       </c>
       <c r="C76" t="n">
-        <v>232.7989091566504</v>
+        <v>232.7988937116663</v>
       </c>
       <c r="D76" t="n">
-        <v>229.1710355477816</v>
+        <v>229.1710203434879</v>
       </c>
       <c r="E76" t="n">
-        <v>230.471592983276</v>
+        <v>230.4715776926971</v>
       </c>
       <c r="F76" t="n">
         <v>84511</v>
@@ -1972,16 +1972,16 @@
         <v>43060</v>
       </c>
       <c r="B78" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C78" t="n">
-        <v>235.3999890684911</v>
+        <v>235.4000045023071</v>
       </c>
       <c r="D78" t="n">
-        <v>228.9656926417911</v>
+        <v>228.9657076537476</v>
       </c>
       <c r="E78" t="n">
-        <v>231.0191828065941</v>
+        <v>231.019197953186</v>
       </c>
       <c r="F78" t="n">
         <v>104948</v>
@@ -2012,16 +2012,16 @@
         <v>43062</v>
       </c>
       <c r="B80" t="n">
-        <v>231.9774932861328</v>
+        <v>231.9774780273438</v>
       </c>
       <c r="C80" t="n">
-        <v>234.4417088876228</v>
+        <v>234.441693466745</v>
       </c>
       <c r="D80" t="n">
-        <v>231.3614598184996</v>
+        <v>231.3614446002314</v>
       </c>
       <c r="E80" t="n">
-        <v>233.3465140619172</v>
+        <v>233.3464987130781</v>
       </c>
       <c r="F80" t="n">
         <v>12911</v>
@@ -2032,16 +2032,16 @@
         <v>43063</v>
       </c>
       <c r="B81" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C81" t="n">
-        <v>234.4416936582497</v>
+        <v>234.4417090292359</v>
       </c>
       <c r="D81" t="n">
-        <v>230.6769480676189</v>
+        <v>230.6769631917725</v>
       </c>
       <c r="E81" t="n">
-        <v>232.0459415108209</v>
+        <v>232.0459567247315</v>
       </c>
       <c r="F81" t="n">
         <v>49924</v>
@@ -2052,16 +2052,16 @@
         <v>43066</v>
       </c>
       <c r="B82" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C82" t="n">
-        <v>233.4833982480083</v>
+        <v>233.4834135561646</v>
       </c>
       <c r="D82" t="n">
-        <v>231.5667801838749</v>
+        <v>231.5667953663696</v>
       </c>
       <c r="E82" t="n">
-        <v>233.4833982480083</v>
+        <v>233.4834135561646</v>
       </c>
       <c r="F82" t="n">
         <v>74064</v>
@@ -2072,16 +2072,16 @@
         <v>43067</v>
       </c>
       <c r="B83" t="n">
-        <v>231.7721557617188</v>
+        <v>231.7721252441406</v>
       </c>
       <c r="C83" t="n">
-        <v>233.0727132271944</v>
+        <v>233.0726825383711</v>
       </c>
       <c r="D83" t="n">
-        <v>231.7721557617188</v>
+        <v>231.7721252441406</v>
       </c>
       <c r="E83" t="n">
-        <v>232.7304512254605</v>
+        <v>232.7304205817031</v>
       </c>
       <c r="F83" t="n">
         <v>48463</v>
@@ -2092,16 +2092,16 @@
         <v>43068</v>
       </c>
       <c r="B84" t="n">
-        <v>232.5250854492188</v>
+        <v>232.5251007080078</v>
       </c>
       <c r="C84" t="n">
-        <v>232.7304208285185</v>
+        <v>232.7304361007821</v>
       </c>
       <c r="D84" t="n">
-        <v>229.3763735216686</v>
+        <v>229.3763885738325</v>
       </c>
       <c r="E84" t="n">
-        <v>231.7721254899398</v>
+        <v>231.772140699318</v>
       </c>
       <c r="F84" t="n">
         <v>67439</v>
@@ -2112,16 +2112,16 @@
         <v>43069</v>
       </c>
       <c r="B85" t="n">
-        <v>235.1261901855469</v>
+        <v>235.1261749267578</v>
       </c>
       <c r="C85" t="n">
-        <v>235.1261901855469</v>
+        <v>235.1261749267578</v>
       </c>
       <c r="D85" t="n">
-        <v>230.0608872062348</v>
+        <v>230.0608722761645</v>
       </c>
       <c r="E85" t="n">
-        <v>232.4566393516838</v>
+        <v>232.4566242661383</v>
       </c>
       <c r="F85" t="n">
         <v>138609</v>
@@ -2132,16 +2132,16 @@
         <v>43070</v>
       </c>
       <c r="B86" t="n">
-        <v>234.7154846191406</v>
+        <v>234.7154693603516</v>
       </c>
       <c r="C86" t="n">
-        <v>237.8641966784879</v>
+        <v>237.8641812150019</v>
       </c>
       <c r="D86" t="n">
-        <v>233.6887259487187</v>
+        <v>233.6887107566789</v>
       </c>
       <c r="E86" t="n">
-        <v>234.7154846191406</v>
+        <v>234.7154693603516</v>
       </c>
       <c r="F86" t="n">
         <v>135061</v>
@@ -2152,16 +2152,16 @@
         <v>43073</v>
       </c>
       <c r="B87" t="n">
-        <v>232.6620178222656</v>
+        <v>232.6619873046875</v>
       </c>
       <c r="C87" t="n">
-        <v>237.5219584941565</v>
+        <v>237.5219273391146</v>
       </c>
       <c r="D87" t="n">
-        <v>232.6620178222656</v>
+        <v>232.6619873046875</v>
       </c>
       <c r="E87" t="n">
-        <v>235.4684681913123</v>
+        <v>235.4684373056205</v>
       </c>
       <c r="F87" t="n">
         <v>80546</v>
@@ -2172,16 +2172,16 @@
         <v>43074</v>
       </c>
       <c r="B88" t="n">
-        <v>230.1293029785156</v>
+        <v>230.1293182373047</v>
       </c>
       <c r="C88" t="n">
-        <v>234.2363101864865</v>
+        <v>234.2363257175919</v>
       </c>
       <c r="D88" t="n">
-        <v>230.1293029785156</v>
+        <v>230.1293182373047</v>
       </c>
       <c r="E88" t="n">
-        <v>232.7304175329016</v>
+        <v>232.7304329641582</v>
       </c>
       <c r="F88" t="n">
         <v>50811</v>
@@ -2192,16 +2192,16 @@
         <v>43075</v>
       </c>
       <c r="B89" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C89" t="n">
-        <v>235.3999890684911</v>
+        <v>235.4000045023071</v>
       </c>
       <c r="D89" t="n">
-        <v>229.5132900190719</v>
+        <v>229.5133050669312</v>
       </c>
       <c r="E89" t="n">
-        <v>229.9239880520325</v>
+        <v>229.9240031268189</v>
       </c>
       <c r="F89" t="n">
         <v>49754</v>
@@ -2212,16 +2212,16 @@
         <v>43076</v>
       </c>
       <c r="B90" t="n">
-        <v>230.7453765869141</v>
+        <v>230.7453918457031</v>
       </c>
       <c r="C90" t="n">
-        <v>232.6619945884931</v>
+        <v>232.6620099740248</v>
       </c>
       <c r="D90" t="n">
-        <v>229.5817185763464</v>
+        <v>229.5817337581848</v>
       </c>
       <c r="E90" t="n">
-        <v>231.2929739463224</v>
+        <v>231.2929892413232</v>
       </c>
       <c r="F90" t="n">
         <v>47133</v>
@@ -2232,16 +2232,16 @@
         <v>43077</v>
       </c>
       <c r="B91" t="n">
-        <v>230.7453765869141</v>
+        <v>230.7453918457031</v>
       </c>
       <c r="C91" t="n">
-        <v>232.0459339373338</v>
+        <v>232.0459492821265</v>
       </c>
       <c r="D91" t="n">
-        <v>228.2811748477515</v>
+        <v>228.2811899435872</v>
       </c>
       <c r="E91" t="n">
-        <v>232.0459339373338</v>
+        <v>232.0459492821265</v>
       </c>
       <c r="F91" t="n">
         <v>61101</v>
@@ -2272,16 +2272,16 @@
         <v>43081</v>
       </c>
       <c r="B93" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C93" t="n">
-        <v>232.9358008707275</v>
+        <v>232.935816142981</v>
       </c>
       <c r="D93" t="n">
-        <v>230.8822834622739</v>
+        <v>230.8822985998901</v>
       </c>
       <c r="E93" t="n">
-        <v>231.5667801838749</v>
+        <v>231.5667953663696</v>
       </c>
       <c r="F93" t="n">
         <v>108939</v>
@@ -2292,16 +2292,16 @@
         <v>43082</v>
       </c>
       <c r="B94" t="n">
-        <v>228.144287109375</v>
+        <v>228.1442718505859</v>
       </c>
       <c r="C94" t="n">
-        <v>235.2630940091604</v>
+        <v>235.2630782742499</v>
       </c>
       <c r="D94" t="n">
-        <v>226.090783285345</v>
+        <v>226.0907681638988</v>
       </c>
       <c r="E94" t="n">
-        <v>233.3465031537696</v>
+        <v>233.3464875470449</v>
       </c>
       <c r="F94" t="n">
         <v>51971</v>
@@ -2312,16 +2312,16 @@
         <v>43083</v>
       </c>
       <c r="B95" t="n">
-        <v>229.44482421875</v>
+        <v>229.4448089599609</v>
       </c>
       <c r="C95" t="n">
-        <v>229.7186229043996</v>
+        <v>229.7186076274021</v>
       </c>
       <c r="D95" t="n">
-        <v>226.5014747261921</v>
+        <v>226.5014596631448</v>
       </c>
       <c r="E95" t="n">
-        <v>226.5699243976045</v>
+        <v>226.5699093300051</v>
       </c>
       <c r="F95" t="n">
         <v>83520</v>
@@ -2372,16 +2372,16 @@
         <v>43088</v>
       </c>
       <c r="B98" t="n">
-        <v>224.5164337158203</v>
+        <v>224.5164184570312</v>
       </c>
       <c r="C98" t="n">
-        <v>226.4330382488716</v>
+        <v>226.4330228598245</v>
       </c>
       <c r="D98" t="n">
-        <v>223.1474265859763</v>
+        <v>223.1474114202289</v>
       </c>
       <c r="E98" t="n">
-        <v>225.9538905210653</v>
+        <v>225.9538751645824</v>
       </c>
       <c r="F98" t="n">
         <v>28066</v>
@@ -2432,16 +2432,16 @@
         <v>43091</v>
       </c>
       <c r="B101" t="n">
-        <v>230.5400390625</v>
+        <v>230.5400238037109</v>
       </c>
       <c r="C101" t="n">
-        <v>230.5400390625</v>
+        <v>230.5400238037109</v>
       </c>
       <c r="D101" t="n">
-        <v>225.2009103704476</v>
+        <v>225.2008954650403</v>
       </c>
       <c r="E101" t="n">
-        <v>226.9806153938569</v>
+        <v>226.9806003706559</v>
       </c>
       <c r="F101" t="n">
         <v>94553</v>
@@ -2452,16 +2452,16 @@
         <v>43095</v>
       </c>
       <c r="B102" t="n">
-        <v>232.7988739013672</v>
+        <v>232.7989044189453</v>
       </c>
       <c r="C102" t="n">
-        <v>233.6887059120314</v>
+        <v>233.6887365462575</v>
       </c>
       <c r="D102" t="n">
-        <v>226.5698999866571</v>
+        <v>226.5699296876797</v>
       </c>
       <c r="E102" t="n">
-        <v>230.6084574085188</v>
+        <v>230.6084876389555</v>
       </c>
       <c r="F102" t="n">
         <v>75564</v>
@@ -2472,16 +2472,16 @@
         <v>43096</v>
       </c>
       <c r="B103" t="n">
-        <v>230.6769561767578</v>
+        <v>230.6769409179688</v>
       </c>
       <c r="C103" t="n">
-        <v>232.7304464137485</v>
+        <v>232.7304310191254</v>
       </c>
       <c r="D103" t="n">
-        <v>230.6769561767578</v>
+        <v>230.6769409179688</v>
       </c>
       <c r="E103" t="n">
-        <v>232.6620103610079</v>
+        <v>232.6619949709117</v>
       </c>
       <c r="F103" t="n">
         <v>56145</v>
@@ -2492,16 +2492,16 @@
         <v>43097</v>
       </c>
       <c r="B104" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C104" t="n">
-        <v>233.0727002150477</v>
+        <v>233.0727154962769</v>
       </c>
       <c r="D104" t="n">
-        <v>228.1442829540446</v>
+        <v>228.144297912146</v>
       </c>
       <c r="E104" t="n">
-        <v>230.7453841179537</v>
+        <v>230.7453992465942</v>
       </c>
       <c r="F104" t="n">
         <v>86715</v>
@@ -2512,16 +2512,16 @@
         <v>43102</v>
       </c>
       <c r="B105" t="n">
-        <v>230.7453765869141</v>
+        <v>230.7453918457031</v>
       </c>
       <c r="C105" t="n">
-        <v>233.6202899674578</v>
+        <v>233.6203054163598</v>
       </c>
       <c r="D105" t="n">
-        <v>228.9656851688368</v>
+        <v>228.965700309938</v>
       </c>
       <c r="E105" t="n">
-        <v>228.9656851688368</v>
+        <v>228.965700309938</v>
       </c>
       <c r="F105" t="n">
         <v>75969</v>
@@ -2532,16 +2532,16 @@
         <v>43103</v>
       </c>
       <c r="B106" t="n">
-        <v>230.7453765869141</v>
+        <v>230.7453918457031</v>
       </c>
       <c r="C106" t="n">
-        <v>232.114369985435</v>
+        <v>232.1143853347532</v>
       </c>
       <c r="D106" t="n">
-        <v>229.3763831883931</v>
+        <v>229.376398356653</v>
       </c>
       <c r="E106" t="n">
-        <v>230.813839878665</v>
+        <v>230.8138551419814</v>
       </c>
       <c r="F106" t="n">
         <v>106056</v>
@@ -2552,16 +2552,16 @@
         <v>43104</v>
       </c>
       <c r="B107" t="n">
-        <v>232.7304382324219</v>
+        <v>232.7304534912109</v>
       </c>
       <c r="C107" t="n">
-        <v>234.0994316756239</v>
+        <v>234.0994470241699</v>
       </c>
       <c r="D107" t="n">
-        <v>228.9656926417911</v>
+        <v>228.9657076537476</v>
       </c>
       <c r="E107" t="n">
-        <v>230.8138474119391</v>
+        <v>230.8138625450684</v>
       </c>
       <c r="F107" t="n">
         <v>136353</v>
@@ -2572,16 +2572,16 @@
         <v>43105</v>
       </c>
       <c r="B108" t="n">
-        <v>235.7422180175781</v>
+        <v>235.7422637939453</v>
       </c>
       <c r="C108" t="n">
-        <v>236.7689765779297</v>
+        <v>236.7690225536726</v>
       </c>
       <c r="D108" t="n">
-        <v>230.8138150689962</v>
+        <v>230.8138598883673</v>
       </c>
       <c r="E108" t="n">
-        <v>231.3614123695445</v>
+        <v>231.3614572952479</v>
       </c>
       <c r="F108" t="n">
         <v>47198</v>
@@ -2612,16 +2612,16 @@
         <v>43109</v>
       </c>
       <c r="B110" t="n">
-        <v>239.2332153320312</v>
+        <v>239.2331695556641</v>
       </c>
       <c r="C110" t="n">
-        <v>241.5605315981914</v>
+        <v>241.5604853765011</v>
       </c>
       <c r="D110" t="n">
-        <v>238.4802552617466</v>
+        <v>238.4802096294555</v>
       </c>
       <c r="E110" t="n">
-        <v>240.5337728193765</v>
+        <v>240.5337267941526</v>
       </c>
       <c r="F110" t="n">
         <v>125476</v>
@@ -2632,16 +2632,16 @@
         <v>43110</v>
       </c>
       <c r="B111" t="n">
-        <v>239.1647644042969</v>
+        <v>239.1647796630859</v>
       </c>
       <c r="C111" t="n">
-        <v>241.4920532820823</v>
+        <v>241.4920686893532</v>
       </c>
       <c r="D111" t="n">
-        <v>238.0011063435787</v>
+        <v>238.001121528126</v>
       </c>
       <c r="E111" t="n">
-        <v>241.3551539363303</v>
+        <v>241.3551693348669</v>
       </c>
       <c r="F111" t="n">
         <v>106434</v>
@@ -2652,16 +2652,16 @@
         <v>43111</v>
       </c>
       <c r="B112" t="n">
-        <v>246.4204711914062</v>
+        <v>246.4204254150391</v>
       </c>
       <c r="C112" t="n">
-        <v>246.4204711914062</v>
+        <v>246.4204254150391</v>
       </c>
       <c r="D112" t="n">
-        <v>238.3433548386773</v>
+        <v>238.3433105627579</v>
       </c>
       <c r="E112" t="n">
-        <v>239.575476265191</v>
+        <v>239.5754317603862</v>
       </c>
       <c r="F112" t="n">
         <v>230476</v>
@@ -2672,16 +2672,16 @@
         <v>43112</v>
       </c>
       <c r="B113" t="n">
-        <v>253.1970367431641</v>
+        <v>253.197021484375</v>
       </c>
       <c r="C113" t="n">
-        <v>255.250526881161</v>
+        <v>255.2505114986194</v>
       </c>
       <c r="D113" t="n">
-        <v>244.2984977475599</v>
+        <v>244.2984830250367</v>
       </c>
       <c r="E113" t="n">
-        <v>244.435397090093</v>
+        <v>244.4353823593196</v>
       </c>
       <c r="F113" t="n">
         <v>209648</v>
@@ -2712,16 +2712,16 @@
         <v>43116</v>
       </c>
       <c r="B115" t="n">
-        <v>258.4676818847656</v>
+        <v>258.4677124023438</v>
       </c>
       <c r="C115" t="n">
-        <v>260.1105012822392</v>
+        <v>260.1105319937869</v>
       </c>
       <c r="D115" t="n">
-        <v>257.5093864617024</v>
+        <v>257.5094168661335</v>
       </c>
       <c r="E115" t="n">
-        <v>257.5093864617024</v>
+        <v>257.5094168661335</v>
       </c>
       <c r="F115" t="n">
         <v>112382</v>
@@ -2792,16 +2792,16 @@
         <v>43122</v>
       </c>
       <c r="B119" t="n">
-        <v>261.13720703125</v>
+        <v>261.1372375488281</v>
       </c>
       <c r="C119" t="n">
-        <v>265.3126498637629</v>
+        <v>265.3126808693007</v>
       </c>
       <c r="D119" t="n">
-        <v>256.0034417264086</v>
+        <v>256.0034716440336</v>
       </c>
       <c r="E119" t="n">
-        <v>256.687938318325</v>
+        <v>256.6879683159431</v>
       </c>
       <c r="F119" t="n">
         <v>99157</v>
@@ -2912,16 +2912,16 @@
         <v>43131</v>
       </c>
       <c r="B125" t="n">
-        <v>257.0302124023438</v>
+        <v>257.0302734375</v>
       </c>
       <c r="C125" t="n">
-        <v>259.9735615087273</v>
+        <v>259.9736232428199</v>
       </c>
       <c r="D125" t="n">
-        <v>255.4558565445929</v>
+        <v>255.4559172058979</v>
       </c>
       <c r="E125" t="n">
-        <v>257.4409103769336</v>
+        <v>257.4409715096153</v>
       </c>
       <c r="F125" t="n">
         <v>347644</v>
@@ -2932,16 +2932,16 @@
         <v>43132</v>
       </c>
       <c r="B126" t="n">
-        <v>259.083740234375</v>
+        <v>259.0836791992188</v>
       </c>
       <c r="C126" t="n">
-        <v>261.0003583069165</v>
+        <v>261.0002968202418</v>
       </c>
       <c r="D126" t="n">
-        <v>256.6879880764362</v>
+        <v>256.6879276056732</v>
       </c>
       <c r="E126" t="n">
-        <v>260.1104989431061</v>
+        <v>260.1104376660653</v>
       </c>
       <c r="F126" t="n">
         <v>203518</v>
@@ -2992,16 +2992,16 @@
         <v>43137</v>
       </c>
       <c r="B129" t="n">
-        <v>265.0388488769531</v>
+        <v>265.0388793945312</v>
       </c>
       <c r="C129" t="n">
-        <v>266.887003280563</v>
+        <v>266.8870340109447</v>
       </c>
       <c r="D129" t="n">
-        <v>260.7949428010556</v>
+        <v>260.7949728299743</v>
       </c>
       <c r="E129" t="n">
-        <v>264.8334862793764</v>
+        <v>264.8335167733082</v>
       </c>
       <c r="F129" t="n">
         <v>121863</v>
@@ -3052,16 +3052,16 @@
         <v>43140</v>
       </c>
       <c r="B132" t="n">
-        <v>258.0569763183594</v>
+        <v>258.0570068359375</v>
       </c>
       <c r="C132" t="n">
-        <v>270.2410995013987</v>
+        <v>270.24113145986</v>
       </c>
       <c r="D132" t="n">
-        <v>256.5510835546181</v>
+        <v>256.5511138941107</v>
       </c>
       <c r="E132" t="n">
-        <v>266.2025552859037</v>
+        <v>266.2025867667705</v>
       </c>
       <c r="F132" t="n">
         <v>222103</v>
@@ -3072,16 +3072,16 @@
         <v>43145</v>
       </c>
       <c r="B133" t="n">
-        <v>265.17578125</v>
+        <v>265.1758117675781</v>
       </c>
       <c r="C133" t="n">
-        <v>270.3779831945716</v>
+        <v>270.3780143108417</v>
       </c>
       <c r="D133" t="n">
-        <v>258.3992233399036</v>
+        <v>258.3992530776061</v>
       </c>
       <c r="E133" t="n">
-        <v>258.3992233399036</v>
+        <v>258.3992530776061</v>
       </c>
       <c r="F133" t="n">
         <v>141282</v>
@@ -3132,16 +3132,16 @@
         <v>43150</v>
       </c>
       <c r="B136" t="n">
-        <v>262.7800598144531</v>
+        <v>262.780029296875</v>
       </c>
       <c r="C136" t="n">
-        <v>267.4346649629567</v>
+        <v>267.4346339048228</v>
       </c>
       <c r="D136" t="n">
-        <v>261.4795023662716</v>
+        <v>261.4794719997318</v>
       </c>
       <c r="E136" t="n">
-        <v>266.2025708116724</v>
+        <v>266.202539896626</v>
       </c>
       <c r="F136" t="n">
         <v>88593</v>
@@ -3232,16 +3232,16 @@
         <v>43157</v>
       </c>
       <c r="B141" t="n">
-        <v>266.3394775390625</v>
+        <v>266.3395080566406</v>
       </c>
       <c r="C141" t="n">
-        <v>269.6935253322872</v>
+        <v>269.6935562341772</v>
       </c>
       <c r="D141" t="n">
-        <v>265.9972155323997</v>
+        <v>265.9972460107609</v>
       </c>
       <c r="E141" t="n">
-        <v>268.9405652638205</v>
+        <v>268.9405960794351</v>
       </c>
       <c r="F141" t="n">
         <v>58114</v>
@@ -3292,16 +3292,16 @@
         <v>43160</v>
       </c>
       <c r="B144" t="n">
-        <v>263.5330200195312</v>
+        <v>263.5329284667969</v>
       </c>
       <c r="C144" t="n">
-        <v>267.4346651227554</v>
+        <v>267.4345722145694</v>
       </c>
       <c r="D144" t="n">
-        <v>262.5062612710216</v>
+        <v>262.5061700749885</v>
       </c>
       <c r="E144" t="n">
-        <v>264.9020135217763</v>
+        <v>264.9019214934465</v>
       </c>
       <c r="F144" t="n">
         <v>57645</v>
@@ -3332,16 +3332,16 @@
         <v>43164</v>
       </c>
       <c r="B146" t="n">
-        <v>263.5330200195312</v>
+        <v>263.5329284667969</v>
       </c>
       <c r="C146" t="n">
-        <v>267.2977657725309</v>
+        <v>267.2976729119044</v>
       </c>
       <c r="D146" t="n">
-        <v>262.9169593216951</v>
+        <v>262.9168679829834</v>
       </c>
       <c r="E146" t="n">
-        <v>266.6817050746948</v>
+        <v>266.6816124280909</v>
       </c>
       <c r="F146" t="n">
         <v>71404</v>
@@ -3352,16 +3352,16 @@
         <v>43165</v>
       </c>
       <c r="B147" t="n">
-        <v>267.9137878417969</v>
+        <v>267.913818359375</v>
       </c>
       <c r="C147" t="n">
-        <v>268.8720831551987</v>
+        <v>268.8721137819344</v>
       </c>
       <c r="D147" t="n">
-        <v>263.9436800140559</v>
+        <v>263.9437100794062</v>
       </c>
       <c r="E147" t="n">
-        <v>264.2174786750279</v>
+        <v>264.2175087715661</v>
       </c>
       <c r="F147" t="n">
         <v>60553</v>
@@ -3372,16 +3372,16 @@
         <v>43166</v>
       </c>
       <c r="B148" t="n">
-        <v>272.6368713378906</v>
+        <v>272.6368103027344</v>
       </c>
       <c r="C148" t="n">
-        <v>273.1160326919399</v>
+        <v>273.1159715495139</v>
       </c>
       <c r="D148" t="n">
-        <v>266.6132726034321</v>
+        <v>266.6132129167775</v>
       </c>
       <c r="E148" t="n">
-        <v>266.6132726034321</v>
+        <v>266.6132129167775</v>
       </c>
       <c r="F148" t="n">
         <v>73125</v>
@@ -3392,16 +3392,16 @@
         <v>43167</v>
       </c>
       <c r="B149" t="n">
-        <v>277.2229919433594</v>
+        <v>277.2230224609375</v>
       </c>
       <c r="C149" t="n">
-        <v>279.2765091083056</v>
+        <v>279.2765398519413</v>
       </c>
       <c r="D149" t="n">
-        <v>273.1159848571144</v>
+        <v>273.1160149225803</v>
       </c>
       <c r="E149" t="n">
-        <v>273.8004814975473</v>
+        <v>273.8005116383648</v>
       </c>
       <c r="F149" t="n">
         <v>360517</v>
@@ -3412,16 +3412,16 @@
         <v>43168</v>
       </c>
       <c r="B150" t="n">
-        <v>289.2017517089844</v>
+        <v>289.2018127441406</v>
       </c>
       <c r="C150" t="n">
-        <v>291.5975308196897</v>
+        <v>291.5975923604679</v>
       </c>
       <c r="D150" t="n">
-        <v>277.9759523011636</v>
+        <v>277.9760109671489</v>
       </c>
       <c r="E150" t="n">
-        <v>278.0443883434895</v>
+        <v>278.0444470239179</v>
       </c>
       <c r="F150" t="n">
         <v>178074</v>
@@ -3432,16 +3432,16 @@
         <v>43171</v>
       </c>
       <c r="B151" t="n">
-        <v>295.4992065429688</v>
+        <v>295.4991760253906</v>
       </c>
       <c r="C151" t="n">
-        <v>296.5259652356011</v>
+        <v>296.5259346119848</v>
       </c>
       <c r="D151" t="n">
-        <v>286.8744934608874</v>
+        <v>286.8744638340235</v>
       </c>
       <c r="E151" t="n">
-        <v>287.4905541251969</v>
+        <v>287.4905244347095</v>
       </c>
       <c r="F151" t="n">
         <v>187725</v>
@@ -3452,16 +3452,16 @@
         <v>43172</v>
       </c>
       <c r="B152" t="n">
-        <v>298.4425354003906</v>
+        <v>298.4425659179688</v>
       </c>
       <c r="C152" t="n">
-        <v>298.4425354003906</v>
+        <v>298.4425659179688</v>
       </c>
       <c r="D152" t="n">
-        <v>293.2403334909926</v>
+        <v>293.2403634766137</v>
       </c>
       <c r="E152" t="n">
-        <v>296.5259447340618</v>
+        <v>296.5259750556568</v>
       </c>
       <c r="F152" t="n">
         <v>244066</v>
@@ -3492,16 +3492,16 @@
         <v>43174</v>
       </c>
       <c r="B154" t="n">
-        <v>284.3418273925781</v>
+        <v>284.3418579101562</v>
       </c>
       <c r="C154" t="n">
-        <v>295.0200300677903</v>
+        <v>295.0200617314287</v>
       </c>
       <c r="D154" t="n">
-        <v>284.3418273925781</v>
+        <v>284.3418579101562</v>
       </c>
       <c r="E154" t="n">
-        <v>292.9665400316529</v>
+        <v>292.9665714748962</v>
       </c>
       <c r="F154" t="n">
         <v>147334</v>
@@ -3572,16 +3572,16 @@
         <v>43180</v>
       </c>
       <c r="B158" t="n">
-        <v>292.6927185058594</v>
+        <v>292.6927795410156</v>
       </c>
       <c r="C158" t="n">
-        <v>293.6510137812303</v>
+        <v>293.6510750162197</v>
       </c>
       <c r="D158" t="n">
-        <v>291.8713225555414</v>
+        <v>291.8713834194122</v>
       </c>
       <c r="E158" t="n">
-        <v>293.1718525217215</v>
+        <v>293.1719136567914</v>
       </c>
       <c r="F158" t="n">
         <v>118055</v>
@@ -3592,16 +3592,16 @@
         <v>43181</v>
       </c>
       <c r="B159" t="n">
-        <v>301.4670104980469</v>
+        <v>301.467041015625</v>
       </c>
       <c r="C159" t="n">
-        <v>302.3923906181979</v>
+        <v>302.3924212294524</v>
       </c>
       <c r="D159" t="n">
-        <v>293.4943261379123</v>
+        <v>293.4943558484136</v>
       </c>
       <c r="E159" t="n">
-        <v>294.6332729516429</v>
+        <v>294.6333027774401</v>
       </c>
       <c r="F159" t="n">
         <v>263759</v>
@@ -3632,16 +3632,16 @@
         <v>43185</v>
       </c>
       <c r="B161" t="n">
-        <v>301.8229370117188</v>
+        <v>301.8229064941406</v>
       </c>
       <c r="C161" t="n">
-        <v>303.9584907595719</v>
+        <v>303.9584600260661</v>
       </c>
       <c r="D161" t="n">
-        <v>300.8975284988483</v>
+        <v>300.8974980748389</v>
       </c>
       <c r="E161" t="n">
-        <v>301.6805686506627</v>
+        <v>301.6805381474795</v>
       </c>
       <c r="F161" t="n">
         <v>81498</v>
@@ -3652,16 +3652,16 @@
         <v>43186</v>
       </c>
       <c r="B162" t="n">
-        <v>298.8331604003906</v>
+        <v>298.8332214355469</v>
       </c>
       <c r="C162" t="n">
-        <v>303.4601744361335</v>
+        <v>303.4602364163339</v>
       </c>
       <c r="D162" t="n">
-        <v>298.8331604003906</v>
+        <v>298.8332214355469</v>
       </c>
       <c r="E162" t="n">
-        <v>302.2500292525688</v>
+        <v>302.2500909856032</v>
       </c>
       <c r="F162" t="n">
         <v>78499</v>
@@ -3672,16 +3672,16 @@
         <v>43187</v>
       </c>
       <c r="B163" t="n">
-        <v>297.6942443847656</v>
+        <v>297.6942138671875</v>
       </c>
       <c r="C163" t="n">
-        <v>299.6874298932564</v>
+        <v>299.6873991713505</v>
       </c>
       <c r="D163" t="n">
-        <v>293.6367316809308</v>
+        <v>293.6367015793011</v>
       </c>
       <c r="E163" t="n">
-        <v>298.9043896936335</v>
+        <v>298.9043590519996</v>
       </c>
       <c r="F163" t="n">
         <v>60149</v>
@@ -3752,16 +3752,16 @@
         <v>43194</v>
       </c>
       <c r="B167" t="n">
-        <v>297.5518493652344</v>
+        <v>297.5518798828125</v>
       </c>
       <c r="C167" t="n">
-        <v>302.8907052506516</v>
+        <v>302.8907363157947</v>
       </c>
       <c r="D167" t="n">
-        <v>293.6367053818018</v>
+        <v>293.6367354978341</v>
       </c>
       <c r="E167" t="n">
-        <v>295.701060724269</v>
+        <v>295.7010910520261</v>
       </c>
       <c r="F167" t="n">
         <v>68913</v>
@@ -3772,16 +3772,16 @@
         <v>43195</v>
       </c>
       <c r="B168" t="n">
-        <v>305.4533081054688</v>
+        <v>305.4533386230469</v>
       </c>
       <c r="C168" t="n">
-        <v>306.0939514287025</v>
+        <v>306.0939820102868</v>
       </c>
       <c r="D168" t="n">
-        <v>303.5313214717552</v>
+        <v>303.5313517973093</v>
       </c>
       <c r="E168" t="n">
-        <v>304.6702681192873</v>
+        <v>304.6702985586326</v>
       </c>
       <c r="F168" t="n">
         <v>84368</v>
@@ -3792,16 +3792,16 @@
         <v>43196</v>
       </c>
       <c r="B169" t="n">
-        <v>302.4635620117188</v>
+        <v>302.4635925292969</v>
       </c>
       <c r="C169" t="n">
-        <v>308.585428922096</v>
+        <v>308.5854600573504</v>
       </c>
       <c r="D169" t="n">
-        <v>301.5381536420078</v>
+        <v>301.5381840662153</v>
       </c>
       <c r="E169" t="n">
-        <v>307.2329155352896</v>
+        <v>307.2329465340798</v>
       </c>
       <c r="F169" t="n">
         <v>105548</v>
@@ -3832,16 +3832,16 @@
         <v>43200</v>
       </c>
       <c r="B171" t="n">
-        <v>305.4533081054688</v>
+        <v>305.4533386230469</v>
       </c>
       <c r="C171" t="n">
-        <v>307.8735697314745</v>
+        <v>307.8736004908589</v>
       </c>
       <c r="D171" t="n">
-        <v>303.2465848098722</v>
+        <v>303.2466151069785</v>
       </c>
       <c r="E171" t="n">
-        <v>306.0939514287025</v>
+        <v>306.0939820102868</v>
       </c>
       <c r="F171" t="n">
         <v>106904</v>
@@ -3872,16 +3872,16 @@
         <v>43202</v>
       </c>
       <c r="B173" t="n">
-        <v>301.8229370117188</v>
+        <v>301.8229064941406</v>
       </c>
       <c r="C173" t="n">
-        <v>308.8702133820121</v>
+        <v>308.8701821518778</v>
       </c>
       <c r="D173" t="n">
-        <v>300.47042341568</v>
+        <v>300.4703930348558</v>
       </c>
       <c r="E173" t="n">
-        <v>308.5143066453781</v>
+        <v>308.5142754512298</v>
       </c>
       <c r="F173" t="n">
         <v>107060</v>
@@ -3892,16 +3892,16 @@
         <v>43203</v>
       </c>
       <c r="B174" t="n">
-        <v>301.8229370117188</v>
+        <v>301.8229064941406</v>
       </c>
       <c r="C174" t="n">
-        <v>305.3821743701325</v>
+        <v>305.3821434926768</v>
       </c>
       <c r="D174" t="n">
-        <v>298.9755697905975</v>
+        <v>298.9755395609191</v>
       </c>
       <c r="E174" t="n">
-        <v>301.8941353582529</v>
+        <v>301.8941048334758</v>
       </c>
       <c r="F174" t="n">
         <v>180213</v>
@@ -3932,16 +3932,16 @@
         <v>43207</v>
       </c>
       <c r="B176" t="n">
-        <v>314.2802429199219</v>
+        <v>314.2802734375</v>
       </c>
       <c r="C176" t="n">
-        <v>315.7039264179295</v>
+        <v>315.7039570737517</v>
       </c>
       <c r="D176" t="n">
-        <v>305.0974135277479</v>
+        <v>305.097443153645</v>
       </c>
       <c r="E176" t="n">
-        <v>306.0939919763533</v>
+        <v>306.0940216990212</v>
       </c>
       <c r="F176" t="n">
         <v>399969</v>
@@ -3952,16 +3952,16 @@
         <v>43208</v>
       </c>
       <c r="B177" t="n">
-        <v>324.6731872558594</v>
+        <v>324.6732177734375</v>
       </c>
       <c r="C177" t="n">
-        <v>326.3816074436626</v>
+        <v>326.3816381218233</v>
       </c>
       <c r="D177" t="n">
-        <v>316.1310296528235</v>
+        <v>316.1310593674836</v>
       </c>
       <c r="E177" t="n">
-        <v>316.1310296528235</v>
+        <v>316.1310593674836</v>
       </c>
       <c r="F177" t="n">
         <v>142808</v>
@@ -3972,16 +3972,16 @@
         <v>43209</v>
       </c>
       <c r="B178" t="n">
-        <v>335.9915771484375</v>
+        <v>335.9915466308594</v>
       </c>
       <c r="C178" t="n">
-        <v>338.8389727594285</v>
+        <v>338.8389419832259</v>
       </c>
       <c r="D178" t="n">
-        <v>324.957958112365</v>
+        <v>324.9579285969529</v>
       </c>
       <c r="E178" t="n">
-        <v>324.957958112365</v>
+        <v>324.9579285969529</v>
       </c>
       <c r="F178" t="n">
         <v>241809</v>
@@ -3992,16 +3992,16 @@
         <v>43210</v>
       </c>
       <c r="B179" t="n">
-        <v>336.3474426269531</v>
+        <v>336.3474731445312</v>
       </c>
       <c r="C179" t="n">
-        <v>340.262585991429</v>
+        <v>340.2626168642371</v>
       </c>
       <c r="D179" t="n">
-        <v>331.9339959257591</v>
+        <v>331.934026042895</v>
       </c>
       <c r="E179" t="n">
-        <v>335.9203376234834</v>
+        <v>335.9203681023093</v>
       </c>
       <c r="F179" t="n">
         <v>100696</v>
@@ -4072,16 +4072,16 @@
         <v>43216</v>
       </c>
       <c r="B183" t="n">
-        <v>343.4660034179688</v>
+        <v>343.4659729003906</v>
       </c>
       <c r="C183" t="n">
-        <v>343.4660034179688</v>
+        <v>343.4659729003906</v>
       </c>
       <c r="D183" t="n">
-        <v>334.6390794373683</v>
+        <v>334.6390497040783</v>
       </c>
       <c r="E183" t="n">
-        <v>334.6390794373683</v>
+        <v>334.6390497040783</v>
       </c>
       <c r="F183" t="n">
         <v>151181</v>
@@ -4092,16 +4092,16 @@
         <v>43217</v>
       </c>
       <c r="B184" t="n">
-        <v>340.4762573242188</v>
+        <v>340.4762268066406</v>
       </c>
       <c r="C184" t="n">
-        <v>347.3811661676123</v>
+        <v>347.3811350311332</v>
       </c>
       <c r="D184" t="n">
-        <v>336.7746511575717</v>
+        <v>336.7746209717761</v>
       </c>
       <c r="E184" t="n">
-        <v>347.309967812477</v>
+        <v>347.3099366823795</v>
       </c>
       <c r="F184" t="n">
         <v>216052</v>
@@ -4112,16 +4112,16 @@
         <v>43220</v>
       </c>
       <c r="B185" t="n">
-        <v>336.7034301757812</v>
+        <v>336.7033996582031</v>
       </c>
       <c r="C185" t="n">
-        <v>341.1880762874682</v>
+        <v>341.188045363418</v>
       </c>
       <c r="D185" t="n">
-        <v>334.8526413828396</v>
+        <v>334.8526110330102</v>
       </c>
       <c r="E185" t="n">
-        <v>340.476234444029</v>
+        <v>340.4762035844976</v>
       </c>
       <c r="F185" t="n">
         <v>66083</v>
@@ -4152,16 +4152,16 @@
         <v>43223</v>
       </c>
       <c r="B187" t="n">
-        <v>343.038818359375</v>
+        <v>343.0387573242188</v>
       </c>
       <c r="C187" t="n">
-        <v>343.6794900972192</v>
+        <v>343.6794289480714</v>
       </c>
       <c r="D187" t="n">
-        <v>335.4220691739383</v>
+        <v>335.4220094939916</v>
       </c>
       <c r="E187" t="n">
-        <v>341.6863332070527</v>
+        <v>341.6862724125372</v>
       </c>
       <c r="F187" t="n">
         <v>146682</v>
@@ -4252,16 +4252,16 @@
         <v>43230</v>
       </c>
       <c r="B192" t="n">
-        <v>337.6288452148438</v>
+        <v>337.6287841796875</v>
       </c>
       <c r="C192" t="n">
-        <v>340.2626742520989</v>
+        <v>340.2626127408098</v>
       </c>
       <c r="D192" t="n">
-        <v>329.1578846174031</v>
+        <v>329.1578251135923</v>
       </c>
       <c r="E192" t="n">
-        <v>340.2626742520989</v>
+        <v>340.2626127408098</v>
       </c>
       <c r="F192" t="n">
         <v>218204</v>
@@ -4292,16 +4292,16 @@
         <v>43234</v>
       </c>
       <c r="B194" t="n">
-        <v>341.6863403320312</v>
+        <v>341.6863708496094</v>
       </c>
       <c r="C194" t="n">
-        <v>350.7267731989587</v>
+        <v>350.7268045239795</v>
       </c>
       <c r="D194" t="n">
-        <v>341.6863403320312</v>
+        <v>341.6863708496094</v>
       </c>
       <c r="E194" t="n">
-        <v>343.2523922069608</v>
+        <v>343.2524228644103</v>
       </c>
       <c r="F194" t="n">
         <v>112773</v>
@@ -4312,16 +4312,16 @@
         <v>43235</v>
       </c>
       <c r="B195" t="n">
-        <v>358.7706604003906</v>
+        <v>358.7706298828125</v>
       </c>
       <c r="C195" t="n">
-        <v>359.9807772437208</v>
+        <v>359.9807466232083</v>
       </c>
       <c r="D195" t="n">
-        <v>344.5337116684001</v>
+        <v>344.5336823618385</v>
       </c>
       <c r="E195" t="n">
-        <v>344.5337116684001</v>
+        <v>344.5336823618385</v>
       </c>
       <c r="F195" t="n">
         <v>409111</v>
@@ -4332,16 +4332,16 @@
         <v>43236</v>
       </c>
       <c r="B196" t="n">
-        <v>363.9671630859375</v>
+        <v>363.9670715332031</v>
       </c>
       <c r="C196" t="n">
-        <v>370.1602297264953</v>
+        <v>370.1601366159495</v>
       </c>
       <c r="D196" t="n">
-        <v>360.9062289414354</v>
+        <v>360.906138158652</v>
       </c>
       <c r="E196" t="n">
-        <v>360.9062289414354</v>
+        <v>360.906138158652</v>
       </c>
       <c r="F196" t="n">
         <v>163245</v>
@@ -4372,16 +4372,16 @@
         <v>43238</v>
       </c>
       <c r="B198" t="n">
-        <v>347.0963745117188</v>
+        <v>347.0963134765625</v>
       </c>
       <c r="C198" t="n">
-        <v>358.7706646781861</v>
+        <v>358.7706015901645</v>
       </c>
       <c r="D198" t="n">
-        <v>339.9067300489835</v>
+        <v>339.9066702780902</v>
       </c>
       <c r="E198" t="n">
-        <v>358.7706646781861</v>
+        <v>358.7706015901645</v>
       </c>
       <c r="F198" t="n">
         <v>310384</v>
@@ -4472,16 +4472,16 @@
         <v>43245</v>
       </c>
       <c r="B203" t="n">
-        <v>340.9745178222656</v>
+        <v>340.9744873046875</v>
       </c>
       <c r="C203" t="n">
-        <v>354.0725213866583</v>
+        <v>354.072489696795</v>
       </c>
       <c r="D203" t="n">
-        <v>340.2626759615953</v>
+        <v>340.2626455077277</v>
       </c>
       <c r="E203" t="n">
-        <v>345.815099138853</v>
+        <v>345.8150681880377</v>
       </c>
       <c r="F203" t="n">
         <v>304724</v>
@@ -4492,16 +4492,16 @@
         <v>43248</v>
       </c>
       <c r="B204" t="n">
-        <v>339.5508422851562</v>
+        <v>339.5508117675781</v>
       </c>
       <c r="C204" t="n">
-        <v>341.5440278750897</v>
+        <v>341.5439971783713</v>
       </c>
       <c r="D204" t="n">
-        <v>329.3002625804031</v>
+        <v>329.3002329841092</v>
       </c>
       <c r="E204" t="n">
-        <v>338.4830653024067</v>
+        <v>338.4830348807965</v>
       </c>
       <c r="F204" t="n">
         <v>219195</v>
@@ -4512,16 +4512,16 @@
         <v>43249</v>
       </c>
       <c r="B205" t="n">
-        <v>338.8389282226562</v>
+        <v>338.8389587402344</v>
       </c>
       <c r="C205" t="n">
-        <v>346.8116122198963</v>
+        <v>346.8116434555354</v>
       </c>
       <c r="D205" t="n">
-        <v>331.5069159449832</v>
+        <v>331.5069458022026</v>
       </c>
       <c r="E205" t="n">
-        <v>341.6863234593874</v>
+        <v>341.6863542334166</v>
       </c>
       <c r="F205" t="n">
         <v>340941</v>
@@ -4552,16 +4552,16 @@
         <v>43252</v>
       </c>
       <c r="B207" t="n">
-        <v>348.8048095703125</v>
+        <v>348.8048400878906</v>
       </c>
       <c r="C207" t="n">
-        <v>351.2962700673565</v>
+        <v>351.2963008029172</v>
       </c>
       <c r="D207" t="n">
-        <v>339.1948743205642</v>
+        <v>339.1949039973513</v>
       </c>
       <c r="E207" t="n">
-        <v>348.0929677614445</v>
+        <v>348.0929982167423</v>
       </c>
       <c r="F207" t="n">
         <v>197871</v>
@@ -4572,16 +4572,16 @@
         <v>43255</v>
       </c>
       <c r="B208" t="n">
-        <v>362.685791015625</v>
+        <v>362.6858215332031</v>
       </c>
       <c r="C208" t="n">
-        <v>362.685791015625</v>
+        <v>362.6858215332031</v>
       </c>
       <c r="D208" t="n">
-        <v>352.2928448874634</v>
+        <v>352.2928745305449</v>
       </c>
       <c r="E208" t="n">
-        <v>353.4317916780544</v>
+        <v>353.4318214169705</v>
       </c>
       <c r="F208" t="n">
         <v>242827</v>
@@ -4612,16 +4612,16 @@
         <v>43257</v>
       </c>
       <c r="B210" t="n">
-        <v>364.0383605957031</v>
+        <v>364.038330078125</v>
       </c>
       <c r="C210" t="n">
-        <v>364.2518989858415</v>
+        <v>364.2518684503623</v>
       </c>
       <c r="D210" t="n">
-        <v>352.5776359191992</v>
+        <v>352.5776063623812</v>
       </c>
       <c r="E210" t="n">
-        <v>352.7200042899627</v>
+        <v>352.71997472121</v>
       </c>
       <c r="F210" t="n">
         <v>162971</v>
@@ -4652,16 +4652,16 @@
         <v>43259</v>
       </c>
       <c r="B212" t="n">
-        <v>365.7467346191406</v>
+        <v>365.7467041015625</v>
       </c>
       <c r="C212" t="n">
-        <v>366.6009447352938</v>
+        <v>366.6009141464411</v>
       </c>
       <c r="D212" t="n">
-        <v>356.7063017251708</v>
+        <v>356.7062719619182</v>
       </c>
       <c r="E212" t="n">
-        <v>362.3298658225175</v>
+        <v>362.3298355900399</v>
       </c>
       <c r="F212" t="n">
         <v>293742</v>
@@ -4672,16 +4672,16 @@
         <v>43262</v>
       </c>
       <c r="B213" t="n">
-        <v>357.7029113769531</v>
+        <v>357.7028503417969</v>
       </c>
       <c r="C213" t="n">
-        <v>374.4312934386277</v>
+        <v>374.4312295490931</v>
       </c>
       <c r="D213" t="n">
-        <v>352.3640551875627</v>
+        <v>352.3639950633801</v>
       </c>
       <c r="E213" t="n">
-        <v>368.7365305024857</v>
+        <v>368.7364675846534</v>
       </c>
       <c r="F213" t="n">
         <v>371642</v>
@@ -4692,16 +4692,16 @@
         <v>43263</v>
       </c>
       <c r="B214" t="n">
-        <v>348.6624145507812</v>
+        <v>348.6624450683594</v>
       </c>
       <c r="C214" t="n">
-        <v>358.1299807148922</v>
+        <v>358.1300120611435</v>
       </c>
       <c r="D214" t="n">
-        <v>341.8287053761229</v>
+        <v>341.8287352955629</v>
       </c>
       <c r="E214" t="n">
-        <v>355.9232571101153</v>
+        <v>355.9232882632174</v>
       </c>
       <c r="F214" t="n">
         <v>229511</v>
@@ -4712,16 +4712,16 @@
         <v>43264</v>
       </c>
       <c r="B215" t="n">
-        <v>352.1505432128906</v>
+        <v>352.1505126953125</v>
       </c>
       <c r="C215" t="n">
-        <v>356.7775295917193</v>
+        <v>356.7774986731637</v>
       </c>
       <c r="D215" t="n">
-        <v>344.0354891294511</v>
+        <v>344.0354593151284</v>
       </c>
       <c r="E215" t="n">
-        <v>348.0218319832813</v>
+        <v>348.0218018234998</v>
       </c>
       <c r="F215" t="n">
         <v>115316</v>
@@ -4732,16 +4732,16 @@
         <v>43265</v>
       </c>
       <c r="B216" t="n">
-        <v>354.4996032714844</v>
+        <v>354.4995727539062</v>
       </c>
       <c r="C216" t="n">
-        <v>355.7809185367221</v>
+        <v>355.7808879088402</v>
       </c>
       <c r="D216" t="n">
-        <v>349.2319171837044</v>
+        <v>349.231887119602</v>
       </c>
       <c r="E216" t="n">
-        <v>351.4386409731756</v>
+        <v>351.4386107191045</v>
       </c>
       <c r="F216" t="n">
         <v>163336</v>
@@ -4752,16 +4752,16 @@
         <v>43266</v>
       </c>
       <c r="B217" t="n">
-        <v>357.4181823730469</v>
+        <v>357.4181518554688</v>
       </c>
       <c r="C217" t="n">
-        <v>357.4181823730469</v>
+        <v>357.4181518554688</v>
       </c>
       <c r="D217" t="n">
-        <v>346.7404697634461</v>
+        <v>346.7404401575673</v>
       </c>
       <c r="E217" t="n">
-        <v>354.4996166593337</v>
+        <v>354.4995863909526</v>
       </c>
       <c r="F217" t="n">
         <v>246296</v>
@@ -4772,16 +4772,16 @@
         <v>43269</v>
       </c>
       <c r="B218" t="n">
-        <v>353.9301452636719</v>
+        <v>353.9300537109375</v>
       </c>
       <c r="C218" t="n">
-        <v>358.5571601251135</v>
+        <v>358.557067375488</v>
       </c>
       <c r="D218" t="n">
-        <v>348.1642116909435</v>
+        <v>348.1641216297096</v>
       </c>
       <c r="E218" t="n">
-        <v>357.4182130818107</v>
+        <v>357.4181206268018</v>
       </c>
       <c r="F218" t="n">
         <v>104843</v>
@@ -4792,16 +4792,16 @@
         <v>43270</v>
       </c>
       <c r="B219" t="n">
-        <v>347.9506225585938</v>
+        <v>347.9505920410156</v>
       </c>
       <c r="C219" t="n">
-        <v>353.289478978466</v>
+        <v>353.2894479926347</v>
       </c>
       <c r="D219" t="n">
-        <v>344.8896884107255</v>
+        <v>344.8896581616116</v>
       </c>
       <c r="E219" t="n">
-        <v>348.7336627664723</v>
+        <v>348.7336321802163</v>
       </c>
       <c r="F219" t="n">
         <v>184986</v>
@@ -4832,16 +4832,16 @@
         <v>43272</v>
       </c>
       <c r="B221" t="n">
-        <v>337.5576782226562</v>
+        <v>337.5576171875</v>
       </c>
       <c r="C221" t="n">
-        <v>347.3811526026883</v>
+        <v>347.3810897913103</v>
       </c>
       <c r="D221" t="n">
-        <v>334.5679140640321</v>
+        <v>334.5678535694671</v>
       </c>
       <c r="E221" t="n">
-        <v>341.7575593831866</v>
+        <v>341.757497588633</v>
       </c>
       <c r="F221" t="n">
         <v>160480</v>
@@ -4892,16 +4892,16 @@
         <v>43277</v>
       </c>
       <c r="B224" t="n">
-        <v>340.6185913085938</v>
+        <v>340.6185607910156</v>
       </c>
       <c r="C224" t="n">
-        <v>341.6151698557499</v>
+        <v>341.6151392488837</v>
       </c>
       <c r="D224" t="n">
-        <v>337.2017222434744</v>
+        <v>337.2016920320292</v>
       </c>
       <c r="E224" t="n">
-        <v>337.2017222434744</v>
+        <v>337.2016920320292</v>
       </c>
       <c r="F224" t="n">
         <v>116477</v>
@@ -4912,16 +4912,16 @@
         <v>43278</v>
       </c>
       <c r="B225" t="n">
-        <v>339.1948547363281</v>
+        <v>339.1949157714844</v>
       </c>
       <c r="C225" t="n">
-        <v>343.6795003712829</v>
+        <v>343.679562213412</v>
       </c>
       <c r="D225" t="n">
-        <v>334.6390390906019</v>
+        <v>334.6390993059788</v>
       </c>
       <c r="E225" t="n">
-        <v>342.2558168357468</v>
+        <v>342.2558784216964</v>
       </c>
       <c r="F225" t="n">
         <v>83103</v>
@@ -4952,16 +4952,16 @@
         <v>43280</v>
       </c>
       <c r="B227" t="n">
-        <v>344.1777954101562</v>
+        <v>344.1778259277344</v>
       </c>
       <c r="C227" t="n">
-        <v>344.1777954101562</v>
+        <v>344.1778259277344</v>
       </c>
       <c r="D227" t="n">
-        <v>333.7136508482497</v>
+        <v>333.7136804379924</v>
       </c>
       <c r="E227" t="n">
-        <v>336.276281149935</v>
+        <v>336.2763109669012</v>
       </c>
       <c r="F227" t="n">
         <v>190059</v>
@@ -4972,16 +4972,16 @@
         <v>43283</v>
       </c>
       <c r="B228" t="n">
-        <v>343.5371398925781</v>
+        <v>343.537109375</v>
       </c>
       <c r="C228" t="n">
-        <v>346.8828104437856</v>
+        <v>346.8827796290002</v>
       </c>
       <c r="D228" t="n">
-        <v>340.974481137859</v>
+        <v>340.9744508479307</v>
       </c>
       <c r="E228" t="n">
-        <v>341.6863512539558</v>
+        <v>341.6863209007896</v>
       </c>
       <c r="F228" t="n">
         <v>58036</v>
@@ -4992,16 +4992,16 @@
         <v>43284</v>
       </c>
       <c r="B229" t="n">
-        <v>340.2626342773438</v>
+        <v>340.2626647949219</v>
       </c>
       <c r="C229" t="n">
-        <v>346.02859514043</v>
+        <v>346.0286261751473</v>
       </c>
       <c r="D229" t="n">
-        <v>340.2626342773438</v>
+        <v>340.2626647949219</v>
       </c>
       <c r="E229" t="n">
-        <v>343.5371347672956</v>
+        <v>343.5371655785581</v>
       </c>
       <c r="F229" t="n">
         <v>56719</v>
@@ -5052,16 +5052,16 @@
         <v>43287</v>
       </c>
       <c r="B232" t="n">
-        <v>342.042236328125</v>
+        <v>342.0422058105469</v>
       </c>
       <c r="C232" t="n">
-        <v>346.6692501297997</v>
+        <v>346.6692191993917</v>
       </c>
       <c r="D232" t="n">
-        <v>340.1914478066608</v>
+        <v>340.1914174542131</v>
       </c>
       <c r="E232" t="n">
-        <v>341.0456578934904</v>
+        <v>341.0456274648287</v>
       </c>
       <c r="F232" t="n">
         <v>56875</v>
@@ -5072,16 +5072,16 @@
         <v>43291</v>
       </c>
       <c r="B233" t="n">
-        <v>351.5810241699219</v>
+        <v>351.5809936523438</v>
       </c>
       <c r="C233" t="n">
-        <v>352.2216959955783</v>
+        <v>352.2216654223892</v>
       </c>
       <c r="D233" t="n">
-        <v>341.7575500579347</v>
+        <v>341.7575203930438</v>
       </c>
       <c r="E233" t="n">
-        <v>341.7575500579347</v>
+        <v>341.7575203930438</v>
       </c>
       <c r="F233" t="n">
         <v>97553</v>
@@ -5112,16 +5112,16 @@
         <v>43293</v>
       </c>
       <c r="B235" t="n">
-        <v>366.6009826660156</v>
+        <v>366.6009521484375</v>
       </c>
       <c r="C235" t="n">
-        <v>369.7331150813234</v>
+        <v>369.7330843030119</v>
       </c>
       <c r="D235" t="n">
-        <v>353.2894694819811</v>
+        <v>353.2894400725154</v>
       </c>
       <c r="E235" t="n">
-        <v>353.2894694819811</v>
+        <v>353.2894400725154</v>
       </c>
       <c r="F235" t="n">
         <v>158172</v>
@@ -5132,16 +5132,16 @@
         <v>43294</v>
       </c>
       <c r="B236" t="n">
-        <v>373.7193908691406</v>
+        <v>373.7194213867188</v>
       </c>
       <c r="C236" t="n">
-        <v>378.9870478537733</v>
+        <v>378.9870788015035</v>
       </c>
       <c r="D236" t="n">
-        <v>362.8993402159495</v>
+        <v>362.8993698499723</v>
       </c>
       <c r="E236" t="n">
-        <v>363.326445241838</v>
+        <v>363.3264749107378</v>
       </c>
       <c r="F236" t="n">
         <v>107608</v>
@@ -5172,16 +5172,16 @@
         <v>43298</v>
       </c>
       <c r="B238" t="n">
-        <v>373.7906188964844</v>
+        <v>373.7906494140625</v>
       </c>
       <c r="C238" t="n">
-        <v>374.929565722654</v>
+        <v>374.9295963332197</v>
       </c>
       <c r="D238" t="n">
-        <v>365.5331977427333</v>
+        <v>365.5332275861466</v>
       </c>
       <c r="E238" t="n">
-        <v>370.1601833900527</v>
+        <v>370.1602136112294</v>
       </c>
       <c r="F238" t="n">
         <v>126219</v>
@@ -5192,16 +5192,16 @@
         <v>43299</v>
       </c>
       <c r="B239" t="n">
-        <v>375.1430969238281</v>
+        <v>375.1431274414062</v>
       </c>
       <c r="C239" t="n">
-        <v>376.353242069533</v>
+        <v>376.3532726855554</v>
       </c>
       <c r="D239" t="n">
-        <v>370.943216416512</v>
+        <v>370.9432465924334</v>
       </c>
       <c r="E239" t="n">
-        <v>373.6482434090275</v>
+        <v>373.6482738050005</v>
       </c>
       <c r="F239" t="n">
         <v>102626</v>
@@ -5212,16 +5212,16 @@
         <v>43300</v>
       </c>
       <c r="B240" t="n">
-        <v>382.0480346679688</v>
+        <v>382.0480651855469</v>
       </c>
       <c r="C240" t="n">
-        <v>382.1192046775964</v>
+        <v>382.1192352008595</v>
       </c>
       <c r="D240" t="n">
-        <v>367.5975478524819</v>
+        <v>367.597577215771</v>
       </c>
       <c r="E240" t="n">
-        <v>374.8583620990341</v>
+        <v>374.858392042309</v>
       </c>
       <c r="F240" t="n">
         <v>96340</v>
@@ -5272,16 +5272,16 @@
         <v>43305</v>
       </c>
       <c r="B243" t="n">
-        <v>386.8886108398438</v>
+        <v>386.8886413574219</v>
       </c>
       <c r="C243" t="n">
-        <v>391.3020583336894</v>
+        <v>391.3020891993981</v>
       </c>
       <c r="D243" t="n">
-        <v>385.9632023334533</v>
+        <v>385.9632327780357</v>
       </c>
       <c r="E243" t="n">
-        <v>388.027557720317</v>
+        <v>388.0275883277347</v>
       </c>
       <c r="F243" t="n">
         <v>89258</v>
@@ -5292,16 +5292,16 @@
         <v>43306</v>
       </c>
       <c r="B244" t="n">
-        <v>392.5833435058594</v>
+        <v>392.5833740234375</v>
       </c>
       <c r="C244" t="n">
-        <v>392.5833435058594</v>
+        <v>392.5833740234375</v>
       </c>
       <c r="D244" t="n">
-        <v>382.4039357112513</v>
+        <v>382.4039654375303</v>
       </c>
       <c r="E244" t="n">
-        <v>386.4614761601839</v>
+        <v>386.4615062018769</v>
       </c>
       <c r="F244" t="n">
         <v>87563</v>
@@ -5312,16 +5312,16 @@
         <v>43307</v>
       </c>
       <c r="B245" t="n">
-        <v>380.8379211425781</v>
+        <v>380.8379516601562</v>
       </c>
       <c r="C245" t="n">
-        <v>395.5019475367201</v>
+        <v>395.5019792293666</v>
       </c>
       <c r="D245" t="n">
-        <v>379.5566058747826</v>
+        <v>379.5566362896855</v>
       </c>
       <c r="E245" t="n">
-        <v>393.010487016667</v>
+        <v>393.0105185096659</v>
       </c>
       <c r="F245" t="n">
         <v>118211</v>
@@ -5332,16 +5332,16 @@
         <v>43308</v>
       </c>
       <c r="B246" t="n">
-        <v>370.2313537597656</v>
+        <v>370.2313842773438</v>
       </c>
       <c r="C246" t="n">
-        <v>384.3971030019906</v>
+        <v>384.3971346872288</v>
       </c>
       <c r="D246" t="n">
-        <v>369.8754187374751</v>
+        <v>369.8754492257141</v>
       </c>
       <c r="E246" t="n">
-        <v>383.6140629521565</v>
+        <v>383.6140945728499</v>
       </c>
       <c r="F246" t="n">
         <v>107087</v>
@@ -5352,16 +5352,16 @@
         <v>43311</v>
       </c>
       <c r="B247" t="n">
-        <v>373.8617858886719</v>
+        <v>373.86181640625</v>
       </c>
       <c r="C247" t="n">
-        <v>377.2074563295386</v>
+        <v>377.207487120217</v>
       </c>
       <c r="D247" t="n">
-        <v>371.227957208414</v>
+        <v>371.227987510998</v>
       </c>
       <c r="E247" t="n">
-        <v>371.227957208414</v>
+        <v>371.227987510998</v>
       </c>
       <c r="F247" t="n">
         <v>72473</v>
@@ -5372,16 +5372,16 @@
         <v>43312</v>
       </c>
       <c r="B248" t="n">
-        <v>380.1260375976562</v>
+        <v>380.1260681152344</v>
       </c>
       <c r="C248" t="n">
-        <v>381.1937860375976</v>
+        <v>381.1938166408976</v>
       </c>
       <c r="D248" t="n">
-        <v>376.5668005791599</v>
+        <v>376.5668308109925</v>
       </c>
       <c r="E248" t="n">
-        <v>377.9904840537546</v>
+        <v>377.9905143998846</v>
       </c>
       <c r="F248" t="n">
         <v>98544</v>
@@ -5392,16 +5392,16 @@
         <v>43313</v>
       </c>
       <c r="B249" t="n">
-        <v>379.7700805664062</v>
+        <v>379.7701416015625</v>
       </c>
       <c r="C249" t="n">
-        <v>386.1767124950243</v>
+        <v>386.1767745598292</v>
       </c>
       <c r="D249" t="n">
-        <v>375.926107075637</v>
+        <v>375.9261674930049</v>
       </c>
       <c r="E249" t="n">
-        <v>378.702303856302</v>
+        <v>378.7023647198493</v>
       </c>
       <c r="F249" t="n">
         <v>84015</v>
@@ -5412,16 +5412,16 @@
         <v>43314</v>
       </c>
       <c r="B250" t="n">
-        <v>390.661376953125</v>
+        <v>390.6614074707031</v>
       </c>
       <c r="C250" t="n">
-        <v>390.8749436539747</v>
+        <v>390.8749741882362</v>
       </c>
       <c r="D250" t="n">
-        <v>377.1362980836333</v>
+        <v>377.1363275446631</v>
       </c>
       <c r="E250" t="n">
-        <v>379.7701268460492</v>
+        <v>379.7701565128276</v>
       </c>
       <c r="F250" t="n">
         <v>67674</v>
@@ -5452,16 +5452,16 @@
         <v>43318</v>
       </c>
       <c r="B252" t="n">
-        <v>399.4170837402344</v>
+        <v>399.4170532226562</v>
       </c>
       <c r="C252" t="n">
-        <v>403.0474908352413</v>
+        <v>403.0474600402808</v>
       </c>
       <c r="D252" t="n">
-        <v>395.0748065624327</v>
+        <v>395.0747763766276</v>
       </c>
       <c r="E252" t="n">
-        <v>395.0748065624327</v>
+        <v>395.0747763766276</v>
       </c>
       <c r="F252" t="n">
         <v>103174</v>
@@ -5492,16 +5492,16 @@
         <v>43320</v>
       </c>
       <c r="B254" t="n">
-        <v>417.9250793457031</v>
+        <v>417.9251098632812</v>
       </c>
       <c r="C254" t="n">
-        <v>423.8334083293842</v>
+        <v>423.8334392783983</v>
       </c>
       <c r="D254" t="n">
-        <v>403.6169611039226</v>
+        <v>403.6169905766983</v>
       </c>
       <c r="E254" t="n">
-        <v>405.6101463226631</v>
+        <v>405.6101759409846</v>
       </c>
       <c r="F254" t="n">
         <v>155172</v>
@@ -5532,16 +5532,16 @@
         <v>43322</v>
       </c>
       <c r="B256" t="n">
-        <v>411.4472961425781</v>
+        <v>411.447265625</v>
       </c>
       <c r="C256" t="n">
-        <v>419.5623490808002</v>
+        <v>419.5623179613181</v>
       </c>
       <c r="D256" t="n">
-        <v>410.023612585701</v>
+        <v>410.0235821737193</v>
       </c>
       <c r="E256" t="n">
-        <v>413.582849809905</v>
+        <v>413.5828191339301</v>
       </c>
       <c r="F256" t="n">
         <v>87106</v>
@@ -5572,16 +5572,16 @@
         <v>43326</v>
       </c>
       <c r="B258" t="n">
-        <v>420.274169921875</v>
+        <v>420.2742004394531</v>
       </c>
       <c r="C258" t="n">
-        <v>421.4843150509387</v>
+        <v>421.4843456563897</v>
       </c>
       <c r="D258" t="n">
-        <v>410.0947621672968</v>
+        <v>410.0947919457125</v>
       </c>
       <c r="E258" t="n">
-        <v>414.0099342516782</v>
+        <v>414.0099643143882</v>
       </c>
       <c r="F258" t="n">
         <v>82646</v>
@@ -5592,16 +5592,16 @@
         <v>43327</v>
       </c>
       <c r="B259" t="n">
-        <v>422.4808654785156</v>
+        <v>422.4808959960938</v>
       </c>
       <c r="C259" t="n">
-        <v>426.7519439851863</v>
+        <v>426.7519748112825</v>
       </c>
       <c r="D259" t="n">
-        <v>418.2809853074265</v>
+        <v>418.2810155216295</v>
       </c>
       <c r="E259" t="n">
-        <v>420.2741420556025</v>
+        <v>420.2741724137797</v>
       </c>
       <c r="F259" t="n">
         <v>76308</v>
@@ -5632,16 +5632,16 @@
         <v>43329</v>
       </c>
       <c r="B261" t="n">
-        <v>420.3453979492188</v>
+        <v>420.3454284667969</v>
       </c>
       <c r="C261" t="n">
-        <v>425.6842255645988</v>
+        <v>425.6842564697821</v>
       </c>
       <c r="D261" t="n">
-        <v>414.2235018632464</v>
+        <v>414.2235319363675</v>
       </c>
       <c r="E261" t="n">
-        <v>423.6198701981683</v>
+        <v>423.6199009534769</v>
       </c>
       <c r="F261" t="n">
         <v>64270</v>
@@ -5652,16 +5652,16 @@
         <v>43332</v>
       </c>
       <c r="B262" t="n">
-        <v>426.0401306152344</v>
+        <v>426.0401611328125</v>
       </c>
       <c r="C262" t="n">
-        <v>428.5315908821063</v>
+        <v>428.5316215781496</v>
       </c>
       <c r="D262" t="n">
-        <v>413.4404609322541</v>
+        <v>413.4404905473083</v>
       </c>
       <c r="E262" t="n">
-        <v>419.9182632925229</v>
+        <v>419.918293371587</v>
       </c>
       <c r="F262" t="n">
         <v>76842</v>
@@ -5672,16 +5672,16 @@
         <v>43333</v>
       </c>
       <c r="B263" t="n">
-        <v>422.125</v>
+        <v>422.1249694824219</v>
       </c>
       <c r="C263" t="n">
-        <v>432.0196430351243</v>
+        <v>432.0196118022117</v>
       </c>
       <c r="D263" t="n">
-        <v>422.0538016574688</v>
+        <v>422.0537711450379</v>
       </c>
       <c r="E263" t="n">
-        <v>426.0401438749331</v>
+        <v>426.0401130743091</v>
       </c>
       <c r="F263" t="n">
         <v>63487</v>
@@ -5692,16 +5692,16 @@
         <v>43334</v>
       </c>
       <c r="B264" t="n">
-        <v>419.9894409179688</v>
+        <v>419.9894714355469</v>
       </c>
       <c r="C264" t="n">
-        <v>426.2537050349228</v>
+        <v>426.2537360076794</v>
       </c>
       <c r="D264" t="n">
-        <v>419.206400820347</v>
+        <v>419.2064312810272</v>
       </c>
       <c r="E264" t="n">
-        <v>421.3419544204027</v>
+        <v>421.3419850362582</v>
       </c>
       <c r="F264" t="n">
         <v>60566</v>
@@ -5732,16 +5732,16 @@
         <v>43336</v>
       </c>
       <c r="B266" t="n">
-        <v>405.7525634765625</v>
+        <v>405.7525024414062</v>
       </c>
       <c r="C266" t="n">
-        <v>415.2201023253259</v>
+        <v>415.2200398660191</v>
       </c>
       <c r="D266" t="n">
-        <v>402.9051678210174</v>
+        <v>402.9051072141795</v>
       </c>
       <c r="E266" t="n">
-        <v>408.3863924168361</v>
+        <v>408.3863309854873</v>
       </c>
       <c r="F266" t="n">
         <v>110243</v>
@@ -5752,16 +5752,16 @@
         <v>43339</v>
       </c>
       <c r="B267" t="n">
-        <v>411.1625671386719</v>
+        <v>411.1625366210938</v>
       </c>
       <c r="C267" t="n">
-        <v>413.2269225008468</v>
+        <v>413.2268918300467</v>
       </c>
       <c r="D267" t="n">
-        <v>405.8949095474701</v>
+        <v>405.8948794208715</v>
       </c>
       <c r="E267" t="n">
-        <v>405.8949095474701</v>
+        <v>405.8948794208715</v>
       </c>
       <c r="F267" t="n">
         <v>61388</v>
@@ -5792,16 +5792,16 @@
         <v>43341</v>
       </c>
       <c r="B269" t="n">
-        <v>419.7046813964844</v>
+        <v>419.7047119140625</v>
       </c>
       <c r="C269" t="n">
-        <v>421.3419315123082</v>
+        <v>421.341962148934</v>
       </c>
       <c r="D269" t="n">
-        <v>415.718339447524</v>
+        <v>415.7183696752471</v>
       </c>
       <c r="E269" t="n">
-        <v>415.718339447524</v>
+        <v>415.7183696752471</v>
       </c>
       <c r="F269" t="n">
         <v>43246</v>
@@ -5812,16 +5812,16 @@
         <v>43342</v>
       </c>
       <c r="B270" t="n">
-        <v>420.0606384277344</v>
+        <v>420.0606689453125</v>
       </c>
       <c r="C270" t="n">
-        <v>423.0503737970776</v>
+        <v>423.0504045318613</v>
       </c>
       <c r="D270" t="n">
-        <v>416.8573080339942</v>
+        <v>416.8573383188491</v>
       </c>
       <c r="E270" t="n">
-        <v>419.5623350335054</v>
+        <v>419.5623655148816</v>
       </c>
       <c r="F270" t="n">
         <v>65848</v>
@@ -5872,16 +5872,16 @@
         <v>43347</v>
       </c>
       <c r="B273" t="n">
-        <v>425.6130676269531</v>
+        <v>425.6130981445312</v>
       </c>
       <c r="C273" t="n">
-        <v>427.1079496011972</v>
+        <v>427.1079802259623</v>
       </c>
       <c r="D273" t="n">
-        <v>417.9963177250562</v>
+        <v>417.9963476964933</v>
       </c>
       <c r="E273" t="n">
-        <v>420.4165798907745</v>
+        <v>420.4166100357508</v>
       </c>
       <c r="F273" t="n">
         <v>35382</v>
@@ -5892,16 +5892,16 @@
         <v>43348</v>
       </c>
       <c r="B274" t="n">
-        <v>446.39892578125</v>
+        <v>446.3989562988281</v>
       </c>
       <c r="C274" t="n">
-        <v>446.8972008127072</v>
+        <v>446.8972313643494</v>
       </c>
       <c r="D274" t="n">
-        <v>425.3282694856966</v>
+        <v>425.3282985628022</v>
       </c>
       <c r="E274" t="n">
-        <v>426.9655195862169</v>
+        <v>426.9655487752514</v>
       </c>
       <c r="F274" t="n">
         <v>107452</v>
@@ -5932,16 +5932,16 @@
         <v>43353</v>
       </c>
       <c r="B276" t="n">
-        <v>462.6290588378906</v>
+        <v>462.6290893554688</v>
       </c>
       <c r="C276" t="n">
-        <v>469.462768016546</v>
+        <v>469.4627989849134</v>
       </c>
       <c r="D276" t="n">
-        <v>459.2833600920387</v>
+        <v>459.283390388916</v>
       </c>
       <c r="E276" t="n">
-        <v>466.188267612185</v>
+        <v>466.1882983645482</v>
       </c>
       <c r="F276" t="n">
         <v>65822</v>
@@ -5972,16 +5972,16 @@
         <v>43355</v>
       </c>
       <c r="B278" t="n">
-        <v>449.5311279296875</v>
+        <v>449.5310668945312</v>
       </c>
       <c r="C278" t="n">
-        <v>459.1410350242219</v>
+        <v>459.1409726842791</v>
       </c>
       <c r="D278" t="n">
-        <v>448.3921526825321</v>
+        <v>448.3920918020204</v>
       </c>
       <c r="E278" t="n">
-        <v>459.0698650080319</v>
+        <v>459.0698026777523</v>
       </c>
       <c r="F278" t="n">
         <v>50876</v>
@@ -5992,16 +5992,16 @@
         <v>43356</v>
       </c>
       <c r="B279" t="n">
-        <v>446.39892578125</v>
+        <v>446.3989562988281</v>
       </c>
       <c r="C279" t="n">
-        <v>452.7343595041292</v>
+        <v>452.7343904548224</v>
       </c>
       <c r="D279" t="n">
-        <v>443.4803606015432</v>
+        <v>443.4803909195968</v>
       </c>
       <c r="E279" t="n">
-        <v>448.2497142289639</v>
+        <v>448.2497448730691</v>
       </c>
       <c r="F279" t="n">
         <v>76764</v>
@@ -6132,16 +6132,16 @@
         <v>43367</v>
       </c>
       <c r="B286" t="n">
-        <v>455.581787109375</v>
+        <v>455.5817565917969</v>
       </c>
       <c r="C286" t="n">
-        <v>472.5949337572724</v>
+        <v>472.5949021000526</v>
       </c>
       <c r="D286" t="n">
-        <v>452.0937480959283</v>
+        <v>452.0937178119998</v>
       </c>
       <c r="E286" t="n">
-        <v>465.618827398367</v>
+        <v>465.6187962084482</v>
       </c>
       <c r="F286" t="n">
         <v>114729</v>
@@ -6152,16 +6152,16 @@
         <v>43368</v>
       </c>
       <c r="B287" t="n">
-        <v>461.7036743164062</v>
+        <v>461.7036437988281</v>
       </c>
       <c r="C287" t="n">
-        <v>461.988411033105</v>
+        <v>461.9883804967065</v>
       </c>
       <c r="D287" t="n">
-        <v>455.0835031551412</v>
+        <v>455.0834730751416</v>
       </c>
       <c r="E287" t="n">
-        <v>457.0766601720329</v>
+        <v>457.0766299602901</v>
       </c>
       <c r="F287" t="n">
         <v>76842</v>
@@ -6212,16 +6212,16 @@
         <v>43371</v>
       </c>
       <c r="B290" t="n">
-        <v>473.0220336914062</v>
+        <v>473.0220031738281</v>
       </c>
       <c r="C290" t="n">
-        <v>474.7304823382609</v>
+        <v>474.7304517104602</v>
       </c>
       <c r="D290" t="n">
-        <v>462.7002567925351</v>
+        <v>462.7002269408786</v>
       </c>
       <c r="E290" t="n">
-        <v>463.7680336553177</v>
+        <v>463.7680037347724</v>
       </c>
       <c r="F290" t="n">
         <v>82437</v>
@@ -6232,16 +6232,16 @@
         <v>43374</v>
       </c>
       <c r="B291" t="n">
-        <v>469.8186950683594</v>
+        <v>469.8186645507812</v>
       </c>
       <c r="C291" t="n">
-        <v>479.7845644628944</v>
+        <v>479.7845332979725</v>
       </c>
       <c r="D291" t="n">
-        <v>464.8357745370967</v>
+        <v>464.8357443431895</v>
       </c>
       <c r="E291" t="n">
-        <v>476.9371408278733</v>
+        <v>476.937109847909</v>
       </c>
       <c r="F291" t="n">
         <v>76882</v>
@@ -6272,16 +6272,16 @@
         <v>43376</v>
       </c>
       <c r="B293" t="n">
-        <v>462.3443298339844</v>
+        <v>462.3442993164062</v>
       </c>
       <c r="C293" t="n">
-        <v>486.9029982795631</v>
+        <v>486.9029661409614</v>
       </c>
       <c r="D293" t="n">
-        <v>459.1409993857687</v>
+        <v>459.1409690796302</v>
       </c>
       <c r="E293" t="n">
-        <v>484.8386713221064</v>
+        <v>484.838639319763</v>
       </c>
       <c r="F293" t="n">
         <v>143969</v>
@@ -6292,16 +6292,16 @@
         <v>43377</v>
       </c>
       <c r="B294" t="n">
-        <v>455.581787109375</v>
+        <v>455.5817565917969</v>
       </c>
       <c r="C294" t="n">
-        <v>472.8085004649586</v>
+        <v>472.8084687934327</v>
       </c>
       <c r="D294" t="n">
-        <v>446.4701553336692</v>
+        <v>446.4701254264423</v>
       </c>
       <c r="E294" t="n">
-        <v>463.4121036350006</v>
+        <v>463.4120725929013</v>
       </c>
       <c r="F294" t="n">
         <v>143591</v>
@@ -6312,16 +6312,16 @@
         <v>43378</v>
       </c>
       <c r="B295" t="n">
-        <v>455.1546936035156</v>
+        <v>455.1546630859375</v>
       </c>
       <c r="C295" t="n">
-        <v>463.625682135659</v>
+        <v>463.6256510501111</v>
       </c>
       <c r="D295" t="n">
-        <v>441.4160755759419</v>
+        <v>441.4160459795217</v>
       </c>
       <c r="E295" t="n">
-        <v>456.3648388698236</v>
+        <v>456.3648082711067</v>
       </c>
       <c r="F295" t="n">
         <v>188272</v>
@@ -6332,16 +6332,16 @@
         <v>43381</v>
       </c>
       <c r="B296" t="n">
-        <v>438.1415405273438</v>
+        <v>438.1415710449219</v>
       </c>
       <c r="C296" t="n">
-        <v>467.8967247511182</v>
+        <v>467.8967573412141</v>
       </c>
       <c r="D296" t="n">
-        <v>435.0094084164173</v>
+        <v>435.0094387158351</v>
       </c>
       <c r="E296" t="n">
-        <v>462.7002373471738</v>
+        <v>462.7002695753223</v>
       </c>
       <c r="F296" t="n">
         <v>227176</v>
@@ -6372,16 +6372,16 @@
         <v>43383</v>
       </c>
       <c r="B298" t="n">
-        <v>438.7110290527344</v>
+        <v>438.7110595703125</v>
       </c>
       <c r="C298" t="n">
-        <v>442.7685414357292</v>
+        <v>442.7685722355556</v>
       </c>
       <c r="D298" t="n">
-        <v>431.0230810302057</v>
+        <v>431.0231110129953</v>
       </c>
       <c r="E298" t="n">
-        <v>433.3010030980707</v>
+        <v>433.3010332393171</v>
       </c>
       <c r="F298" t="n">
         <v>196176</v>
@@ -6432,16 +6432,16 @@
         <v>43389</v>
       </c>
       <c r="B301" t="n">
-        <v>473.8762512207031</v>
+        <v>473.876220703125</v>
       </c>
       <c r="C301" t="n">
-        <v>477.7913953357964</v>
+        <v>477.7913645660835</v>
       </c>
       <c r="D301" t="n">
-        <v>447.5379342984066</v>
+        <v>447.5379054770132</v>
       </c>
       <c r="E301" t="n">
-        <v>458.3580147901026</v>
+        <v>458.3579852718972</v>
       </c>
       <c r="F301" t="n">
         <v>117924</v>
@@ -6452,16 +6452,16 @@
         <v>43390</v>
       </c>
       <c r="B302" t="n">
-        <v>491.3164367675781</v>
+        <v>491.3164672851562</v>
       </c>
       <c r="C302" t="n">
-        <v>494.3774271396515</v>
+        <v>494.3774578473596</v>
       </c>
       <c r="D302" t="n">
-        <v>464.9069518694333</v>
+        <v>464.9069807466153</v>
       </c>
       <c r="E302" t="n">
-        <v>469.10686071584</v>
+        <v>469.1068898538948</v>
       </c>
       <c r="F302" t="n">
         <v>187503</v>
@@ -6472,16 +6472,16 @@
         <v>43391</v>
       </c>
       <c r="B303" t="n">
-        <v>493.8791809082031</v>
+        <v>493.879150390625</v>
       </c>
       <c r="C303" t="n">
-        <v>498.2214586079846</v>
+        <v>498.2214278220903</v>
       </c>
       <c r="D303" t="n">
-        <v>489.4657331907928</v>
+        <v>489.4657029459287</v>
       </c>
       <c r="E303" t="n">
-        <v>492.3131005362102</v>
+        <v>492.3130701154026</v>
       </c>
       <c r="F303" t="n">
         <v>132636</v>
@@ -6492,16 +6492,16 @@
         <v>43392</v>
       </c>
       <c r="B304" t="n">
-        <v>491.1741027832031</v>
+        <v>491.1741333007812</v>
       </c>
       <c r="C304" t="n">
-        <v>496.299420138737</v>
+        <v>496.2994509747608</v>
       </c>
       <c r="D304" t="n">
-        <v>484.4115352074307</v>
+        <v>484.4115653048377</v>
       </c>
       <c r="E304" t="n">
-        <v>491.1741027832031</v>
+        <v>491.1741333007812</v>
       </c>
       <c r="F304" t="n">
         <v>87498</v>
@@ -6512,16 +6512,16 @@
         <v>43395</v>
       </c>
       <c r="B305" t="n">
-        <v>489.1097106933594</v>
+        <v>489.1097412109375</v>
       </c>
       <c r="C305" t="n">
-        <v>497.1536216345586</v>
+        <v>497.1536526540297</v>
       </c>
       <c r="D305" t="n">
-        <v>487.1877238013593</v>
+        <v>487.1877541990168</v>
       </c>
       <c r="E305" t="n">
-        <v>496.7264882523276</v>
+        <v>496.726519245148</v>
       </c>
       <c r="F305" t="n">
         <v>60501</v>
@@ -6532,16 +6532,16 @@
         <v>43396</v>
       </c>
       <c r="B306" t="n">
-        <v>511.461669921875</v>
+        <v>511.4617309570312</v>
       </c>
       <c r="C306" t="n">
-        <v>517.4411398059367</v>
+        <v>517.4412015546516</v>
       </c>
       <c r="D306" t="n">
-        <v>487.2588837324458</v>
+        <v>487.2589418793684</v>
       </c>
       <c r="E306" t="n">
-        <v>494.7332635855321</v>
+        <v>494.733322624408</v>
       </c>
       <c r="F306" t="n">
         <v>160702</v>
@@ -6552,16 +6552,16 @@
         <v>43397</v>
       </c>
       <c r="B307" t="n">
-        <v>494.5197448730469</v>
+        <v>494.519775390625</v>
       </c>
       <c r="C307" t="n">
-        <v>514.6649930964529</v>
+        <v>514.6650248572254</v>
       </c>
       <c r="D307" t="n">
-        <v>488.3267077266366</v>
+        <v>488.3267378620328</v>
       </c>
       <c r="E307" t="n">
-        <v>512.5294395987868</v>
+        <v>512.5294712277711</v>
       </c>
       <c r="F307" t="n">
         <v>107960</v>
@@ -6572,16 +6572,16 @@
         <v>43398</v>
       </c>
       <c r="B308" t="n">
-        <v>497.224853515625</v>
+        <v>497.2248840332031</v>
       </c>
       <c r="C308" t="n">
-        <v>503.5602883802679</v>
+        <v>503.5603192866885</v>
       </c>
       <c r="D308" t="n">
-        <v>489.67930169078</v>
+        <v>489.6793317452438</v>
       </c>
       <c r="E308" t="n">
-        <v>496.7977200802437</v>
+        <v>496.7977505716062</v>
       </c>
       <c r="F308" t="n">
         <v>118198</v>
@@ -6592,16 +6592,16 @@
         <v>43399</v>
       </c>
       <c r="B309" t="n">
-        <v>491.885986328125</v>
+        <v>491.8860168457031</v>
       </c>
       <c r="C309" t="n">
-        <v>494.3062200555082</v>
+        <v>494.3062507232424</v>
       </c>
       <c r="D309" t="n">
-        <v>475.3711436536239</v>
+        <v>475.3711731465886</v>
       </c>
       <c r="E309" t="n">
-        <v>489.8216026618011</v>
+        <v>489.8216330513008</v>
       </c>
       <c r="F309" t="n">
         <v>181243</v>
@@ -6612,16 +6612,16 @@
         <v>43402</v>
       </c>
       <c r="B310" t="n">
-        <v>484.2691955566406</v>
+        <v>484.2692565917969</v>
       </c>
       <c r="C310" t="n">
-        <v>487.9707727255595</v>
+        <v>487.9708342272462</v>
       </c>
       <c r="D310" t="n">
-        <v>477.4354579653848</v>
+        <v>477.4355181392469</v>
       </c>
       <c r="E310" t="n">
-        <v>479.4998415768361</v>
+        <v>479.499902010884</v>
       </c>
       <c r="F310" t="n">
         <v>124850</v>
@@ -6652,16 +6652,16 @@
         <v>43404</v>
       </c>
       <c r="B312" t="n">
-        <v>515.8040161132812</v>
+        <v>515.803955078125</v>
       </c>
       <c r="C312" t="n">
-        <v>520.0039537233914</v>
+        <v>520.003892191256</v>
       </c>
       <c r="D312" t="n">
-        <v>508.9703345728159</v>
+        <v>508.9702743462901</v>
       </c>
       <c r="E312" t="n">
-        <v>508.9703345728159</v>
+        <v>508.9702743462901</v>
       </c>
       <c r="F312" t="n">
         <v>139717</v>
@@ -6692,16 +6692,16 @@
         <v>43409</v>
       </c>
       <c r="B314" t="n">
-        <v>487.6149291992188</v>
+        <v>487.6148681640625</v>
       </c>
       <c r="C314" t="n">
-        <v>501.851879637278</v>
+        <v>501.8518168200711</v>
       </c>
       <c r="D314" t="n">
-        <v>480.4964539801891</v>
+        <v>480.4963938360582</v>
       </c>
       <c r="E314" t="n">
-        <v>498.2926420277632</v>
+        <v>498.292579656069</v>
       </c>
       <c r="F314" t="n">
         <v>153555</v>
@@ -6712,16 +6712,16 @@
         <v>43410</v>
       </c>
       <c r="B315" t="n">
-        <v>485.4793395996094</v>
+        <v>485.4793090820312</v>
       </c>
       <c r="C315" t="n">
-        <v>488.3267634762448</v>
+        <v>488.3267327796756</v>
       </c>
       <c r="D315" t="n">
-        <v>480.5675886598367</v>
+        <v>480.5675584510147</v>
       </c>
       <c r="E315" t="n">
-        <v>487.6148933410799</v>
+        <v>487.6148626892594</v>
       </c>
       <c r="F315" t="n">
         <v>70726</v>
@@ -6732,16 +6732,16 @@
         <v>43411</v>
       </c>
       <c r="B316" t="n">
-        <v>466.1883239746094</v>
+        <v>466.188232421875</v>
       </c>
       <c r="C316" t="n">
-        <v>486.9030490394698</v>
+        <v>486.902953418659</v>
       </c>
       <c r="D316" t="n">
-        <v>458.4292054105508</v>
+        <v>458.4291153815966</v>
       </c>
       <c r="E316" t="n">
-        <v>486.9030490394698</v>
+        <v>486.902953418659</v>
       </c>
       <c r="F316" t="n">
         <v>167692</v>
@@ -6792,16 +6792,16 @@
         <v>43416</v>
       </c>
       <c r="B319" t="n">
-        <v>497.01025390625</v>
+        <v>497.0102844238281</v>
       </c>
       <c r="C319" t="n">
-        <v>497.01025390625</v>
+        <v>497.0102844238281</v>
       </c>
       <c r="D319" t="n">
-        <v>482.4303546376204</v>
+        <v>482.430384259959</v>
       </c>
       <c r="E319" t="n">
-        <v>486.9551430766307</v>
+        <v>486.9551729768019</v>
       </c>
       <c r="F319" t="n">
         <v>67570</v>
@@ -6832,16 +6832,16 @@
         <v>43418</v>
       </c>
       <c r="B321" t="n">
-        <v>512.4521484375</v>
+        <v>512.4520874023438</v>
       </c>
       <c r="C321" t="n">
-        <v>512.8830507869616</v>
+        <v>512.8829897004831</v>
       </c>
       <c r="D321" t="n">
-        <v>503.8334725606678</v>
+        <v>503.8334125520312</v>
       </c>
       <c r="E321" t="n">
-        <v>509.938370355574</v>
+        <v>509.938309619819</v>
       </c>
       <c r="F321" t="n">
         <v>103291</v>
@@ -6852,16 +6852,16 @@
         <v>43420</v>
       </c>
       <c r="B322" t="n">
-        <v>522.1481323242188</v>
+        <v>522.1480712890625</v>
       </c>
       <c r="C322" t="n">
-        <v>522.1481323242188</v>
+        <v>522.1480712890625</v>
       </c>
       <c r="D322" t="n">
-        <v>509.2200907556082</v>
+        <v>509.220031231642</v>
       </c>
       <c r="E322" t="n">
-        <v>512.0929634723677</v>
+        <v>512.0929036125845</v>
       </c>
       <c r="F322" t="n">
         <v>83637</v>
@@ -6872,16 +6872,16 @@
         <v>43423</v>
       </c>
       <c r="B323" t="n">
-        <v>523.5127563476562</v>
+        <v>523.5126953125</v>
       </c>
       <c r="C323" t="n">
-        <v>523.5846210514604</v>
+        <v>523.5845600079256</v>
       </c>
       <c r="D323" t="n">
-        <v>515.7559992365758</v>
+        <v>515.7559391057621</v>
       </c>
       <c r="E323" t="n">
-        <v>519.2752543737025</v>
+        <v>519.275193832587</v>
       </c>
       <c r="F323" t="n">
         <v>66070</v>
@@ -6892,16 +6892,16 @@
         <v>43425</v>
       </c>
       <c r="B324" t="n">
-        <v>529.402099609375</v>
+        <v>529.4021606445312</v>
       </c>
       <c r="C324" t="n">
-        <v>529.402099609375</v>
+        <v>529.4021606445312</v>
       </c>
       <c r="D324" t="n">
-        <v>510.0100687434812</v>
+        <v>510.0101275429159</v>
       </c>
       <c r="E324" t="n">
-        <v>519.9933714051233</v>
+        <v>519.9934313555403</v>
       </c>
       <c r="F324" t="n">
         <v>65457</v>
@@ -6912,16 +6912,16 @@
         <v>43426</v>
       </c>
       <c r="B325" t="n">
-        <v>530.6948852539062</v>
+        <v>530.6949462890625</v>
       </c>
       <c r="C325" t="n">
-        <v>535.3633457897967</v>
+        <v>535.363407361872</v>
       </c>
       <c r="D325" t="n">
-        <v>524.0154140349154</v>
+        <v>524.0154743018664</v>
       </c>
       <c r="E325" t="n">
-        <v>528.6120670535926</v>
+        <v>528.6121278492041</v>
       </c>
       <c r="F325" t="n">
         <v>55036</v>
@@ -6932,16 +6932,16 @@
         <v>43427</v>
       </c>
       <c r="B326" t="n">
-        <v>531.7003784179688</v>
+        <v>531.700439453125</v>
       </c>
       <c r="C326" t="n">
-        <v>540.8218190672163</v>
+        <v>540.8218811494445</v>
       </c>
       <c r="D326" t="n">
-        <v>528.612026527081</v>
+        <v>528.6120872077179</v>
       </c>
       <c r="E326" t="n">
-        <v>531.556706222967</v>
+        <v>531.5567672416307</v>
       </c>
       <c r="F326" t="n">
         <v>87641</v>
@@ -6972,16 +6972,16 @@
         <v>43431</v>
       </c>
       <c r="B328" t="n">
-        <v>549.3687744140625</v>
+        <v>549.36865234375</v>
       </c>
       <c r="C328" t="n">
-        <v>550.0870212371809</v>
+        <v>550.0868990072732</v>
       </c>
       <c r="D328" t="n">
-        <v>536.0816941449797</v>
+        <v>536.0815750270702</v>
       </c>
       <c r="E328" t="n">
-        <v>536.0816941449797</v>
+        <v>536.0815750270702</v>
       </c>
       <c r="F328" t="n">
         <v>111782</v>
@@ -6992,16 +6992,16 @@
         <v>43432</v>
       </c>
       <c r="B329" t="n">
-        <v>545.8494262695312</v>
+        <v>545.849365234375</v>
       </c>
       <c r="C329" t="n">
-        <v>551.8825156058812</v>
+        <v>551.8824538961239</v>
       </c>
       <c r="D329" t="n">
-        <v>542.3301146280619</v>
+        <v>542.330053986424</v>
       </c>
       <c r="E329" t="n">
-        <v>548.7222987289401</v>
+        <v>548.7222373725484</v>
       </c>
       <c r="F329" t="n">
         <v>68365</v>
@@ -7012,16 +7012,16 @@
         <v>43433</v>
       </c>
       <c r="B330" t="n">
-        <v>542.9765014648438</v>
+        <v>542.9764404296875</v>
       </c>
       <c r="C330" t="n">
-        <v>548.2914013193791</v>
+        <v>548.2913396867832</v>
       </c>
       <c r="D330" t="n">
-        <v>529.4021360947859</v>
+        <v>529.4020765855032</v>
       </c>
       <c r="E330" t="n">
-        <v>545.9930461598316</v>
+        <v>545.9929847855902</v>
       </c>
       <c r="F330" t="n">
         <v>103670</v>
@@ -7032,16 +7032,16 @@
         <v>43434</v>
       </c>
       <c r="B331" t="n">
-        <v>537.5899047851562</v>
+        <v>537.5899658203125</v>
       </c>
       <c r="C331" t="n">
-        <v>547.2141143252957</v>
+        <v>547.2141764531345</v>
       </c>
       <c r="D331" t="n">
-        <v>537.5899047851562</v>
+        <v>537.5899658203125</v>
       </c>
       <c r="E331" t="n">
-        <v>542.8329404708712</v>
+        <v>542.8330021012944</v>
       </c>
       <c r="F331" t="n">
         <v>144308</v>
@@ -7052,16 +7052,16 @@
         <v>43437</v>
       </c>
       <c r="B332" t="n">
-        <v>529.186767578125</v>
+        <v>529.1867065429688</v>
       </c>
       <c r="C332" t="n">
-        <v>545.5622585269272</v>
+        <v>545.5621956030603</v>
       </c>
       <c r="D332" t="n">
-        <v>528.1094258769613</v>
+        <v>528.109364966063</v>
       </c>
       <c r="E332" t="n">
-        <v>539.5291678690518</v>
+        <v>539.5291056410274</v>
       </c>
       <c r="F332" t="n">
         <v>159359</v>
@@ -7152,16 +7152,16 @@
         <v>43444</v>
       </c>
       <c r="B337" t="n">
-        <v>540.1036376953125</v>
+        <v>540.103759765625</v>
       </c>
       <c r="C337" t="n">
-        <v>547.5731634482931</v>
+        <v>547.5732872068137</v>
       </c>
       <c r="D337" t="n">
-        <v>539.8881579625667</v>
+        <v>539.888279984178</v>
       </c>
       <c r="E337" t="n">
-        <v>545.8494399295113</v>
+        <v>545.8495632984484</v>
       </c>
       <c r="F337" t="n">
         <v>67100</v>
@@ -7172,16 +7172,16 @@
         <v>43445</v>
       </c>
       <c r="B338" t="n">
-        <v>541.5401000976562</v>
+        <v>541.5401611328125</v>
       </c>
       <c r="C338" t="n">
-        <v>544.9157397777561</v>
+        <v>544.9158011933694</v>
       </c>
       <c r="D338" t="n">
-        <v>530.5513192563691</v>
+        <v>530.5513790530169</v>
       </c>
       <c r="E338" t="n">
-        <v>544.9157397777561</v>
+        <v>544.9158011933694</v>
       </c>
       <c r="F338" t="n">
         <v>121498</v>
@@ -7192,16 +7192,16 @@
         <v>43446</v>
       </c>
       <c r="B339" t="n">
-        <v>543.335693359375</v>
+        <v>543.3355712890625</v>
       </c>
       <c r="C339" t="n">
-        <v>550.7333548450068</v>
+        <v>550.7332311126742</v>
       </c>
       <c r="D339" t="n">
-        <v>539.4572866336977</v>
+        <v>539.4571654347403</v>
       </c>
       <c r="E339" t="n">
-        <v>541.5401050455487</v>
+        <v>541.539983378648</v>
       </c>
       <c r="F339" t="n">
         <v>122528</v>
@@ -7212,16 +7212,16 @@
         <v>43447</v>
       </c>
       <c r="B340" t="n">
-        <v>545.8494262695312</v>
+        <v>545.849365234375</v>
       </c>
       <c r="C340" t="n">
-        <v>547.2140549806483</v>
+        <v>547.2139937929036</v>
       </c>
       <c r="D340" t="n">
-        <v>535.2915485167144</v>
+        <v>535.2914886621068</v>
       </c>
       <c r="E340" t="n">
-        <v>544.4129900398268</v>
+        <v>544.4129291652883</v>
       </c>
       <c r="F340" t="n">
         <v>85033</v>
@@ -7252,16 +7252,16 @@
         <v>43451</v>
       </c>
       <c r="B342" t="n">
-        <v>547.2140502929688</v>
+        <v>547.214111328125</v>
       </c>
       <c r="C342" t="n">
-        <v>561.5066621205802</v>
+        <v>561.5067247499056</v>
       </c>
       <c r="D342" t="n">
-        <v>545.8494215935417</v>
+        <v>545.84948247649</v>
       </c>
       <c r="E342" t="n">
-        <v>551.5951664631389</v>
+        <v>551.595227986956</v>
       </c>
       <c r="F342" t="n">
         <v>111025</v>
@@ -7272,16 +7272,16 @@
         <v>43452</v>
       </c>
       <c r="B343" t="n">
-        <v>570.4127197265625</v>
+        <v>570.4126586914062</v>
       </c>
       <c r="C343" t="n">
-        <v>573.1419775842055</v>
+        <v>573.1419162570139</v>
       </c>
       <c r="D343" t="n">
-        <v>545.8495133509767</v>
+        <v>545.8494549441264</v>
       </c>
       <c r="E343" t="n">
-        <v>551.9544111798516</v>
+        <v>551.9543521197666</v>
       </c>
       <c r="F343" t="n">
         <v>168814</v>
@@ -7392,16 +7392,16 @@
         <v>43462</v>
       </c>
       <c r="B349" t="n">
-        <v>599.4288330078125</v>
+        <v>599.428955078125</v>
       </c>
       <c r="C349" t="n">
-        <v>601.5834586362921</v>
+        <v>601.583581145382</v>
       </c>
       <c r="D349" t="n">
-        <v>579.7495149218122</v>
+        <v>579.7496329845422</v>
       </c>
       <c r="E349" t="n">
-        <v>583.556056407465</v>
+        <v>583.5561752453758</v>
       </c>
       <c r="F349" t="n">
         <v>152029</v>
@@ -7412,16 +7412,16 @@
         <v>43467</v>
       </c>
       <c r="B350" t="n">
-        <v>598.2796630859375</v>
+        <v>598.2797241210938</v>
       </c>
       <c r="C350" t="n">
-        <v>610.4176492769902</v>
+        <v>610.4177115504368</v>
       </c>
       <c r="D350" t="n">
-        <v>593.3957799050366</v>
+        <v>593.3958404419501</v>
       </c>
       <c r="E350" t="n">
-        <v>599.2851970325067</v>
+        <v>599.2852581702454</v>
       </c>
       <c r="F350" t="n">
         <v>124863</v>
@@ -7452,16 +7452,16 @@
         <v>43469</v>
       </c>
       <c r="B352" t="n">
-        <v>584.6334838867188</v>
+        <v>584.633544921875</v>
       </c>
       <c r="C352" t="n">
-        <v>597.9206202146979</v>
+        <v>597.9206826370181</v>
       </c>
       <c r="D352" t="n">
-        <v>576.6612478272082</v>
+        <v>576.6613080300709</v>
       </c>
       <c r="E352" t="n">
-        <v>597.9206202146979</v>
+        <v>597.9206826370181</v>
       </c>
       <c r="F352" t="n">
         <v>186720</v>
@@ -7492,16 +7492,16 @@
         <v>43473</v>
       </c>
       <c r="B354" t="n">
-        <v>596.125</v>
+        <v>596.1250610351562</v>
       </c>
       <c r="C354" t="n">
-        <v>600.8652678469101</v>
+        <v>600.8653293674058</v>
       </c>
       <c r="D354" t="n">
-        <v>589.94823884177</v>
+        <v>589.9482992445093</v>
       </c>
       <c r="E354" t="n">
-        <v>591.0974449251435</v>
+        <v>591.0975054455459</v>
       </c>
       <c r="F354" t="n">
         <v>213026</v>
@@ -7512,16 +7512,16 @@
         <v>43474</v>
       </c>
       <c r="B355" t="n">
-        <v>594.5449829101562</v>
+        <v>594.544921875</v>
       </c>
       <c r="C355" t="n">
-        <v>600.5780727945665</v>
+        <v>600.5780111400617</v>
       </c>
       <c r="D355" t="n">
-        <v>591.8157252399899</v>
+        <v>591.8156644850154</v>
       </c>
       <c r="E355" t="n">
-        <v>600.5062080978595</v>
+        <v>600.5061464507322</v>
       </c>
       <c r="F355" t="n">
         <v>147321</v>
@@ -7552,16 +7552,16 @@
         <v>43476</v>
       </c>
       <c r="B357" t="n">
-        <v>570.6281127929688</v>
+        <v>570.628173828125</v>
       </c>
       <c r="C357" t="n">
-        <v>587.1472153175711</v>
+        <v>587.1472781196329</v>
       </c>
       <c r="D357" t="n">
-        <v>569.6944435294589</v>
+        <v>569.6945044647485</v>
       </c>
       <c r="E357" t="n">
-        <v>583.9152480690574</v>
+        <v>583.9153105254236</v>
       </c>
       <c r="F357" t="n">
         <v>387970</v>
@@ -7612,16 +7612,16 @@
         <v>43481</v>
       </c>
       <c r="B360" t="n">
-        <v>596.125</v>
+        <v>596.1250610351562</v>
       </c>
       <c r="C360" t="n">
-        <v>599.5724467353573</v>
+        <v>599.5725081234856</v>
       </c>
       <c r="D360" t="n">
-        <v>578.1694053243783</v>
+        <v>578.1694645211239</v>
       </c>
       <c r="E360" t="n">
-        <v>578.1694053243783</v>
+        <v>578.1694645211239</v>
       </c>
       <c r="F360" t="n">
         <v>342845</v>
@@ -7632,16 +7632,16 @@
         <v>43482</v>
       </c>
       <c r="B361" t="n">
-        <v>600.4343872070312</v>
+        <v>600.4344482421875</v>
       </c>
       <c r="C361" t="n">
-        <v>604.7437533632822</v>
+        <v>604.7438148364927</v>
       </c>
       <c r="D361" t="n">
-        <v>587.7218256520052</v>
+        <v>587.7218853949083</v>
       </c>
       <c r="E361" t="n">
-        <v>598.9261433553005</v>
+        <v>598.9262042371413</v>
       </c>
       <c r="F361" t="n">
         <v>221295</v>
@@ -7692,16 +7692,16 @@
         <v>43487</v>
       </c>
       <c r="B364" t="n">
-        <v>621.9091796875</v>
+        <v>621.9092407226562</v>
       </c>
       <c r="C364" t="n">
-        <v>624.4948220034996</v>
+        <v>624.4948832924149</v>
       </c>
       <c r="D364" t="n">
-        <v>614.2242317709398</v>
+        <v>614.224292051883</v>
       </c>
       <c r="E364" t="n">
-        <v>618.3181177949477</v>
+        <v>618.3181784776715</v>
       </c>
       <c r="F364" t="n">
         <v>56158</v>
@@ -7712,16 +7712,16 @@
         <v>43488</v>
       </c>
       <c r="B365" t="n">
-        <v>621.3345947265625</v>
+        <v>621.3346557617188</v>
       </c>
       <c r="C365" t="n">
-        <v>624.2075242323521</v>
+        <v>624.2075855497229</v>
       </c>
       <c r="D365" t="n">
-        <v>616.0197523224966</v>
+        <v>616.0198128355635</v>
       </c>
       <c r="E365" t="n">
-        <v>621.3345947265625</v>
+        <v>621.3346557617188</v>
       </c>
       <c r="F365" t="n">
         <v>67413</v>
@@ -7732,16 +7732,16 @@
         <v>43489</v>
       </c>
       <c r="B366" t="n">
-        <v>631.5333862304688</v>
+        <v>631.5335083007812</v>
       </c>
       <c r="C366" t="n">
-        <v>631.5333862304688</v>
+        <v>631.5335083007812</v>
       </c>
       <c r="D366" t="n">
-        <v>616.9534874630561</v>
+        <v>616.9536067151918</v>
       </c>
       <c r="E366" t="n">
-        <v>619.7545523215402</v>
+        <v>619.7546721150992</v>
       </c>
       <c r="F366" t="n">
         <v>78173</v>
@@ -7752,16 +7752,16 @@
         <v>43493</v>
       </c>
       <c r="B367" t="n">
-        <v>633.3289184570312</v>
+        <v>633.3289794921875</v>
       </c>
       <c r="C367" t="n">
-        <v>651.499934675485</v>
+        <v>651.4999974618179</v>
       </c>
       <c r="D367" t="n">
-        <v>610.489384990946</v>
+        <v>610.4894438250113</v>
       </c>
       <c r="E367" t="n">
-        <v>611.2794391172413</v>
+        <v>611.2794980274457</v>
       </c>
       <c r="F367" t="n">
         <v>160193</v>
@@ -7792,16 +7792,16 @@
         <v>43495</v>
       </c>
       <c r="B369" t="n">
-        <v>616.2352294921875</v>
+        <v>616.2352905273438</v>
       </c>
       <c r="C369" t="n">
-        <v>636.9200245560744</v>
+        <v>636.9200876399608</v>
       </c>
       <c r="D369" t="n">
-        <v>612.3568232712602</v>
+        <v>612.3568839222787</v>
       </c>
       <c r="E369" t="n">
-        <v>624.5666163985063</v>
+        <v>624.5666782588467</v>
       </c>
       <c r="F369" t="n">
         <v>160897</v>
@@ -7812,16 +7812,16 @@
         <v>43496</v>
       </c>
       <c r="B370" t="n">
-        <v>612.3568115234375</v>
+        <v>612.3568725585938</v>
       </c>
       <c r="C370" t="n">
-        <v>622.7710735423368</v>
+        <v>622.771135615509</v>
       </c>
       <c r="D370" t="n">
-        <v>601.2243600235304</v>
+        <v>601.224419949087</v>
       </c>
       <c r="E370" t="n">
-        <v>621.2627727233632</v>
+        <v>621.2628346461992</v>
       </c>
       <c r="F370" t="n">
         <v>241027</v>
@@ -7892,16 +7892,16 @@
         <v>43502</v>
       </c>
       <c r="B374" t="n">
-        <v>617.6717529296875</v>
+        <v>617.6716918945312</v>
       </c>
       <c r="C374" t="n">
-        <v>626.7213877810843</v>
+        <v>626.7213258516895</v>
       </c>
       <c r="D374" t="n">
-        <v>612.859676816962</v>
+        <v>612.8596162573104</v>
       </c>
       <c r="E374" t="n">
-        <v>621.2628724258041</v>
+        <v>621.2628110357917</v>
       </c>
       <c r="F374" t="n">
         <v>112512</v>
@@ -7912,16 +7912,16 @@
         <v>43503</v>
       </c>
       <c r="B375" t="n">
-        <v>616.2352294921875</v>
+        <v>616.2352905273438</v>
       </c>
       <c r="C375" t="n">
-        <v>622.5556057728818</v>
+        <v>622.5556674340411</v>
       </c>
       <c r="D375" t="n">
-        <v>603.3790543853162</v>
+        <v>603.3791141471297</v>
       </c>
       <c r="E375" t="n">
-        <v>621.1191696117214</v>
+        <v>621.1192311306086</v>
       </c>
       <c r="F375" t="n">
         <v>104504</v>
@@ -7932,16 +7932,16 @@
         <v>43504</v>
       </c>
       <c r="B376" t="n">
-        <v>640.7266845703125</v>
+        <v>640.7267456054688</v>
       </c>
       <c r="C376" t="n">
-        <v>640.7266845703125</v>
+        <v>640.7267456054688</v>
       </c>
       <c r="D376" t="n">
-        <v>609.8431040496826</v>
+        <v>609.8431621428915</v>
       </c>
       <c r="E376" t="n">
-        <v>625.5722101555159</v>
+        <v>625.5722697470679</v>
       </c>
       <c r="F376" t="n">
         <v>269863</v>
@@ -7952,16 +7952,16 @@
         <v>43507</v>
       </c>
       <c r="B377" t="n">
-        <v>640.942138671875</v>
+        <v>640.9422607421875</v>
       </c>
       <c r="C377" t="n">
-        <v>649.6326208095448</v>
+        <v>649.6327445349987</v>
       </c>
       <c r="D377" t="n">
-        <v>633.1853257980567</v>
+        <v>633.1854463910494</v>
       </c>
       <c r="E377" t="n">
-        <v>640.7266589428041</v>
+        <v>640.7267809720776</v>
       </c>
       <c r="F377" t="n">
         <v>159215</v>
@@ -7972,16 +7972,16 @@
         <v>43508</v>
       </c>
       <c r="B378" t="n">
-        <v>667.2291870117188</v>
+        <v>667.2291259765625</v>
       </c>
       <c r="C378" t="n">
-        <v>669.3838129976359</v>
+        <v>669.3837517653841</v>
       </c>
       <c r="D378" t="n">
-        <v>643.5277866222542</v>
+        <v>643.5277277551967</v>
       </c>
       <c r="E378" t="n">
-        <v>645.6106622536108</v>
+        <v>645.610603196021</v>
       </c>
       <c r="F378" t="n">
         <v>195928</v>
@@ -7992,16 +7992,16 @@
         <v>43509</v>
       </c>
       <c r="B379" t="n">
-        <v>651.1409301757812</v>
+        <v>651.1409912109375</v>
       </c>
       <c r="C379" t="n">
-        <v>669.4556211237972</v>
+        <v>669.455683875694</v>
       </c>
       <c r="D379" t="n">
-        <v>650.2790684199256</v>
+        <v>650.2791293742946</v>
       </c>
       <c r="E379" t="n">
-        <v>667.2291306282719</v>
+        <v>667.229193171467</v>
       </c>
       <c r="F379" t="n">
         <v>182730</v>
@@ -8012,16 +8012,16 @@
         <v>43510</v>
       </c>
       <c r="B380" t="n">
-        <v>660.7650146484375</v>
+        <v>660.76513671875</v>
       </c>
       <c r="C380" t="n">
-        <v>667.8754448771806</v>
+        <v>667.8755682610803</v>
       </c>
       <c r="D380" t="n">
-        <v>646.5442113625379</v>
+        <v>646.5443308056866</v>
       </c>
       <c r="E380" t="n">
-        <v>654.7319829696715</v>
+        <v>654.7321039254365</v>
       </c>
       <c r="F380" t="n">
         <v>132140</v>
@@ -8032,16 +8032,16 @@
         <v>43511</v>
       </c>
       <c r="B381" t="n">
-        <v>654.6602172851562</v>
+        <v>654.6602783203125</v>
       </c>
       <c r="C381" t="n">
-        <v>660.0469249917048</v>
+        <v>660.0469865290736</v>
       </c>
       <c r="D381" t="n">
-        <v>640.3676043250778</v>
+        <v>640.3676640277077</v>
       </c>
       <c r="E381" t="n">
-        <v>653.5828757438466</v>
+        <v>653.5829366785603</v>
       </c>
       <c r="F381" t="n">
         <v>315705</v>
@@ -8052,16 +8052,16 @@
         <v>43514</v>
       </c>
       <c r="B382" t="n">
-        <v>658.6104736328125</v>
+        <v>658.6104125976562</v>
       </c>
       <c r="C382" t="n">
-        <v>664.7153713098178</v>
+        <v>664.7153097089048</v>
       </c>
       <c r="D382" t="n">
-        <v>650.7818522480502</v>
+        <v>650.7817919383928</v>
       </c>
       <c r="E382" t="n">
-        <v>660.7651568533082</v>
+        <v>660.7650956184718</v>
       </c>
       <c r="F382" t="n">
         <v>91084</v>
@@ -8072,16 +8072,16 @@
         <v>43515</v>
       </c>
       <c r="B383" t="n">
-        <v>661.4833984375</v>
+        <v>661.4833374023438</v>
       </c>
       <c r="C383" t="n">
-        <v>662.8480273216194</v>
+        <v>662.8479661605486</v>
       </c>
       <c r="D383" t="n">
-        <v>651.0691344015784</v>
+        <v>651.0690743273475</v>
       </c>
       <c r="E383" t="n">
-        <v>660.0469620256898</v>
+        <v>660.0469011230737</v>
       </c>
       <c r="F383" t="n">
         <v>188559</v>
@@ -8112,16 +8112,16 @@
         <v>43517</v>
       </c>
       <c r="B385" t="n">
-        <v>681.3063354492188</v>
+        <v>681.3062133789062</v>
       </c>
       <c r="C385" t="n">
-        <v>681.3063354492188</v>
+        <v>681.3062133789062</v>
       </c>
       <c r="D385" t="n">
-        <v>663.6380818217434</v>
+        <v>663.637962917069</v>
       </c>
       <c r="E385" t="n">
-        <v>663.6380818217434</v>
+        <v>663.637962917069</v>
       </c>
       <c r="F385" t="n">
         <v>232784</v>
@@ -8132,16 +8132,16 @@
         <v>43518</v>
       </c>
       <c r="B386" t="n">
-        <v>670.8202514648438</v>
+        <v>670.8201904296875</v>
       </c>
       <c r="C386" t="n">
-        <v>685.6874966920099</v>
+        <v>685.6874343041444</v>
       </c>
       <c r="D386" t="n">
-        <v>670.5329641877216</v>
+        <v>670.5329031787044</v>
       </c>
       <c r="E386" t="n">
-        <v>678.2897778416174</v>
+        <v>678.2897161268398</v>
       </c>
       <c r="F386" t="n">
         <v>142026</v>
@@ -8172,16 +8172,16 @@
         <v>43522</v>
       </c>
       <c r="B388" t="n">
-        <v>673.3340454101562</v>
+        <v>673.333984375</v>
       </c>
       <c r="C388" t="n">
-        <v>679.5826153003328</v>
+        <v>679.5825536987676</v>
       </c>
       <c r="D388" t="n">
-        <v>659.1851037974504</v>
+        <v>659.1850440448417</v>
       </c>
       <c r="E388" t="n">
-        <v>673.1186228259008</v>
+        <v>673.1185618102719</v>
       </c>
       <c r="F388" t="n">
         <v>234558</v>
@@ -8192,16 +8192,16 @@
         <v>43523</v>
       </c>
       <c r="B389" t="n">
-        <v>646.4006958007812</v>
+        <v>646.400634765625</v>
       </c>
       <c r="C389" t="n">
-        <v>669.3119839804588</v>
+        <v>669.3119207819476</v>
       </c>
       <c r="D389" t="n">
-        <v>646.4006958007812</v>
+        <v>646.400634765625</v>
       </c>
       <c r="E389" t="n">
-        <v>667.1573008921292</v>
+        <v>667.15723789707</v>
       </c>
       <c r="F389" t="n">
         <v>481207</v>
@@ -8212,16 +8212,16 @@
         <v>43524</v>
       </c>
       <c r="B390" t="n">
-        <v>639.218505859375</v>
+        <v>639.2183837890625</v>
       </c>
       <c r="C390" t="n">
-        <v>654.0856945287965</v>
+        <v>654.085569619326</v>
       </c>
       <c r="D390" t="n">
-        <v>634.2627572457012</v>
+        <v>634.2626361217784</v>
       </c>
       <c r="E390" t="n">
-        <v>652.6492580838765</v>
+        <v>652.6491334487195</v>
       </c>
       <c r="F390" t="n">
         <v>276723</v>
@@ -8232,16 +8232,16 @@
         <v>43525</v>
       </c>
       <c r="B391" t="n">
-        <v>646.9034423828125</v>
+        <v>646.9033813476562</v>
       </c>
       <c r="C391" t="n">
-        <v>651.715575842952</v>
+        <v>651.7155143537724</v>
       </c>
       <c r="D391" t="n">
-        <v>639.8648753556274</v>
+        <v>639.8648149845581</v>
       </c>
       <c r="E391" t="n">
-        <v>639.8648753556274</v>
+        <v>639.8648149845581</v>
       </c>
       <c r="F391" t="n">
         <v>193907</v>
@@ -8252,16 +8252,16 @@
         <v>43530</v>
       </c>
       <c r="B392" t="n">
-        <v>627.655029296875</v>
+        <v>627.6550903320312</v>
       </c>
       <c r="C392" t="n">
-        <v>657.1021735564907</v>
+        <v>657.1022374551802</v>
       </c>
       <c r="D392" t="n">
-        <v>614.5833732054725</v>
+        <v>614.5834329694998</v>
       </c>
       <c r="E392" t="n">
-        <v>651.8591381811863</v>
+        <v>651.8592015700265</v>
       </c>
       <c r="F392" t="n">
         <v>217799</v>
@@ -8292,16 +8292,16 @@
         <v>43532</v>
       </c>
       <c r="B394" t="n">
-        <v>654.3011474609375</v>
+        <v>654.3010864257812</v>
       </c>
       <c r="C394" t="n">
-        <v>654.3011474609375</v>
+        <v>654.3010864257812</v>
       </c>
       <c r="D394" t="n">
-        <v>611.495057299448</v>
+        <v>611.4950002573712</v>
       </c>
       <c r="E394" t="n">
-        <v>621.1910743696039</v>
+        <v>621.1910164230537</v>
       </c>
       <c r="F394" t="n">
         <v>586768</v>
@@ -8312,16 +8312,16 @@
         <v>43535</v>
       </c>
       <c r="B395" t="n">
-        <v>653.5828247070312</v>
+        <v>653.5828857421875</v>
       </c>
       <c r="C395" t="n">
-        <v>656.1684670729056</v>
+        <v>656.1685283495234</v>
       </c>
       <c r="D395" t="n">
-        <v>641.8039905392596</v>
+        <v>641.8040504744437</v>
       </c>
       <c r="E395" t="n">
-        <v>649.9917055736198</v>
+        <v>649.9917662734176</v>
       </c>
       <c r="F395" t="n">
         <v>211500</v>
@@ -8352,16 +8352,16 @@
         <v>43537</v>
       </c>
       <c r="B397" t="n">
-        <v>640.8704223632812</v>
+        <v>640.8703002929688</v>
       </c>
       <c r="C397" t="n">
-        <v>653.080217908204</v>
+        <v>653.0800935122207</v>
       </c>
       <c r="D397" t="n">
-        <v>630.5998303128064</v>
+        <v>630.5997101987931</v>
       </c>
       <c r="E397" t="n">
-        <v>647.3344149542404</v>
+        <v>647.3342916526937</v>
       </c>
       <c r="F397" t="n">
         <v>145482</v>
@@ -8372,16 +8372,16 @@
         <v>43538</v>
       </c>
       <c r="B398" t="n">
-        <v>639.218505859375</v>
+        <v>639.2183837890625</v>
       </c>
       <c r="C398" t="n">
-        <v>651.2128216389566</v>
+        <v>651.212697278113</v>
       </c>
       <c r="D398" t="n">
-        <v>629.8815832099955</v>
+        <v>629.8814629227369</v>
       </c>
       <c r="E398" t="n">
-        <v>642.8096255574749</v>
+        <v>642.8095028013732</v>
       </c>
       <c r="F398" t="n">
         <v>180995</v>
@@ -8432,16 +8432,16 @@
         <v>43543</v>
       </c>
       <c r="B401" t="n">
-        <v>653.5828247070312</v>
+        <v>653.5828857421875</v>
       </c>
       <c r="C401" t="n">
-        <v>655.2347406518323</v>
+        <v>655.2348018412537</v>
       </c>
       <c r="D401" t="n">
-        <v>645.6105893984259</v>
+        <v>645.6106496890909</v>
       </c>
       <c r="E401" t="n">
-        <v>645.6105893984259</v>
+        <v>645.6106496890909</v>
       </c>
       <c r="F401" t="n">
         <v>173822</v>
@@ -8452,16 +8452,16 @@
         <v>43544</v>
       </c>
       <c r="B402" t="n">
-        <v>653.5828247070312</v>
+        <v>653.5828857421875</v>
       </c>
       <c r="C402" t="n">
-        <v>658.2512852976253</v>
+        <v>658.251346768748</v>
       </c>
       <c r="D402" t="n">
-        <v>648.9144212880281</v>
+        <v>648.9144818872231</v>
       </c>
       <c r="E402" t="n">
-        <v>654.3010714023499</v>
+        <v>654.30113250458</v>
       </c>
       <c r="F402" t="n">
         <v>122072</v>
@@ -8472,16 +8472,16 @@
         <v>43545</v>
       </c>
       <c r="B403" t="n">
-        <v>650.7818603515625</v>
+        <v>650.7817993164062</v>
       </c>
       <c r="C403" t="n">
-        <v>654.6602673281091</v>
+        <v>654.660205929207</v>
       </c>
       <c r="D403" t="n">
-        <v>646.4007434993596</v>
+        <v>646.4006828750971</v>
       </c>
       <c r="E403" t="n">
-        <v>653.5829257044461</v>
+        <v>653.5828644065853</v>
       </c>
       <c r="F403" t="n">
         <v>181165</v>
@@ -8492,16 +8492,16 @@
         <v>43546</v>
       </c>
       <c r="B404" t="n">
-        <v>657.0748291015625</v>
+        <v>657.0747680664062</v>
       </c>
       <c r="C404" t="n">
-        <v>663.2681009756196</v>
+        <v>663.2680393651752</v>
       </c>
       <c r="D404" t="n">
-        <v>635.5458643439046</v>
+        <v>635.5458053085566</v>
       </c>
       <c r="E404" t="n">
-        <v>647.7849212904769</v>
+        <v>647.7848611182527</v>
       </c>
       <c r="F404" t="n">
         <v>199032</v>
@@ -8532,16 +8532,16 @@
         <v>43550</v>
       </c>
       <c r="B406" t="n">
-        <v>667.3969116210938</v>
+        <v>667.3968505859375</v>
       </c>
       <c r="C406" t="n">
-        <v>670.346060764781</v>
+        <v>670.3459994599175</v>
       </c>
       <c r="D406" t="n">
-        <v>658.4756914442885</v>
+        <v>658.4756312250007</v>
       </c>
       <c r="E406" t="n">
-        <v>667.2494248191418</v>
+        <v>667.2493637974736</v>
       </c>
       <c r="F406" t="n">
         <v>144960</v>
@@ -8572,16 +8572,16 @@
         <v>43552</v>
       </c>
       <c r="B408" t="n">
-        <v>656.1900024414062</v>
+        <v>656.18994140625</v>
       </c>
       <c r="C408" t="n">
-        <v>665.3324223095999</v>
+        <v>665.3323604240663</v>
       </c>
       <c r="D408" t="n">
-        <v>645.204320576497</v>
+        <v>645.2042605631681</v>
       </c>
       <c r="E408" t="n">
-        <v>657.0747470715997</v>
+        <v>657.0746859541495</v>
       </c>
       <c r="F408" t="n">
         <v>222599</v>
@@ -8612,16 +8612,16 @@
         <v>43556</v>
       </c>
       <c r="B410" t="n">
-        <v>678.3087158203125</v>
+        <v>678.3087768554688</v>
       </c>
       <c r="C410" t="n">
-        <v>681.1841504570795</v>
+        <v>681.1842117509711</v>
       </c>
       <c r="D410" t="n">
-        <v>665.4061169771885</v>
+        <v>665.406176851351</v>
       </c>
       <c r="E410" t="n">
-        <v>673.1476762830629</v>
+        <v>673.1477368538217</v>
       </c>
       <c r="F410" t="n">
         <v>165645</v>
@@ -8652,16 +8652,16 @@
         <v>43558</v>
       </c>
       <c r="B412" t="n">
-        <v>689.3681640625</v>
+        <v>689.3681030273438</v>
       </c>
       <c r="C412" t="n">
-        <v>696.7410950187081</v>
+        <v>696.7410333307686</v>
       </c>
       <c r="D412" t="n">
-        <v>677.4240229561865</v>
+        <v>677.4239629785386</v>
       </c>
       <c r="E412" t="n">
-        <v>679.7833420815233</v>
+        <v>679.7832818949864</v>
       </c>
       <c r="F412" t="n">
         <v>159059</v>
@@ -8692,16 +8692,16 @@
         <v>43560</v>
       </c>
       <c r="B414" t="n">
-        <v>701.017333984375</v>
+        <v>701.0174560546875</v>
       </c>
       <c r="C414" t="n">
-        <v>702.2707074966779</v>
+        <v>702.2708297852442</v>
       </c>
       <c r="D414" t="n">
-        <v>682.4375799852958</v>
+        <v>682.4376988202584</v>
       </c>
       <c r="E414" t="n">
-        <v>689.8105103494357</v>
+        <v>689.8106304682694</v>
       </c>
       <c r="F414" t="n">
         <v>143643</v>
@@ -8712,16 +8712,16 @@
         <v>43563</v>
       </c>
       <c r="B415" t="n">
-        <v>712.0030517578125</v>
+        <v>712.0029907226562</v>
       </c>
       <c r="C415" t="n">
-        <v>712.0030517578125</v>
+        <v>712.0029907226562</v>
       </c>
       <c r="D415" t="n">
-        <v>694.6767276497193</v>
+        <v>694.6766680998304</v>
       </c>
       <c r="E415" t="n">
-        <v>701.8284581450785</v>
+        <v>701.8283979821206</v>
       </c>
       <c r="F415" t="n">
         <v>133157</v>
@@ -8732,16 +8732,16 @@
         <v>43564</v>
       </c>
       <c r="B416" t="n">
-        <v>701.9021606445312</v>
+        <v>701.902099609375</v>
       </c>
       <c r="C416" t="n">
-        <v>710.8970944839187</v>
+        <v>710.8970326665921</v>
       </c>
       <c r="D416" t="n">
-        <v>698.5106099329405</v>
+        <v>698.5105491927027</v>
       </c>
       <c r="E416" t="n">
-        <v>707.8005173633237</v>
+        <v>707.8004558152653</v>
       </c>
       <c r="F416" t="n">
         <v>71169</v>
@@ -8772,16 +8772,16 @@
         <v>43566</v>
       </c>
       <c r="B418" t="n">
-        <v>696.7410888671875</v>
+        <v>696.7410278320312</v>
       </c>
       <c r="C418" t="n">
-        <v>701.828414703427</v>
+        <v>701.8283532226163</v>
       </c>
       <c r="D418" t="n">
-        <v>682.2164279233924</v>
+        <v>682.2163681606097</v>
       </c>
       <c r="E418" t="n">
-        <v>688.6308414111518</v>
+        <v>688.6307810864605</v>
       </c>
       <c r="F418" t="n">
         <v>167666</v>
@@ -8812,16 +8812,16 @@
         <v>43570</v>
       </c>
       <c r="B420" t="n">
-        <v>702.4920043945312</v>
+        <v>702.491943359375</v>
       </c>
       <c r="C420" t="n">
-        <v>707.4318437644937</v>
+        <v>707.4317823001455</v>
       </c>
       <c r="D420" t="n">
-        <v>694.8241581147256</v>
+        <v>694.8240977457807</v>
       </c>
       <c r="E420" t="n">
-        <v>702.3445175961053</v>
+        <v>702.3444565737632</v>
       </c>
       <c r="F420" t="n">
         <v>105769</v>
@@ -8832,16 +8832,16 @@
         <v>43571</v>
       </c>
       <c r="B421" t="n">
-        <v>700.3538818359375</v>
+        <v>700.3538208007812</v>
       </c>
       <c r="C421" t="n">
-        <v>706.252179947325</v>
+        <v>706.2521183981379</v>
       </c>
       <c r="D421" t="n">
-        <v>693.4970075747659</v>
+        <v>693.4969471371796</v>
       </c>
       <c r="E421" t="n">
-        <v>706.252179947325</v>
+        <v>706.2521183981379</v>
       </c>
       <c r="F421" t="n">
         <v>72630</v>
@@ -8852,16 +8852,16 @@
         <v>43572</v>
       </c>
       <c r="B422" t="n">
-        <v>700.4275512695312</v>
+        <v>700.427490234375</v>
       </c>
       <c r="C422" t="n">
-        <v>705.4411043448246</v>
+        <v>705.441042872788</v>
       </c>
       <c r="D422" t="n">
-        <v>693.7919369721723</v>
+        <v>693.7918765152425</v>
       </c>
       <c r="E422" t="n">
-        <v>700.8698942549393</v>
+        <v>700.8698331812374</v>
       </c>
       <c r="F422" t="n">
         <v>106252</v>
@@ -8872,16 +8872,16 @@
         <v>43573</v>
       </c>
       <c r="B423" t="n">
-        <v>684.7969970703125</v>
+        <v>684.7969360351562</v>
       </c>
       <c r="C423" t="n">
-        <v>704.5564133693659</v>
+        <v>704.556350573076</v>
       </c>
       <c r="D423" t="n">
-        <v>684.7969970703125</v>
+        <v>684.7969360351562</v>
       </c>
       <c r="E423" t="n">
-        <v>700.5013186947467</v>
+        <v>700.5012562598826</v>
       </c>
       <c r="F423" t="n">
         <v>125776</v>
@@ -8892,16 +8892,16 @@
         <v>43577</v>
       </c>
       <c r="B424" t="n">
-        <v>697.9207153320312</v>
+        <v>697.9207763671875</v>
       </c>
       <c r="C424" t="n">
-        <v>703.3766698473084</v>
+        <v>703.3767313596035</v>
       </c>
       <c r="D424" t="n">
-        <v>686.2714897715088</v>
+        <v>686.2715497879069</v>
       </c>
       <c r="E424" t="n">
-        <v>686.3452038176474</v>
+        <v>686.3452638404921</v>
       </c>
       <c r="F424" t="n">
         <v>77260</v>
@@ -8932,16 +8932,16 @@
         <v>43579</v>
       </c>
       <c r="B426" t="n">
-        <v>717.38525390625</v>
+        <v>717.3851928710938</v>
       </c>
       <c r="C426" t="n">
-        <v>727.7073337570685</v>
+        <v>727.7072718437095</v>
       </c>
       <c r="D426" t="n">
-        <v>715.3208496739924</v>
+        <v>715.3207888144757</v>
       </c>
       <c r="E426" t="n">
-        <v>722.9149814617102</v>
+        <v>722.9149199560846</v>
       </c>
       <c r="F426" t="n">
         <v>136444</v>
@@ -8972,16 +8972,16 @@
         <v>43581</v>
       </c>
       <c r="B428" t="n">
-        <v>697.9207153320312</v>
+        <v>697.9207763671875</v>
       </c>
       <c r="C428" t="n">
-        <v>723.7259135380083</v>
+        <v>723.7259768299026</v>
       </c>
       <c r="D428" t="n">
-        <v>697.9207153320312</v>
+        <v>697.9207763671875</v>
       </c>
       <c r="E428" t="n">
-        <v>722.546254041681</v>
+        <v>722.5463172304108</v>
       </c>
       <c r="F428" t="n">
         <v>338189</v>
@@ -8992,16 +8992,16 @@
         <v>43584</v>
       </c>
       <c r="B429" t="n">
-        <v>699.6903076171875</v>
+        <v>699.6902465820312</v>
       </c>
       <c r="C429" t="n">
-        <v>708.7590146926256</v>
+        <v>708.7589528663908</v>
       </c>
       <c r="D429" t="n">
-        <v>673.5164179469361</v>
+        <v>673.5163591949721</v>
       </c>
       <c r="E429" t="n">
-        <v>697.9208181121107</v>
+        <v>697.9207572313101</v>
       </c>
       <c r="F429" t="n">
         <v>175687</v>
@@ -9052,16 +9052,16 @@
         <v>43588</v>
       </c>
       <c r="B432" t="n">
-        <v>738.0294799804688</v>
+        <v>738.0294189453125</v>
       </c>
       <c r="C432" t="n">
-        <v>738.1031940314342</v>
+        <v>738.1031329901817</v>
       </c>
       <c r="D432" t="n">
-        <v>705.6623210001189</v>
+        <v>705.6622626417319</v>
       </c>
       <c r="E432" t="n">
-        <v>714.7310273338567</v>
+        <v>714.7309682254861</v>
       </c>
       <c r="F432" t="n">
         <v>687008</v>
@@ -9092,16 +9092,16 @@
         <v>43592</v>
       </c>
       <c r="B434" t="n">
-        <v>733.605712890625</v>
+        <v>733.6056518554688</v>
       </c>
       <c r="C434" t="n">
-        <v>736.5548618848549</v>
+        <v>736.5548006043327</v>
       </c>
       <c r="D434" t="n">
-        <v>718.34379348357</v>
+        <v>718.343733718188</v>
       </c>
       <c r="E434" t="n">
-        <v>724.0208906250796</v>
+        <v>724.0208303873695</v>
       </c>
       <c r="F434" t="n">
         <v>269719</v>
@@ -9112,16 +9112,16 @@
         <v>43593</v>
       </c>
       <c r="B435" t="n">
-        <v>733.605712890625</v>
+        <v>733.6056518554688</v>
       </c>
       <c r="C435" t="n">
-        <v>744.5913956008127</v>
+        <v>744.5913336516602</v>
       </c>
       <c r="D435" t="n">
-        <v>724.7582072184031</v>
+        <v>724.7581469193492</v>
       </c>
       <c r="E435" t="n">
-        <v>735.3014882346903</v>
+        <v>735.3014270584474</v>
       </c>
       <c r="F435" t="n">
         <v>163597</v>
@@ -9132,16 +9132,16 @@
         <v>43594</v>
       </c>
       <c r="B436" t="n">
-        <v>733.605712890625</v>
+        <v>733.6056518554688</v>
       </c>
       <c r="C436" t="n">
-        <v>735.8913180335362</v>
+        <v>735.8912568082202</v>
       </c>
       <c r="D436" t="n">
-        <v>718.9336232824161</v>
+        <v>718.9335634679609</v>
       </c>
       <c r="E436" t="n">
-        <v>733.605712890625</v>
+        <v>733.6056518554688</v>
       </c>
       <c r="F436" t="n">
         <v>311336</v>
@@ -9152,16 +9152,16 @@
         <v>43595</v>
       </c>
       <c r="B437" t="n">
-        <v>745.2549438476562</v>
+        <v>745.2548828125</v>
       </c>
       <c r="C437" t="n">
-        <v>746.065974498236</v>
+        <v>746.0659133966576</v>
       </c>
       <c r="D437" t="n">
-        <v>727.6336464517544</v>
+        <v>727.6335868597536</v>
       </c>
       <c r="E437" t="n">
-        <v>735.006577670347</v>
+        <v>735.0065174745151</v>
       </c>
       <c r="F437" t="n">
         <v>130275</v>
@@ -9192,16 +9192,16 @@
         <v>43599</v>
       </c>
       <c r="B439" t="n">
-        <v>726.1591186523438</v>
+        <v>726.1590576171875</v>
       </c>
       <c r="C439" t="n">
-        <v>736.2599986839919</v>
+        <v>736.2599367998361</v>
       </c>
       <c r="D439" t="n">
-        <v>720.7031632851472</v>
+        <v>720.7031027085751</v>
       </c>
       <c r="E439" t="n">
-        <v>726.7489484926062</v>
+        <v>726.7488874078737</v>
       </c>
       <c r="F439" t="n">
         <v>135127</v>
@@ -9212,16 +9212,16 @@
         <v>43600</v>
       </c>
       <c r="B440" t="n">
-        <v>715.17333984375</v>
+        <v>715.1734008789062</v>
       </c>
       <c r="C440" t="n">
-        <v>726.2327359088459</v>
+        <v>726.232797887846</v>
       </c>
       <c r="D440" t="n">
-        <v>712.2241910355358</v>
+        <v>712.2242518190023</v>
       </c>
       <c r="E440" t="n">
-        <v>720.9242680540605</v>
+        <v>720.924329580019</v>
       </c>
       <c r="F440" t="n">
         <v>136379</v>
@@ -9232,16 +9232,16 @@
         <v>43601</v>
       </c>
       <c r="B441" t="n">
-        <v>713.4776611328125</v>
+        <v>713.4777221679688</v>
       </c>
       <c r="C441" t="n">
-        <v>725.9378595254442</v>
+        <v>725.9379216265205</v>
       </c>
       <c r="D441" t="n">
-        <v>704.1877538599894</v>
+        <v>704.1878141004312</v>
       </c>
       <c r="E441" t="n">
-        <v>715.1733777703154</v>
+        <v>715.1734389505333</v>
       </c>
       <c r="F441" t="n">
         <v>192694</v>
@@ -9252,16 +9252,16 @@
         <v>43602</v>
       </c>
       <c r="B442" t="n">
-        <v>733.605712890625</v>
+        <v>733.6056518554688</v>
       </c>
       <c r="C442" t="n">
-        <v>735.9650320860089</v>
+        <v>735.96497085456</v>
       </c>
       <c r="D442" t="n">
-        <v>712.8877798099464</v>
+        <v>712.8877204984985</v>
       </c>
       <c r="E442" t="n">
-        <v>713.4776682983246</v>
+        <v>713.4776089377987</v>
       </c>
       <c r="F442" t="n">
         <v>136509</v>
@@ -9292,16 +9292,16 @@
         <v>43606</v>
       </c>
       <c r="B444" t="n">
-        <v>766.046630859375</v>
+        <v>766.0465698242188</v>
       </c>
       <c r="C444" t="n">
-        <v>770.2491537466567</v>
+        <v>770.2490923766624</v>
       </c>
       <c r="D444" t="n">
-        <v>750.2685361045108</v>
+        <v>750.2684763264823</v>
       </c>
       <c r="E444" t="n">
-        <v>755.7245500934678</v>
+        <v>755.7244898807286</v>
       </c>
       <c r="F444" t="n">
         <v>224959</v>
@@ -9352,16 +9352,16 @@
         <v>43609</v>
       </c>
       <c r="B447" t="n">
-        <v>736.5548706054688</v>
+        <v>736.5548095703125</v>
       </c>
       <c r="C447" t="n">
-        <v>761.0329836159879</v>
+        <v>761.0329205524349</v>
       </c>
       <c r="D447" t="n">
-        <v>726.2327903139212</v>
+        <v>726.2327301341116</v>
       </c>
       <c r="E447" t="n">
-        <v>759.4109223051905</v>
+        <v>759.4108593760509</v>
       </c>
       <c r="F447" t="n">
         <v>221503</v>
@@ -9372,16 +9372,16 @@
         <v>43612</v>
       </c>
       <c r="B448" t="n">
-        <v>731.836181640625</v>
+        <v>731.8361206054688</v>
       </c>
       <c r="C448" t="n">
-        <v>746.5820431475281</v>
+        <v>746.5819808825665</v>
       </c>
       <c r="D448" t="n">
-        <v>731.836181640625</v>
+        <v>731.8361206054688</v>
       </c>
       <c r="E448" t="n">
-        <v>742.6743769365024</v>
+        <v>742.6743149974403</v>
       </c>
       <c r="F448" t="n">
         <v>96223</v>
@@ -9452,16 +9452,16 @@
         <v>43616</v>
       </c>
       <c r="B452" t="n">
-        <v>751.1533203125</v>
+        <v>751.1532592773438</v>
       </c>
       <c r="C452" t="n">
-        <v>780.6449872728404</v>
+        <v>780.6449238413311</v>
       </c>
       <c r="D452" t="n">
-        <v>749.5312589686873</v>
+        <v>749.5311980653321</v>
       </c>
       <c r="E452" t="n">
-        <v>768.6271313725395</v>
+        <v>768.6270689175442</v>
       </c>
       <c r="F452" t="n">
         <v>226903</v>
@@ -9472,16 +9472,16 @@
         <v>43619</v>
       </c>
       <c r="B453" t="n">
-        <v>736.5548706054688</v>
+        <v>736.5548095703125</v>
       </c>
       <c r="C453" t="n">
-        <v>752.406678688583</v>
+        <v>752.4066163398552</v>
       </c>
       <c r="D453" t="n">
-        <v>733.6057215763217</v>
+        <v>733.6056607855488</v>
       </c>
       <c r="E453" t="n">
-        <v>752.0380497323229</v>
+        <v>752.0379874141418</v>
       </c>
       <c r="F453" t="n">
         <v>267306</v>
@@ -9492,16 +9492,16 @@
         <v>43620</v>
       </c>
       <c r="B454" t="n">
-        <v>746.9508056640625</v>
+        <v>746.9507446289062</v>
       </c>
       <c r="C454" t="n">
-        <v>751.8906455027208</v>
+        <v>751.8905840639183</v>
       </c>
       <c r="D454" t="n">
-        <v>735.8176934945669</v>
+        <v>735.8176333691242</v>
       </c>
       <c r="E454" t="n">
-        <v>741.347363203825</v>
+        <v>741.3473026265395</v>
       </c>
       <c r="F454" t="n">
         <v>256221</v>
@@ -9592,16 +9592,16 @@
         <v>43627</v>
       </c>
       <c r="B459" t="n">
-        <v>714.4360961914062</v>
+        <v>714.4361572265625</v>
       </c>
       <c r="C459" t="n">
-        <v>736.2599151851655</v>
+        <v>736.2599780847576</v>
       </c>
       <c r="D459" t="n">
-        <v>708.6114538174628</v>
+        <v>708.6115143550127</v>
       </c>
       <c r="E459" t="n">
-        <v>733.4582531064216</v>
+        <v>733.4583157666642</v>
       </c>
       <c r="F459" t="n">
         <v>166153</v>
@@ -9612,16 +9612,16 @@
         <v>43628</v>
       </c>
       <c r="B460" t="n">
-        <v>713.5513916015625</v>
+        <v>713.5513305664062</v>
       </c>
       <c r="C460" t="n">
-        <v>717.9751151502583</v>
+        <v>717.9750537367092</v>
       </c>
       <c r="D460" t="n">
-        <v>705.9572594810519</v>
+        <v>705.9571990954761</v>
       </c>
       <c r="E460" t="n">
-        <v>714.5098503647299</v>
+        <v>714.5097892475899</v>
       </c>
       <c r="F460" t="n">
         <v>341893</v>
@@ -9632,16 +9632,16 @@
         <v>43629</v>
       </c>
       <c r="B461" t="n">
-        <v>707.800537109375</v>
+        <v>707.8004760742188</v>
       </c>
       <c r="C461" t="n">
-        <v>728.8870998760784</v>
+        <v>728.8870370225827</v>
       </c>
       <c r="D461" t="n">
-        <v>702.270809190761</v>
+        <v>702.2707486324451</v>
       </c>
       <c r="E461" t="n">
-        <v>717.311586964043</v>
+        <v>717.3115251087285</v>
       </c>
       <c r="F461" t="n">
         <v>234349</v>
@@ -9652,16 +9652,16 @@
         <v>43630</v>
       </c>
       <c r="B462" t="n">
-        <v>690.1055297851562</v>
+        <v>690.10546875</v>
       </c>
       <c r="C462" t="n">
-        <v>718.7861663414552</v>
+        <v>718.7861027696911</v>
       </c>
       <c r="D462" t="n">
-        <v>690.1055297851562</v>
+        <v>690.10546875</v>
       </c>
       <c r="E462" t="n">
-        <v>707.7267691194622</v>
+        <v>707.7267065258268</v>
       </c>
       <c r="F462" t="n">
         <v>150777</v>
@@ -9712,16 +9712,16 @@
         <v>43635</v>
       </c>
       <c r="B465" t="n">
-        <v>724.8319702148438</v>
+        <v>724.8319091796875</v>
       </c>
       <c r="C465" t="n">
-        <v>728.9608377750978</v>
+        <v>728.9607763922664</v>
       </c>
       <c r="D465" t="n">
-        <v>714.0675463142754</v>
+        <v>714.0674861855476</v>
       </c>
       <c r="E465" t="n">
-        <v>720.4082464247889</v>
+        <v>720.4081857621364</v>
       </c>
       <c r="F465" t="n">
         <v>115851</v>
@@ -9732,16 +9732,16 @@
         <v>43637</v>
       </c>
       <c r="B466" t="n">
-        <v>733.458251953125</v>
+        <v>733.4581909179688</v>
       </c>
       <c r="C466" t="n">
-        <v>733.458251953125</v>
+        <v>733.4581909179688</v>
       </c>
       <c r="D466" t="n">
-        <v>723.3573143933651</v>
+        <v>723.3572541987642</v>
       </c>
       <c r="E466" t="n">
-        <v>728.4446401978315</v>
+        <v>728.4445795798858</v>
       </c>
       <c r="F466" t="n">
         <v>181934</v>
@@ -9752,16 +9752,16 @@
         <v>43640</v>
       </c>
       <c r="B467" t="n">
-        <v>745.0337524414062</v>
+        <v>745.03369140625</v>
       </c>
       <c r="C467" t="n">
-        <v>752.0380547946963</v>
+        <v>752.037993185729</v>
       </c>
       <c r="D467" t="n">
-        <v>733.8269273656755</v>
+        <v>733.8268672486123</v>
       </c>
       <c r="E467" t="n">
-        <v>734.0481282167337</v>
+        <v>734.0480680815492</v>
       </c>
       <c r="F467" t="n">
         <v>155459</v>
@@ -9872,16 +9872,16 @@
         <v>43648</v>
       </c>
       <c r="B473" t="n">
-        <v>715.17333984375</v>
+        <v>715.1734008789062</v>
       </c>
       <c r="C473" t="n">
-        <v>746.139637088113</v>
+        <v>746.1397007660311</v>
       </c>
       <c r="D473" t="n">
-        <v>711.8555621068912</v>
+        <v>711.8556228588977</v>
       </c>
       <c r="E473" t="n">
-        <v>746.139637088113</v>
+        <v>746.1397007660311</v>
       </c>
       <c r="F473" t="n">
         <v>313670</v>
@@ -9892,16 +9892,16 @@
         <v>43649</v>
       </c>
       <c r="B474" t="n">
-        <v>709.5700073242188</v>
+        <v>709.570068359375</v>
       </c>
       <c r="C474" t="n">
-        <v>721.44037613449</v>
+        <v>721.440438190701</v>
       </c>
       <c r="D474" t="n">
-        <v>705.3674259579516</v>
+        <v>705.3674866316139</v>
       </c>
       <c r="E474" t="n">
-        <v>712.9615580384484</v>
+        <v>712.961619365336</v>
       </c>
       <c r="F474" t="n">
         <v>330638</v>
@@ -9912,16 +9912,16 @@
         <v>43650</v>
       </c>
       <c r="B475" t="n">
-        <v>708.0953369140625</v>
+        <v>708.0953979492188</v>
       </c>
       <c r="C475" t="n">
-        <v>725.4954311363819</v>
+        <v>725.4954936713608</v>
       </c>
       <c r="D475" t="n">
-        <v>708.0953369140625</v>
+        <v>708.0953979492188</v>
       </c>
       <c r="E475" t="n">
-        <v>718.1225009030987</v>
+        <v>718.1225628025588</v>
       </c>
       <c r="F475" t="n">
         <v>244483</v>
@@ -9932,16 +9932,16 @@
         <v>43651</v>
       </c>
       <c r="B476" t="n">
-        <v>713.1826782226562</v>
+        <v>713.1826171875</v>
       </c>
       <c r="C476" t="n">
-        <v>716.2055998890098</v>
+        <v>716.2055385951478</v>
       </c>
       <c r="D476" t="n">
-        <v>699.2479055299024</v>
+        <v>699.2478456873032</v>
       </c>
       <c r="E476" t="n">
-        <v>709.6436995113913</v>
+        <v>709.6436387791057</v>
       </c>
       <c r="F476" t="n">
         <v>198236</v>
@@ -9952,16 +9952,16 @@
         <v>43654</v>
       </c>
       <c r="B477" t="n">
-        <v>700.4275512695312</v>
+        <v>700.427490234375</v>
       </c>
       <c r="C477" t="n">
-        <v>718.4174767422902</v>
+        <v>718.4174141394944</v>
       </c>
       <c r="D477" t="n">
-        <v>689.3681549809131</v>
+        <v>689.3680949094711</v>
       </c>
       <c r="E477" t="n">
-        <v>715.5420419237837</v>
+        <v>715.5419795715528</v>
       </c>
       <c r="F477" t="n">
         <v>449084</v>
@@ -9992,16 +9992,16 @@
         <v>43657</v>
       </c>
       <c r="B479" t="n">
-        <v>709.0537719726562</v>
+        <v>709.0538330078125</v>
       </c>
       <c r="C479" t="n">
-        <v>740.4624091183467</v>
+        <v>740.4624728571499</v>
       </c>
       <c r="D479" t="n">
-        <v>709.0537719726562</v>
+        <v>709.0538330078125</v>
       </c>
       <c r="E479" t="n">
-        <v>737.2920597875352</v>
+        <v>737.2921232534356</v>
       </c>
       <c r="F479" t="n">
         <v>268402</v>
@@ -10012,16 +10012,16 @@
         <v>43658</v>
       </c>
       <c r="B480" t="n">
-        <v>693.27587890625</v>
+        <v>693.2757568359375</v>
       </c>
       <c r="C480" t="n">
-        <v>719.6709101922801</v>
+        <v>719.6707834743954</v>
       </c>
       <c r="D480" t="n">
-        <v>693.27587890625</v>
+        <v>693.2757568359375</v>
       </c>
       <c r="E480" t="n">
-        <v>713.3302102543602</v>
+        <v>713.3300846529303</v>
       </c>
       <c r="F480" t="n">
         <v>217604</v>
@@ -10052,16 +10052,16 @@
         <v>43662</v>
       </c>
       <c r="B482" t="n">
-        <v>683.6909790039062</v>
+        <v>683.6910400390625</v>
       </c>
       <c r="C482" t="n">
-        <v>700.1326155031132</v>
+        <v>700.132678006064</v>
       </c>
       <c r="D482" t="n">
-        <v>678.3087384634996</v>
+        <v>678.308799018167</v>
       </c>
       <c r="E482" t="n">
-        <v>683.9121798347784</v>
+        <v>683.9122408896819</v>
       </c>
       <c r="F482" t="n">
         <v>150151</v>
@@ -10152,16 +10152,16 @@
         <v>43669</v>
       </c>
       <c r="B487" t="n">
-        <v>702.1971435546875</v>
+        <v>702.1970825195312</v>
       </c>
       <c r="C487" t="n">
-        <v>702.1971435546875</v>
+        <v>702.1970825195312</v>
       </c>
       <c r="D487" t="n">
-        <v>681.3317802038953</v>
+        <v>681.3317209823617</v>
       </c>
       <c r="E487" t="n">
-        <v>686.0504190843093</v>
+        <v>686.0503594526305</v>
       </c>
       <c r="F487" t="n">
         <v>2326127</v>
@@ -10212,16 +10212,16 @@
         <v>43672</v>
       </c>
       <c r="B490" t="n">
-        <v>702.1971435546875</v>
+        <v>702.1970825195312</v>
       </c>
       <c r="C490" t="n">
-        <v>704.1141199446249</v>
+        <v>704.1140587428446</v>
       </c>
       <c r="D490" t="n">
-        <v>696.2987862646315</v>
+        <v>696.298725742162</v>
       </c>
       <c r="E490" t="n">
-        <v>702.6395452944955</v>
+        <v>702.6394842208855</v>
       </c>
       <c r="F490" t="n">
         <v>214891</v>
@@ -10252,16 +10252,16 @@
         <v>43676</v>
       </c>
       <c r="B492" t="n">
-        <v>690.62158203125</v>
+        <v>690.6215209960938</v>
       </c>
       <c r="C492" t="n">
-        <v>701.1648634116639</v>
+        <v>701.1648014447226</v>
       </c>
       <c r="D492" t="n">
-        <v>686.2715724421442</v>
+        <v>686.2715117914294</v>
       </c>
       <c r="E492" t="n">
-        <v>700.4276054824103</v>
+        <v>700.4275435806258</v>
       </c>
       <c r="F492" t="n">
         <v>254421</v>
@@ -10272,16 +10272,16 @@
         <v>43677</v>
       </c>
       <c r="B493" t="n">
-        <v>700.4275512695312</v>
+        <v>700.427490234375</v>
       </c>
       <c r="C493" t="n">
-        <v>700.4275512695312</v>
+        <v>700.427490234375</v>
       </c>
       <c r="D493" t="n">
-        <v>675.3596098244755</v>
+        <v>675.3595509737361</v>
       </c>
       <c r="E493" t="n">
-        <v>692.5385046862017</v>
+        <v>692.5384443384958</v>
       </c>
       <c r="F493" t="n">
         <v>490519</v>
@@ -10292,16 +10292,16 @@
         <v>43678</v>
       </c>
       <c r="B494" t="n">
-        <v>677.055419921875</v>
+        <v>677.0552978515625</v>
       </c>
       <c r="C494" t="n">
-        <v>711.4869841552428</v>
+        <v>711.4868558770606</v>
       </c>
       <c r="D494" t="n">
-        <v>672.1155806418019</v>
+        <v>672.1154594621221</v>
       </c>
       <c r="E494" t="n">
-        <v>707.800518536081</v>
+        <v>707.8003909225533</v>
       </c>
       <c r="F494" t="n">
         <v>781314</v>
@@ -10312,16 +10312,16 @@
         <v>43679</v>
       </c>
       <c r="B495" t="n">
-        <v>674.622314453125</v>
+        <v>674.6222534179688</v>
       </c>
       <c r="C495" t="n">
-        <v>684.1334225572709</v>
+        <v>684.1333606616155</v>
       </c>
       <c r="D495" t="n">
-        <v>657.369705000169</v>
+        <v>657.3696455259094</v>
       </c>
       <c r="E495" t="n">
-        <v>679.7096404270576</v>
+        <v>679.7095789316354</v>
       </c>
       <c r="F495" t="n">
         <v>683082</v>
@@ -10332,16 +10332,16 @@
         <v>43682</v>
       </c>
       <c r="B496" t="n">
-        <v>675.5808715820312</v>
+        <v>675.580810546875</v>
       </c>
       <c r="C496" t="n">
-        <v>678.3825926038681</v>
+        <v>678.3825313155912</v>
       </c>
       <c r="D496" t="n">
-        <v>662.0883822436379</v>
+        <v>662.0883224274567</v>
       </c>
       <c r="E496" t="n">
-        <v>667.9130251447273</v>
+        <v>667.9129648023204</v>
       </c>
       <c r="F496" t="n">
         <v>339376</v>
@@ -10352,16 +10352,16 @@
         <v>43683</v>
       </c>
       <c r="B497" t="n">
-        <v>715.17333984375</v>
+        <v>715.1734008789062</v>
       </c>
       <c r="C497" t="n">
-        <v>717.2378026990284</v>
+        <v>717.2378639103724</v>
       </c>
       <c r="D497" t="n">
-        <v>683.7646996229191</v>
+        <v>683.7647579775626</v>
       </c>
       <c r="E497" t="n">
-        <v>692.3172898562688</v>
+        <v>692.3173489408174</v>
       </c>
       <c r="F497" t="n">
         <v>933500</v>
@@ -10372,16 +10372,16 @@
         <v>43684</v>
       </c>
       <c r="B498" t="n">
-        <v>729.7717895507812</v>
+        <v>729.771728515625</v>
       </c>
       <c r="C498" t="n">
-        <v>736.5548319619454</v>
+        <v>736.5547703594831</v>
       </c>
       <c r="D498" t="n">
-        <v>706.6207654732358</v>
+        <v>706.6207063743375</v>
       </c>
       <c r="E498" t="n">
-        <v>710.0123160235828</v>
+        <v>710.0122566410289</v>
       </c>
       <c r="F498" t="n">
         <v>500391</v>
@@ -10392,16 +10392,16 @@
         <v>43685</v>
       </c>
       <c r="B499" t="n">
-        <v>714.0675048828125</v>
+        <v>714.0674438476562</v>
       </c>
       <c r="C499" t="n">
-        <v>736.9235565291212</v>
+        <v>736.9234935403364</v>
       </c>
       <c r="D499" t="n">
-        <v>705.0725123306354</v>
+        <v>705.0724520643291</v>
       </c>
       <c r="E499" t="n">
-        <v>731.393828750477</v>
+        <v>731.3937662343475</v>
       </c>
       <c r="F499" t="n">
         <v>426052</v>
@@ -10472,16 +10472,16 @@
         <v>43691</v>
       </c>
       <c r="B503" t="n">
-        <v>741.1998291015625</v>
+        <v>741.1998901367188</v>
       </c>
       <c r="C503" t="n">
-        <v>755.355802661426</v>
+        <v>755.355864862276</v>
       </c>
       <c r="D503" t="n">
-        <v>731.0251772542147</v>
+        <v>731.0252374515246</v>
       </c>
       <c r="E503" t="n">
-        <v>734.7116427631291</v>
+        <v>734.7117032640065</v>
       </c>
       <c r="F503" t="n">
         <v>464383</v>
@@ -10512,16 +10512,16 @@
         <v>43693</v>
       </c>
       <c r="B505" t="n">
-        <v>751.1533203125</v>
+        <v>751.1532592773438</v>
       </c>
       <c r="C505" t="n">
-        <v>754.2498975113654</v>
+        <v>754.249836224596</v>
       </c>
       <c r="D505" t="n">
-        <v>732.7947058361743</v>
+        <v>732.794646292752</v>
       </c>
       <c r="E505" t="n">
-        <v>737.2922022143149</v>
+        <v>737.2921423054473</v>
       </c>
       <c r="F505" t="n">
         <v>284065</v>
@@ -10592,16 +10592,16 @@
         <v>43699</v>
       </c>
       <c r="B509" t="n">
-        <v>743.1904907226562</v>
+        <v>743.1905517578125</v>
       </c>
       <c r="C509" t="n">
-        <v>754.5447430163649</v>
+        <v>754.5448049839988</v>
       </c>
       <c r="D509" t="n">
-        <v>735.9649880844896</v>
+        <v>735.9650485262451</v>
       </c>
       <c r="E509" t="n">
-        <v>750.710849553085</v>
+        <v>750.7109112058572</v>
       </c>
       <c r="F509" t="n">
         <v>188833</v>
@@ -10652,16 +10652,16 @@
         <v>43704</v>
       </c>
       <c r="B512" t="n">
-        <v>738.7667846679688</v>
+        <v>738.7667236328125</v>
       </c>
       <c r="C512" t="n">
-        <v>738.7667846679688</v>
+        <v>738.7667236328125</v>
       </c>
       <c r="D512" t="n">
-        <v>710.3810629845611</v>
+        <v>710.3810042945657</v>
       </c>
       <c r="E512" t="n">
-        <v>722.6938339255971</v>
+        <v>722.6937742183497</v>
       </c>
       <c r="F512" t="n">
         <v>286491</v>
@@ -10672,16 +10672,16 @@
         <v>43705</v>
       </c>
       <c r="B513" t="n">
-        <v>733.605712890625</v>
+        <v>733.6056518554688</v>
       </c>
       <c r="C513" t="n">
-        <v>737.2921784781785</v>
+        <v>737.2921171363124</v>
       </c>
       <c r="D513" t="n">
-        <v>724.8319212708758</v>
+        <v>724.831860965689</v>
       </c>
       <c r="E513" t="n">
-        <v>729.9192473030715</v>
+        <v>729.919186574625</v>
       </c>
       <c r="F513" t="n">
         <v>171487</v>
@@ -10692,16 +10692,16 @@
         <v>43706</v>
       </c>
       <c r="B514" t="n">
-        <v>766.7837524414062</v>
+        <v>766.7838134765625</v>
       </c>
       <c r="C514" t="n">
-        <v>771.4287349116321</v>
+        <v>771.4287963165239</v>
       </c>
       <c r="D514" t="n">
-        <v>734.3429413306004</v>
+        <v>734.3429997835032</v>
       </c>
       <c r="E514" t="n">
-        <v>734.3429413306004</v>
+        <v>734.3429997835032</v>
       </c>
       <c r="F514" t="n">
         <v>327430</v>
@@ -10712,16 +10712,16 @@
         <v>43707</v>
       </c>
       <c r="B515" t="n">
-        <v>799.9620361328125</v>
+        <v>799.9619750976562</v>
       </c>
       <c r="C515" t="n">
-        <v>799.9620361328125</v>
+        <v>799.9619750976562</v>
       </c>
       <c r="D515" t="n">
-        <v>762.3601222897596</v>
+        <v>762.3600641235378</v>
       </c>
       <c r="E515" t="n">
-        <v>766.0465878835608</v>
+        <v>766.0465294360706</v>
       </c>
       <c r="F515" t="n">
         <v>691612</v>
@@ -10732,16 +10732,16 @@
         <v>43710</v>
       </c>
       <c r="B516" t="n">
-        <v>771.94482421875</v>
+        <v>771.9448852539062</v>
       </c>
       <c r="C516" t="n">
-        <v>794.7271598141383</v>
+        <v>794.7272226506194</v>
       </c>
       <c r="D516" t="n">
-        <v>771.94482421875</v>
+        <v>771.9448852539062</v>
       </c>
       <c r="E516" t="n">
-        <v>788.90257633355</v>
+        <v>788.9026387095003</v>
       </c>
       <c r="F516" t="n">
         <v>288486</v>
@@ -10792,16 +10792,16 @@
         <v>43713</v>
       </c>
       <c r="B519" t="n">
-        <v>754.5447998046875</v>
+        <v>754.5447387695312</v>
       </c>
       <c r="C519" t="n">
-        <v>772.0186692621071</v>
+        <v>772.0186068134889</v>
       </c>
       <c r="D519" t="n">
-        <v>753.1439980279011</v>
+        <v>753.1439371060559</v>
       </c>
       <c r="E519" t="n">
-        <v>769.1432342758549</v>
+        <v>769.1431720598307</v>
       </c>
       <c r="F519" t="n">
         <v>227216</v>
@@ -10832,16 +10832,16 @@
         <v>43717</v>
       </c>
       <c r="B521" t="n">
-        <v>763.5397338867188</v>
+        <v>763.539794921875</v>
       </c>
       <c r="C521" t="n">
-        <v>774.1567283059956</v>
+        <v>774.1567901898437</v>
       </c>
       <c r="D521" t="n">
-        <v>745.9184376727111</v>
+        <v>745.9184972992718</v>
       </c>
       <c r="E521" t="n">
-        <v>745.9184376727111</v>
+        <v>745.9184972992718</v>
       </c>
       <c r="F521" t="n">
         <v>322904</v>
@@ -10912,16 +10912,16 @@
         <v>43721</v>
       </c>
       <c r="B525" t="n">
-        <v>759.410888671875</v>
+        <v>759.4108276367188</v>
       </c>
       <c r="C525" t="n">
-        <v>779.6864780902634</v>
+        <v>779.6864154255233</v>
       </c>
       <c r="D525" t="n">
-        <v>759.410888671875</v>
+        <v>759.4108276367188</v>
       </c>
       <c r="E525" t="n">
-        <v>779.3177904607991</v>
+        <v>779.3177278256909</v>
       </c>
       <c r="F525" t="n">
         <v>153881</v>
@@ -10932,16 +10932,16 @@
         <v>43724</v>
       </c>
       <c r="B526" t="n">
-        <v>788.9026489257812</v>
+        <v>788.9027099609375</v>
       </c>
       <c r="C526" t="n">
-        <v>788.9026489257812</v>
+        <v>788.9027099609375</v>
       </c>
       <c r="D526" t="n">
-        <v>750.6371907658834</v>
+        <v>750.6372488405499</v>
       </c>
       <c r="E526" t="n">
-        <v>760.1482404209721</v>
+        <v>760.1482992314815</v>
       </c>
       <c r="F526" t="n">
         <v>255829</v>
@@ -10952,16 +10952,16 @@
         <v>43725</v>
       </c>
       <c r="B527" t="n">
-        <v>831.1494140625</v>
+        <v>831.1494750976562</v>
       </c>
       <c r="C527" t="n">
-        <v>832.8451892799262</v>
+        <v>832.8452504396112</v>
       </c>
       <c r="D527" t="n">
-        <v>775.4838641438894</v>
+        <v>775.4839210912661</v>
       </c>
       <c r="E527" t="n">
-        <v>781.5296484753329</v>
+        <v>781.5297058666796</v>
       </c>
       <c r="F527" t="n">
         <v>516981</v>
@@ -10972,16 +10972,16 @@
         <v>43726</v>
       </c>
       <c r="B528" t="n">
-        <v>822.0807495117188</v>
+        <v>822.080810546875</v>
       </c>
       <c r="C528" t="n">
-        <v>831.075741758477</v>
+        <v>831.0758034614639</v>
       </c>
       <c r="D528" t="n">
-        <v>813.3069581065021</v>
+        <v>813.3070184902507</v>
       </c>
       <c r="E528" t="n">
-        <v>822.0807495117188</v>
+        <v>822.080810546875</v>
       </c>
       <c r="F528" t="n">
         <v>309810</v>
@@ -10992,16 +10992,16 @@
         <v>43727</v>
       </c>
       <c r="B529" t="n">
-        <v>826.7994384765625</v>
+        <v>826.7993774414062</v>
       </c>
       <c r="C529" t="n">
-        <v>831.9604783850976</v>
+        <v>831.9604169689483</v>
       </c>
       <c r="D529" t="n">
-        <v>819.1315926637169</v>
+        <v>819.1315321946086</v>
       </c>
       <c r="E529" t="n">
-        <v>822.1544556072568</v>
+        <v>822.1543949149977</v>
       </c>
       <c r="F529" t="n">
         <v>114064</v>
@@ -11012,16 +11012,16 @@
         <v>43728</v>
       </c>
       <c r="B530" t="n">
-        <v>819.9425659179688</v>
+        <v>819.942626953125</v>
       </c>
       <c r="C530" t="n">
-        <v>843.3147306606849</v>
+        <v>843.3147934356261</v>
       </c>
       <c r="D530" t="n">
-        <v>818.7628477535394</v>
+        <v>818.7629087008795</v>
       </c>
       <c r="E530" t="n">
-        <v>833.1400796553557</v>
+        <v>833.1401416729129</v>
       </c>
       <c r="F530" t="n">
         <v>328551</v>
@@ -11032,16 +11032,16 @@
         <v>43731</v>
       </c>
       <c r="B531" t="n">
-        <v>824.8825073242188</v>
+        <v>824.8824462890625</v>
       </c>
       <c r="C531" t="n">
-        <v>828.8638878923888</v>
+        <v>828.86382656264</v>
       </c>
       <c r="D531" t="n">
-        <v>816.3299163770042</v>
+        <v>816.3298559746759</v>
       </c>
       <c r="E531" t="n">
-        <v>824.2926775133442</v>
+        <v>824.292616521831</v>
       </c>
       <c r="F531" t="n">
         <v>128162</v>
@@ -11052,16 +11052,16 @@
         <v>43732</v>
       </c>
       <c r="B532" t="n">
-        <v>813.9705200195312</v>
+        <v>813.9705810546875</v>
       </c>
       <c r="C532" t="n">
-        <v>830.5595845854463</v>
+        <v>830.559646864525</v>
       </c>
       <c r="D532" t="n">
-        <v>808.8831943655513</v>
+        <v>808.8832550192371</v>
       </c>
       <c r="E532" t="n">
-        <v>828.7900953204605</v>
+        <v>828.790157466855</v>
       </c>
       <c r="F532" t="n">
         <v>236567</v>
@@ -11092,16 +11092,16 @@
         <v>43734</v>
       </c>
       <c r="B534" t="n">
-        <v>818.836669921875</v>
+        <v>818.8366088867188</v>
       </c>
       <c r="C534" t="n">
-        <v>827.020572695468</v>
+        <v>827.0205110502928</v>
       </c>
       <c r="D534" t="n">
-        <v>804.01709416706</v>
+        <v>804.0170342365382</v>
       </c>
       <c r="E534" t="n">
-        <v>826.1358280358776</v>
+        <v>826.1357664566505</v>
       </c>
       <c r="F534" t="n">
         <v>152164</v>
@@ -11112,16 +11112,16 @@
         <v>43735</v>
       </c>
       <c r="B535" t="n">
-        <v>829.0112915039062</v>
+        <v>829.01123046875</v>
       </c>
       <c r="C535" t="n">
-        <v>829.0112915039062</v>
+        <v>829.01123046875</v>
       </c>
       <c r="D535" t="n">
-        <v>811.0951381660786</v>
+        <v>811.0950784499818</v>
       </c>
       <c r="E535" t="n">
-        <v>818.173095687427</v>
+        <v>818.1730354502224</v>
       </c>
       <c r="F535" t="n">
         <v>111112</v>
@@ -11152,16 +11152,16 @@
         <v>43739</v>
       </c>
       <c r="B537" t="n">
-        <v>823.9239501953125</v>
+        <v>823.9240112304688</v>
       </c>
       <c r="C537" t="n">
-        <v>840.5130143524692</v>
+        <v>840.5130766165206</v>
       </c>
       <c r="D537" t="n">
-        <v>818.8366246666855</v>
+        <v>818.8366853249796</v>
       </c>
       <c r="E537" t="n">
-        <v>840.5130143524692</v>
+        <v>840.5130766165206</v>
       </c>
       <c r="F537" t="n">
         <v>140869</v>
@@ -11192,16 +11192,16 @@
         <v>43741</v>
       </c>
       <c r="B539" t="n">
-        <v>787.4281005859375</v>
+        <v>787.4280395507812</v>
       </c>
       <c r="C539" t="n">
-        <v>812.2010706827356</v>
+        <v>812.201007727376</v>
       </c>
       <c r="D539" t="n">
-        <v>782.7831173394447</v>
+        <v>782.7830566643306</v>
       </c>
       <c r="E539" t="n">
-        <v>812.2010706827356</v>
+        <v>812.201007727376</v>
       </c>
       <c r="F539" t="n">
         <v>247000</v>
@@ -11292,16 +11292,16 @@
         <v>43748</v>
       </c>
       <c r="B544" t="n">
-        <v>792.5153198242188</v>
+        <v>792.5152587890625</v>
       </c>
       <c r="C544" t="n">
-        <v>808.8832432381029</v>
+        <v>808.8831809423796</v>
       </c>
       <c r="D544" t="n">
-        <v>783.8890151190678</v>
+        <v>783.8889547482621</v>
       </c>
       <c r="E544" t="n">
-        <v>798.9297921592629</v>
+        <v>798.9297306300995</v>
       </c>
       <c r="F544" t="n">
         <v>229776</v>
@@ -11312,16 +11312,16 @@
         <v>43749</v>
       </c>
       <c r="B545" t="n">
-        <v>804.2382202148438</v>
+        <v>804.23828125</v>
       </c>
       <c r="C545" t="n">
-        <v>813.9704692548243</v>
+        <v>813.9705310285792</v>
       </c>
       <c r="D545" t="n">
-        <v>792.7364233307106</v>
+        <v>792.7364834929738</v>
       </c>
       <c r="E545" t="n">
-        <v>800.9203840327723</v>
+        <v>800.9204448161316</v>
       </c>
       <c r="F545" t="n">
         <v>153190</v>
@@ -11352,16 +11352,16 @@
         <v>43753</v>
       </c>
       <c r="B547" t="n">
-        <v>817.9519653320312</v>
+        <v>817.951904296875</v>
       </c>
       <c r="C547" t="n">
-        <v>824.3663791006722</v>
+        <v>824.3663175868757</v>
       </c>
       <c r="D547" t="n">
-        <v>804.0171335541686</v>
+        <v>804.0170735588223</v>
       </c>
       <c r="E547" t="n">
-        <v>807.556112365897</v>
+        <v>807.5560521064739</v>
       </c>
       <c r="F547" t="n">
         <v>148942</v>
@@ -11372,16 +11372,16 @@
         <v>43754</v>
       </c>
       <c r="B548" t="n">
-        <v>813.9705200195312</v>
+        <v>813.9705810546875</v>
       </c>
       <c r="C548" t="n">
-        <v>817.951900210513</v>
+        <v>817.951961544211</v>
       </c>
       <c r="D548" t="n">
-        <v>806.4501026090501</v>
+        <v>806.4501630802918</v>
       </c>
       <c r="E548" t="n">
-        <v>816.1823522559995</v>
+        <v>816.1824134570088</v>
       </c>
       <c r="F548" t="n">
         <v>165832</v>
@@ -11452,16 +11452,16 @@
         <v>43760</v>
       </c>
       <c r="B552" t="n">
-        <v>867.0555419921875</v>
+        <v>867.0556030273438</v>
       </c>
       <c r="C552" t="n">
-        <v>867.0555419921875</v>
+        <v>867.0556030273438</v>
       </c>
       <c r="D552" t="n">
-        <v>846.0426957709227</v>
+        <v>846.0427553269092</v>
       </c>
       <c r="E552" t="n">
-        <v>854.0054560783693</v>
+        <v>854.0055161948831</v>
       </c>
       <c r="F552" t="n">
         <v>268545</v>
@@ -11472,16 +11472,16 @@
         <v>43761</v>
       </c>
       <c r="B553" t="n">
-        <v>865.9495849609375</v>
+        <v>865.9496459960938</v>
       </c>
       <c r="C553" t="n">
-        <v>866.6131287478433</v>
+        <v>866.6131898297684</v>
       </c>
       <c r="D553" t="n">
-        <v>846.485086109451</v>
+        <v>846.4851457726812</v>
       </c>
       <c r="E553" t="n">
-        <v>864.4012378721218</v>
+        <v>864.401298798145</v>
       </c>
       <c r="F553" t="n">
         <v>247404</v>
@@ -11492,16 +11492,16 @@
         <v>43762</v>
       </c>
       <c r="B554" t="n">
-        <v>860.4197998046875</v>
+        <v>860.419921875</v>
       </c>
       <c r="C554" t="n">
-        <v>875.2393737703771</v>
+        <v>875.2394979431867</v>
       </c>
       <c r="D554" t="n">
-        <v>855.7748762302243</v>
+        <v>855.7749976415478</v>
       </c>
       <c r="E554" t="n">
-        <v>863.7376358947455</v>
+        <v>863.7377584357694</v>
       </c>
       <c r="F554" t="n">
         <v>162584</v>
@@ -11512,16 +11512,16 @@
         <v>43763</v>
       </c>
       <c r="B555" t="n">
-        <v>855.9961547851562</v>
+        <v>855.9962158203125</v>
       </c>
       <c r="C555" t="n">
-        <v>871.2580730686105</v>
+        <v>871.2581351919885</v>
       </c>
       <c r="D555" t="n">
-        <v>852.4571762526242</v>
+        <v>852.4572370354404</v>
       </c>
       <c r="E555" t="n">
-        <v>865.9496052698125</v>
+        <v>865.9496670146802</v>
       </c>
       <c r="F555" t="n">
         <v>281561</v>
@@ -11532,16 +11532,16 @@
         <v>43766</v>
       </c>
       <c r="B556" t="n">
-        <v>854.6690063476562</v>
+        <v>854.6690673828125</v>
       </c>
       <c r="C556" t="n">
-        <v>862.1894237447216</v>
+        <v>862.1894853169393</v>
       </c>
       <c r="D556" t="n">
-        <v>834.9833062583699</v>
+        <v>834.9833658876955</v>
       </c>
       <c r="E556" t="n">
-        <v>860.1987336527819</v>
+        <v>860.1987950828369</v>
       </c>
       <c r="F556" t="n">
         <v>116033</v>
@@ -11552,16 +11552,16 @@
         <v>43767</v>
       </c>
       <c r="B557" t="n">
-        <v>836.0892333984375</v>
+        <v>836.0892944335938</v>
       </c>
       <c r="C557" t="n">
-        <v>858.8715685414666</v>
+        <v>858.8716312397509</v>
       </c>
       <c r="D557" t="n">
-        <v>831.0019078650099</v>
+        <v>831.0019685287875</v>
       </c>
       <c r="E557" t="n">
-        <v>852.4571554355111</v>
+        <v>852.4572176655382</v>
       </c>
       <c r="F557" t="n">
         <v>184529</v>
@@ -11572,16 +11572,16 @@
         <v>43768</v>
       </c>
       <c r="B558" t="n">
-        <v>826.1358642578125</v>
+        <v>826.1358032226562</v>
       </c>
       <c r="C558" t="n">
-        <v>842.7249300591559</v>
+        <v>842.7248677983947</v>
       </c>
       <c r="D558" t="n">
-        <v>815.0765261832718</v>
+        <v>815.0764659651826</v>
       </c>
       <c r="E558" t="n">
-        <v>833.8774243858039</v>
+        <v>833.877362778699</v>
       </c>
       <c r="F558" t="n">
         <v>414767</v>
@@ -11632,16 +11632,16 @@
         <v>43773</v>
       </c>
       <c r="B561" t="n">
-        <v>854.6690063476562</v>
+        <v>854.6690673828125</v>
       </c>
       <c r="C561" t="n">
-        <v>861.7470220845005</v>
+        <v>861.7470836251247</v>
       </c>
       <c r="D561" t="n">
-        <v>842.9460666261286</v>
+        <v>842.9461268241052</v>
       </c>
       <c r="E561" t="n">
-        <v>855.996152638792</v>
+        <v>855.9962137687247</v>
       </c>
       <c r="F561" t="n">
         <v>124324</v>
@@ -11652,16 +11652,16 @@
         <v>43774</v>
       </c>
       <c r="B562" t="n">
-        <v>855.9961547851562</v>
+        <v>855.9962158203125</v>
       </c>
       <c r="C562" t="n">
-        <v>869.4885838023446</v>
+        <v>869.4886457995524</v>
       </c>
       <c r="D562" t="n">
-        <v>848.2545952280965</v>
+        <v>848.2546557112557</v>
       </c>
       <c r="E562" t="n">
-        <v>858.2080457127528</v>
+        <v>858.2081069056236</v>
       </c>
       <c r="F562" t="n">
         <v>167131</v>
@@ -11812,16 +11812,16 @@
         <v>43787</v>
       </c>
       <c r="B570" t="n">
-        <v>805.7865600585938</v>
+        <v>805.78662109375</v>
       </c>
       <c r="C570" t="n">
-        <v>832.7714768048862</v>
+        <v>832.7715398840436</v>
       </c>
       <c r="D570" t="n">
-        <v>805.565359227745</v>
+        <v>805.5654202461462</v>
       </c>
       <c r="E570" t="n">
-        <v>829.6748412415876</v>
+        <v>829.6749040861871</v>
       </c>
       <c r="F570" t="n">
         <v>210918</v>
@@ -11872,16 +11872,16 @@
         <v>43791</v>
       </c>
       <c r="B573" t="n">
-        <v>837.2259521484375</v>
+        <v>837.2260131835938</v>
       </c>
       <c r="C573" t="n">
-        <v>839.0058519275486</v>
+        <v>839.0059130924625</v>
       </c>
       <c r="D573" t="n">
-        <v>820.316786177245</v>
+        <v>820.3168459796951</v>
       </c>
       <c r="E573" t="n">
-        <v>835.0010479071394</v>
+        <v>835.0011087800964</v>
       </c>
       <c r="F573" t="n">
         <v>175470</v>
@@ -11932,16 +11932,16 @@
         <v>43796</v>
       </c>
       <c r="B576" t="n">
-        <v>823.6542358398438</v>
+        <v>823.6541748046875</v>
       </c>
       <c r="C576" t="n">
-        <v>825.2116335642778</v>
+        <v>825.211572413714</v>
       </c>
       <c r="D576" t="n">
-        <v>800.9603634984489</v>
+        <v>800.9603041449742</v>
       </c>
       <c r="E576" t="n">
-        <v>817.6470291287546</v>
+        <v>817.6469685387498</v>
       </c>
       <c r="F576" t="n">
         <v>228902</v>
@@ -11972,16 +11972,16 @@
         <v>43798</v>
       </c>
       <c r="B578" t="n">
-        <v>826.1015014648438</v>
+        <v>826.1015625</v>
       </c>
       <c r="C578" t="n">
-        <v>845.4580741776076</v>
+        <v>845.4581366428926</v>
       </c>
       <c r="D578" t="n">
-        <v>817.4244456448969</v>
+        <v>817.424506038963</v>
       </c>
       <c r="E578" t="n">
-        <v>837.2259637912168</v>
+        <v>837.2260256482857</v>
       </c>
       <c r="F578" t="n">
         <v>210857</v>
@@ -11992,16 +11992,16 @@
         <v>43801</v>
       </c>
       <c r="B579" t="n">
-        <v>827.6589965820312</v>
+        <v>827.658935546875</v>
       </c>
       <c r="C579" t="n">
-        <v>838.3384549369663</v>
+        <v>838.3383931142606</v>
       </c>
       <c r="D579" t="n">
-        <v>823.6541923195779</v>
+        <v>823.6541315797532</v>
       </c>
       <c r="E579" t="n">
-        <v>828.3264442808328</v>
+        <v>828.326383196456</v>
       </c>
       <c r="F579" t="n">
         <v>162406</v>
@@ -12012,16 +12012,16 @@
         <v>43802</v>
       </c>
       <c r="B580" t="n">
-        <v>828.1038818359375</v>
+        <v>828.1039428710938</v>
       </c>
       <c r="C580" t="n">
-        <v>835.4460421282926</v>
+        <v>835.4461037046005</v>
       </c>
       <c r="D580" t="n">
-        <v>820.9842237719485</v>
+        <v>820.9842842823524</v>
       </c>
       <c r="E580" t="n">
-        <v>828.9938317145838</v>
+        <v>828.9938928153337</v>
       </c>
       <c r="F580" t="n">
         <v>140261</v>
@@ -12032,16 +12032,16 @@
         <v>43803</v>
       </c>
       <c r="B581" t="n">
-        <v>820.9842529296875</v>
+        <v>820.9843139648438</v>
       </c>
       <c r="C581" t="n">
-        <v>831.6637699223692</v>
+        <v>831.6638317514822</v>
       </c>
       <c r="D581" t="n">
-        <v>815.4220512318982</v>
+        <v>815.4221118535388</v>
       </c>
       <c r="E581" t="n">
-        <v>831.6637699223692</v>
+        <v>831.6638317514822</v>
       </c>
       <c r="F581" t="n">
         <v>148560</v>
@@ -12052,16 +12052,16 @@
         <v>43804</v>
       </c>
       <c r="B582" t="n">
-        <v>827.6589965820312</v>
+        <v>827.658935546875</v>
       </c>
       <c r="C582" t="n">
-        <v>827.8814397917504</v>
+        <v>827.8813787401903</v>
       </c>
       <c r="D582" t="n">
-        <v>808.9699297021895</v>
+        <v>808.9698700452459</v>
       </c>
       <c r="E582" t="n">
-        <v>818.7594381137817</v>
+        <v>818.7593777349174</v>
       </c>
       <c r="F582" t="n">
         <v>164740</v>
@@ -12072,16 +12072,16 @@
         <v>43805</v>
       </c>
       <c r="B583" t="n">
-        <v>824.7666015625</v>
+        <v>824.7666625976562</v>
       </c>
       <c r="C583" t="n">
-        <v>833.221155101445</v>
+        <v>833.2212167622632</v>
       </c>
       <c r="D583" t="n">
-        <v>820.9842407067104</v>
+        <v>820.9843014619607</v>
       </c>
       <c r="E583" t="n">
-        <v>823.2091449666292</v>
+        <v>823.209205886529</v>
       </c>
       <c r="F583" t="n">
         <v>143460</v>
@@ -12112,16 +12112,16 @@
         <v>43809</v>
       </c>
       <c r="B585" t="n">
-        <v>819.8718872070312</v>
+        <v>819.8719482421875</v>
       </c>
       <c r="C585" t="n">
-        <v>825.6565913343355</v>
+        <v>825.6566528001326</v>
       </c>
       <c r="D585" t="n">
-        <v>812.3072241649378</v>
+        <v>812.3072846369446</v>
       </c>
       <c r="E585" t="n">
-        <v>816.5345306559764</v>
+        <v>816.5345914426839</v>
       </c>
       <c r="F585" t="n">
         <v>105717</v>
@@ -12152,16 +12152,16 @@
         <v>43811</v>
       </c>
       <c r="B587" t="n">
-        <v>835.2235717773438</v>
+        <v>835.2236328125</v>
       </c>
       <c r="C587" t="n">
-        <v>836.5585261636726</v>
+        <v>836.5585872963826</v>
       </c>
       <c r="D587" t="n">
-        <v>819.4268575175364</v>
+        <v>819.4269173983253</v>
       </c>
       <c r="E587" t="n">
-        <v>820.7618119038652</v>
+        <v>820.7618718822077</v>
       </c>
       <c r="F587" t="n">
         <v>149190</v>
@@ -12212,16 +12212,16 @@
         <v>43816</v>
       </c>
       <c r="B590" t="n">
-        <v>828.1038818359375</v>
+        <v>828.1039428710938</v>
       </c>
       <c r="C590" t="n">
-        <v>829.8837815932303</v>
+        <v>829.8838427595736</v>
       </c>
       <c r="D590" t="n">
-        <v>819.2043240146558</v>
+        <v>819.2043843938726</v>
       </c>
       <c r="E590" t="n">
-        <v>819.6493284713878</v>
+        <v>819.6493888834036</v>
       </c>
       <c r="F590" t="n">
         <v>131975</v>
@@ -12232,16 +12232,16 @@
         <v>43817</v>
       </c>
       <c r="B591" t="n">
-        <v>850.13037109375</v>
+        <v>850.1303100585938</v>
       </c>
       <c r="C591" t="n">
-        <v>850.13037109375</v>
+        <v>850.1303100585938</v>
       </c>
       <c r="D591" t="n">
-        <v>822.0967410714518</v>
+        <v>822.0966820489716</v>
       </c>
       <c r="E591" t="n">
-        <v>827.6590020476028</v>
+        <v>827.6589426257798</v>
       </c>
       <c r="F591" t="n">
         <v>317726</v>
@@ -12252,16 +12252,16 @@
         <v>43818</v>
       </c>
       <c r="B592" t="n">
-        <v>851.020263671875</v>
+        <v>851.0203247070312</v>
       </c>
       <c r="C592" t="n">
-        <v>855.4700721528143</v>
+        <v>855.4701335071107</v>
       </c>
       <c r="D592" t="n">
-        <v>831.6637502703173</v>
+        <v>831.6638099172249</v>
       </c>
       <c r="E592" t="n">
-        <v>851.2427659028857</v>
+        <v>851.2428269539998</v>
       </c>
       <c r="F592" t="n">
         <v>220621</v>
@@ -12472,16 +12472,16 @@
         <v>43839</v>
       </c>
       <c r="B603" t="n">
-        <v>915.5421142578125</v>
+        <v>915.5421752929688</v>
       </c>
       <c r="C603" t="n">
-        <v>921.1043160723813</v>
+        <v>921.1043774783449</v>
       </c>
       <c r="D603" t="n">
-        <v>877.9414788621859</v>
+        <v>877.9415373906736</v>
       </c>
       <c r="E603" t="n">
-        <v>880.1663832019419</v>
+        <v>880.1664418787541</v>
       </c>
       <c r="F603" t="n">
         <v>555906</v>
@@ -12512,16 +12512,16 @@
         <v>43843</v>
       </c>
       <c r="B605" t="n">
-        <v>923.7742309570312</v>
+        <v>923.7742919921875</v>
       </c>
       <c r="C605" t="n">
-        <v>944.2431975265949</v>
+        <v>944.2432599141667</v>
       </c>
       <c r="D605" t="n">
-        <v>914.2071658472175</v>
+        <v>914.2072262502634</v>
       </c>
       <c r="E605" t="n">
-        <v>921.1043221178721</v>
+        <v>921.1043829766236</v>
       </c>
       <c r="F605" t="n">
         <v>375341</v>
@@ -12532,16 +12532,16 @@
         <v>43844</v>
       </c>
       <c r="B606" t="n">
-        <v>917.5444946289062</v>
+        <v>917.5445556640625</v>
       </c>
       <c r="C606" t="n">
-        <v>929.5589069372982</v>
+        <v>929.5589687716543</v>
       </c>
       <c r="D606" t="n">
-        <v>911.0922840033685</v>
+        <v>911.0923446093229</v>
       </c>
       <c r="E606" t="n">
-        <v>919.991842116827</v>
+        <v>919.991903314781</v>
       </c>
       <c r="F606" t="n">
         <v>179395</v>
@@ -12572,16 +12572,16 @@
         <v>43846</v>
       </c>
       <c r="B608" t="n">
-        <v>930.0039672851562</v>
+        <v>930.00390625</v>
       </c>
       <c r="C608" t="n">
-        <v>950.027990273312</v>
+        <v>950.0279279240008</v>
       </c>
       <c r="D608" t="n">
-        <v>917.7671102639265</v>
+        <v>917.767050031862</v>
       </c>
       <c r="E608" t="n">
-        <v>950.027990273312</v>
+        <v>950.0279279240008</v>
       </c>
       <c r="F608" t="n">
         <v>135840</v>
@@ -12592,16 +12592,16 @@
         <v>43847</v>
       </c>
       <c r="B609" t="n">
-        <v>961.3748168945312</v>
+        <v>961.3748779296875</v>
       </c>
       <c r="C609" t="n">
-        <v>961.3748168945312</v>
+        <v>961.3748779296875</v>
       </c>
       <c r="D609" t="n">
-        <v>927.7789872130055</v>
+        <v>927.779046115251</v>
       </c>
       <c r="E609" t="n">
-        <v>927.7789872130055</v>
+        <v>927.779046115251</v>
       </c>
       <c r="F609" t="n">
         <v>135692</v>
@@ -12632,16 +12632,16 @@
         <v>43851</v>
       </c>
       <c r="B611" t="n">
-        <v>956.925048828125</v>
+        <v>956.9251098632812</v>
       </c>
       <c r="C611" t="n">
-        <v>974.724165424784</v>
+        <v>974.7242275952141</v>
       </c>
       <c r="D611" t="n">
-        <v>956.702546587832</v>
+        <v>956.7026076087966</v>
       </c>
       <c r="E611" t="n">
-        <v>967.8270092194491</v>
+        <v>967.8270709499607</v>
       </c>
       <c r="F611" t="n">
         <v>145221</v>
@@ -12692,16 +12692,16 @@
         <v>43854</v>
       </c>
       <c r="B614" t="n">
-        <v>952.69775390625</v>
+        <v>952.6976928710938</v>
       </c>
       <c r="C614" t="n">
-        <v>982.7337856638734</v>
+        <v>982.7337227044407</v>
       </c>
       <c r="D614" t="n">
-        <v>952.69775390625</v>
+        <v>952.6976928710938</v>
       </c>
       <c r="E614" t="n">
-        <v>975.8366293752512</v>
+        <v>975.8365668576889</v>
       </c>
       <c r="F614" t="n">
         <v>152264</v>
@@ -12752,16 +12752,16 @@
         <v>43859</v>
       </c>
       <c r="B617" t="n">
-        <v>978.9515380859375</v>
+        <v>978.9514770507812</v>
       </c>
       <c r="C617" t="n">
-        <v>996.3057104109973</v>
+        <v>996.3056482938523</v>
       </c>
       <c r="D617" t="n">
-        <v>972.054381413948</v>
+        <v>972.0543208088121</v>
       </c>
       <c r="E617" t="n">
-        <v>991.8559014433525</v>
+        <v>991.8558396036418</v>
       </c>
       <c r="F617" t="n">
         <v>129214</v>
@@ -12772,16 +12772,16 @@
         <v>43860</v>
       </c>
       <c r="B618" t="n">
-        <v>982.7337646484375</v>
+        <v>982.7337036132812</v>
       </c>
       <c r="C618" t="n">
-        <v>993.4132817348734</v>
+        <v>993.4132200364389</v>
       </c>
       <c r="D618" t="n">
-        <v>961.8197939868294</v>
+        <v>961.819734250588</v>
       </c>
       <c r="E618" t="n">
-        <v>977.6165083434412</v>
+        <v>977.616447626105</v>
       </c>
       <c r="F618" t="n">
         <v>201453</v>
@@ -12852,16 +12852,16 @@
         <v>43866</v>
       </c>
       <c r="B622" t="n">
-        <v>945.578125</v>
+        <v>945.5781860351562</v>
       </c>
       <c r="C622" t="n">
-        <v>950.0278745470912</v>
+        <v>950.0279358694697</v>
       </c>
       <c r="D622" t="n">
-        <v>909.9798924839915</v>
+        <v>909.9799512213539</v>
       </c>
       <c r="E622" t="n">
-        <v>924.6641545416221</v>
+        <v>924.6642142268238</v>
       </c>
       <c r="F622" t="n">
         <v>652008</v>
@@ -12932,16 +12932,16 @@
         <v>43872</v>
       </c>
       <c r="B626" t="n">
-        <v>770.92431640625</v>
+        <v>770.9243774414062</v>
       </c>
       <c r="C626" t="n">
-        <v>778.4889207089454</v>
+        <v>778.4889823430019</v>
       </c>
       <c r="D626" t="n">
-        <v>716.4145114858223</v>
+        <v>716.4145682053611</v>
       </c>
       <c r="E626" t="n">
-        <v>758.6874009426435</v>
+        <v>758.6874610089861</v>
       </c>
       <c r="F626" t="n">
         <v>856496</v>
@@ -12952,16 +12952,16 @@
         <v>43873</v>
       </c>
       <c r="B627" t="n">
-        <v>749.7877807617188</v>
+        <v>749.7877197265625</v>
       </c>
       <c r="C627" t="n">
-        <v>783.1611677382641</v>
+        <v>783.161103986406</v>
       </c>
       <c r="D627" t="n">
-        <v>747.7853787238224</v>
+        <v>747.7853178516682</v>
       </c>
       <c r="E627" t="n">
-        <v>781.1587657003678</v>
+        <v>781.1587021115117</v>
       </c>
       <c r="F627" t="n">
         <v>527262</v>
@@ -12992,16 +12992,16 @@
         <v>43875</v>
       </c>
       <c r="B629" t="n">
-        <v>770.92431640625</v>
+        <v>770.9243774414062</v>
       </c>
       <c r="C629" t="n">
-        <v>776.2640752895095</v>
+        <v>776.2641367474218</v>
       </c>
       <c r="D629" t="n">
-        <v>731.3212768736464</v>
+        <v>731.3213347733746</v>
       </c>
       <c r="E629" t="n">
-        <v>734.2136290502549</v>
+        <v>734.2136871789746</v>
       </c>
       <c r="F629" t="n">
         <v>682665</v>
@@ -13032,16 +13032,16 @@
         <v>43879</v>
       </c>
       <c r="B631" t="n">
-        <v>807.6349487304688</v>
+        <v>807.635009765625</v>
       </c>
       <c r="C631" t="n">
-        <v>838.5609296259686</v>
+        <v>838.5609929982849</v>
       </c>
       <c r="D631" t="n">
-        <v>778.7113699003957</v>
+        <v>778.7114287497189</v>
       </c>
       <c r="E631" t="n">
-        <v>805.1875421905826</v>
+        <v>805.1876030407818</v>
       </c>
       <c r="F631" t="n">
         <v>685347</v>
@@ -13052,16 +13052,16 @@
         <v>43880</v>
       </c>
       <c r="B632" t="n">
-        <v>815.8670654296875</v>
+        <v>815.8671264648438</v>
       </c>
       <c r="C632" t="n">
-        <v>867.7069582526968</v>
+        <v>867.7070231660045</v>
       </c>
       <c r="D632" t="n">
-        <v>807.8574571071105</v>
+        <v>807.8575175430666</v>
       </c>
       <c r="E632" t="n">
-        <v>862.1447564886054</v>
+        <v>862.1448209858037</v>
       </c>
       <c r="F632" t="n">
         <v>1460101</v>
@@ -13192,16 +13192,16 @@
         <v>43893</v>
       </c>
       <c r="B639" t="n">
-        <v>622.9691162109375</v>
+        <v>622.9691772460938</v>
       </c>
       <c r="C639" t="n">
-        <v>705.0675398646607</v>
+        <v>705.0676089433781</v>
       </c>
       <c r="D639" t="n">
-        <v>622.9691162109375</v>
+        <v>622.9691772460938</v>
       </c>
       <c r="E639" t="n">
-        <v>686.3784150180403</v>
+        <v>686.3784822656979</v>
       </c>
       <c r="F639" t="n">
         <v>1233255</v>
@@ -13212,16 +13212,16 @@
         <v>43894</v>
       </c>
       <c r="B640" t="n">
-        <v>423.8414611816406</v>
+        <v>423.8414916992188</v>
       </c>
       <c r="C640" t="n">
-        <v>489.4757241972176</v>
+        <v>489.4757594406165</v>
       </c>
       <c r="D640" t="n">
-        <v>362.8795089609787</v>
+        <v>362.8795350891534</v>
       </c>
       <c r="E640" t="n">
-        <v>469.4517037470661</v>
+        <v>469.4517375486885</v>
       </c>
       <c r="F640" t="n">
         <v>6553269</v>
@@ -13272,16 +13272,16 @@
         <v>43899</v>
       </c>
       <c r="B643" t="n">
-        <v>306.1448364257812</v>
+        <v>306.1448059082031</v>
       </c>
       <c r="C643" t="n">
-        <v>347.0828315630422</v>
+        <v>347.0827969646228</v>
       </c>
       <c r="D643" t="n">
-        <v>302.8075091700803</v>
+        <v>302.8074789851785</v>
       </c>
       <c r="E643" t="n">
-        <v>333.7334930228257</v>
+        <v>333.7334597551147</v>
       </c>
       <c r="F643" t="n">
         <v>800099</v>
@@ -13292,16 +13292,16 @@
         <v>43900</v>
       </c>
       <c r="B644" t="n">
-        <v>304.8098754882812</v>
+        <v>304.8099060058594</v>
       </c>
       <c r="C644" t="n">
-        <v>342.1880071868422</v>
+        <v>342.1880414467205</v>
       </c>
       <c r="D644" t="n">
-        <v>289.9031114483475</v>
+        <v>289.9031404734598</v>
       </c>
       <c r="E644" t="n">
-        <v>337.0707805360925</v>
+        <v>337.0708142836338</v>
       </c>
       <c r="F644" t="n">
         <v>1215566</v>
@@ -13312,16 +13312,16 @@
         <v>43901</v>
       </c>
       <c r="B645" t="n">
-        <v>282.5610046386719</v>
+        <v>282.5609741210938</v>
       </c>
       <c r="C645" t="n">
-        <v>321.4965667309677</v>
+        <v>321.4965320082126</v>
       </c>
       <c r="D645" t="n">
-        <v>270.5465914893395</v>
+        <v>270.5465622693601</v>
       </c>
       <c r="E645" t="n">
-        <v>300.3601221114257</v>
+        <v>300.3600896714805</v>
       </c>
       <c r="F645" t="n">
         <v>1075370</v>
@@ -13352,16 +13352,16 @@
         <v>43903</v>
       </c>
       <c r="B647" t="n">
-        <v>222.4889831542969</v>
+        <v>222.4889678955078</v>
       </c>
       <c r="C647" t="n">
-        <v>244.737879993856</v>
+        <v>244.7378632091881</v>
       </c>
       <c r="D647" t="n">
-        <v>200.4625738072628</v>
+        <v>200.4625600590938</v>
       </c>
       <c r="E647" t="n">
-        <v>244.737879993856</v>
+        <v>244.7378632091881</v>
       </c>
       <c r="F647" t="n">
         <v>1357909</v>
@@ -13412,16 +13412,16 @@
         <v>43908</v>
       </c>
       <c r="B650" t="n">
-        <v>160.1920623779297</v>
+        <v>160.1920776367188</v>
       </c>
       <c r="C650" t="n">
-        <v>185.3333098683354</v>
+        <v>185.333327521906</v>
       </c>
       <c r="D650" t="n">
-        <v>150.1800520223756</v>
+        <v>150.1800663274898</v>
       </c>
       <c r="E650" t="n">
-        <v>185.1108223891792</v>
+        <v>185.1108400215572</v>
       </c>
       <c r="F650" t="n">
         <v>1085342</v>
@@ -13432,16 +13432,16 @@
         <v>43909</v>
       </c>
       <c r="B651" t="n">
-        <v>168.8691253662109</v>
+        <v>168.8691101074219</v>
       </c>
       <c r="C651" t="n">
-        <v>176.6562464954477</v>
+        <v>176.6562305330248</v>
       </c>
       <c r="D651" t="n">
-        <v>143.0604143646761</v>
+        <v>143.0604014379278</v>
       </c>
       <c r="E651" t="n">
-        <v>153.5173853548549</v>
+        <v>153.5173714832286</v>
       </c>
       <c r="F651" t="n">
         <v>1315084</v>
@@ -13532,16 +13532,16 @@
         <v>43916</v>
       </c>
       <c r="B656" t="n">
-        <v>220.9315643310547</v>
+        <v>220.9315490722656</v>
       </c>
       <c r="C656" t="n">
-        <v>242.7354870129028</v>
+        <v>242.735470248211</v>
       </c>
       <c r="D656" t="n">
-        <v>190.6730575776279</v>
+        <v>190.6730444086632</v>
       </c>
       <c r="E656" t="n">
-        <v>190.6730575776279</v>
+        <v>190.6730444086632</v>
       </c>
       <c r="F656" t="n">
         <v>1984360</v>
@@ -13552,16 +13552,16 @@
         <v>43917</v>
       </c>
       <c r="B657" t="n">
-        <v>231.3885498046875</v>
+        <v>231.3885345458984</v>
       </c>
       <c r="C657" t="n">
-        <v>241.1780588454579</v>
+        <v>241.1780429411052</v>
       </c>
       <c r="D657" t="n">
-        <v>206.2472851849431</v>
+        <v>206.2472715840807</v>
       </c>
       <c r="E657" t="n">
-        <v>212.2544919647103</v>
+        <v>212.254477967706</v>
       </c>
       <c r="F657" t="n">
         <v>1391484</v>
@@ -13652,16 +13652,16 @@
         <v>43924</v>
       </c>
       <c r="B662" t="n">
-        <v>191.1180419921875</v>
+        <v>191.1180572509766</v>
       </c>
       <c r="C662" t="n">
-        <v>202.4649780176419</v>
+        <v>202.4649941823658</v>
       </c>
       <c r="D662" t="n">
-        <v>183.1084331465933</v>
+        <v>183.1084477658983</v>
       </c>
       <c r="E662" t="n">
-        <v>200.4625758062433</v>
+        <v>200.4625918110963</v>
       </c>
       <c r="F662" t="n">
         <v>765433</v>
@@ -13692,16 +13692,16 @@
         <v>43928</v>
       </c>
       <c r="B664" t="n">
-        <v>226.9387512207031</v>
+        <v>226.9387359619141</v>
       </c>
       <c r="C664" t="n">
-        <v>254.9723657459614</v>
+        <v>254.9723486022629</v>
       </c>
       <c r="D664" t="n">
-        <v>226.4937762578128</v>
+        <v>226.4937610289427</v>
       </c>
       <c r="E664" t="n">
-        <v>251.4125365254284</v>
+        <v>251.4125196210838</v>
       </c>
       <c r="F664" t="n">
         <v>1047412</v>
@@ -13752,16 +13752,16 @@
         <v>43934</v>
       </c>
       <c r="B667" t="n">
-        <v>231.1660461425781</v>
+        <v>231.1660614013672</v>
       </c>
       <c r="C667" t="n">
-        <v>234.0583982008221</v>
+        <v>234.0584136505294</v>
       </c>
       <c r="D667" t="n">
-        <v>221.5990105121156</v>
+        <v>221.5990251394046</v>
       </c>
       <c r="E667" t="n">
-        <v>224.713864813645</v>
+        <v>224.713879646539</v>
       </c>
       <c r="F667" t="n">
         <v>570405</v>
@@ -13792,16 +13792,16 @@
         <v>43936</v>
       </c>
       <c r="B669" t="n">
-        <v>263.4269714355469</v>
+        <v>263.4269409179688</v>
       </c>
       <c r="C669" t="n">
-        <v>285.4533667965793</v>
+        <v>285.4533337272798</v>
       </c>
       <c r="D669" t="n">
-        <v>253.6374328687861</v>
+        <v>253.6374034853098</v>
       </c>
       <c r="E669" t="n">
-        <v>259.6446396538167</v>
+        <v>259.6446095744155</v>
       </c>
       <c r="F669" t="n">
         <v>1641419</v>
@@ -13852,16 +13852,16 @@
         <v>43941</v>
       </c>
       <c r="B672" t="n">
-        <v>265.4293518066406</v>
+        <v>265.4293212890625</v>
       </c>
       <c r="C672" t="n">
-        <v>270.9915536148703</v>
+        <v>270.9915224577813</v>
       </c>
       <c r="D672" t="n">
-        <v>252.9699642634744</v>
+        <v>252.9699351784068</v>
       </c>
       <c r="E672" t="n">
-        <v>258.0871911077421</v>
+        <v>258.0871614343244</v>
       </c>
       <c r="F672" t="n">
         <v>627032</v>
@@ -13892,16 +13892,16 @@
         <v>43944</v>
       </c>
       <c r="B674" t="n">
-        <v>225.1588439941406</v>
+        <v>225.1588287353516</v>
       </c>
       <c r="C674" t="n">
-        <v>243.6254236293111</v>
+        <v>243.6254071190605</v>
       </c>
       <c r="D674" t="n">
-        <v>216.036797920926</v>
+        <v>216.0367832803288</v>
       </c>
       <c r="E674" t="n">
-        <v>237.8407194046269</v>
+        <v>237.8407032863998</v>
       </c>
       <c r="F674" t="n">
         <v>2199225</v>
@@ -13912,16 +13912,16 @@
         <v>43945</v>
       </c>
       <c r="B675" t="n">
-        <v>201.7975006103516</v>
+        <v>201.7975158691406</v>
       </c>
       <c r="C675" t="n">
-        <v>219.5966182449923</v>
+        <v>219.5966348496503</v>
       </c>
       <c r="D675" t="n">
-        <v>183.7758954811484</v>
+        <v>183.7759093772453</v>
       </c>
       <c r="E675" t="n">
-        <v>218.261693277618</v>
+        <v>218.2617097813364</v>
       </c>
       <c r="F675" t="n">
         <v>2006627</v>
@@ -13932,16 +13932,16 @@
         <v>43948</v>
       </c>
       <c r="B676" t="n">
-        <v>210.4745483398438</v>
+        <v>210.4745635986328</v>
       </c>
       <c r="C676" t="n">
-        <v>216.9267292350107</v>
+        <v>216.926744961564</v>
       </c>
       <c r="D676" t="n">
-        <v>204.9123320818714</v>
+        <v>204.9123469374161</v>
       </c>
       <c r="E676" t="n">
-        <v>210.0295734005987</v>
+        <v>210.0295886271283</v>
       </c>
       <c r="F676" t="n">
         <v>1136627</v>
@@ -14192,16 +14192,16 @@
         <v>43966</v>
       </c>
       <c r="B689" t="n">
-        <v>149.0675964355469</v>
+        <v>149.0676116943359</v>
       </c>
       <c r="C689" t="n">
-        <v>162.8619231365464</v>
+        <v>162.861939807344</v>
       </c>
       <c r="D689" t="n">
-        <v>149.0675964355469</v>
+        <v>149.0676116943359</v>
       </c>
       <c r="E689" t="n">
-        <v>156.4097421134657</v>
+        <v>156.4097581238081</v>
       </c>
       <c r="F689" t="n">
         <v>3004141</v>
@@ -14232,16 +14232,16 @@
         <v>43970</v>
       </c>
       <c r="B691" t="n">
-        <v>156.8547210693359</v>
+        <v>156.854736328125</v>
       </c>
       <c r="C691" t="n">
-        <v>170.871520843808</v>
+        <v>170.8715374661479</v>
       </c>
       <c r="D691" t="n">
-        <v>156.8547210693359</v>
+        <v>156.854736328125</v>
       </c>
       <c r="E691" t="n">
-        <v>160.8595252216723</v>
+        <v>160.8595408700477</v>
       </c>
       <c r="F691" t="n">
         <v>1437035</v>
@@ -14272,16 +14272,16 @@
         <v>43972</v>
       </c>
       <c r="B693" t="n">
-        <v>156.8547210693359</v>
+        <v>156.854736328125</v>
       </c>
       <c r="C693" t="n">
-        <v>170.4265458843718</v>
+        <v>170.4265624634247</v>
       </c>
       <c r="D693" t="n">
-        <v>155.0748064728859</v>
+        <v>155.0748215585253</v>
       </c>
       <c r="E693" t="n">
-        <v>169.9815709249356</v>
+        <v>169.9815874607014</v>
       </c>
       <c r="F693" t="n">
         <v>2204133</v>
@@ -14312,16 +14312,16 @@
         <v>43976</v>
       </c>
       <c r="B695" t="n">
-        <v>173.5413970947266</v>
+        <v>173.5414123535156</v>
       </c>
       <c r="C695" t="n">
-        <v>176.6562365152245</v>
+        <v>176.6562520478887</v>
       </c>
       <c r="D695" t="n">
-        <v>154.8523162956244</v>
+        <v>154.8523299111586</v>
       </c>
       <c r="E695" t="n">
-        <v>155.7422661989938</v>
+        <v>155.7422798927777</v>
       </c>
       <c r="F695" t="n">
         <v>2267000</v>
@@ -14332,16 +14332,16 @@
         <v>43977</v>
       </c>
       <c r="B696" t="n">
-        <v>164.4193572998047</v>
+        <v>164.4193420410156</v>
       </c>
       <c r="C696" t="n">
-        <v>186.2232802390231</v>
+        <v>186.2232629567407</v>
       </c>
       <c r="D696" t="n">
-        <v>163.9743822926179</v>
+        <v>163.9743670751244</v>
       </c>
       <c r="E696" t="n">
-        <v>180.8835506353685</v>
+        <v>180.883533848635</v>
       </c>
       <c r="F696" t="n">
         <v>1999101</v>
@@ -14412,16 +14412,16 @@
         <v>43983</v>
       </c>
       <c r="B700" t="n">
-        <v>184.8883209228516</v>
+        <v>184.8883361816406</v>
       </c>
       <c r="C700" t="n">
-        <v>192.2304514556743</v>
+        <v>192.2304673204076</v>
       </c>
       <c r="D700" t="n">
-        <v>183.3308939278756</v>
+        <v>183.3309090581306</v>
       </c>
       <c r="E700" t="n">
-        <v>185.3332958475007</v>
+        <v>185.3333111430134</v>
       </c>
       <c r="F700" t="n">
         <v>1349623</v>
@@ -14452,16 +14452,16 @@
         <v>43985</v>
       </c>
       <c r="B702" t="n">
-        <v>239.1756439208984</v>
+        <v>239.1756286621094</v>
       </c>
       <c r="C702" t="n">
-        <v>239.1756439208984</v>
+        <v>239.1756286621094</v>
       </c>
       <c r="D702" t="n">
-        <v>196.6802532298526</v>
+        <v>196.6802406821598</v>
       </c>
       <c r="E702" t="n">
-        <v>198.2376804070371</v>
+        <v>198.2376677599845</v>
       </c>
       <c r="F702" t="n">
         <v>3635130</v>
@@ -14472,16 +14472,16 @@
         <v>43986</v>
       </c>
       <c r="B703" t="n">
-        <v>232.5009918212891</v>
+        <v>232.5009765625</v>
       </c>
       <c r="C703" t="n">
-        <v>261.8695490314464</v>
+        <v>261.8695318452306</v>
       </c>
       <c r="D703" t="n">
-        <v>227.1612621969187</v>
+        <v>227.1612472885703</v>
       </c>
       <c r="E703" t="n">
-        <v>251.8575375373684</v>
+        <v>251.8575210082302</v>
       </c>
       <c r="F703" t="n">
         <v>3720763</v>
@@ -14492,16 +14492,16 @@
         <v>43987</v>
       </c>
       <c r="B704" t="n">
-        <v>239.1756439208984</v>
+        <v>239.1756286621094</v>
       </c>
       <c r="C704" t="n">
-        <v>250.9675693559012</v>
+        <v>250.9675533448177</v>
       </c>
       <c r="D704" t="n">
-        <v>231.388537552387</v>
+        <v>231.3885227903952</v>
       </c>
       <c r="E704" t="n">
-        <v>248.0752172485919</v>
+        <v>248.075201422033</v>
       </c>
       <c r="F704" t="n">
         <v>2000080</v>
@@ -14632,16 +14632,16 @@
         <v>43999</v>
       </c>
       <c r="B711" t="n">
-        <v>224.2689056396484</v>
+        <v>224.2688903808594</v>
       </c>
       <c r="C711" t="n">
-        <v>234.9483646864547</v>
+        <v>234.9483487010575</v>
       </c>
       <c r="D711" t="n">
-        <v>221.5990261192404</v>
+        <v>221.5990110421044</v>
       </c>
       <c r="E711" t="n">
-        <v>228.2736954028476</v>
+        <v>228.2736798715809</v>
       </c>
       <c r="F711" t="n">
         <v>1568971</v>
@@ -14672,16 +14672,16 @@
         <v>44001</v>
       </c>
       <c r="B713" t="n">
-        <v>231.1660461425781</v>
+        <v>231.1660614013672</v>
       </c>
       <c r="C713" t="n">
-        <v>235.3933378670069</v>
+        <v>235.3933534048307</v>
       </c>
       <c r="D713" t="n">
-        <v>226.0487897211243</v>
+        <v>226.0488046421339</v>
       </c>
       <c r="E713" t="n">
-        <v>234.5033731699819</v>
+        <v>234.503388649061</v>
       </c>
       <c r="F713" t="n">
         <v>1213992</v>
@@ -14752,16 +14752,16 @@
         <v>44007</v>
       </c>
       <c r="B717" t="n">
-        <v>250.3000793457031</v>
+        <v>250.3000946044922</v>
       </c>
       <c r="C717" t="n">
-        <v>255.4173355925531</v>
+        <v>255.4173511633002</v>
       </c>
       <c r="D717" t="n">
-        <v>237.3957318868463</v>
+        <v>237.3957463589608</v>
       </c>
       <c r="E717" t="n">
-        <v>248.2976772941018</v>
+        <v>248.2976924308205</v>
       </c>
       <c r="F717" t="n">
         <v>2280068</v>
@@ -14772,16 +14772,16 @@
         <v>44008</v>
       </c>
       <c r="B718" t="n">
-        <v>263.8719177246094</v>
+        <v>263.8719482421875</v>
       </c>
       <c r="C718" t="n">
-        <v>270.7690737604885</v>
+        <v>270.7691050757434</v>
       </c>
       <c r="D718" t="n">
-        <v>256.307284501661</v>
+        <v>256.3073141443666</v>
       </c>
       <c r="E718" t="n">
-        <v>266.9867423903095</v>
+        <v>266.9867732681264</v>
       </c>
       <c r="F718" t="n">
         <v>3269179</v>
@@ -14792,16 +14792,16 @@
         <v>44011</v>
       </c>
       <c r="B719" t="n">
-        <v>277.2212219238281</v>
+        <v>277.2212524414062</v>
       </c>
       <c r="C719" t="n">
-        <v>284.1183771406632</v>
+        <v>284.1184084175067</v>
       </c>
       <c r="D719" t="n">
-        <v>271.436489196794</v>
+        <v>271.4365190775665</v>
       </c>
       <c r="E719" t="n">
-        <v>274.5513430100119</v>
+        <v>274.5513732336795</v>
       </c>
       <c r="F719" t="n">
         <v>2764722</v>
@@ -14812,16 +14812,16 @@
         <v>44012</v>
       </c>
       <c r="B720" t="n">
-        <v>244.7378845214844</v>
+        <v>244.7378692626953</v>
       </c>
       <c r="C720" t="n">
-        <v>290.1256437690779</v>
+        <v>290.1256256804767</v>
       </c>
       <c r="D720" t="n">
-        <v>240.510592567893</v>
+        <v>240.510577572665</v>
       </c>
       <c r="E720" t="n">
-        <v>266.9867670139398</v>
+        <v>266.9867503679891</v>
       </c>
       <c r="F720" t="n">
         <v>5939743</v>
@@ -14852,16 +14852,16 @@
         <v>44014</v>
       </c>
       <c r="B722" t="n">
-        <v>199.3501129150391</v>
+        <v>199.35009765625</v>
       </c>
       <c r="C722" t="n">
-        <v>232.5009692399297</v>
+        <v>232.5009514436857</v>
       </c>
       <c r="D722" t="n">
-        <v>198.4601629836482</v>
+        <v>198.4601477929782</v>
       </c>
       <c r="E722" t="n">
-        <v>230.2760796527471</v>
+        <v>230.2760620268021</v>
       </c>
       <c r="F722" t="n">
         <v>4660441</v>
@@ -14952,16 +14952,16 @@
         <v>44021</v>
       </c>
       <c r="B727" t="n">
-        <v>206.9147491455078</v>
+        <v>206.9147338867188</v>
       </c>
       <c r="C727" t="n">
-        <v>210.2520761917486</v>
+        <v>210.2520606868507</v>
       </c>
       <c r="D727" t="n">
-        <v>184.8883404607196</v>
+        <v>184.8883268262532</v>
       </c>
       <c r="E727" t="n">
-        <v>186.8907425919463</v>
+        <v>186.8907288098141</v>
       </c>
       <c r="F727" t="n">
         <v>3744947</v>
@@ -15052,16 +15052,16 @@
         <v>44028</v>
       </c>
       <c r="B732" t="n">
-        <v>215.4793853759766</v>
+        <v>215.4794006347656</v>
       </c>
       <c r="C732" t="n">
-        <v>221.0168516147299</v>
+        <v>221.0168672656448</v>
       </c>
       <c r="D732" t="n">
-        <v>214.2755915759661</v>
+        <v>214.2756067495107</v>
       </c>
       <c r="E732" t="n">
-        <v>218.368505254707</v>
+        <v>218.3685207180839</v>
       </c>
       <c r="F732" t="n">
         <v>1169687</v>
@@ -15092,16 +15092,16 @@
         <v>44032</v>
       </c>
       <c r="B734" t="n">
-        <v>214.7570953369141</v>
+        <v>214.7571105957031</v>
       </c>
       <c r="C734" t="n">
-        <v>217.8869737751215</v>
+        <v>217.8869892562928</v>
       </c>
       <c r="D734" t="n">
-        <v>212.1087491465653</v>
+        <v>212.1087642171857</v>
       </c>
       <c r="E734" t="n">
-        <v>217.4054562859672</v>
+        <v>217.405471732926</v>
       </c>
       <c r="F734" t="n">
         <v>991145</v>
@@ -15132,16 +15132,16 @@
         <v>44034</v>
       </c>
       <c r="B736" t="n">
-        <v>196.7001800537109</v>
+        <v>196.7001953125</v>
       </c>
       <c r="C736" t="n">
-        <v>205.3674950928536</v>
+        <v>205.3675110239996</v>
       </c>
       <c r="D736" t="n">
-        <v>193.5703015308713</v>
+        <v>193.5703165468637</v>
       </c>
       <c r="E736" t="n">
-        <v>203.6821838352425</v>
+        <v>203.6821996356524</v>
       </c>
       <c r="F736" t="n">
         <v>1479746</v>
@@ -15152,16 +15152,16 @@
         <v>44035</v>
       </c>
       <c r="B737" t="n">
-        <v>188.9958953857422</v>
+        <v>188.9959106445312</v>
       </c>
       <c r="C737" t="n">
-        <v>198.1447431759173</v>
+        <v>198.1447591733485</v>
       </c>
       <c r="D737" t="n">
-        <v>188.5143778577701</v>
+        <v>188.5143930776833</v>
       </c>
       <c r="E737" t="n">
-        <v>196.7001905920011</v>
+        <v>196.7002064728048</v>
       </c>
       <c r="F737" t="n">
         <v>1310991</v>
@@ -15192,16 +15192,16 @@
         <v>44039</v>
       </c>
       <c r="B739" t="n">
-        <v>196.7001800537109</v>
+        <v>196.7001953125</v>
       </c>
       <c r="C739" t="n">
-        <v>205.8490125950281</v>
+        <v>205.8490285635273</v>
       </c>
       <c r="D739" t="n">
-        <v>193.8110602819586</v>
+        <v>193.8110753166276</v>
       </c>
       <c r="E739" t="n">
-        <v>203.6821838352425</v>
+        <v>203.6821996356524</v>
       </c>
       <c r="F739" t="n">
         <v>1197033</v>
@@ -15212,16 +15212,16 @@
         <v>44040</v>
       </c>
       <c r="B740" t="n">
-        <v>197.4224395751953</v>
+        <v>197.4224548339844</v>
       </c>
       <c r="C740" t="n">
-        <v>201.0338205354361</v>
+        <v>201.0338360733489</v>
       </c>
       <c r="D740" t="n">
-        <v>194.0518025869337</v>
+        <v>194.0518175852061</v>
       </c>
       <c r="E740" t="n">
-        <v>196.7001633831472</v>
+        <v>196.7001785861115</v>
       </c>
       <c r="F740" t="n">
         <v>894446</v>
@@ -15412,16 +15412,16 @@
         <v>44054</v>
       </c>
       <c r="B750" t="n">
-        <v>195.2555999755859</v>
+        <v>195.255615234375</v>
       </c>
       <c r="C750" t="n">
-        <v>200.0707894400583</v>
+        <v>200.0708050751437</v>
       </c>
       <c r="D750" t="n">
-        <v>184.4214421289028</v>
+        <v>184.4214565410266</v>
       </c>
       <c r="E750" t="n">
-        <v>185.8660092993372</v>
+        <v>185.8660238243507</v>
       </c>
       <c r="F750" t="n">
         <v>2032416</v>
@@ -45932,19 +45932,39 @@
         <v>46295</v>
       </c>
       <c r="B2276" t="n">
-        <v>61.66</v>
+        <v>61.65999984741211</v>
       </c>
       <c r="C2276" t="n">
-        <v>63.39</v>
+        <v>63.38999938964844</v>
       </c>
       <c r="D2276" t="n">
-        <v>61.03</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="E2276" t="n">
         <v>63</v>
       </c>
       <c r="F2276" t="n">
         <v>847100</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2277" t="n">
+        <v>62.26</v>
+      </c>
+      <c r="C2277" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>674800</v>
       </c>
     </row>
   </sheetData>
